--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,8 +107,35 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001A2733"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -140,8 +167,33 @@
         <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="56">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -722,11 +774,317 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1037,6 +1395,251 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="72" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="79" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="81" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="71" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="74" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="80" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="82" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="82" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="70" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="73" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="80" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="75" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="76" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="80" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="82" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="73" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1111,6 +1714,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1464,1478 +2157,1568 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="54" t="n"/>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="118" t="n"/>
-      <c r="K1" s="118" t="n"/>
-      <c r="L1" s="56" t="inlineStr">
+      <c r="A1" s="125" t="n"/>
+      <c r="B1" s="126" t="n"/>
+      <c r="C1" s="126" t="n"/>
+      <c r="D1" s="126" t="n"/>
+      <c r="E1" s="126" t="n"/>
+      <c r="F1" s="126" t="n"/>
+      <c r="G1" s="126" t="n"/>
+      <c r="H1" s="126" t="n"/>
+      <c r="I1" s="126" t="n"/>
+      <c r="J1" s="126" t="n"/>
+      <c r="K1" s="127" t="n"/>
+      <c r="L1" s="128" t="inlineStr">
         <is>
           <t>COMPETENCE ASSESSMENT</t>
         </is>
       </c>
-      <c r="M1" s="118" t="n"/>
-      <c r="N1" s="118" t="n"/>
-      <c r="O1" s="118" t="n"/>
-      <c r="P1" s="118" t="n"/>
-      <c r="Q1" s="118" t="n"/>
-      <c r="R1" s="118" t="n"/>
-      <c r="S1" s="118" t="n"/>
-      <c r="T1" s="118" t="n"/>
-      <c r="U1" s="118" t="n"/>
-      <c r="V1" s="118" t="n"/>
-      <c r="W1" s="118" t="n"/>
-      <c r="X1" s="118" t="n"/>
-      <c r="Y1" s="118" t="n"/>
-      <c r="Z1" s="118" t="n"/>
-      <c r="AA1" s="118" t="n"/>
-      <c r="AB1" s="118" t="n"/>
-      <c r="AC1" s="118" t="n"/>
-      <c r="AD1" s="118" t="n"/>
-      <c r="AE1" s="118" t="n"/>
-      <c r="AF1" s="118" t="n"/>
-      <c r="AG1" s="118" t="n"/>
-      <c r="AH1" s="118" t="n"/>
-      <c r="AI1" s="118" t="n"/>
-      <c r="AJ1" s="118" t="n"/>
-      <c r="AK1" s="118" t="n"/>
-      <c r="AL1" s="118" t="n"/>
-      <c r="AM1" s="118" t="n"/>
-      <c r="AN1" s="118" t="n"/>
-      <c r="AO1" s="118" t="n"/>
-      <c r="AP1" s="118" t="n"/>
-      <c r="AQ1" s="57" t="inlineStr">
+      <c r="M1" s="129" t="n"/>
+      <c r="N1" s="129" t="n"/>
+      <c r="O1" s="129" t="n"/>
+      <c r="P1" s="129" t="n"/>
+      <c r="Q1" s="129" t="n"/>
+      <c r="R1" s="129" t="n"/>
+      <c r="S1" s="129" t="n"/>
+      <c r="T1" s="129" t="n"/>
+      <c r="U1" s="129" t="n"/>
+      <c r="V1" s="129" t="n"/>
+      <c r="W1" s="129" t="n"/>
+      <c r="X1" s="129" t="n"/>
+      <c r="Y1" s="129" t="n"/>
+      <c r="Z1" s="129" t="n"/>
+      <c r="AA1" s="129" t="n"/>
+      <c r="AB1" s="129" t="n"/>
+      <c r="AC1" s="129" t="n"/>
+      <c r="AD1" s="129" t="n"/>
+      <c r="AE1" s="129" t="n"/>
+      <c r="AF1" s="129" t="n"/>
+      <c r="AG1" s="129" t="n"/>
+      <c r="AH1" s="129" t="n"/>
+      <c r="AI1" s="129" t="n"/>
+      <c r="AJ1" s="129" t="n"/>
+      <c r="AK1" s="129" t="n"/>
+      <c r="AL1" s="129" t="n"/>
+      <c r="AM1" s="129" t="n"/>
+      <c r="AN1" s="129" t="n"/>
+      <c r="AO1" s="129" t="n"/>
+      <c r="AP1" s="130" t="n"/>
+      <c r="AQ1" s="131" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="119" t="n"/>
-      <c r="AS1" s="119" t="n"/>
-      <c r="AT1" s="119" t="n"/>
-      <c r="AU1" s="119" t="n"/>
-      <c r="AV1" s="120" t="n"/>
-      <c r="AW1" s="60" t="inlineStr">
+      <c r="AR1" s="132" t="n"/>
+      <c r="AS1" s="132" t="n"/>
+      <c r="AT1" s="132" t="n"/>
+      <c r="AU1" s="132" t="n"/>
+      <c r="AV1" s="133" t="n"/>
+      <c r="AW1" s="134" t="inlineStr">
         <is>
           <t>FRM-804</t>
         </is>
       </c>
-      <c r="AX1" s="119" t="n"/>
-      <c r="AY1" s="119" t="n"/>
-      <c r="AZ1" s="119" t="n"/>
-      <c r="BA1" s="119" t="n"/>
-      <c r="BB1" s="119" t="n"/>
-      <c r="BC1" s="119" t="n"/>
-      <c r="BD1" s="120" t="n"/>
+      <c r="AX1" s="135" t="n"/>
+      <c r="AY1" s="135" t="n"/>
+      <c r="AZ1" s="135" t="n"/>
+      <c r="BA1" s="135" t="n"/>
+      <c r="BB1" s="135" t="n"/>
+      <c r="BC1" s="135" t="n"/>
+      <c r="BD1" s="136" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="121" t="n"/>
-      <c r="L2" s="121" t="n"/>
-      <c r="AQ2" s="63" t="inlineStr">
+      <c r="A2" s="137" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+      <c r="G2" s="53" t="n"/>
+      <c r="H2" s="53" t="n"/>
+      <c r="I2" s="53" t="n"/>
+      <c r="J2" s="53" t="n"/>
+      <c r="K2" s="138" t="n"/>
+      <c r="L2" s="139" t="n"/>
+      <c r="M2" s="140" t="n"/>
+      <c r="N2" s="140" t="n"/>
+      <c r="O2" s="140" t="n"/>
+      <c r="P2" s="140" t="n"/>
+      <c r="Q2" s="140" t="n"/>
+      <c r="R2" s="140" t="n"/>
+      <c r="S2" s="140" t="n"/>
+      <c r="T2" s="140" t="n"/>
+      <c r="U2" s="140" t="n"/>
+      <c r="V2" s="140" t="n"/>
+      <c r="W2" s="140" t="n"/>
+      <c r="X2" s="140" t="n"/>
+      <c r="Y2" s="140" t="n"/>
+      <c r="Z2" s="140" t="n"/>
+      <c r="AA2" s="140" t="n"/>
+      <c r="AB2" s="140" t="n"/>
+      <c r="AC2" s="140" t="n"/>
+      <c r="AD2" s="140" t="n"/>
+      <c r="AE2" s="140" t="n"/>
+      <c r="AF2" s="140" t="n"/>
+      <c r="AG2" s="140" t="n"/>
+      <c r="AH2" s="140" t="n"/>
+      <c r="AI2" s="140" t="n"/>
+      <c r="AJ2" s="140" t="n"/>
+      <c r="AK2" s="140" t="n"/>
+      <c r="AL2" s="140" t="n"/>
+      <c r="AM2" s="140" t="n"/>
+      <c r="AN2" s="140" t="n"/>
+      <c r="AO2" s="140" t="n"/>
+      <c r="AP2" s="141" t="n"/>
+      <c r="AQ2" s="142" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="122" t="n"/>
-      <c r="AS2" s="122" t="n"/>
-      <c r="AT2" s="122" t="n"/>
-      <c r="AU2" s="122" t="n"/>
-      <c r="AV2" s="123" t="n"/>
-      <c r="AW2" s="66" t="inlineStr">
+      <c r="AR2" s="143" t="n"/>
+      <c r="AS2" s="143" t="n"/>
+      <c r="AT2" s="143" t="n"/>
+      <c r="AU2" s="143" t="n"/>
+      <c r="AV2" s="144" t="n"/>
+      <c r="AW2" s="145" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="122" t="n"/>
-      <c r="AY2" s="122" t="n"/>
-      <c r="AZ2" s="122" t="n"/>
-      <c r="BA2" s="122" t="n"/>
-      <c r="BB2" s="122" t="n"/>
-      <c r="BC2" s="122" t="n"/>
-      <c r="BD2" s="123" t="n"/>
+      <c r="AX2" s="146" t="n"/>
+      <c r="AY2" s="146" t="n"/>
+      <c r="AZ2" s="146" t="n"/>
+      <c r="BA2" s="146" t="n"/>
+      <c r="BB2" s="146" t="n"/>
+      <c r="BC2" s="146" t="n"/>
+      <c r="BD2" s="147" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="121" t="n"/>
-      <c r="L3" s="124" t="n"/>
-      <c r="M3" s="122" t="n"/>
-      <c r="N3" s="122" t="n"/>
-      <c r="O3" s="122" t="n"/>
-      <c r="P3" s="122" t="n"/>
-      <c r="Q3" s="122" t="n"/>
-      <c r="R3" s="122" t="n"/>
-      <c r="S3" s="122" t="n"/>
-      <c r="T3" s="122" t="n"/>
-      <c r="U3" s="122" t="n"/>
-      <c r="V3" s="122" t="n"/>
-      <c r="W3" s="122" t="n"/>
-      <c r="X3" s="122" t="n"/>
-      <c r="Y3" s="122" t="n"/>
-      <c r="Z3" s="122" t="n"/>
-      <c r="AA3" s="122" t="n"/>
-      <c r="AB3" s="122" t="n"/>
-      <c r="AC3" s="122" t="n"/>
-      <c r="AD3" s="122" t="n"/>
-      <c r="AE3" s="122" t="n"/>
-      <c r="AF3" s="122" t="n"/>
-      <c r="AG3" s="122" t="n"/>
-      <c r="AH3" s="122" t="n"/>
-      <c r="AI3" s="122" t="n"/>
-      <c r="AJ3" s="122" t="n"/>
-      <c r="AK3" s="122" t="n"/>
-      <c r="AL3" s="122" t="n"/>
-      <c r="AM3" s="122" t="n"/>
-      <c r="AN3" s="122" t="n"/>
-      <c r="AO3" s="122" t="n"/>
-      <c r="AP3" s="122" t="n"/>
-      <c r="AQ3" s="63" t="inlineStr">
+      <c r="A3" s="137" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="138" t="n"/>
+      <c r="L3" s="139" t="n"/>
+      <c r="M3" s="140" t="n"/>
+      <c r="N3" s="140" t="n"/>
+      <c r="O3" s="140" t="n"/>
+      <c r="P3" s="140" t="n"/>
+      <c r="Q3" s="140" t="n"/>
+      <c r="R3" s="140" t="n"/>
+      <c r="S3" s="140" t="n"/>
+      <c r="T3" s="140" t="n"/>
+      <c r="U3" s="140" t="n"/>
+      <c r="V3" s="140" t="n"/>
+      <c r="W3" s="140" t="n"/>
+      <c r="X3" s="140" t="n"/>
+      <c r="Y3" s="140" t="n"/>
+      <c r="Z3" s="140" t="n"/>
+      <c r="AA3" s="140" t="n"/>
+      <c r="AB3" s="140" t="n"/>
+      <c r="AC3" s="140" t="n"/>
+      <c r="AD3" s="140" t="n"/>
+      <c r="AE3" s="140" t="n"/>
+      <c r="AF3" s="140" t="n"/>
+      <c r="AG3" s="140" t="n"/>
+      <c r="AH3" s="140" t="n"/>
+      <c r="AI3" s="140" t="n"/>
+      <c r="AJ3" s="140" t="n"/>
+      <c r="AK3" s="140" t="n"/>
+      <c r="AL3" s="140" t="n"/>
+      <c r="AM3" s="140" t="n"/>
+      <c r="AN3" s="140" t="n"/>
+      <c r="AO3" s="140" t="n"/>
+      <c r="AP3" s="141" t="n"/>
+      <c r="AQ3" s="142" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="122" t="n"/>
-      <c r="AS3" s="122" t="n"/>
-      <c r="AT3" s="122" t="n"/>
-      <c r="AU3" s="122" t="n"/>
-      <c r="AV3" s="123" t="n"/>
-      <c r="AW3" s="66" t="inlineStr">
+      <c r="AR3" s="143" t="n"/>
+      <c r="AS3" s="143" t="n"/>
+      <c r="AT3" s="143" t="n"/>
+      <c r="AU3" s="143" t="n"/>
+      <c r="AV3" s="144" t="n"/>
+      <c r="AW3" s="145" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="122" t="n"/>
-      <c r="AY3" s="122" t="n"/>
-      <c r="AZ3" s="122" t="n"/>
-      <c r="BA3" s="122" t="n"/>
-      <c r="BB3" s="122" t="n"/>
-      <c r="BC3" s="122" t="n"/>
-      <c r="BD3" s="123" t="n"/>
+      <c r="AX3" s="146" t="n"/>
+      <c r="AY3" s="146" t="n"/>
+      <c r="AZ3" s="146" t="n"/>
+      <c r="BA3" s="146" t="n"/>
+      <c r="BB3" s="146" t="n"/>
+      <c r="BC3" s="146" t="n"/>
+      <c r="BD3" s="147" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="121" t="n"/>
-      <c r="L4" s="68" t="inlineStr">
+      <c r="A4" s="137" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="138" t="n"/>
+      <c r="L4" s="148" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="63" t="inlineStr">
+      <c r="M4" s="149" t="n"/>
+      <c r="N4" s="149" t="n"/>
+      <c r="O4" s="149" t="n"/>
+      <c r="P4" s="149" t="n"/>
+      <c r="Q4" s="149" t="n"/>
+      <c r="R4" s="149" t="n"/>
+      <c r="S4" s="149" t="n"/>
+      <c r="T4" s="149" t="n"/>
+      <c r="U4" s="149" t="n"/>
+      <c r="V4" s="149" t="n"/>
+      <c r="W4" s="149" t="n"/>
+      <c r="X4" s="149" t="n"/>
+      <c r="Y4" s="149" t="n"/>
+      <c r="Z4" s="149" t="n"/>
+      <c r="AA4" s="149" t="n"/>
+      <c r="AB4" s="149" t="n"/>
+      <c r="AC4" s="149" t="n"/>
+      <c r="AD4" s="149" t="n"/>
+      <c r="AE4" s="149" t="n"/>
+      <c r="AF4" s="149" t="n"/>
+      <c r="AG4" s="149" t="n"/>
+      <c r="AH4" s="149" t="n"/>
+      <c r="AI4" s="149" t="n"/>
+      <c r="AJ4" s="149" t="n"/>
+      <c r="AK4" s="149" t="n"/>
+      <c r="AL4" s="149" t="n"/>
+      <c r="AM4" s="149" t="n"/>
+      <c r="AN4" s="149" t="n"/>
+      <c r="AO4" s="149" t="n"/>
+      <c r="AP4" s="150" t="n"/>
+      <c r="AQ4" s="142" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="122" t="n"/>
-      <c r="AS4" s="122" t="n"/>
-      <c r="AT4" s="122" t="n"/>
-      <c r="AU4" s="122" t="n"/>
-      <c r="AV4" s="123" t="n"/>
-      <c r="AW4" s="66" t="inlineStr">
+      <c r="AR4" s="143" t="n"/>
+      <c r="AS4" s="143" t="n"/>
+      <c r="AT4" s="143" t="n"/>
+      <c r="AU4" s="143" t="n"/>
+      <c r="AV4" s="144" t="n"/>
+      <c r="AW4" s="145" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="122" t="n"/>
-      <c r="AY4" s="122" t="n"/>
-      <c r="AZ4" s="122" t="n"/>
-      <c r="BA4" s="122" t="n"/>
-      <c r="BB4" s="122" t="n"/>
-      <c r="BC4" s="122" t="n"/>
-      <c r="BD4" s="123" t="n"/>
+      <c r="AX4" s="146" t="n"/>
+      <c r="AY4" s="146" t="n"/>
+      <c r="AZ4" s="146" t="n"/>
+      <c r="BA4" s="146" t="n"/>
+      <c r="BB4" s="146" t="n"/>
+      <c r="BC4" s="146" t="n"/>
+      <c r="BD4" s="147" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="124" t="n"/>
-      <c r="B5" s="122" t="n"/>
-      <c r="C5" s="122" t="n"/>
-      <c r="D5" s="122" t="n"/>
-      <c r="E5" s="122" t="n"/>
-      <c r="F5" s="122" t="n"/>
-      <c r="G5" s="122" t="n"/>
-      <c r="H5" s="122" t="n"/>
-      <c r="I5" s="122" t="n"/>
-      <c r="J5" s="122" t="n"/>
-      <c r="K5" s="122" t="n"/>
-      <c r="L5" s="69" t="inlineStr">
+      <c r="A5" s="151" t="n"/>
+      <c r="B5" s="152" t="n"/>
+      <c r="C5" s="152" t="n"/>
+      <c r="D5" s="152" t="n"/>
+      <c r="E5" s="152" t="n"/>
+      <c r="F5" s="152" t="n"/>
+      <c r="G5" s="152" t="n"/>
+      <c r="H5" s="152" t="n"/>
+      <c r="I5" s="152" t="n"/>
+      <c r="J5" s="152" t="n"/>
+      <c r="K5" s="153" t="n"/>
+      <c r="L5" s="154" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="122" t="n"/>
-      <c r="N5" s="122" t="n"/>
-      <c r="O5" s="122" t="n"/>
-      <c r="P5" s="122" t="n"/>
-      <c r="Q5" s="122" t="n"/>
-      <c r="R5" s="122" t="n"/>
-      <c r="S5" s="122" t="n"/>
-      <c r="T5" s="122" t="n"/>
-      <c r="U5" s="122" t="n"/>
-      <c r="V5" s="122" t="n"/>
-      <c r="W5" s="122" t="n"/>
-      <c r="X5" s="122" t="n"/>
-      <c r="Y5" s="122" t="n"/>
-      <c r="Z5" s="122" t="n"/>
-      <c r="AA5" s="122" t="n"/>
-      <c r="AB5" s="122" t="n"/>
-      <c r="AC5" s="122" t="n"/>
-      <c r="AD5" s="122" t="n"/>
-      <c r="AE5" s="122" t="n"/>
-      <c r="AF5" s="122" t="n"/>
-      <c r="AG5" s="122" t="n"/>
-      <c r="AH5" s="122" t="n"/>
-      <c r="AI5" s="122" t="n"/>
-      <c r="AJ5" s="122" t="n"/>
-      <c r="AK5" s="122" t="n"/>
-      <c r="AL5" s="122" t="n"/>
-      <c r="AM5" s="122" t="n"/>
-      <c r="AN5" s="122" t="n"/>
-      <c r="AO5" s="122" t="n"/>
-      <c r="AP5" s="122" t="n"/>
-      <c r="AQ5" s="63" t="inlineStr">
+      <c r="M5" s="155" t="n"/>
+      <c r="N5" s="155" t="n"/>
+      <c r="O5" s="155" t="n"/>
+      <c r="P5" s="155" t="n"/>
+      <c r="Q5" s="155" t="n"/>
+      <c r="R5" s="155" t="n"/>
+      <c r="S5" s="155" t="n"/>
+      <c r="T5" s="155" t="n"/>
+      <c r="U5" s="155" t="n"/>
+      <c r="V5" s="155" t="n"/>
+      <c r="W5" s="155" t="n"/>
+      <c r="X5" s="155" t="n"/>
+      <c r="Y5" s="155" t="n"/>
+      <c r="Z5" s="155" t="n"/>
+      <c r="AA5" s="155" t="n"/>
+      <c r="AB5" s="155" t="n"/>
+      <c r="AC5" s="155" t="n"/>
+      <c r="AD5" s="155" t="n"/>
+      <c r="AE5" s="155" t="n"/>
+      <c r="AF5" s="155" t="n"/>
+      <c r="AG5" s="155" t="n"/>
+      <c r="AH5" s="155" t="n"/>
+      <c r="AI5" s="155" t="n"/>
+      <c r="AJ5" s="155" t="n"/>
+      <c r="AK5" s="155" t="n"/>
+      <c r="AL5" s="155" t="n"/>
+      <c r="AM5" s="155" t="n"/>
+      <c r="AN5" s="155" t="n"/>
+      <c r="AO5" s="155" t="n"/>
+      <c r="AP5" s="156" t="n"/>
+      <c r="AQ5" s="157" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="122" t="n"/>
-      <c r="AS5" s="122" t="n"/>
-      <c r="AT5" s="122" t="n"/>
-      <c r="AU5" s="122" t="n"/>
-      <c r="AV5" s="123" t="n"/>
-      <c r="AW5" s="66" t="inlineStr">
+      <c r="AR5" s="158" t="n"/>
+      <c r="AS5" s="158" t="n"/>
+      <c r="AT5" s="158" t="n"/>
+      <c r="AU5" s="158" t="n"/>
+      <c r="AV5" s="159" t="n"/>
+      <c r="AW5" s="160" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="122" t="n"/>
-      <c r="AY5" s="122" t="n"/>
-      <c r="AZ5" s="122" t="n"/>
-      <c r="BA5" s="122" t="n"/>
-      <c r="BB5" s="122" t="n"/>
-      <c r="BC5" s="122" t="n"/>
-      <c r="BD5" s="123" t="n"/>
+      <c r="AX5" s="161" t="n"/>
+      <c r="AY5" s="161" t="n"/>
+      <c r="AZ5" s="161" t="n"/>
+      <c r="BA5" s="161" t="n"/>
+      <c r="BB5" s="161" t="n"/>
+      <c r="BC5" s="161" t="n"/>
+      <c r="BD5" s="162" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="70" t="n"/>
-      <c r="B6" s="117" t="n"/>
-      <c r="C6" s="117" t="n"/>
-      <c r="D6" s="117" t="n"/>
-      <c r="E6" s="117" t="n"/>
-      <c r="F6" s="117" t="n"/>
-      <c r="G6" s="117" t="n"/>
-      <c r="H6" s="117" t="n"/>
-      <c r="I6" s="117" t="n"/>
-      <c r="J6" s="117" t="n"/>
-      <c r="K6" s="117" t="n"/>
-      <c r="L6" s="117" t="n"/>
-      <c r="M6" s="117" t="n"/>
-      <c r="N6" s="117" t="n"/>
-      <c r="O6" s="117" t="n"/>
-      <c r="P6" s="117" t="n"/>
-      <c r="Q6" s="117" t="n"/>
-      <c r="R6" s="117" t="n"/>
-      <c r="S6" s="117" t="n"/>
-      <c r="T6" s="117" t="n"/>
-      <c r="U6" s="117" t="n"/>
-      <c r="V6" s="117" t="n"/>
-      <c r="W6" s="117" t="n"/>
-      <c r="X6" s="117" t="n"/>
-      <c r="Y6" s="117" t="n"/>
-      <c r="Z6" s="117" t="n"/>
-      <c r="AA6" s="117" t="n"/>
-      <c r="AB6" s="117" t="n"/>
-      <c r="AC6" s="117" t="n"/>
-      <c r="AD6" s="117" t="n"/>
-      <c r="AE6" s="117" t="n"/>
-      <c r="AF6" s="117" t="n"/>
-      <c r="AG6" s="117" t="n"/>
-      <c r="AH6" s="117" t="n"/>
-      <c r="AI6" s="117" t="n"/>
-      <c r="AJ6" s="117" t="n"/>
-      <c r="AK6" s="117" t="n"/>
-      <c r="AL6" s="117" t="n"/>
-      <c r="AM6" s="117" t="n"/>
-      <c r="AN6" s="117" t="n"/>
-      <c r="AO6" s="117" t="n"/>
-      <c r="AP6" s="117" t="n"/>
-      <c r="AQ6" s="117" t="n"/>
-      <c r="AR6" s="117" t="n"/>
-      <c r="AS6" s="117" t="n"/>
-      <c r="AT6" s="117" t="n"/>
-      <c r="AU6" s="117" t="n"/>
-      <c r="AV6" s="117" t="n"/>
-      <c r="AW6" s="117" t="n"/>
-      <c r="AX6" s="117" t="n"/>
-      <c r="AY6" s="117" t="n"/>
-      <c r="AZ6" s="117" t="n"/>
-      <c r="BA6" s="117" t="n"/>
-      <c r="BB6" s="117" t="n"/>
-      <c r="BC6" s="117" t="n"/>
-      <c r="BD6" s="117" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="163" t="n"/>
+      <c r="B6" s="163" t="n"/>
+      <c r="C6" s="163" t="n"/>
+      <c r="D6" s="163" t="n"/>
+      <c r="E6" s="163" t="n"/>
+      <c r="F6" s="163" t="n"/>
+      <c r="G6" s="163" t="n"/>
+      <c r="H6" s="163" t="n"/>
+      <c r="I6" s="163" t="n"/>
+      <c r="J6" s="163" t="n"/>
+      <c r="K6" s="163" t="n"/>
+      <c r="L6" s="163" t="n"/>
+      <c r="M6" s="163" t="n"/>
+      <c r="N6" s="163" t="n"/>
+      <c r="O6" s="163" t="n"/>
+      <c r="P6" s="163" t="n"/>
+      <c r="Q6" s="163" t="n"/>
+      <c r="R6" s="163" t="n"/>
+      <c r="S6" s="163" t="n"/>
+      <c r="T6" s="163" t="n"/>
+      <c r="U6" s="163" t="n"/>
+      <c r="V6" s="163" t="n"/>
+      <c r="W6" s="163" t="n"/>
+      <c r="X6" s="163" t="n"/>
+      <c r="Y6" s="163" t="n"/>
+      <c r="Z6" s="163" t="n"/>
+      <c r="AA6" s="163" t="n"/>
+      <c r="AB6" s="163" t="n"/>
+      <c r="AC6" s="163" t="n"/>
+      <c r="AD6" s="163" t="n"/>
+      <c r="AE6" s="163" t="n"/>
+      <c r="AF6" s="163" t="n"/>
+      <c r="AG6" s="163" t="n"/>
+      <c r="AH6" s="163" t="n"/>
+      <c r="AI6" s="163" t="n"/>
+      <c r="AJ6" s="163" t="n"/>
+      <c r="AK6" s="163" t="n"/>
+      <c r="AL6" s="163" t="n"/>
+      <c r="AM6" s="163" t="n"/>
+      <c r="AN6" s="163" t="n"/>
+      <c r="AO6" s="163" t="n"/>
+      <c r="AP6" s="163" t="n"/>
+      <c r="AQ6" s="163" t="n"/>
+      <c r="AR6" s="163" t="n"/>
+      <c r="AS6" s="163" t="n"/>
+      <c r="AT6" s="163" t="n"/>
+      <c r="AU6" s="163" t="n"/>
+      <c r="AV6" s="163" t="n"/>
+      <c r="AW6" s="163" t="n"/>
+      <c r="AX6" s="163" t="n"/>
+      <c r="AY6" s="163" t="n"/>
+      <c r="AZ6" s="163" t="n"/>
+      <c r="BA6" s="163" t="n"/>
+      <c r="BB6" s="163" t="n"/>
+      <c r="BC6" s="163" t="n"/>
+      <c r="BD6" s="163" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="71" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. ASSESSMENT HEADER</t>
         </is>
       </c>
-      <c r="B7" s="119" t="n"/>
-      <c r="C7" s="119" t="n"/>
-      <c r="D7" s="119" t="n"/>
-      <c r="E7" s="119" t="n"/>
-      <c r="F7" s="119" t="n"/>
-      <c r="G7" s="119" t="n"/>
-      <c r="H7" s="119" t="n"/>
-      <c r="I7" s="119" t="n"/>
-      <c r="J7" s="119" t="n"/>
-      <c r="K7" s="119" t="n"/>
-      <c r="L7" s="119" t="n"/>
-      <c r="M7" s="119" t="n"/>
-      <c r="N7" s="119" t="n"/>
-      <c r="O7" s="119" t="n"/>
-      <c r="P7" s="119" t="n"/>
-      <c r="Q7" s="119" t="n"/>
-      <c r="R7" s="119" t="n"/>
-      <c r="S7" s="119" t="n"/>
-      <c r="T7" s="119" t="n"/>
-      <c r="U7" s="119" t="n"/>
-      <c r="V7" s="119" t="n"/>
-      <c r="W7" s="119" t="n"/>
-      <c r="X7" s="119" t="n"/>
-      <c r="Y7" s="119" t="n"/>
-      <c r="Z7" s="119" t="n"/>
-      <c r="AA7" s="119" t="n"/>
-      <c r="AB7" s="119" t="n"/>
-      <c r="AC7" s="119" t="n"/>
-      <c r="AD7" s="119" t="n"/>
-      <c r="AE7" s="119" t="n"/>
-      <c r="AF7" s="119" t="n"/>
-      <c r="AG7" s="119" t="n"/>
-      <c r="AH7" s="119" t="n"/>
-      <c r="AI7" s="119" t="n"/>
-      <c r="AJ7" s="119" t="n"/>
-      <c r="AK7" s="119" t="n"/>
-      <c r="AL7" s="119" t="n"/>
-      <c r="AM7" s="119" t="n"/>
-      <c r="AN7" s="119" t="n"/>
-      <c r="AO7" s="119" t="n"/>
-      <c r="AP7" s="119" t="n"/>
-      <c r="AQ7" s="119" t="n"/>
-      <c r="AR7" s="119" t="n"/>
-      <c r="AS7" s="119" t="n"/>
-      <c r="AT7" s="119" t="n"/>
-      <c r="AU7" s="119" t="n"/>
-      <c r="AV7" s="119" t="n"/>
-      <c r="AW7" s="119" t="n"/>
-      <c r="AX7" s="119" t="n"/>
-      <c r="AY7" s="119" t="n"/>
-      <c r="AZ7" s="119" t="n"/>
-      <c r="BA7" s="119" t="n"/>
-      <c r="BB7" s="119" t="n"/>
-      <c r="BC7" s="119" t="n"/>
-      <c r="BD7" s="120" t="n"/>
+      <c r="B7" s="165" t="n"/>
+      <c r="C7" s="165" t="n"/>
+      <c r="D7" s="165" t="n"/>
+      <c r="E7" s="165" t="n"/>
+      <c r="F7" s="165" t="n"/>
+      <c r="G7" s="165" t="n"/>
+      <c r="H7" s="165" t="n"/>
+      <c r="I7" s="165" t="n"/>
+      <c r="J7" s="165" t="n"/>
+      <c r="K7" s="165" t="n"/>
+      <c r="L7" s="165" t="n"/>
+      <c r="M7" s="165" t="n"/>
+      <c r="N7" s="165" t="n"/>
+      <c r="O7" s="165" t="n"/>
+      <c r="P7" s="165" t="n"/>
+      <c r="Q7" s="165" t="n"/>
+      <c r="R7" s="165" t="n"/>
+      <c r="S7" s="165" t="n"/>
+      <c r="T7" s="165" t="n"/>
+      <c r="U7" s="165" t="n"/>
+      <c r="V7" s="165" t="n"/>
+      <c r="W7" s="165" t="n"/>
+      <c r="X7" s="165" t="n"/>
+      <c r="Y7" s="165" t="n"/>
+      <c r="Z7" s="165" t="n"/>
+      <c r="AA7" s="165" t="n"/>
+      <c r="AB7" s="165" t="n"/>
+      <c r="AC7" s="165" t="n"/>
+      <c r="AD7" s="165" t="n"/>
+      <c r="AE7" s="165" t="n"/>
+      <c r="AF7" s="165" t="n"/>
+      <c r="AG7" s="165" t="n"/>
+      <c r="AH7" s="165" t="n"/>
+      <c r="AI7" s="165" t="n"/>
+      <c r="AJ7" s="165" t="n"/>
+      <c r="AK7" s="165" t="n"/>
+      <c r="AL7" s="165" t="n"/>
+      <c r="AM7" s="165" t="n"/>
+      <c r="AN7" s="165" t="n"/>
+      <c r="AO7" s="165" t="n"/>
+      <c r="AP7" s="165" t="n"/>
+      <c r="AQ7" s="165" t="n"/>
+      <c r="AR7" s="165" t="n"/>
+      <c r="AS7" s="165" t="n"/>
+      <c r="AT7" s="165" t="n"/>
+      <c r="AU7" s="165" t="n"/>
+      <c r="AV7" s="165" t="n"/>
+      <c r="AW7" s="165" t="n"/>
+      <c r="AX7" s="165" t="n"/>
+      <c r="AY7" s="165" t="n"/>
+      <c r="AZ7" s="165" t="n"/>
+      <c r="BA7" s="165" t="n"/>
+      <c r="BB7" s="165" t="n"/>
+      <c r="BC7" s="165" t="n"/>
+      <c r="BD7" s="166" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="72" t="inlineStr">
+      <c r="A8" s="167" t="inlineStr">
         <is>
           <t>Employee</t>
         </is>
       </c>
-      <c r="B8" s="105" t="n"/>
-      <c r="C8" s="105" t="n"/>
-      <c r="D8" s="105" t="n"/>
-      <c r="E8" s="105" t="n"/>
-      <c r="F8" s="105" t="n"/>
-      <c r="G8" s="105" t="n"/>
-      <c r="H8" s="105" t="n"/>
-      <c r="I8" s="105" t="n"/>
-      <c r="J8" s="106" t="n"/>
-      <c r="K8" s="75" t="n"/>
-      <c r="L8" s="107" t="n"/>
-      <c r="M8" s="107" t="n"/>
-      <c r="N8" s="107" t="n"/>
-      <c r="O8" s="107" t="n"/>
-      <c r="P8" s="107" t="n"/>
-      <c r="Q8" s="107" t="n"/>
-      <c r="R8" s="107" t="n"/>
-      <c r="S8" s="107" t="n"/>
-      <c r="T8" s="107" t="n"/>
-      <c r="U8" s="107" t="n"/>
-      <c r="V8" s="107" t="n"/>
-      <c r="W8" s="107" t="n"/>
-      <c r="X8" s="107" t="n"/>
-      <c r="Y8" s="107" t="n"/>
-      <c r="Z8" s="107" t="n"/>
-      <c r="AA8" s="107" t="n"/>
-      <c r="AB8" s="108" t="n"/>
-      <c r="AC8" s="72" t="inlineStr">
+      <c r="B8" s="168" t="n"/>
+      <c r="C8" s="168" t="n"/>
+      <c r="D8" s="168" t="n"/>
+      <c r="E8" s="168" t="n"/>
+      <c r="F8" s="168" t="n"/>
+      <c r="G8" s="168" t="n"/>
+      <c r="H8" s="168" t="n"/>
+      <c r="I8" s="168" t="n"/>
+      <c r="J8" s="168" t="n"/>
+      <c r="K8" s="169" t="n"/>
+      <c r="L8" s="170" t="n"/>
+      <c r="M8" s="170" t="n"/>
+      <c r="N8" s="170" t="n"/>
+      <c r="O8" s="170" t="n"/>
+      <c r="P8" s="170" t="n"/>
+      <c r="Q8" s="170" t="n"/>
+      <c r="R8" s="170" t="n"/>
+      <c r="S8" s="170" t="n"/>
+      <c r="T8" s="170" t="n"/>
+      <c r="U8" s="170" t="n"/>
+      <c r="V8" s="170" t="n"/>
+      <c r="W8" s="170" t="n"/>
+      <c r="X8" s="170" t="n"/>
+      <c r="Y8" s="170" t="n"/>
+      <c r="Z8" s="170" t="n"/>
+      <c r="AA8" s="170" t="n"/>
+      <c r="AB8" s="170" t="n"/>
+      <c r="AC8" s="171" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="AD8" s="105" t="n"/>
-      <c r="AE8" s="105" t="n"/>
-      <c r="AF8" s="105" t="n"/>
-      <c r="AG8" s="105" t="n"/>
-      <c r="AH8" s="105" t="n"/>
-      <c r="AI8" s="105" t="n"/>
-      <c r="AJ8" s="105" t="n"/>
-      <c r="AK8" s="105" t="n"/>
-      <c r="AL8" s="106" t="n"/>
-      <c r="AM8" s="75" t="n"/>
-      <c r="AN8" s="107" t="n"/>
-      <c r="AO8" s="107" t="n"/>
-      <c r="AP8" s="107" t="n"/>
-      <c r="AQ8" s="107" t="n"/>
-      <c r="AR8" s="107" t="n"/>
-      <c r="AS8" s="107" t="n"/>
-      <c r="AT8" s="107" t="n"/>
-      <c r="AU8" s="107" t="n"/>
-      <c r="AV8" s="107" t="n"/>
-      <c r="AW8" s="107" t="n"/>
-      <c r="AX8" s="107" t="n"/>
-      <c r="AY8" s="107" t="n"/>
-      <c r="AZ8" s="107" t="n"/>
-      <c r="BA8" s="107" t="n"/>
-      <c r="BB8" s="107" t="n"/>
-      <c r="BC8" s="107" t="n"/>
-      <c r="BD8" s="108" t="n"/>
+      <c r="AD8" s="168" t="n"/>
+      <c r="AE8" s="168" t="n"/>
+      <c r="AF8" s="168" t="n"/>
+      <c r="AG8" s="168" t="n"/>
+      <c r="AH8" s="168" t="n"/>
+      <c r="AI8" s="168" t="n"/>
+      <c r="AJ8" s="168" t="n"/>
+      <c r="AK8" s="168" t="n"/>
+      <c r="AL8" s="168" t="n"/>
+      <c r="AM8" s="169" t="n"/>
+      <c r="AN8" s="170" t="n"/>
+      <c r="AO8" s="170" t="n"/>
+      <c r="AP8" s="170" t="n"/>
+      <c r="AQ8" s="170" t="n"/>
+      <c r="AR8" s="170" t="n"/>
+      <c r="AS8" s="170" t="n"/>
+      <c r="AT8" s="170" t="n"/>
+      <c r="AU8" s="170" t="n"/>
+      <c r="AV8" s="170" t="n"/>
+      <c r="AW8" s="170" t="n"/>
+      <c r="AX8" s="170" t="n"/>
+      <c r="AY8" s="170" t="n"/>
+      <c r="AZ8" s="170" t="n"/>
+      <c r="BA8" s="170" t="n"/>
+      <c r="BB8" s="170" t="n"/>
+      <c r="BC8" s="170" t="n"/>
+      <c r="BD8" s="172" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="173" t="inlineStr">
         <is>
           <t>Assessor</t>
         </is>
       </c>
-      <c r="B9" s="105" t="n"/>
-      <c r="C9" s="105" t="n"/>
-      <c r="D9" s="105" t="n"/>
-      <c r="E9" s="105" t="n"/>
-      <c r="F9" s="105" t="n"/>
-      <c r="G9" s="105" t="n"/>
-      <c r="H9" s="105" t="n"/>
-      <c r="I9" s="105" t="n"/>
-      <c r="J9" s="106" t="n"/>
-      <c r="K9" s="75" t="n"/>
-      <c r="L9" s="107" t="n"/>
-      <c r="M9" s="107" t="n"/>
-      <c r="N9" s="107" t="n"/>
-      <c r="O9" s="107" t="n"/>
-      <c r="P9" s="107" t="n"/>
-      <c r="Q9" s="107" t="n"/>
-      <c r="R9" s="107" t="n"/>
-      <c r="S9" s="107" t="n"/>
-      <c r="T9" s="107" t="n"/>
-      <c r="U9" s="107" t="n"/>
-      <c r="V9" s="107" t="n"/>
-      <c r="W9" s="107" t="n"/>
-      <c r="X9" s="107" t="n"/>
-      <c r="Y9" s="107" t="n"/>
-      <c r="Z9" s="107" t="n"/>
-      <c r="AA9" s="107" t="n"/>
-      <c r="AB9" s="108" t="n"/>
-      <c r="AC9" s="72" t="inlineStr">
+      <c r="B9" s="174" t="n"/>
+      <c r="C9" s="174" t="n"/>
+      <c r="D9" s="174" t="n"/>
+      <c r="E9" s="174" t="n"/>
+      <c r="F9" s="174" t="n"/>
+      <c r="G9" s="174" t="n"/>
+      <c r="H9" s="174" t="n"/>
+      <c r="I9" s="174" t="n"/>
+      <c r="J9" s="174" t="n"/>
+      <c r="K9" s="175" t="n"/>
+      <c r="L9" s="176" t="n"/>
+      <c r="M9" s="176" t="n"/>
+      <c r="N9" s="176" t="n"/>
+      <c r="O9" s="176" t="n"/>
+      <c r="P9" s="176" t="n"/>
+      <c r="Q9" s="176" t="n"/>
+      <c r="R9" s="176" t="n"/>
+      <c r="S9" s="176" t="n"/>
+      <c r="T9" s="176" t="n"/>
+      <c r="U9" s="176" t="n"/>
+      <c r="V9" s="176" t="n"/>
+      <c r="W9" s="176" t="n"/>
+      <c r="X9" s="176" t="n"/>
+      <c r="Y9" s="176" t="n"/>
+      <c r="Z9" s="176" t="n"/>
+      <c r="AA9" s="176" t="n"/>
+      <c r="AB9" s="176" t="n"/>
+      <c r="AC9" s="177" t="inlineStr">
         <is>
           <t>Date And Assessment Type</t>
         </is>
       </c>
-      <c r="AD9" s="105" t="n"/>
-      <c r="AE9" s="105" t="n"/>
-      <c r="AF9" s="105" t="n"/>
-      <c r="AG9" s="105" t="n"/>
-      <c r="AH9" s="105" t="n"/>
-      <c r="AI9" s="105" t="n"/>
-      <c r="AJ9" s="105" t="n"/>
-      <c r="AK9" s="105" t="n"/>
-      <c r="AL9" s="106" t="n"/>
-      <c r="AM9" s="75" t="n"/>
-      <c r="AN9" s="107" t="n"/>
-      <c r="AO9" s="107" t="n"/>
-      <c r="AP9" s="107" t="n"/>
-      <c r="AQ9" s="107" t="n"/>
-      <c r="AR9" s="107" t="n"/>
-      <c r="AS9" s="107" t="n"/>
-      <c r="AT9" s="107" t="n"/>
-      <c r="AU9" s="107" t="n"/>
-      <c r="AV9" s="107" t="n"/>
-      <c r="AW9" s="107" t="n"/>
-      <c r="AX9" s="107" t="n"/>
-      <c r="AY9" s="107" t="n"/>
-      <c r="AZ9" s="107" t="n"/>
-      <c r="BA9" s="107" t="n"/>
-      <c r="BB9" s="107" t="n"/>
-      <c r="BC9" s="107" t="n"/>
-      <c r="BD9" s="108" t="n"/>
+      <c r="AD9" s="174" t="n"/>
+      <c r="AE9" s="174" t="n"/>
+      <c r="AF9" s="174" t="n"/>
+      <c r="AG9" s="174" t="n"/>
+      <c r="AH9" s="174" t="n"/>
+      <c r="AI9" s="174" t="n"/>
+      <c r="AJ9" s="174" t="n"/>
+      <c r="AK9" s="174" t="n"/>
+      <c r="AL9" s="174" t="n"/>
+      <c r="AM9" s="175" t="n"/>
+      <c r="AN9" s="176" t="n"/>
+      <c r="AO9" s="176" t="n"/>
+      <c r="AP9" s="176" t="n"/>
+      <c r="AQ9" s="176" t="n"/>
+      <c r="AR9" s="176" t="n"/>
+      <c r="AS9" s="176" t="n"/>
+      <c r="AT9" s="176" t="n"/>
+      <c r="AU9" s="176" t="n"/>
+      <c r="AV9" s="176" t="n"/>
+      <c r="AW9" s="176" t="n"/>
+      <c r="AX9" s="176" t="n"/>
+      <c r="AY9" s="176" t="n"/>
+      <c r="AZ9" s="176" t="n"/>
+      <c r="BA9" s="176" t="n"/>
+      <c r="BB9" s="176" t="n"/>
+      <c r="BC9" s="176" t="n"/>
+      <c r="BD9" s="178" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="71" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. EVIDENCE-BASED ASSESSMENT SECTION</t>
         </is>
       </c>
-      <c r="B10" s="105" t="n"/>
-      <c r="C10" s="105" t="n"/>
-      <c r="D10" s="105" t="n"/>
-      <c r="E10" s="105" t="n"/>
-      <c r="F10" s="105" t="n"/>
-      <c r="G10" s="105" t="n"/>
-      <c r="H10" s="105" t="n"/>
-      <c r="I10" s="105" t="n"/>
-      <c r="J10" s="105" t="n"/>
-      <c r="K10" s="105" t="n"/>
-      <c r="L10" s="105" t="n"/>
-      <c r="M10" s="105" t="n"/>
-      <c r="N10" s="105" t="n"/>
-      <c r="O10" s="105" t="n"/>
-      <c r="P10" s="105" t="n"/>
-      <c r="Q10" s="105" t="n"/>
-      <c r="R10" s="105" t="n"/>
-      <c r="S10" s="105" t="n"/>
-      <c r="T10" s="105" t="n"/>
-      <c r="U10" s="105" t="n"/>
-      <c r="V10" s="105" t="n"/>
-      <c r="W10" s="105" t="n"/>
-      <c r="X10" s="105" t="n"/>
-      <c r="Y10" s="105" t="n"/>
-      <c r="Z10" s="105" t="n"/>
-      <c r="AA10" s="105" t="n"/>
-      <c r="AB10" s="105" t="n"/>
-      <c r="AC10" s="105" t="n"/>
-      <c r="AD10" s="105" t="n"/>
-      <c r="AE10" s="105" t="n"/>
-      <c r="AF10" s="105" t="n"/>
-      <c r="AG10" s="105" t="n"/>
-      <c r="AH10" s="105" t="n"/>
-      <c r="AI10" s="105" t="n"/>
-      <c r="AJ10" s="105" t="n"/>
-      <c r="AK10" s="105" t="n"/>
-      <c r="AL10" s="105" t="n"/>
-      <c r="AM10" s="105" t="n"/>
-      <c r="AN10" s="105" t="n"/>
-      <c r="AO10" s="105" t="n"/>
-      <c r="AP10" s="105" t="n"/>
-      <c r="AQ10" s="105" t="n"/>
-      <c r="AR10" s="105" t="n"/>
-      <c r="AS10" s="105" t="n"/>
-      <c r="AT10" s="105" t="n"/>
-      <c r="AU10" s="105" t="n"/>
-      <c r="AV10" s="105" t="n"/>
-      <c r="AW10" s="105" t="n"/>
-      <c r="AX10" s="105" t="n"/>
-      <c r="AY10" s="105" t="n"/>
-      <c r="AZ10" s="105" t="n"/>
-      <c r="BA10" s="105" t="n"/>
-      <c r="BB10" s="105" t="n"/>
-      <c r="BC10" s="105" t="n"/>
-      <c r="BD10" s="106" t="n"/>
+      <c r="B10" s="165" t="n"/>
+      <c r="C10" s="165" t="n"/>
+      <c r="D10" s="165" t="n"/>
+      <c r="E10" s="165" t="n"/>
+      <c r="F10" s="165" t="n"/>
+      <c r="G10" s="165" t="n"/>
+      <c r="H10" s="165" t="n"/>
+      <c r="I10" s="165" t="n"/>
+      <c r="J10" s="165" t="n"/>
+      <c r="K10" s="165" t="n"/>
+      <c r="L10" s="165" t="n"/>
+      <c r="M10" s="165" t="n"/>
+      <c r="N10" s="165" t="n"/>
+      <c r="O10" s="165" t="n"/>
+      <c r="P10" s="165" t="n"/>
+      <c r="Q10" s="165" t="n"/>
+      <c r="R10" s="165" t="n"/>
+      <c r="S10" s="165" t="n"/>
+      <c r="T10" s="165" t="n"/>
+      <c r="U10" s="165" t="n"/>
+      <c r="V10" s="165" t="n"/>
+      <c r="W10" s="165" t="n"/>
+      <c r="X10" s="165" t="n"/>
+      <c r="Y10" s="165" t="n"/>
+      <c r="Z10" s="165" t="n"/>
+      <c r="AA10" s="165" t="n"/>
+      <c r="AB10" s="165" t="n"/>
+      <c r="AC10" s="165" t="n"/>
+      <c r="AD10" s="165" t="n"/>
+      <c r="AE10" s="165" t="n"/>
+      <c r="AF10" s="165" t="n"/>
+      <c r="AG10" s="165" t="n"/>
+      <c r="AH10" s="165" t="n"/>
+      <c r="AI10" s="165" t="n"/>
+      <c r="AJ10" s="165" t="n"/>
+      <c r="AK10" s="165" t="n"/>
+      <c r="AL10" s="165" t="n"/>
+      <c r="AM10" s="165" t="n"/>
+      <c r="AN10" s="165" t="n"/>
+      <c r="AO10" s="165" t="n"/>
+      <c r="AP10" s="165" t="n"/>
+      <c r="AQ10" s="165" t="n"/>
+      <c r="AR10" s="165" t="n"/>
+      <c r="AS10" s="165" t="n"/>
+      <c r="AT10" s="165" t="n"/>
+      <c r="AU10" s="165" t="n"/>
+      <c r="AV10" s="165" t="n"/>
+      <c r="AW10" s="165" t="n"/>
+      <c r="AX10" s="165" t="n"/>
+      <c r="AY10" s="165" t="n"/>
+      <c r="AZ10" s="165" t="n"/>
+      <c r="BA10" s="165" t="n"/>
+      <c r="BB10" s="165" t="n"/>
+      <c r="BC10" s="165" t="n"/>
+      <c r="BD10" s="166" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="167" t="inlineStr">
         <is>
           <t>Required Tasks / Knowledge / Behaviors</t>
         </is>
       </c>
-      <c r="B11" s="105" t="n"/>
-      <c r="C11" s="105" t="n"/>
-      <c r="D11" s="105" t="n"/>
-      <c r="E11" s="105" t="n"/>
-      <c r="F11" s="105" t="n"/>
-      <c r="G11" s="105" t="n"/>
-      <c r="H11" s="105" t="n"/>
-      <c r="I11" s="105" t="n"/>
-      <c r="J11" s="106" t="n"/>
-      <c r="K11" s="75" t="n"/>
-      <c r="L11" s="107" t="n"/>
-      <c r="M11" s="107" t="n"/>
-      <c r="N11" s="107" t="n"/>
-      <c r="O11" s="107" t="n"/>
-      <c r="P11" s="107" t="n"/>
-      <c r="Q11" s="107" t="n"/>
-      <c r="R11" s="107" t="n"/>
-      <c r="S11" s="107" t="n"/>
-      <c r="T11" s="107" t="n"/>
-      <c r="U11" s="107" t="n"/>
-      <c r="V11" s="107" t="n"/>
-      <c r="W11" s="107" t="n"/>
-      <c r="X11" s="107" t="n"/>
-      <c r="Y11" s="107" t="n"/>
-      <c r="Z11" s="107" t="n"/>
-      <c r="AA11" s="107" t="n"/>
-      <c r="AB11" s="108" t="n"/>
-      <c r="AC11" s="72" t="inlineStr">
+      <c r="B11" s="168" t="n"/>
+      <c r="C11" s="168" t="n"/>
+      <c r="D11" s="168" t="n"/>
+      <c r="E11" s="168" t="n"/>
+      <c r="F11" s="168" t="n"/>
+      <c r="G11" s="168" t="n"/>
+      <c r="H11" s="168" t="n"/>
+      <c r="I11" s="168" t="n"/>
+      <c r="J11" s="168" t="n"/>
+      <c r="K11" s="169" t="n"/>
+      <c r="L11" s="170" t="n"/>
+      <c r="M11" s="170" t="n"/>
+      <c r="N11" s="170" t="n"/>
+      <c r="O11" s="170" t="n"/>
+      <c r="P11" s="170" t="n"/>
+      <c r="Q11" s="170" t="n"/>
+      <c r="R11" s="170" t="n"/>
+      <c r="S11" s="170" t="n"/>
+      <c r="T11" s="170" t="n"/>
+      <c r="U11" s="170" t="n"/>
+      <c r="V11" s="170" t="n"/>
+      <c r="W11" s="170" t="n"/>
+      <c r="X11" s="170" t="n"/>
+      <c r="Y11" s="170" t="n"/>
+      <c r="Z11" s="170" t="n"/>
+      <c r="AA11" s="170" t="n"/>
+      <c r="AB11" s="170" t="n"/>
+      <c r="AC11" s="171" t="inlineStr">
         <is>
           <t>Observed Evidence</t>
         </is>
       </c>
-      <c r="AD11" s="105" t="n"/>
-      <c r="AE11" s="105" t="n"/>
-      <c r="AF11" s="105" t="n"/>
-      <c r="AG11" s="105" t="n"/>
-      <c r="AH11" s="105" t="n"/>
-      <c r="AI11" s="105" t="n"/>
-      <c r="AJ11" s="105" t="n"/>
-      <c r="AK11" s="105" t="n"/>
-      <c r="AL11" s="106" t="n"/>
-      <c r="AM11" s="75" t="n"/>
-      <c r="AN11" s="107" t="n"/>
-      <c r="AO11" s="107" t="n"/>
-      <c r="AP11" s="107" t="n"/>
-      <c r="AQ11" s="107" t="n"/>
-      <c r="AR11" s="107" t="n"/>
-      <c r="AS11" s="107" t="n"/>
-      <c r="AT11" s="107" t="n"/>
-      <c r="AU11" s="107" t="n"/>
-      <c r="AV11" s="107" t="n"/>
-      <c r="AW11" s="107" t="n"/>
-      <c r="AX11" s="107" t="n"/>
-      <c r="AY11" s="107" t="n"/>
-      <c r="AZ11" s="107" t="n"/>
-      <c r="BA11" s="107" t="n"/>
-      <c r="BB11" s="107" t="n"/>
-      <c r="BC11" s="107" t="n"/>
-      <c r="BD11" s="108" t="n"/>
+      <c r="AD11" s="168" t="n"/>
+      <c r="AE11" s="168" t="n"/>
+      <c r="AF11" s="168" t="n"/>
+      <c r="AG11" s="168" t="n"/>
+      <c r="AH11" s="168" t="n"/>
+      <c r="AI11" s="168" t="n"/>
+      <c r="AJ11" s="168" t="n"/>
+      <c r="AK11" s="168" t="n"/>
+      <c r="AL11" s="168" t="n"/>
+      <c r="AM11" s="169" t="n"/>
+      <c r="AN11" s="170" t="n"/>
+      <c r="AO11" s="170" t="n"/>
+      <c r="AP11" s="170" t="n"/>
+      <c r="AQ11" s="170" t="n"/>
+      <c r="AR11" s="170" t="n"/>
+      <c r="AS11" s="170" t="n"/>
+      <c r="AT11" s="170" t="n"/>
+      <c r="AU11" s="170" t="n"/>
+      <c r="AV11" s="170" t="n"/>
+      <c r="AW11" s="170" t="n"/>
+      <c r="AX11" s="170" t="n"/>
+      <c r="AY11" s="170" t="n"/>
+      <c r="AZ11" s="170" t="n"/>
+      <c r="BA11" s="170" t="n"/>
+      <c r="BB11" s="170" t="n"/>
+      <c r="BC11" s="170" t="n"/>
+      <c r="BD11" s="172" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="173" t="inlineStr">
         <is>
           <t>Pass Standard</t>
         </is>
       </c>
-      <c r="B12" s="105" t="n"/>
-      <c r="C12" s="105" t="n"/>
-      <c r="D12" s="105" t="n"/>
-      <c r="E12" s="105" t="n"/>
-      <c r="F12" s="105" t="n"/>
-      <c r="G12" s="105" t="n"/>
-      <c r="H12" s="105" t="n"/>
-      <c r="I12" s="105" t="n"/>
-      <c r="J12" s="106" t="n"/>
-      <c r="K12" s="75" t="n"/>
-      <c r="L12" s="107" t="n"/>
-      <c r="M12" s="107" t="n"/>
-      <c r="N12" s="107" t="n"/>
-      <c r="O12" s="107" t="n"/>
-      <c r="P12" s="107" t="n"/>
-      <c r="Q12" s="107" t="n"/>
-      <c r="R12" s="107" t="n"/>
-      <c r="S12" s="107" t="n"/>
-      <c r="T12" s="107" t="n"/>
-      <c r="U12" s="107" t="n"/>
-      <c r="V12" s="107" t="n"/>
-      <c r="W12" s="107" t="n"/>
-      <c r="X12" s="107" t="n"/>
-      <c r="Y12" s="107" t="n"/>
-      <c r="Z12" s="107" t="n"/>
-      <c r="AA12" s="107" t="n"/>
-      <c r="AB12" s="108" t="n"/>
-      <c r="AC12" s="72" t="inlineStr">
+      <c r="B12" s="174" t="n"/>
+      <c r="C12" s="174" t="n"/>
+      <c r="D12" s="174" t="n"/>
+      <c r="E12" s="174" t="n"/>
+      <c r="F12" s="174" t="n"/>
+      <c r="G12" s="174" t="n"/>
+      <c r="H12" s="174" t="n"/>
+      <c r="I12" s="174" t="n"/>
+      <c r="J12" s="174" t="n"/>
+      <c r="K12" s="175" t="n"/>
+      <c r="L12" s="176" t="n"/>
+      <c r="M12" s="176" t="n"/>
+      <c r="N12" s="176" t="n"/>
+      <c r="O12" s="176" t="n"/>
+      <c r="P12" s="176" t="n"/>
+      <c r="Q12" s="176" t="n"/>
+      <c r="R12" s="176" t="n"/>
+      <c r="S12" s="176" t="n"/>
+      <c r="T12" s="176" t="n"/>
+      <c r="U12" s="176" t="n"/>
+      <c r="V12" s="176" t="n"/>
+      <c r="W12" s="176" t="n"/>
+      <c r="X12" s="176" t="n"/>
+      <c r="Y12" s="176" t="n"/>
+      <c r="Z12" s="176" t="n"/>
+      <c r="AA12" s="176" t="n"/>
+      <c r="AB12" s="176" t="n"/>
+      <c r="AC12" s="177" t="inlineStr">
         <is>
           <t>Comments By Criterion</t>
         </is>
       </c>
-      <c r="AD12" s="105" t="n"/>
-      <c r="AE12" s="105" t="n"/>
-      <c r="AF12" s="105" t="n"/>
-      <c r="AG12" s="105" t="n"/>
-      <c r="AH12" s="105" t="n"/>
-      <c r="AI12" s="105" t="n"/>
-      <c r="AJ12" s="105" t="n"/>
-      <c r="AK12" s="105" t="n"/>
-      <c r="AL12" s="106" t="n"/>
-      <c r="AM12" s="75" t="n"/>
-      <c r="AN12" s="107" t="n"/>
-      <c r="AO12" s="107" t="n"/>
-      <c r="AP12" s="107" t="n"/>
-      <c r="AQ12" s="107" t="n"/>
-      <c r="AR12" s="107" t="n"/>
-      <c r="AS12" s="107" t="n"/>
-      <c r="AT12" s="107" t="n"/>
-      <c r="AU12" s="107" t="n"/>
-      <c r="AV12" s="107" t="n"/>
-      <c r="AW12" s="107" t="n"/>
-      <c r="AX12" s="107" t="n"/>
-      <c r="AY12" s="107" t="n"/>
-      <c r="AZ12" s="107" t="n"/>
-      <c r="BA12" s="107" t="n"/>
-      <c r="BB12" s="107" t="n"/>
-      <c r="BC12" s="107" t="n"/>
-      <c r="BD12" s="108" t="n"/>
+      <c r="AD12" s="174" t="n"/>
+      <c r="AE12" s="174" t="n"/>
+      <c r="AF12" s="174" t="n"/>
+      <c r="AG12" s="174" t="n"/>
+      <c r="AH12" s="174" t="n"/>
+      <c r="AI12" s="174" t="n"/>
+      <c r="AJ12" s="174" t="n"/>
+      <c r="AK12" s="174" t="n"/>
+      <c r="AL12" s="174" t="n"/>
+      <c r="AM12" s="175" t="n"/>
+      <c r="AN12" s="176" t="n"/>
+      <c r="AO12" s="176" t="n"/>
+      <c r="AP12" s="176" t="n"/>
+      <c r="AQ12" s="176" t="n"/>
+      <c r="AR12" s="176" t="n"/>
+      <c r="AS12" s="176" t="n"/>
+      <c r="AT12" s="176" t="n"/>
+      <c r="AU12" s="176" t="n"/>
+      <c r="AV12" s="176" t="n"/>
+      <c r="AW12" s="176" t="n"/>
+      <c r="AX12" s="176" t="n"/>
+      <c r="AY12" s="176" t="n"/>
+      <c r="AZ12" s="176" t="n"/>
+      <c r="BA12" s="176" t="n"/>
+      <c r="BB12" s="176" t="n"/>
+      <c r="BC12" s="176" t="n"/>
+      <c r="BD12" s="178" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="71" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. GAP AND DEVELOPMENT SECTION</t>
         </is>
       </c>
-      <c r="B13" s="105" t="n"/>
-      <c r="C13" s="105" t="n"/>
-      <c r="D13" s="105" t="n"/>
-      <c r="E13" s="105" t="n"/>
-      <c r="F13" s="105" t="n"/>
-      <c r="G13" s="105" t="n"/>
-      <c r="H13" s="105" t="n"/>
-      <c r="I13" s="105" t="n"/>
-      <c r="J13" s="105" t="n"/>
-      <c r="K13" s="105" t="n"/>
-      <c r="L13" s="105" t="n"/>
-      <c r="M13" s="105" t="n"/>
-      <c r="N13" s="105" t="n"/>
-      <c r="O13" s="105" t="n"/>
-      <c r="P13" s="105" t="n"/>
-      <c r="Q13" s="105" t="n"/>
-      <c r="R13" s="105" t="n"/>
-      <c r="S13" s="105" t="n"/>
-      <c r="T13" s="105" t="n"/>
-      <c r="U13" s="105" t="n"/>
-      <c r="V13" s="105" t="n"/>
-      <c r="W13" s="105" t="n"/>
-      <c r="X13" s="105" t="n"/>
-      <c r="Y13" s="105" t="n"/>
-      <c r="Z13" s="105" t="n"/>
-      <c r="AA13" s="105" t="n"/>
-      <c r="AB13" s="105" t="n"/>
-      <c r="AC13" s="105" t="n"/>
-      <c r="AD13" s="105" t="n"/>
-      <c r="AE13" s="105" t="n"/>
-      <c r="AF13" s="105" t="n"/>
-      <c r="AG13" s="105" t="n"/>
-      <c r="AH13" s="105" t="n"/>
-      <c r="AI13" s="105" t="n"/>
-      <c r="AJ13" s="105" t="n"/>
-      <c r="AK13" s="105" t="n"/>
-      <c r="AL13" s="105" t="n"/>
-      <c r="AM13" s="105" t="n"/>
-      <c r="AN13" s="105" t="n"/>
-      <c r="AO13" s="105" t="n"/>
-      <c r="AP13" s="105" t="n"/>
-      <c r="AQ13" s="105" t="n"/>
-      <c r="AR13" s="105" t="n"/>
-      <c r="AS13" s="105" t="n"/>
-      <c r="AT13" s="105" t="n"/>
-      <c r="AU13" s="105" t="n"/>
-      <c r="AV13" s="105" t="n"/>
-      <c r="AW13" s="105" t="n"/>
-      <c r="AX13" s="105" t="n"/>
-      <c r="AY13" s="105" t="n"/>
-      <c r="AZ13" s="105" t="n"/>
-      <c r="BA13" s="105" t="n"/>
-      <c r="BB13" s="105" t="n"/>
-      <c r="BC13" s="105" t="n"/>
-      <c r="BD13" s="106" t="n"/>
+      <c r="B13" s="165" t="n"/>
+      <c r="C13" s="165" t="n"/>
+      <c r="D13" s="165" t="n"/>
+      <c r="E13" s="165" t="n"/>
+      <c r="F13" s="165" t="n"/>
+      <c r="G13" s="165" t="n"/>
+      <c r="H13" s="165" t="n"/>
+      <c r="I13" s="165" t="n"/>
+      <c r="J13" s="165" t="n"/>
+      <c r="K13" s="165" t="n"/>
+      <c r="L13" s="165" t="n"/>
+      <c r="M13" s="165" t="n"/>
+      <c r="N13" s="165" t="n"/>
+      <c r="O13" s="165" t="n"/>
+      <c r="P13" s="165" t="n"/>
+      <c r="Q13" s="165" t="n"/>
+      <c r="R13" s="165" t="n"/>
+      <c r="S13" s="165" t="n"/>
+      <c r="T13" s="165" t="n"/>
+      <c r="U13" s="165" t="n"/>
+      <c r="V13" s="165" t="n"/>
+      <c r="W13" s="165" t="n"/>
+      <c r="X13" s="165" t="n"/>
+      <c r="Y13" s="165" t="n"/>
+      <c r="Z13" s="165" t="n"/>
+      <c r="AA13" s="165" t="n"/>
+      <c r="AB13" s="165" t="n"/>
+      <c r="AC13" s="165" t="n"/>
+      <c r="AD13" s="165" t="n"/>
+      <c r="AE13" s="165" t="n"/>
+      <c r="AF13" s="165" t="n"/>
+      <c r="AG13" s="165" t="n"/>
+      <c r="AH13" s="165" t="n"/>
+      <c r="AI13" s="165" t="n"/>
+      <c r="AJ13" s="165" t="n"/>
+      <c r="AK13" s="165" t="n"/>
+      <c r="AL13" s="165" t="n"/>
+      <c r="AM13" s="165" t="n"/>
+      <c r="AN13" s="165" t="n"/>
+      <c r="AO13" s="165" t="n"/>
+      <c r="AP13" s="165" t="n"/>
+      <c r="AQ13" s="165" t="n"/>
+      <c r="AR13" s="165" t="n"/>
+      <c r="AS13" s="165" t="n"/>
+      <c r="AT13" s="165" t="n"/>
+      <c r="AU13" s="165" t="n"/>
+      <c r="AV13" s="165" t="n"/>
+      <c r="AW13" s="165" t="n"/>
+      <c r="AX13" s="165" t="n"/>
+      <c r="AY13" s="165" t="n"/>
+      <c r="AZ13" s="165" t="n"/>
+      <c r="BA13" s="165" t="n"/>
+      <c r="BB13" s="165" t="n"/>
+      <c r="BC13" s="165" t="n"/>
+      <c r="BD13" s="166" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="72" t="inlineStr">
+      <c r="A14" s="167" t="inlineStr">
         <is>
           <t>Restrictions</t>
         </is>
       </c>
-      <c r="B14" s="105" t="n"/>
-      <c r="C14" s="105" t="n"/>
-      <c r="D14" s="105" t="n"/>
-      <c r="E14" s="105" t="n"/>
-      <c r="F14" s="105" t="n"/>
-      <c r="G14" s="105" t="n"/>
-      <c r="H14" s="105" t="n"/>
-      <c r="I14" s="105" t="n"/>
-      <c r="J14" s="106" t="n"/>
-      <c r="K14" s="75" t="n"/>
-      <c r="L14" s="107" t="n"/>
-      <c r="M14" s="107" t="n"/>
-      <c r="N14" s="107" t="n"/>
-      <c r="O14" s="107" t="n"/>
-      <c r="P14" s="107" t="n"/>
-      <c r="Q14" s="107" t="n"/>
-      <c r="R14" s="107" t="n"/>
-      <c r="S14" s="107" t="n"/>
-      <c r="T14" s="107" t="n"/>
-      <c r="U14" s="107" t="n"/>
-      <c r="V14" s="107" t="n"/>
-      <c r="W14" s="107" t="n"/>
-      <c r="X14" s="107" t="n"/>
-      <c r="Y14" s="107" t="n"/>
-      <c r="Z14" s="107" t="n"/>
-      <c r="AA14" s="107" t="n"/>
-      <c r="AB14" s="108" t="n"/>
-      <c r="AC14" s="72" t="inlineStr">
+      <c r="B14" s="168" t="n"/>
+      <c r="C14" s="168" t="n"/>
+      <c r="D14" s="168" t="n"/>
+      <c r="E14" s="168" t="n"/>
+      <c r="F14" s="168" t="n"/>
+      <c r="G14" s="168" t="n"/>
+      <c r="H14" s="168" t="n"/>
+      <c r="I14" s="168" t="n"/>
+      <c r="J14" s="168" t="n"/>
+      <c r="K14" s="169" t="n"/>
+      <c r="L14" s="170" t="n"/>
+      <c r="M14" s="170" t="n"/>
+      <c r="N14" s="170" t="n"/>
+      <c r="O14" s="170" t="n"/>
+      <c r="P14" s="170" t="n"/>
+      <c r="Q14" s="170" t="n"/>
+      <c r="R14" s="170" t="n"/>
+      <c r="S14" s="170" t="n"/>
+      <c r="T14" s="170" t="n"/>
+      <c r="U14" s="170" t="n"/>
+      <c r="V14" s="170" t="n"/>
+      <c r="W14" s="170" t="n"/>
+      <c r="X14" s="170" t="n"/>
+      <c r="Y14" s="170" t="n"/>
+      <c r="Z14" s="170" t="n"/>
+      <c r="AA14" s="170" t="n"/>
+      <c r="AB14" s="170" t="n"/>
+      <c r="AC14" s="171" t="inlineStr">
         <is>
           <t>Retraining</t>
         </is>
       </c>
-      <c r="AD14" s="105" t="n"/>
-      <c r="AE14" s="105" t="n"/>
-      <c r="AF14" s="105" t="n"/>
-      <c r="AG14" s="105" t="n"/>
-      <c r="AH14" s="105" t="n"/>
-      <c r="AI14" s="105" t="n"/>
-      <c r="AJ14" s="105" t="n"/>
-      <c r="AK14" s="105" t="n"/>
-      <c r="AL14" s="106" t="n"/>
-      <c r="AM14" s="75" t="n"/>
-      <c r="AN14" s="107" t="n"/>
-      <c r="AO14" s="107" t="n"/>
-      <c r="AP14" s="107" t="n"/>
-      <c r="AQ14" s="107" t="n"/>
-      <c r="AR14" s="107" t="n"/>
-      <c r="AS14" s="107" t="n"/>
-      <c r="AT14" s="107" t="n"/>
-      <c r="AU14" s="107" t="n"/>
-      <c r="AV14" s="107" t="n"/>
-      <c r="AW14" s="107" t="n"/>
-      <c r="AX14" s="107" t="n"/>
-      <c r="AY14" s="107" t="n"/>
-      <c r="AZ14" s="107" t="n"/>
-      <c r="BA14" s="107" t="n"/>
-      <c r="BB14" s="107" t="n"/>
-      <c r="BC14" s="107" t="n"/>
-      <c r="BD14" s="108" t="n"/>
+      <c r="AD14" s="168" t="n"/>
+      <c r="AE14" s="168" t="n"/>
+      <c r="AF14" s="168" t="n"/>
+      <c r="AG14" s="168" t="n"/>
+      <c r="AH14" s="168" t="n"/>
+      <c r="AI14" s="168" t="n"/>
+      <c r="AJ14" s="168" t="n"/>
+      <c r="AK14" s="168" t="n"/>
+      <c r="AL14" s="168" t="n"/>
+      <c r="AM14" s="169" t="n"/>
+      <c r="AN14" s="170" t="n"/>
+      <c r="AO14" s="170" t="n"/>
+      <c r="AP14" s="170" t="n"/>
+      <c r="AQ14" s="170" t="n"/>
+      <c r="AR14" s="170" t="n"/>
+      <c r="AS14" s="170" t="n"/>
+      <c r="AT14" s="170" t="n"/>
+      <c r="AU14" s="170" t="n"/>
+      <c r="AV14" s="170" t="n"/>
+      <c r="AW14" s="170" t="n"/>
+      <c r="AX14" s="170" t="n"/>
+      <c r="AY14" s="170" t="n"/>
+      <c r="AZ14" s="170" t="n"/>
+      <c r="BA14" s="170" t="n"/>
+      <c r="BB14" s="170" t="n"/>
+      <c r="BC14" s="170" t="n"/>
+      <c r="BD14" s="172" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="173" t="inlineStr">
         <is>
           <t>Mentoring Or Re-Assessment Requirements</t>
         </is>
       </c>
-      <c r="B15" s="105" t="n"/>
-      <c r="C15" s="105" t="n"/>
-      <c r="D15" s="105" t="n"/>
-      <c r="E15" s="105" t="n"/>
-      <c r="F15" s="105" t="n"/>
-      <c r="G15" s="105" t="n"/>
-      <c r="H15" s="105" t="n"/>
-      <c r="I15" s="105" t="n"/>
-      <c r="J15" s="106" t="n"/>
-      <c r="K15" s="75" t="n"/>
-      <c r="L15" s="107" t="n"/>
-      <c r="M15" s="107" t="n"/>
-      <c r="N15" s="107" t="n"/>
-      <c r="O15" s="107" t="n"/>
-      <c r="P15" s="107" t="n"/>
-      <c r="Q15" s="107" t="n"/>
-      <c r="R15" s="107" t="n"/>
-      <c r="S15" s="107" t="n"/>
-      <c r="T15" s="107" t="n"/>
-      <c r="U15" s="107" t="n"/>
-      <c r="V15" s="107" t="n"/>
-      <c r="W15" s="107" t="n"/>
-      <c r="X15" s="107" t="n"/>
-      <c r="Y15" s="107" t="n"/>
-      <c r="Z15" s="107" t="n"/>
-      <c r="AA15" s="107" t="n"/>
-      <c r="AB15" s="108" t="n"/>
-      <c r="AC15" s="72" t="inlineStr">
+      <c r="B15" s="174" t="n"/>
+      <c r="C15" s="174" t="n"/>
+      <c r="D15" s="174" t="n"/>
+      <c r="E15" s="174" t="n"/>
+      <c r="F15" s="174" t="n"/>
+      <c r="G15" s="174" t="n"/>
+      <c r="H15" s="174" t="n"/>
+      <c r="I15" s="174" t="n"/>
+      <c r="J15" s="174" t="n"/>
+      <c r="K15" s="175" t="n"/>
+      <c r="L15" s="176" t="n"/>
+      <c r="M15" s="176" t="n"/>
+      <c r="N15" s="176" t="n"/>
+      <c r="O15" s="176" t="n"/>
+      <c r="P15" s="176" t="n"/>
+      <c r="Q15" s="176" t="n"/>
+      <c r="R15" s="176" t="n"/>
+      <c r="S15" s="176" t="n"/>
+      <c r="T15" s="176" t="n"/>
+      <c r="U15" s="176" t="n"/>
+      <c r="V15" s="176" t="n"/>
+      <c r="W15" s="176" t="n"/>
+      <c r="X15" s="176" t="n"/>
+      <c r="Y15" s="176" t="n"/>
+      <c r="Z15" s="176" t="n"/>
+      <c r="AA15" s="176" t="n"/>
+      <c r="AB15" s="176" t="n"/>
+      <c r="AC15" s="177" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AD15" s="105" t="n"/>
-      <c r="AE15" s="105" t="n"/>
-      <c r="AF15" s="105" t="n"/>
-      <c r="AG15" s="105" t="n"/>
-      <c r="AH15" s="105" t="n"/>
-      <c r="AI15" s="105" t="n"/>
-      <c r="AJ15" s="105" t="n"/>
-      <c r="AK15" s="105" t="n"/>
-      <c r="AL15" s="106" t="n"/>
-      <c r="AM15" s="75" t="n"/>
-      <c r="AN15" s="107" t="n"/>
-      <c r="AO15" s="107" t="n"/>
-      <c r="AP15" s="107" t="n"/>
-      <c r="AQ15" s="107" t="n"/>
-      <c r="AR15" s="107" t="n"/>
-      <c r="AS15" s="107" t="n"/>
-      <c r="AT15" s="107" t="n"/>
-      <c r="AU15" s="107" t="n"/>
-      <c r="AV15" s="107" t="n"/>
-      <c r="AW15" s="107" t="n"/>
-      <c r="AX15" s="107" t="n"/>
-      <c r="AY15" s="107" t="n"/>
-      <c r="AZ15" s="107" t="n"/>
-      <c r="BA15" s="107" t="n"/>
-      <c r="BB15" s="107" t="n"/>
-      <c r="BC15" s="107" t="n"/>
-      <c r="BD15" s="108" t="n"/>
+      <c r="AD15" s="174" t="n"/>
+      <c r="AE15" s="174" t="n"/>
+      <c r="AF15" s="174" t="n"/>
+      <c r="AG15" s="174" t="n"/>
+      <c r="AH15" s="174" t="n"/>
+      <c r="AI15" s="174" t="n"/>
+      <c r="AJ15" s="174" t="n"/>
+      <c r="AK15" s="174" t="n"/>
+      <c r="AL15" s="174" t="n"/>
+      <c r="AM15" s="175" t="n"/>
+      <c r="AN15" s="176" t="n"/>
+      <c r="AO15" s="176" t="n"/>
+      <c r="AP15" s="176" t="n"/>
+      <c r="AQ15" s="176" t="n"/>
+      <c r="AR15" s="176" t="n"/>
+      <c r="AS15" s="176" t="n"/>
+      <c r="AT15" s="176" t="n"/>
+      <c r="AU15" s="176" t="n"/>
+      <c r="AV15" s="176" t="n"/>
+      <c r="AW15" s="176" t="n"/>
+      <c r="AX15" s="176" t="n"/>
+      <c r="AY15" s="176" t="n"/>
+      <c r="AZ15" s="176" t="n"/>
+      <c r="BA15" s="176" t="n"/>
+      <c r="BB15" s="176" t="n"/>
+      <c r="BC15" s="176" t="n"/>
+      <c r="BD15" s="178" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="71" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. DECISION SECTION</t>
         </is>
       </c>
-      <c r="B16" s="105" t="n"/>
-      <c r="C16" s="105" t="n"/>
-      <c r="D16" s="105" t="n"/>
-      <c r="E16" s="105" t="n"/>
-      <c r="F16" s="105" t="n"/>
-      <c r="G16" s="105" t="n"/>
-      <c r="H16" s="105" t="n"/>
-      <c r="I16" s="105" t="n"/>
-      <c r="J16" s="105" t="n"/>
-      <c r="K16" s="105" t="n"/>
-      <c r="L16" s="105" t="n"/>
-      <c r="M16" s="105" t="n"/>
-      <c r="N16" s="105" t="n"/>
-      <c r="O16" s="105" t="n"/>
-      <c r="P16" s="105" t="n"/>
-      <c r="Q16" s="105" t="n"/>
-      <c r="R16" s="105" t="n"/>
-      <c r="S16" s="105" t="n"/>
-      <c r="T16" s="105" t="n"/>
-      <c r="U16" s="105" t="n"/>
-      <c r="V16" s="105" t="n"/>
-      <c r="W16" s="105" t="n"/>
-      <c r="X16" s="105" t="n"/>
-      <c r="Y16" s="105" t="n"/>
-      <c r="Z16" s="105" t="n"/>
-      <c r="AA16" s="105" t="n"/>
-      <c r="AB16" s="105" t="n"/>
-      <c r="AC16" s="105" t="n"/>
-      <c r="AD16" s="105" t="n"/>
-      <c r="AE16" s="105" t="n"/>
-      <c r="AF16" s="105" t="n"/>
-      <c r="AG16" s="105" t="n"/>
-      <c r="AH16" s="105" t="n"/>
-      <c r="AI16" s="105" t="n"/>
-      <c r="AJ16" s="105" t="n"/>
-      <c r="AK16" s="105" t="n"/>
-      <c r="AL16" s="105" t="n"/>
-      <c r="AM16" s="105" t="n"/>
-      <c r="AN16" s="105" t="n"/>
-      <c r="AO16" s="105" t="n"/>
-      <c r="AP16" s="105" t="n"/>
-      <c r="AQ16" s="105" t="n"/>
-      <c r="AR16" s="105" t="n"/>
-      <c r="AS16" s="105" t="n"/>
-      <c r="AT16" s="105" t="n"/>
-      <c r="AU16" s="105" t="n"/>
-      <c r="AV16" s="105" t="n"/>
-      <c r="AW16" s="105" t="n"/>
-      <c r="AX16" s="105" t="n"/>
-      <c r="AY16" s="105" t="n"/>
-      <c r="AZ16" s="105" t="n"/>
-      <c r="BA16" s="105" t="n"/>
-      <c r="BB16" s="105" t="n"/>
-      <c r="BC16" s="105" t="n"/>
-      <c r="BD16" s="106" t="n"/>
+      <c r="B16" s="165" t="n"/>
+      <c r="C16" s="165" t="n"/>
+      <c r="D16" s="165" t="n"/>
+      <c r="E16" s="165" t="n"/>
+      <c r="F16" s="165" t="n"/>
+      <c r="G16" s="165" t="n"/>
+      <c r="H16" s="165" t="n"/>
+      <c r="I16" s="165" t="n"/>
+      <c r="J16" s="165" t="n"/>
+      <c r="K16" s="165" t="n"/>
+      <c r="L16" s="165" t="n"/>
+      <c r="M16" s="165" t="n"/>
+      <c r="N16" s="165" t="n"/>
+      <c r="O16" s="165" t="n"/>
+      <c r="P16" s="165" t="n"/>
+      <c r="Q16" s="165" t="n"/>
+      <c r="R16" s="165" t="n"/>
+      <c r="S16" s="165" t="n"/>
+      <c r="T16" s="165" t="n"/>
+      <c r="U16" s="165" t="n"/>
+      <c r="V16" s="165" t="n"/>
+      <c r="W16" s="165" t="n"/>
+      <c r="X16" s="165" t="n"/>
+      <c r="Y16" s="165" t="n"/>
+      <c r="Z16" s="165" t="n"/>
+      <c r="AA16" s="165" t="n"/>
+      <c r="AB16" s="165" t="n"/>
+      <c r="AC16" s="165" t="n"/>
+      <c r="AD16" s="165" t="n"/>
+      <c r="AE16" s="165" t="n"/>
+      <c r="AF16" s="165" t="n"/>
+      <c r="AG16" s="165" t="n"/>
+      <c r="AH16" s="165" t="n"/>
+      <c r="AI16" s="165" t="n"/>
+      <c r="AJ16" s="165" t="n"/>
+      <c r="AK16" s="165" t="n"/>
+      <c r="AL16" s="165" t="n"/>
+      <c r="AM16" s="165" t="n"/>
+      <c r="AN16" s="165" t="n"/>
+      <c r="AO16" s="165" t="n"/>
+      <c r="AP16" s="165" t="n"/>
+      <c r="AQ16" s="165" t="n"/>
+      <c r="AR16" s="165" t="n"/>
+      <c r="AS16" s="165" t="n"/>
+      <c r="AT16" s="165" t="n"/>
+      <c r="AU16" s="165" t="n"/>
+      <c r="AV16" s="165" t="n"/>
+      <c r="AW16" s="165" t="n"/>
+      <c r="AX16" s="165" t="n"/>
+      <c r="AY16" s="165" t="n"/>
+      <c r="AZ16" s="165" t="n"/>
+      <c r="BA16" s="165" t="n"/>
+      <c r="BB16" s="165" t="n"/>
+      <c r="BC16" s="165" t="n"/>
+      <c r="BD16" s="166" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="72" t="inlineStr">
+      <c r="A17" s="167" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="B17" s="105" t="n"/>
-      <c r="C17" s="105" t="n"/>
-      <c r="D17" s="105" t="n"/>
-      <c r="E17" s="105" t="n"/>
-      <c r="F17" s="105" t="n"/>
-      <c r="G17" s="105" t="n"/>
-      <c r="H17" s="105" t="n"/>
-      <c r="I17" s="105" t="n"/>
-      <c r="J17" s="106" t="n"/>
-      <c r="K17" s="75" t="n"/>
-      <c r="L17" s="107" t="n"/>
-      <c r="M17" s="107" t="n"/>
-      <c r="N17" s="107" t="n"/>
-      <c r="O17" s="107" t="n"/>
-      <c r="P17" s="107" t="n"/>
-      <c r="Q17" s="107" t="n"/>
-      <c r="R17" s="107" t="n"/>
-      <c r="S17" s="107" t="n"/>
-      <c r="T17" s="107" t="n"/>
-      <c r="U17" s="107" t="n"/>
-      <c r="V17" s="107" t="n"/>
-      <c r="W17" s="107" t="n"/>
-      <c r="X17" s="107" t="n"/>
-      <c r="Y17" s="107" t="n"/>
-      <c r="Z17" s="107" t="n"/>
-      <c r="AA17" s="107" t="n"/>
-      <c r="AB17" s="108" t="n"/>
-      <c r="AC17" s="72" t="inlineStr">
+      <c r="B17" s="168" t="n"/>
+      <c r="C17" s="168" t="n"/>
+      <c r="D17" s="168" t="n"/>
+      <c r="E17" s="168" t="n"/>
+      <c r="F17" s="168" t="n"/>
+      <c r="G17" s="168" t="n"/>
+      <c r="H17" s="168" t="n"/>
+      <c r="I17" s="168" t="n"/>
+      <c r="J17" s="168" t="n"/>
+      <c r="K17" s="169" t="n"/>
+      <c r="L17" s="170" t="n"/>
+      <c r="M17" s="170" t="n"/>
+      <c r="N17" s="170" t="n"/>
+      <c r="O17" s="170" t="n"/>
+      <c r="P17" s="170" t="n"/>
+      <c r="Q17" s="170" t="n"/>
+      <c r="R17" s="170" t="n"/>
+      <c r="S17" s="179" t="n"/>
+      <c r="T17" s="170" t="n"/>
+      <c r="U17" s="170" t="n"/>
+      <c r="V17" s="170" t="n"/>
+      <c r="W17" s="170" t="n"/>
+      <c r="X17" s="170" t="n"/>
+      <c r="Y17" s="170" t="n"/>
+      <c r="Z17" s="170" t="n"/>
+      <c r="AA17" s="170" t="n"/>
+      <c r="AB17" s="170" t="n"/>
+      <c r="AC17" s="171" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AD17" s="105" t="n"/>
-      <c r="AE17" s="105" t="n"/>
-      <c r="AF17" s="105" t="n"/>
-      <c r="AG17" s="105" t="n"/>
-      <c r="AH17" s="105" t="n"/>
-      <c r="AI17" s="105" t="n"/>
-      <c r="AJ17" s="105" t="n"/>
-      <c r="AK17" s="105" t="n"/>
-      <c r="AL17" s="106" t="n"/>
-      <c r="AM17" s="75" t="n"/>
-      <c r="AN17" s="107" t="n"/>
-      <c r="AO17" s="107" t="n"/>
-      <c r="AP17" s="107" t="n"/>
-      <c r="AQ17" s="107" t="n"/>
-      <c r="AR17" s="107" t="n"/>
-      <c r="AS17" s="107" t="n"/>
-      <c r="AT17" s="107" t="n"/>
-      <c r="AU17" s="107" t="n"/>
-      <c r="AV17" s="107" t="n"/>
-      <c r="AW17" s="107" t="n"/>
-      <c r="AX17" s="107" t="n"/>
-      <c r="AY17" s="107" t="n"/>
-      <c r="AZ17" s="107" t="n"/>
-      <c r="BA17" s="107" t="n"/>
-      <c r="BB17" s="107" t="n"/>
-      <c r="BC17" s="107" t="n"/>
-      <c r="BD17" s="108" t="n"/>
+      <c r="AD17" s="168" t="n"/>
+      <c r="AE17" s="168" t="n"/>
+      <c r="AF17" s="168" t="n"/>
+      <c r="AG17" s="168" t="n"/>
+      <c r="AH17" s="168" t="n"/>
+      <c r="AI17" s="168" t="n"/>
+      <c r="AJ17" s="168" t="n"/>
+      <c r="AK17" s="180" t="n"/>
+      <c r="AL17" s="168" t="n"/>
+      <c r="AM17" s="169" t="n"/>
+      <c r="AN17" s="170" t="n"/>
+      <c r="AO17" s="170" t="n"/>
+      <c r="AP17" s="170" t="n"/>
+      <c r="AQ17" s="170" t="n"/>
+      <c r="AR17" s="170" t="n"/>
+      <c r="AS17" s="170" t="n"/>
+      <c r="AT17" s="170" t="n"/>
+      <c r="AU17" s="170" t="n"/>
+      <c r="AV17" s="170" t="n"/>
+      <c r="AW17" s="170" t="n"/>
+      <c r="AX17" s="170" t="n"/>
+      <c r="AY17" s="170" t="n"/>
+      <c r="AZ17" s="170" t="n"/>
+      <c r="BA17" s="170" t="n"/>
+      <c r="BB17" s="170" t="n"/>
+      <c r="BC17" s="170" t="n"/>
+      <c r="BD17" s="172" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="72" t="inlineStr">
+      <c r="A18" s="181" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B18" s="105" t="n"/>
-      <c r="C18" s="105" t="n"/>
-      <c r="D18" s="105" t="n"/>
-      <c r="E18" s="105" t="n"/>
-      <c r="F18" s="105" t="n"/>
-      <c r="G18" s="105" t="n"/>
-      <c r="H18" s="105" t="n"/>
-      <c r="I18" s="105" t="n"/>
-      <c r="J18" s="106" t="n"/>
-      <c r="K18" s="75" t="n"/>
-      <c r="L18" s="107" t="n"/>
-      <c r="M18" s="107" t="n"/>
-      <c r="N18" s="107" t="n"/>
-      <c r="O18" s="107" t="n"/>
-      <c r="P18" s="107" t="n"/>
-      <c r="Q18" s="107" t="n"/>
-      <c r="R18" s="107" t="n"/>
-      <c r="S18" s="107" t="n"/>
-      <c r="T18" s="107" t="n"/>
-      <c r="U18" s="107" t="n"/>
-      <c r="V18" s="107" t="n"/>
-      <c r="W18" s="107" t="n"/>
-      <c r="X18" s="107" t="n"/>
-      <c r="Y18" s="107" t="n"/>
-      <c r="Z18" s="107" t="n"/>
-      <c r="AA18" s="107" t="n"/>
-      <c r="AB18" s="108" t="n"/>
-      <c r="AC18" s="72" t="inlineStr">
+      <c r="B18" s="58" t="n"/>
+      <c r="C18" s="58" t="n"/>
+      <c r="D18" s="58" t="n"/>
+      <c r="E18" s="58" t="n"/>
+      <c r="F18" s="58" t="n"/>
+      <c r="G18" s="58" t="n"/>
+      <c r="H18" s="58" t="n"/>
+      <c r="I18" s="58" t="n"/>
+      <c r="J18" s="58" t="n"/>
+      <c r="K18" s="182" t="n"/>
+      <c r="L18" s="183" t="n"/>
+      <c r="M18" s="183" t="n"/>
+      <c r="N18" s="183" t="n"/>
+      <c r="O18" s="183" t="n"/>
+      <c r="P18" s="183" t="n"/>
+      <c r="Q18" s="183" t="n"/>
+      <c r="R18" s="183" t="n"/>
+      <c r="S18" s="184" t="n"/>
+      <c r="T18" s="183" t="n"/>
+      <c r="U18" s="183" t="n"/>
+      <c r="V18" s="183" t="n"/>
+      <c r="W18" s="183" t="n"/>
+      <c r="X18" s="183" t="n"/>
+      <c r="Y18" s="183" t="n"/>
+      <c r="Z18" s="183" t="n"/>
+      <c r="AA18" s="183" t="n"/>
+      <c r="AB18" s="183" t="n"/>
+      <c r="AC18" s="185" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AD18" s="105" t="n"/>
-      <c r="AE18" s="105" t="n"/>
-      <c r="AF18" s="105" t="n"/>
-      <c r="AG18" s="105" t="n"/>
-      <c r="AH18" s="105" t="n"/>
-      <c r="AI18" s="105" t="n"/>
-      <c r="AJ18" s="105" t="n"/>
-      <c r="AK18" s="105" t="n"/>
-      <c r="AL18" s="106" t="n"/>
-      <c r="AM18" s="75" t="n"/>
-      <c r="AN18" s="107" t="n"/>
-      <c r="AO18" s="107" t="n"/>
-      <c r="AP18" s="107" t="n"/>
-      <c r="AQ18" s="107" t="n"/>
-      <c r="AR18" s="107" t="n"/>
-      <c r="AS18" s="107" t="n"/>
-      <c r="AT18" s="107" t="n"/>
-      <c r="AU18" s="107" t="n"/>
-      <c r="AV18" s="107" t="n"/>
-      <c r="AW18" s="107" t="n"/>
-      <c r="AX18" s="107" t="n"/>
-      <c r="AY18" s="107" t="n"/>
-      <c r="AZ18" s="107" t="n"/>
-      <c r="BA18" s="107" t="n"/>
-      <c r="BB18" s="107" t="n"/>
-      <c r="BC18" s="107" t="n"/>
-      <c r="BD18" s="108" t="n"/>
+      <c r="AD18" s="58" t="n"/>
+      <c r="AE18" s="58" t="n"/>
+      <c r="AF18" s="58" t="n"/>
+      <c r="AG18" s="58" t="n"/>
+      <c r="AH18" s="58" t="n"/>
+      <c r="AI18" s="58" t="n"/>
+      <c r="AJ18" s="58" t="n"/>
+      <c r="AK18" s="186" t="n"/>
+      <c r="AL18" s="58" t="n"/>
+      <c r="AM18" s="182" t="n"/>
+      <c r="AN18" s="183" t="n"/>
+      <c r="AO18" s="183" t="n"/>
+      <c r="AP18" s="183" t="n"/>
+      <c r="AQ18" s="183" t="n"/>
+      <c r="AR18" s="183" t="n"/>
+      <c r="AS18" s="183" t="n"/>
+      <c r="AT18" s="183" t="n"/>
+      <c r="AU18" s="183" t="n"/>
+      <c r="AV18" s="183" t="n"/>
+      <c r="AW18" s="183" t="n"/>
+      <c r="AX18" s="183" t="n"/>
+      <c r="AY18" s="183" t="n"/>
+      <c r="AZ18" s="183" t="n"/>
+      <c r="BA18" s="183" t="n"/>
+      <c r="BB18" s="183" t="n"/>
+      <c r="BC18" s="183" t="n"/>
+      <c r="BD18" s="187" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="181" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="B19" s="105" t="n"/>
-      <c r="C19" s="105" t="n"/>
-      <c r="D19" s="105" t="n"/>
-      <c r="E19" s="105" t="n"/>
-      <c r="F19" s="105" t="n"/>
-      <c r="G19" s="105" t="n"/>
-      <c r="H19" s="105" t="n"/>
-      <c r="I19" s="105" t="n"/>
-      <c r="J19" s="106" t="n"/>
-      <c r="K19" s="75" t="n"/>
-      <c r="L19" s="107" t="n"/>
-      <c r="M19" s="107" t="n"/>
-      <c r="N19" s="107" t="n"/>
-      <c r="O19" s="107" t="n"/>
-      <c r="P19" s="107" t="n"/>
-      <c r="Q19" s="107" t="n"/>
-      <c r="R19" s="107" t="n"/>
-      <c r="S19" s="107" t="n"/>
-      <c r="T19" s="107" t="n"/>
-      <c r="U19" s="107" t="n"/>
-      <c r="V19" s="107" t="n"/>
-      <c r="W19" s="107" t="n"/>
-      <c r="X19" s="107" t="n"/>
-      <c r="Y19" s="107" t="n"/>
-      <c r="Z19" s="107" t="n"/>
-      <c r="AA19" s="107" t="n"/>
-      <c r="AB19" s="108" t="n"/>
-      <c r="AC19" s="72" t="inlineStr">
+      <c r="B19" s="58" t="n"/>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="58" t="n"/>
+      <c r="G19" s="58" t="n"/>
+      <c r="H19" s="58" t="n"/>
+      <c r="I19" s="58" t="n"/>
+      <c r="J19" s="58" t="n"/>
+      <c r="K19" s="182" t="n"/>
+      <c r="L19" s="183" t="n"/>
+      <c r="M19" s="183" t="n"/>
+      <c r="N19" s="183" t="n"/>
+      <c r="O19" s="183" t="n"/>
+      <c r="P19" s="183" t="n"/>
+      <c r="Q19" s="183" t="n"/>
+      <c r="R19" s="183" t="n"/>
+      <c r="S19" s="184" t="n"/>
+      <c r="T19" s="183" t="n"/>
+      <c r="U19" s="183" t="n"/>
+      <c r="V19" s="183" t="n"/>
+      <c r="W19" s="183" t="n"/>
+      <c r="X19" s="183" t="n"/>
+      <c r="Y19" s="183" t="n"/>
+      <c r="Z19" s="183" t="n"/>
+      <c r="AA19" s="183" t="n"/>
+      <c r="AB19" s="183" t="n"/>
+      <c r="AC19" s="185" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="AD19" s="105" t="n"/>
-      <c r="AE19" s="105" t="n"/>
-      <c r="AF19" s="105" t="n"/>
-      <c r="AG19" s="105" t="n"/>
-      <c r="AH19" s="105" t="n"/>
-      <c r="AI19" s="105" t="n"/>
-      <c r="AJ19" s="105" t="n"/>
-      <c r="AK19" s="105" t="n"/>
-      <c r="AL19" s="106" t="n"/>
-      <c r="AM19" s="75" t="n"/>
-      <c r="AN19" s="107" t="n"/>
-      <c r="AO19" s="107" t="n"/>
-      <c r="AP19" s="107" t="n"/>
-      <c r="AQ19" s="107" t="n"/>
-      <c r="AR19" s="107" t="n"/>
-      <c r="AS19" s="107" t="n"/>
-      <c r="AT19" s="107" t="n"/>
-      <c r="AU19" s="107" t="n"/>
-      <c r="AV19" s="107" t="n"/>
-      <c r="AW19" s="107" t="n"/>
-      <c r="AX19" s="107" t="n"/>
-      <c r="AY19" s="107" t="n"/>
-      <c r="AZ19" s="107" t="n"/>
-      <c r="BA19" s="107" t="n"/>
-      <c r="BB19" s="107" t="n"/>
-      <c r="BC19" s="107" t="n"/>
-      <c r="BD19" s="108" t="n"/>
+      <c r="AD19" s="58" t="n"/>
+      <c r="AE19" s="58" t="n"/>
+      <c r="AF19" s="58" t="n"/>
+      <c r="AG19" s="58" t="n"/>
+      <c r="AH19" s="58" t="n"/>
+      <c r="AI19" s="58" t="n"/>
+      <c r="AJ19" s="58" t="n"/>
+      <c r="AK19" s="186" t="n"/>
+      <c r="AL19" s="58" t="n"/>
+      <c r="AM19" s="182" t="n"/>
+      <c r="AN19" s="183" t="n"/>
+      <c r="AO19" s="183" t="n"/>
+      <c r="AP19" s="183" t="n"/>
+      <c r="AQ19" s="183" t="n"/>
+      <c r="AR19" s="183" t="n"/>
+      <c r="AS19" s="183" t="n"/>
+      <c r="AT19" s="183" t="n"/>
+      <c r="AU19" s="183" t="n"/>
+      <c r="AV19" s="183" t="n"/>
+      <c r="AW19" s="183" t="n"/>
+      <c r="AX19" s="183" t="n"/>
+      <c r="AY19" s="183" t="n"/>
+      <c r="AZ19" s="183" t="n"/>
+      <c r="BA19" s="183" t="n"/>
+      <c r="BB19" s="183" t="n"/>
+      <c r="BC19" s="183" t="n"/>
+      <c r="BD19" s="187" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="78" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="188" t="inlineStr">
         <is>
           <t>Prepared By</t>
         </is>
       </c>
-      <c r="B20" s="102" t="n"/>
-      <c r="C20" s="102" t="n"/>
-      <c r="D20" s="102" t="n"/>
-      <c r="E20" s="102" t="n"/>
-      <c r="F20" s="102" t="n"/>
-      <c r="G20" s="102" t="n"/>
-      <c r="H20" s="102" t="n"/>
-      <c r="I20" s="102" t="n"/>
-      <c r="J20" s="102" t="n"/>
-      <c r="K20" s="102" t="n"/>
-      <c r="L20" s="102" t="n"/>
-      <c r="M20" s="102" t="n"/>
-      <c r="N20" s="102" t="n"/>
-      <c r="O20" s="102" t="n"/>
-      <c r="P20" s="102" t="n"/>
-      <c r="Q20" s="102" t="n"/>
-      <c r="R20" s="103" t="n"/>
-      <c r="S20" s="78" t="inlineStr">
+      <c r="B20" s="58" t="n"/>
+      <c r="C20" s="58" t="n"/>
+      <c r="D20" s="58" t="n"/>
+      <c r="E20" s="58" t="n"/>
+      <c r="F20" s="58" t="n"/>
+      <c r="G20" s="58" t="n"/>
+      <c r="H20" s="58" t="n"/>
+      <c r="I20" s="58" t="n"/>
+      <c r="J20" s="58" t="n"/>
+      <c r="K20" s="186" t="n"/>
+      <c r="L20" s="58" t="n"/>
+      <c r="M20" s="58" t="n"/>
+      <c r="N20" s="58" t="n"/>
+      <c r="O20" s="58" t="n"/>
+      <c r="P20" s="58" t="n"/>
+      <c r="Q20" s="58" t="n"/>
+      <c r="R20" s="58" t="n"/>
+      <c r="S20" s="189" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="T20" s="102" t="n"/>
-      <c r="U20" s="102" t="n"/>
-      <c r="V20" s="102" t="n"/>
-      <c r="W20" s="102" t="n"/>
-      <c r="X20" s="102" t="n"/>
-      <c r="Y20" s="102" t="n"/>
-      <c r="Z20" s="102" t="n"/>
-      <c r="AA20" s="102" t="n"/>
-      <c r="AB20" s="102" t="n"/>
-      <c r="AC20" s="102" t="n"/>
-      <c r="AD20" s="102" t="n"/>
-      <c r="AE20" s="102" t="n"/>
-      <c r="AF20" s="102" t="n"/>
-      <c r="AG20" s="102" t="n"/>
-      <c r="AH20" s="102" t="n"/>
-      <c r="AI20" s="102" t="n"/>
-      <c r="AJ20" s="103" t="n"/>
-      <c r="AK20" s="78" t="inlineStr">
+      <c r="T20" s="58" t="n"/>
+      <c r="U20" s="58" t="n"/>
+      <c r="V20" s="58" t="n"/>
+      <c r="W20" s="58" t="n"/>
+      <c r="X20" s="58" t="n"/>
+      <c r="Y20" s="58" t="n"/>
+      <c r="Z20" s="58" t="n"/>
+      <c r="AA20" s="58" t="n"/>
+      <c r="AB20" s="58" t="n"/>
+      <c r="AC20" s="186" t="n"/>
+      <c r="AD20" s="58" t="n"/>
+      <c r="AE20" s="58" t="n"/>
+      <c r="AF20" s="58" t="n"/>
+      <c r="AG20" s="58" t="n"/>
+      <c r="AH20" s="58" t="n"/>
+      <c r="AI20" s="58" t="n"/>
+      <c r="AJ20" s="58" t="n"/>
+      <c r="AK20" s="189" t="inlineStr">
         <is>
           <t>Approved By</t>
         </is>
       </c>
-      <c r="AL20" s="102" t="n"/>
-      <c r="AM20" s="102" t="n"/>
-      <c r="AN20" s="102" t="n"/>
-      <c r="AO20" s="102" t="n"/>
-      <c r="AP20" s="102" t="n"/>
-      <c r="AQ20" s="102" t="n"/>
-      <c r="AR20" s="102" t="n"/>
-      <c r="AS20" s="102" t="n"/>
-      <c r="AT20" s="102" t="n"/>
-      <c r="AU20" s="102" t="n"/>
-      <c r="AV20" s="102" t="n"/>
-      <c r="AW20" s="102" t="n"/>
-      <c r="AX20" s="102" t="n"/>
-      <c r="AY20" s="102" t="n"/>
-      <c r="AZ20" s="102" t="n"/>
-      <c r="BA20" s="102" t="n"/>
-      <c r="BB20" s="102" t="n"/>
-      <c r="BC20" s="102" t="n"/>
-      <c r="BD20" s="103" t="n"/>
+      <c r="AL20" s="58" t="n"/>
+      <c r="AM20" s="186" t="n"/>
+      <c r="AN20" s="58" t="n"/>
+      <c r="AO20" s="58" t="n"/>
+      <c r="AP20" s="58" t="n"/>
+      <c r="AQ20" s="58" t="n"/>
+      <c r="AR20" s="58" t="n"/>
+      <c r="AS20" s="58" t="n"/>
+      <c r="AT20" s="58" t="n"/>
+      <c r="AU20" s="58" t="n"/>
+      <c r="AV20" s="58" t="n"/>
+      <c r="AW20" s="58" t="n"/>
+      <c r="AX20" s="58" t="n"/>
+      <c r="AY20" s="58" t="n"/>
+      <c r="AZ20" s="58" t="n"/>
+      <c r="BA20" s="58" t="n"/>
+      <c r="BB20" s="58" t="n"/>
+      <c r="BC20" s="58" t="n"/>
+      <c r="BD20" s="190" t="n"/>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="79" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="191" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B21" s="80" t="n"/>
-      <c r="C21" s="80" t="n"/>
-      <c r="D21" s="80" t="n"/>
-      <c r="E21" s="80" t="n"/>
-      <c r="F21" s="80" t="n"/>
-      <c r="G21" s="80" t="n"/>
-      <c r="H21" s="80" t="n"/>
-      <c r="I21" s="80" t="n"/>
-      <c r="J21" s="80" t="n"/>
-      <c r="K21" s="80" t="n"/>
-      <c r="L21" s="80" t="n"/>
-      <c r="M21" s="80" t="n"/>
-      <c r="N21" s="80" t="n"/>
-      <c r="O21" s="80" t="n"/>
-      <c r="P21" s="80" t="n"/>
-      <c r="Q21" s="80" t="n"/>
-      <c r="R21" s="109" t="n"/>
-      <c r="S21" s="79" t="inlineStr">
+      <c r="B21" s="183" t="n"/>
+      <c r="C21" s="183" t="n"/>
+      <c r="D21" s="183" t="n"/>
+      <c r="E21" s="183" t="n"/>
+      <c r="F21" s="183" t="n"/>
+      <c r="G21" s="183" t="n"/>
+      <c r="H21" s="183" t="n"/>
+      <c r="I21" s="183" t="n"/>
+      <c r="J21" s="183" t="n"/>
+      <c r="K21" s="184" t="n"/>
+      <c r="L21" s="183" t="n"/>
+      <c r="M21" s="183" t="n"/>
+      <c r="N21" s="183" t="n"/>
+      <c r="O21" s="183" t="n"/>
+      <c r="P21" s="183" t="n"/>
+      <c r="Q21" s="183" t="n"/>
+      <c r="R21" s="183" t="n"/>
+      <c r="S21" s="192" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T21" s="80" t="n"/>
-      <c r="U21" s="80" t="n"/>
-      <c r="V21" s="80" t="n"/>
-      <c r="W21" s="80" t="n"/>
-      <c r="X21" s="80" t="n"/>
-      <c r="Y21" s="80" t="n"/>
-      <c r="Z21" s="80" t="n"/>
-      <c r="AA21" s="80" t="n"/>
-      <c r="AB21" s="80" t="n"/>
-      <c r="AC21" s="80" t="n"/>
-      <c r="AD21" s="80" t="n"/>
-      <c r="AE21" s="80" t="n"/>
-      <c r="AF21" s="80" t="n"/>
-      <c r="AG21" s="80" t="n"/>
-      <c r="AH21" s="80" t="n"/>
-      <c r="AI21" s="80" t="n"/>
-      <c r="AJ21" s="109" t="n"/>
-      <c r="AK21" s="79" t="inlineStr">
+      <c r="T21" s="183" t="n"/>
+      <c r="U21" s="183" t="n"/>
+      <c r="V21" s="183" t="n"/>
+      <c r="W21" s="183" t="n"/>
+      <c r="X21" s="183" t="n"/>
+      <c r="Y21" s="183" t="n"/>
+      <c r="Z21" s="183" t="n"/>
+      <c r="AA21" s="183" t="n"/>
+      <c r="AB21" s="183" t="n"/>
+      <c r="AC21" s="184" t="n"/>
+      <c r="AD21" s="183" t="n"/>
+      <c r="AE21" s="183" t="n"/>
+      <c r="AF21" s="183" t="n"/>
+      <c r="AG21" s="183" t="n"/>
+      <c r="AH21" s="183" t="n"/>
+      <c r="AI21" s="183" t="n"/>
+      <c r="AJ21" s="183" t="n"/>
+      <c r="AK21" s="192" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL21" s="80" t="n"/>
-      <c r="AM21" s="80" t="n"/>
-      <c r="AN21" s="80" t="n"/>
-      <c r="AO21" s="80" t="n"/>
-      <c r="AP21" s="80" t="n"/>
-      <c r="AQ21" s="80" t="n"/>
-      <c r="AR21" s="80" t="n"/>
-      <c r="AS21" s="80" t="n"/>
-      <c r="AT21" s="80" t="n"/>
-      <c r="AU21" s="80" t="n"/>
-      <c r="AV21" s="80" t="n"/>
-      <c r="AW21" s="80" t="n"/>
-      <c r="AX21" s="80" t="n"/>
-      <c r="AY21" s="80" t="n"/>
-      <c r="AZ21" s="80" t="n"/>
-      <c r="BA21" s="80" t="n"/>
-      <c r="BB21" s="80" t="n"/>
-      <c r="BC21" s="80" t="n"/>
-      <c r="BD21" s="109" t="n"/>
+      <c r="AL21" s="183" t="n"/>
+      <c r="AM21" s="184" t="n"/>
+      <c r="AN21" s="183" t="n"/>
+      <c r="AO21" s="183" t="n"/>
+      <c r="AP21" s="183" t="n"/>
+      <c r="AQ21" s="183" t="n"/>
+      <c r="AR21" s="183" t="n"/>
+      <c r="AS21" s="183" t="n"/>
+      <c r="AT21" s="183" t="n"/>
+      <c r="AU21" s="183" t="n"/>
+      <c r="AV21" s="183" t="n"/>
+      <c r="AW21" s="183" t="n"/>
+      <c r="AX21" s="183" t="n"/>
+      <c r="AY21" s="183" t="n"/>
+      <c r="AZ21" s="183" t="n"/>
+      <c r="BA21" s="183" t="n"/>
+      <c r="BB21" s="183" t="n"/>
+      <c r="BC21" s="183" t="n"/>
+      <c r="BD21" s="187" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="110" t="n"/>
-      <c r="B22" s="83" t="n"/>
-      <c r="C22" s="83" t="n"/>
-      <c r="D22" s="83" t="n"/>
-      <c r="E22" s="83" t="n"/>
-      <c r="F22" s="83" t="n"/>
-      <c r="G22" s="83" t="n"/>
-      <c r="H22" s="83" t="n"/>
-      <c r="I22" s="83" t="n"/>
-      <c r="J22" s="83" t="n"/>
-      <c r="K22" s="83" t="n"/>
-      <c r="L22" s="83" t="n"/>
-      <c r="M22" s="83" t="n"/>
-      <c r="N22" s="83" t="n"/>
-      <c r="O22" s="83" t="n"/>
-      <c r="P22" s="83" t="n"/>
-      <c r="Q22" s="83" t="n"/>
-      <c r="R22" s="111" t="n"/>
-      <c r="S22" s="110" t="n"/>
-      <c r="T22" s="83" t="n"/>
-      <c r="U22" s="83" t="n"/>
-      <c r="V22" s="83" t="n"/>
-      <c r="W22" s="83" t="n"/>
-      <c r="X22" s="83" t="n"/>
-      <c r="Y22" s="83" t="n"/>
-      <c r="Z22" s="83" t="n"/>
-      <c r="AA22" s="83" t="n"/>
-      <c r="AB22" s="83" t="n"/>
-      <c r="AC22" s="83" t="n"/>
-      <c r="AD22" s="83" t="n"/>
-      <c r="AE22" s="83" t="n"/>
-      <c r="AF22" s="83" t="n"/>
-      <c r="AG22" s="83" t="n"/>
-      <c r="AH22" s="83" t="n"/>
-      <c r="AI22" s="83" t="n"/>
-      <c r="AJ22" s="111" t="n"/>
-      <c r="AK22" s="110" t="n"/>
-      <c r="AL22" s="83" t="n"/>
-      <c r="AM22" s="83" t="n"/>
-      <c r="AN22" s="83" t="n"/>
-      <c r="AO22" s="83" t="n"/>
-      <c r="AP22" s="83" t="n"/>
-      <c r="AQ22" s="83" t="n"/>
-      <c r="AR22" s="83" t="n"/>
-      <c r="AS22" s="83" t="n"/>
-      <c r="AT22" s="83" t="n"/>
-      <c r="AU22" s="83" t="n"/>
-      <c r="AV22" s="83" t="n"/>
-      <c r="AW22" s="83" t="n"/>
-      <c r="AX22" s="83" t="n"/>
-      <c r="AY22" s="83" t="n"/>
-      <c r="AZ22" s="83" t="n"/>
-      <c r="BA22" s="83" t="n"/>
-      <c r="BB22" s="83" t="n"/>
-      <c r="BC22" s="83" t="n"/>
-      <c r="BD22" s="111" t="n"/>
+      <c r="A22" s="193" t="n"/>
+      <c r="B22" s="183" t="n"/>
+      <c r="C22" s="183" t="n"/>
+      <c r="D22" s="183" t="n"/>
+      <c r="E22" s="183" t="n"/>
+      <c r="F22" s="183" t="n"/>
+      <c r="G22" s="183" t="n"/>
+      <c r="H22" s="183" t="n"/>
+      <c r="I22" s="183" t="n"/>
+      <c r="J22" s="183" t="n"/>
+      <c r="K22" s="184" t="n"/>
+      <c r="L22" s="183" t="n"/>
+      <c r="M22" s="183" t="n"/>
+      <c r="N22" s="183" t="n"/>
+      <c r="O22" s="183" t="n"/>
+      <c r="P22" s="183" t="n"/>
+      <c r="Q22" s="183" t="n"/>
+      <c r="R22" s="183" t="n"/>
+      <c r="S22" s="184" t="n"/>
+      <c r="T22" s="183" t="n"/>
+      <c r="U22" s="183" t="n"/>
+      <c r="V22" s="183" t="n"/>
+      <c r="W22" s="183" t="n"/>
+      <c r="X22" s="183" t="n"/>
+      <c r="Y22" s="183" t="n"/>
+      <c r="Z22" s="183" t="n"/>
+      <c r="AA22" s="183" t="n"/>
+      <c r="AB22" s="183" t="n"/>
+      <c r="AC22" s="184" t="n"/>
+      <c r="AD22" s="183" t="n"/>
+      <c r="AE22" s="183" t="n"/>
+      <c r="AF22" s="183" t="n"/>
+      <c r="AG22" s="183" t="n"/>
+      <c r="AH22" s="183" t="n"/>
+      <c r="AI22" s="183" t="n"/>
+      <c r="AJ22" s="183" t="n"/>
+      <c r="AK22" s="184" t="n"/>
+      <c r="AL22" s="183" t="n"/>
+      <c r="AM22" s="184" t="n"/>
+      <c r="AN22" s="183" t="n"/>
+      <c r="AO22" s="183" t="n"/>
+      <c r="AP22" s="183" t="n"/>
+      <c r="AQ22" s="183" t="n"/>
+      <c r="AR22" s="183" t="n"/>
+      <c r="AS22" s="183" t="n"/>
+      <c r="AT22" s="183" t="n"/>
+      <c r="AU22" s="183" t="n"/>
+      <c r="AV22" s="183" t="n"/>
+      <c r="AW22" s="183" t="n"/>
+      <c r="AX22" s="183" t="n"/>
+      <c r="AY22" s="183" t="n"/>
+      <c r="AZ22" s="183" t="n"/>
+      <c r="BA22" s="183" t="n"/>
+      <c r="BB22" s="183" t="n"/>
+      <c r="BC22" s="183" t="n"/>
+      <c r="BD22" s="187" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="112" t="n"/>
-      <c r="B23" s="113" t="n"/>
-      <c r="C23" s="113" t="n"/>
-      <c r="D23" s="113" t="n"/>
-      <c r="E23" s="113" t="n"/>
-      <c r="F23" s="113" t="n"/>
-      <c r="G23" s="113" t="n"/>
-      <c r="H23" s="113" t="n"/>
-      <c r="I23" s="113" t="n"/>
-      <c r="J23" s="113" t="n"/>
-      <c r="K23" s="113" t="n"/>
-      <c r="L23" s="113" t="n"/>
-      <c r="M23" s="113" t="n"/>
-      <c r="N23" s="113" t="n"/>
-      <c r="O23" s="113" t="n"/>
-      <c r="P23" s="113" t="n"/>
-      <c r="Q23" s="113" t="n"/>
-      <c r="R23" s="114" t="n"/>
-      <c r="S23" s="112" t="n"/>
-      <c r="T23" s="113" t="n"/>
-      <c r="U23" s="113" t="n"/>
-      <c r="V23" s="113" t="n"/>
-      <c r="W23" s="113" t="n"/>
-      <c r="X23" s="113" t="n"/>
-      <c r="Y23" s="113" t="n"/>
-      <c r="Z23" s="113" t="n"/>
-      <c r="AA23" s="113" t="n"/>
-      <c r="AB23" s="113" t="n"/>
-      <c r="AC23" s="113" t="n"/>
-      <c r="AD23" s="113" t="n"/>
-      <c r="AE23" s="113" t="n"/>
-      <c r="AF23" s="113" t="n"/>
-      <c r="AG23" s="113" t="n"/>
-      <c r="AH23" s="113" t="n"/>
-      <c r="AI23" s="113" t="n"/>
-      <c r="AJ23" s="114" t="n"/>
-      <c r="AK23" s="112" t="n"/>
-      <c r="AL23" s="113" t="n"/>
-      <c r="AM23" s="113" t="n"/>
-      <c r="AN23" s="113" t="n"/>
-      <c r="AO23" s="113" t="n"/>
-      <c r="AP23" s="113" t="n"/>
-      <c r="AQ23" s="113" t="n"/>
-      <c r="AR23" s="113" t="n"/>
-      <c r="AS23" s="113" t="n"/>
-      <c r="AT23" s="113" t="n"/>
-      <c r="AU23" s="113" t="n"/>
-      <c r="AV23" s="113" t="n"/>
-      <c r="AW23" s="113" t="n"/>
-      <c r="AX23" s="113" t="n"/>
-      <c r="AY23" s="113" t="n"/>
-      <c r="AZ23" s="113" t="n"/>
-      <c r="BA23" s="113" t="n"/>
-      <c r="BB23" s="113" t="n"/>
-      <c r="BC23" s="113" t="n"/>
-      <c r="BD23" s="114" t="n"/>
+      <c r="A23" s="194" t="n"/>
+      <c r="B23" s="176" t="n"/>
+      <c r="C23" s="176" t="n"/>
+      <c r="D23" s="176" t="n"/>
+      <c r="E23" s="176" t="n"/>
+      <c r="F23" s="176" t="n"/>
+      <c r="G23" s="176" t="n"/>
+      <c r="H23" s="176" t="n"/>
+      <c r="I23" s="176" t="n"/>
+      <c r="J23" s="176" t="n"/>
+      <c r="K23" s="195" t="n"/>
+      <c r="L23" s="176" t="n"/>
+      <c r="M23" s="176" t="n"/>
+      <c r="N23" s="176" t="n"/>
+      <c r="O23" s="176" t="n"/>
+      <c r="P23" s="176" t="n"/>
+      <c r="Q23" s="176" t="n"/>
+      <c r="R23" s="176" t="n"/>
+      <c r="S23" s="195" t="n"/>
+      <c r="T23" s="176" t="n"/>
+      <c r="U23" s="176" t="n"/>
+      <c r="V23" s="176" t="n"/>
+      <c r="W23" s="176" t="n"/>
+      <c r="X23" s="176" t="n"/>
+      <c r="Y23" s="176" t="n"/>
+      <c r="Z23" s="176" t="n"/>
+      <c r="AA23" s="176" t="n"/>
+      <c r="AB23" s="176" t="n"/>
+      <c r="AC23" s="195" t="n"/>
+      <c r="AD23" s="176" t="n"/>
+      <c r="AE23" s="176" t="n"/>
+      <c r="AF23" s="176" t="n"/>
+      <c r="AG23" s="176" t="n"/>
+      <c r="AH23" s="176" t="n"/>
+      <c r="AI23" s="176" t="n"/>
+      <c r="AJ23" s="176" t="n"/>
+      <c r="AK23" s="195" t="n"/>
+      <c r="AL23" s="176" t="n"/>
+      <c r="AM23" s="195" t="n"/>
+      <c r="AN23" s="176" t="n"/>
+      <c r="AO23" s="176" t="n"/>
+      <c r="AP23" s="176" t="n"/>
+      <c r="AQ23" s="176" t="n"/>
+      <c r="AR23" s="176" t="n"/>
+      <c r="AS23" s="176" t="n"/>
+      <c r="AT23" s="176" t="n"/>
+      <c r="AU23" s="176" t="n"/>
+      <c r="AV23" s="176" t="n"/>
+      <c r="AW23" s="176" t="n"/>
+      <c r="AX23" s="176" t="n"/>
+      <c r="AY23" s="176" t="n"/>
+      <c r="AZ23" s="176" t="n"/>
+      <c r="BA23" s="176" t="n"/>
+      <c r="BB23" s="176" t="n"/>
+      <c r="BC23" s="176" t="n"/>
+      <c r="BD23" s="178" t="n"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="88" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="164" t="inlineStr">
         <is>
           <t>NOTICE: Competence decisions shall be evidence-based. Record required tasks or behaviors, observed evidence, pass standard, restrictions, re-training needs and the explicit authorization decision.</t>
         </is>
       </c>
-      <c r="B24" s="105" t="n"/>
-      <c r="C24" s="105" t="n"/>
-      <c r="D24" s="105" t="n"/>
-      <c r="E24" s="105" t="n"/>
-      <c r="F24" s="105" t="n"/>
-      <c r="G24" s="105" t="n"/>
-      <c r="H24" s="105" t="n"/>
-      <c r="I24" s="105" t="n"/>
-      <c r="J24" s="105" t="n"/>
-      <c r="K24" s="105" t="n"/>
-      <c r="L24" s="105" t="n"/>
-      <c r="M24" s="105" t="n"/>
-      <c r="N24" s="105" t="n"/>
-      <c r="O24" s="105" t="n"/>
-      <c r="P24" s="105" t="n"/>
-      <c r="Q24" s="105" t="n"/>
-      <c r="R24" s="105" t="n"/>
-      <c r="S24" s="105" t="n"/>
-      <c r="T24" s="105" t="n"/>
-      <c r="U24" s="105" t="n"/>
-      <c r="V24" s="105" t="n"/>
-      <c r="W24" s="105" t="n"/>
-      <c r="X24" s="105" t="n"/>
-      <c r="Y24" s="105" t="n"/>
-      <c r="Z24" s="105" t="n"/>
-      <c r="AA24" s="105" t="n"/>
-      <c r="AB24" s="105" t="n"/>
-      <c r="AC24" s="105" t="n"/>
-      <c r="AD24" s="105" t="n"/>
-      <c r="AE24" s="105" t="n"/>
-      <c r="AF24" s="105" t="n"/>
-      <c r="AG24" s="105" t="n"/>
-      <c r="AH24" s="105" t="n"/>
-      <c r="AI24" s="105" t="n"/>
-      <c r="AJ24" s="105" t="n"/>
-      <c r="AK24" s="105" t="n"/>
-      <c r="AL24" s="105" t="n"/>
-      <c r="AM24" s="105" t="n"/>
-      <c r="AN24" s="105" t="n"/>
-      <c r="AO24" s="105" t="n"/>
-      <c r="AP24" s="105" t="n"/>
-      <c r="AQ24" s="105" t="n"/>
-      <c r="AR24" s="105" t="n"/>
-      <c r="AS24" s="105" t="n"/>
-      <c r="AT24" s="105" t="n"/>
-      <c r="AU24" s="105" t="n"/>
-      <c r="AV24" s="105" t="n"/>
-      <c r="AW24" s="105" t="n"/>
-      <c r="AX24" s="105" t="n"/>
-      <c r="AY24" s="105" t="n"/>
-      <c r="AZ24" s="105" t="n"/>
-      <c r="BA24" s="105" t="n"/>
-      <c r="BB24" s="105" t="n"/>
-      <c r="BC24" s="105" t="n"/>
-      <c r="BD24" s="106" t="n"/>
+      <c r="B24" s="165" t="n"/>
+      <c r="C24" s="165" t="n"/>
+      <c r="D24" s="165" t="n"/>
+      <c r="E24" s="165" t="n"/>
+      <c r="F24" s="165" t="n"/>
+      <c r="G24" s="165" t="n"/>
+      <c r="H24" s="165" t="n"/>
+      <c r="I24" s="165" t="n"/>
+      <c r="J24" s="165" t="n"/>
+      <c r="K24" s="165" t="n"/>
+      <c r="L24" s="165" t="n"/>
+      <c r="M24" s="165" t="n"/>
+      <c r="N24" s="165" t="n"/>
+      <c r="O24" s="165" t="n"/>
+      <c r="P24" s="165" t="n"/>
+      <c r="Q24" s="165" t="n"/>
+      <c r="R24" s="165" t="n"/>
+      <c r="S24" s="165" t="n"/>
+      <c r="T24" s="165" t="n"/>
+      <c r="U24" s="165" t="n"/>
+      <c r="V24" s="165" t="n"/>
+      <c r="W24" s="165" t="n"/>
+      <c r="X24" s="165" t="n"/>
+      <c r="Y24" s="165" t="n"/>
+      <c r="Z24" s="165" t="n"/>
+      <c r="AA24" s="165" t="n"/>
+      <c r="AB24" s="165" t="n"/>
+      <c r="AC24" s="165" t="n"/>
+      <c r="AD24" s="165" t="n"/>
+      <c r="AE24" s="165" t="n"/>
+      <c r="AF24" s="165" t="n"/>
+      <c r="AG24" s="165" t="n"/>
+      <c r="AH24" s="165" t="n"/>
+      <c r="AI24" s="165" t="n"/>
+      <c r="AJ24" s="165" t="n"/>
+      <c r="AK24" s="165" t="n"/>
+      <c r="AL24" s="165" t="n"/>
+      <c r="AM24" s="165" t="n"/>
+      <c r="AN24" s="165" t="n"/>
+      <c r="AO24" s="165" t="n"/>
+      <c r="AP24" s="165" t="n"/>
+      <c r="AQ24" s="165" t="n"/>
+      <c r="AR24" s="165" t="n"/>
+      <c r="AS24" s="165" t="n"/>
+      <c r="AT24" s="165" t="n"/>
+      <c r="AU24" s="165" t="n"/>
+      <c r="AV24" s="165" t="n"/>
+      <c r="AW24" s="165" t="n"/>
+      <c r="AX24" s="165" t="n"/>
+      <c r="AY24" s="165" t="n"/>
+      <c r="AZ24" s="165" t="n"/>
+      <c r="BA24" s="165" t="n"/>
+      <c r="BB24" s="165" t="n"/>
+      <c r="BC24" s="165" t="n"/>
+      <c r="BD24" s="166" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="62">
+  <mergeCells count="61">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="K11:AB11"/>
     <mergeCell ref="AQ3:AV3"/>
@@ -2970,7 +3753,6 @@
     <mergeCell ref="K17:AB17"/>
     <mergeCell ref="A11:J11"/>
     <mergeCell ref="A20:R20"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AC18:AL18"/>
     <mergeCell ref="AM15:BD15"/>
@@ -3028,6 +3810,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3099,1062 +3882,1152 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="54" t="n"/>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="118" t="n"/>
-      <c r="K1" s="118" t="n"/>
-      <c r="L1" s="56" t="inlineStr">
+      <c r="A1" s="125" t="n"/>
+      <c r="B1" s="126" t="n"/>
+      <c r="C1" s="126" t="n"/>
+      <c r="D1" s="126" t="n"/>
+      <c r="E1" s="126" t="n"/>
+      <c r="F1" s="126" t="n"/>
+      <c r="G1" s="126" t="n"/>
+      <c r="H1" s="126" t="n"/>
+      <c r="I1" s="126" t="n"/>
+      <c r="J1" s="126" t="n"/>
+      <c r="K1" s="127" t="n"/>
+      <c r="L1" s="128" t="inlineStr">
         <is>
           <t>COMPETENCE ASSESSMENT — ASSESSMENT CRITERIA</t>
         </is>
       </c>
-      <c r="M1" s="118" t="n"/>
-      <c r="N1" s="118" t="n"/>
-      <c r="O1" s="118" t="n"/>
-      <c r="P1" s="118" t="n"/>
-      <c r="Q1" s="118" t="n"/>
-      <c r="R1" s="118" t="n"/>
-      <c r="S1" s="118" t="n"/>
-      <c r="T1" s="118" t="n"/>
-      <c r="U1" s="118" t="n"/>
-      <c r="V1" s="118" t="n"/>
-      <c r="W1" s="118" t="n"/>
-      <c r="X1" s="118" t="n"/>
-      <c r="Y1" s="118" t="n"/>
-      <c r="Z1" s="118" t="n"/>
-      <c r="AA1" s="118" t="n"/>
-      <c r="AB1" s="118" t="n"/>
-      <c r="AC1" s="118" t="n"/>
-      <c r="AD1" s="118" t="n"/>
-      <c r="AE1" s="118" t="n"/>
-      <c r="AF1" s="118" t="n"/>
-      <c r="AG1" s="118" t="n"/>
-      <c r="AH1" s="118" t="n"/>
-      <c r="AI1" s="118" t="n"/>
-      <c r="AJ1" s="118" t="n"/>
-      <c r="AK1" s="118" t="n"/>
-      <c r="AL1" s="118" t="n"/>
-      <c r="AM1" s="118" t="n"/>
-      <c r="AN1" s="118" t="n"/>
-      <c r="AO1" s="118" t="n"/>
-      <c r="AP1" s="118" t="n"/>
-      <c r="AQ1" s="57" t="inlineStr">
+      <c r="M1" s="129" t="n"/>
+      <c r="N1" s="129" t="n"/>
+      <c r="O1" s="129" t="n"/>
+      <c r="P1" s="129" t="n"/>
+      <c r="Q1" s="129" t="n"/>
+      <c r="R1" s="129" t="n"/>
+      <c r="S1" s="129" t="n"/>
+      <c r="T1" s="129" t="n"/>
+      <c r="U1" s="129" t="n"/>
+      <c r="V1" s="129" t="n"/>
+      <c r="W1" s="129" t="n"/>
+      <c r="X1" s="129" t="n"/>
+      <c r="Y1" s="129" t="n"/>
+      <c r="Z1" s="129" t="n"/>
+      <c r="AA1" s="129" t="n"/>
+      <c r="AB1" s="129" t="n"/>
+      <c r="AC1" s="129" t="n"/>
+      <c r="AD1" s="129" t="n"/>
+      <c r="AE1" s="129" t="n"/>
+      <c r="AF1" s="129" t="n"/>
+      <c r="AG1" s="129" t="n"/>
+      <c r="AH1" s="129" t="n"/>
+      <c r="AI1" s="129" t="n"/>
+      <c r="AJ1" s="129" t="n"/>
+      <c r="AK1" s="129" t="n"/>
+      <c r="AL1" s="129" t="n"/>
+      <c r="AM1" s="129" t="n"/>
+      <c r="AN1" s="129" t="n"/>
+      <c r="AO1" s="129" t="n"/>
+      <c r="AP1" s="130" t="n"/>
+      <c r="AQ1" s="131" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="119" t="n"/>
-      <c r="AS1" s="119" t="n"/>
-      <c r="AT1" s="119" t="n"/>
-      <c r="AU1" s="119" t="n"/>
-      <c r="AV1" s="120" t="n"/>
-      <c r="AW1" s="60" t="inlineStr">
+      <c r="AR1" s="132" t="n"/>
+      <c r="AS1" s="132" t="n"/>
+      <c r="AT1" s="132" t="n"/>
+      <c r="AU1" s="132" t="n"/>
+      <c r="AV1" s="133" t="n"/>
+      <c r="AW1" s="134" t="inlineStr">
         <is>
           <t>FRM-804</t>
         </is>
       </c>
-      <c r="AX1" s="119" t="n"/>
-      <c r="AY1" s="119" t="n"/>
-      <c r="AZ1" s="119" t="n"/>
-      <c r="BA1" s="119" t="n"/>
-      <c r="BB1" s="119" t="n"/>
-      <c r="BC1" s="119" t="n"/>
-      <c r="BD1" s="120" t="n"/>
+      <c r="AX1" s="135" t="n"/>
+      <c r="AY1" s="135" t="n"/>
+      <c r="AZ1" s="135" t="n"/>
+      <c r="BA1" s="135" t="n"/>
+      <c r="BB1" s="135" t="n"/>
+      <c r="BC1" s="135" t="n"/>
+      <c r="BD1" s="136" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="121" t="n"/>
-      <c r="L2" s="121" t="n"/>
-      <c r="AQ2" s="63" t="inlineStr">
+      <c r="A2" s="137" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+      <c r="G2" s="53" t="n"/>
+      <c r="H2" s="53" t="n"/>
+      <c r="I2" s="53" t="n"/>
+      <c r="J2" s="53" t="n"/>
+      <c r="K2" s="138" t="n"/>
+      <c r="L2" s="139" t="n"/>
+      <c r="M2" s="140" t="n"/>
+      <c r="N2" s="140" t="n"/>
+      <c r="O2" s="140" t="n"/>
+      <c r="P2" s="140" t="n"/>
+      <c r="Q2" s="140" t="n"/>
+      <c r="R2" s="140" t="n"/>
+      <c r="S2" s="140" t="n"/>
+      <c r="T2" s="140" t="n"/>
+      <c r="U2" s="140" t="n"/>
+      <c r="V2" s="140" t="n"/>
+      <c r="W2" s="140" t="n"/>
+      <c r="X2" s="140" t="n"/>
+      <c r="Y2" s="140" t="n"/>
+      <c r="Z2" s="140" t="n"/>
+      <c r="AA2" s="140" t="n"/>
+      <c r="AB2" s="140" t="n"/>
+      <c r="AC2" s="140" t="n"/>
+      <c r="AD2" s="140" t="n"/>
+      <c r="AE2" s="140" t="n"/>
+      <c r="AF2" s="140" t="n"/>
+      <c r="AG2" s="140" t="n"/>
+      <c r="AH2" s="140" t="n"/>
+      <c r="AI2" s="140" t="n"/>
+      <c r="AJ2" s="140" t="n"/>
+      <c r="AK2" s="140" t="n"/>
+      <c r="AL2" s="140" t="n"/>
+      <c r="AM2" s="140" t="n"/>
+      <c r="AN2" s="140" t="n"/>
+      <c r="AO2" s="140" t="n"/>
+      <c r="AP2" s="141" t="n"/>
+      <c r="AQ2" s="142" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="122" t="n"/>
-      <c r="AS2" s="122" t="n"/>
-      <c r="AT2" s="122" t="n"/>
-      <c r="AU2" s="122" t="n"/>
-      <c r="AV2" s="123" t="n"/>
-      <c r="AW2" s="66" t="inlineStr">
+      <c r="AR2" s="143" t="n"/>
+      <c r="AS2" s="143" t="n"/>
+      <c r="AT2" s="143" t="n"/>
+      <c r="AU2" s="143" t="n"/>
+      <c r="AV2" s="144" t="n"/>
+      <c r="AW2" s="145" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="122" t="n"/>
-      <c r="AY2" s="122" t="n"/>
-      <c r="AZ2" s="122" t="n"/>
-      <c r="BA2" s="122" t="n"/>
-      <c r="BB2" s="122" t="n"/>
-      <c r="BC2" s="122" t="n"/>
-      <c r="BD2" s="123" t="n"/>
+      <c r="AX2" s="146" t="n"/>
+      <c r="AY2" s="146" t="n"/>
+      <c r="AZ2" s="146" t="n"/>
+      <c r="BA2" s="146" t="n"/>
+      <c r="BB2" s="146" t="n"/>
+      <c r="BC2" s="146" t="n"/>
+      <c r="BD2" s="147" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="121" t="n"/>
-      <c r="L3" s="124" t="n"/>
-      <c r="M3" s="122" t="n"/>
-      <c r="N3" s="122" t="n"/>
-      <c r="O3" s="122" t="n"/>
-      <c r="P3" s="122" t="n"/>
-      <c r="Q3" s="122" t="n"/>
-      <c r="R3" s="122" t="n"/>
-      <c r="S3" s="122" t="n"/>
-      <c r="T3" s="122" t="n"/>
-      <c r="U3" s="122" t="n"/>
-      <c r="V3" s="122" t="n"/>
-      <c r="W3" s="122" t="n"/>
-      <c r="X3" s="122" t="n"/>
-      <c r="Y3" s="122" t="n"/>
-      <c r="Z3" s="122" t="n"/>
-      <c r="AA3" s="122" t="n"/>
-      <c r="AB3" s="122" t="n"/>
-      <c r="AC3" s="122" t="n"/>
-      <c r="AD3" s="122" t="n"/>
-      <c r="AE3" s="122" t="n"/>
-      <c r="AF3" s="122" t="n"/>
-      <c r="AG3" s="122" t="n"/>
-      <c r="AH3" s="122" t="n"/>
-      <c r="AI3" s="122" t="n"/>
-      <c r="AJ3" s="122" t="n"/>
-      <c r="AK3" s="122" t="n"/>
-      <c r="AL3" s="122" t="n"/>
-      <c r="AM3" s="122" t="n"/>
-      <c r="AN3" s="122" t="n"/>
-      <c r="AO3" s="122" t="n"/>
-      <c r="AP3" s="122" t="n"/>
-      <c r="AQ3" s="63" t="inlineStr">
+      <c r="A3" s="137" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="138" t="n"/>
+      <c r="L3" s="139" t="n"/>
+      <c r="M3" s="140" t="n"/>
+      <c r="N3" s="140" t="n"/>
+      <c r="O3" s="140" t="n"/>
+      <c r="P3" s="140" t="n"/>
+      <c r="Q3" s="140" t="n"/>
+      <c r="R3" s="140" t="n"/>
+      <c r="S3" s="140" t="n"/>
+      <c r="T3" s="140" t="n"/>
+      <c r="U3" s="140" t="n"/>
+      <c r="V3" s="140" t="n"/>
+      <c r="W3" s="140" t="n"/>
+      <c r="X3" s="140" t="n"/>
+      <c r="Y3" s="140" t="n"/>
+      <c r="Z3" s="140" t="n"/>
+      <c r="AA3" s="140" t="n"/>
+      <c r="AB3" s="140" t="n"/>
+      <c r="AC3" s="140" t="n"/>
+      <c r="AD3" s="140" t="n"/>
+      <c r="AE3" s="140" t="n"/>
+      <c r="AF3" s="140" t="n"/>
+      <c r="AG3" s="140" t="n"/>
+      <c r="AH3" s="140" t="n"/>
+      <c r="AI3" s="140" t="n"/>
+      <c r="AJ3" s="140" t="n"/>
+      <c r="AK3" s="140" t="n"/>
+      <c r="AL3" s="140" t="n"/>
+      <c r="AM3" s="140" t="n"/>
+      <c r="AN3" s="140" t="n"/>
+      <c r="AO3" s="140" t="n"/>
+      <c r="AP3" s="141" t="n"/>
+      <c r="AQ3" s="142" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="122" t="n"/>
-      <c r="AS3" s="122" t="n"/>
-      <c r="AT3" s="122" t="n"/>
-      <c r="AU3" s="122" t="n"/>
-      <c r="AV3" s="123" t="n"/>
-      <c r="AW3" s="66" t="inlineStr">
+      <c r="AR3" s="143" t="n"/>
+      <c r="AS3" s="143" t="n"/>
+      <c r="AT3" s="143" t="n"/>
+      <c r="AU3" s="143" t="n"/>
+      <c r="AV3" s="144" t="n"/>
+      <c r="AW3" s="145" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="122" t="n"/>
-      <c r="AY3" s="122" t="n"/>
-      <c r="AZ3" s="122" t="n"/>
-      <c r="BA3" s="122" t="n"/>
-      <c r="BB3" s="122" t="n"/>
-      <c r="BC3" s="122" t="n"/>
-      <c r="BD3" s="123" t="n"/>
+      <c r="AX3" s="146" t="n"/>
+      <c r="AY3" s="146" t="n"/>
+      <c r="AZ3" s="146" t="n"/>
+      <c r="BA3" s="146" t="n"/>
+      <c r="BB3" s="146" t="n"/>
+      <c r="BC3" s="146" t="n"/>
+      <c r="BD3" s="147" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="121" t="n"/>
-      <c r="L4" s="68" t="inlineStr">
+      <c r="A4" s="137" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="138" t="n"/>
+      <c r="L4" s="148" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="63" t="inlineStr">
+      <c r="M4" s="149" t="n"/>
+      <c r="N4" s="149" t="n"/>
+      <c r="O4" s="149" t="n"/>
+      <c r="P4" s="149" t="n"/>
+      <c r="Q4" s="149" t="n"/>
+      <c r="R4" s="149" t="n"/>
+      <c r="S4" s="149" t="n"/>
+      <c r="T4" s="149" t="n"/>
+      <c r="U4" s="149" t="n"/>
+      <c r="V4" s="149" t="n"/>
+      <c r="W4" s="149" t="n"/>
+      <c r="X4" s="149" t="n"/>
+      <c r="Y4" s="149" t="n"/>
+      <c r="Z4" s="149" t="n"/>
+      <c r="AA4" s="149" t="n"/>
+      <c r="AB4" s="149" t="n"/>
+      <c r="AC4" s="149" t="n"/>
+      <c r="AD4" s="149" t="n"/>
+      <c r="AE4" s="149" t="n"/>
+      <c r="AF4" s="149" t="n"/>
+      <c r="AG4" s="149" t="n"/>
+      <c r="AH4" s="149" t="n"/>
+      <c r="AI4" s="149" t="n"/>
+      <c r="AJ4" s="149" t="n"/>
+      <c r="AK4" s="149" t="n"/>
+      <c r="AL4" s="149" t="n"/>
+      <c r="AM4" s="149" t="n"/>
+      <c r="AN4" s="149" t="n"/>
+      <c r="AO4" s="149" t="n"/>
+      <c r="AP4" s="150" t="n"/>
+      <c r="AQ4" s="142" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="122" t="n"/>
-      <c r="AS4" s="122" t="n"/>
-      <c r="AT4" s="122" t="n"/>
-      <c r="AU4" s="122" t="n"/>
-      <c r="AV4" s="123" t="n"/>
-      <c r="AW4" s="66" t="inlineStr">
+      <c r="AR4" s="143" t="n"/>
+      <c r="AS4" s="143" t="n"/>
+      <c r="AT4" s="143" t="n"/>
+      <c r="AU4" s="143" t="n"/>
+      <c r="AV4" s="144" t="n"/>
+      <c r="AW4" s="145" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="122" t="n"/>
-      <c r="AY4" s="122" t="n"/>
-      <c r="AZ4" s="122" t="n"/>
-      <c r="BA4" s="122" t="n"/>
-      <c r="BB4" s="122" t="n"/>
-      <c r="BC4" s="122" t="n"/>
-      <c r="BD4" s="123" t="n"/>
+      <c r="AX4" s="146" t="n"/>
+      <c r="AY4" s="146" t="n"/>
+      <c r="AZ4" s="146" t="n"/>
+      <c r="BA4" s="146" t="n"/>
+      <c r="BB4" s="146" t="n"/>
+      <c r="BC4" s="146" t="n"/>
+      <c r="BD4" s="147" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="124" t="n"/>
-      <c r="B5" s="122" t="n"/>
-      <c r="C5" s="122" t="n"/>
-      <c r="D5" s="122" t="n"/>
-      <c r="E5" s="122" t="n"/>
-      <c r="F5" s="122" t="n"/>
-      <c r="G5" s="122" t="n"/>
-      <c r="H5" s="122" t="n"/>
-      <c r="I5" s="122" t="n"/>
-      <c r="J5" s="122" t="n"/>
-      <c r="K5" s="122" t="n"/>
-      <c r="L5" s="69" t="inlineStr">
+      <c r="A5" s="151" t="n"/>
+      <c r="B5" s="152" t="n"/>
+      <c r="C5" s="152" t="n"/>
+      <c r="D5" s="152" t="n"/>
+      <c r="E5" s="152" t="n"/>
+      <c r="F5" s="152" t="n"/>
+      <c r="G5" s="152" t="n"/>
+      <c r="H5" s="152" t="n"/>
+      <c r="I5" s="152" t="n"/>
+      <c r="J5" s="152" t="n"/>
+      <c r="K5" s="153" t="n"/>
+      <c r="L5" s="154" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="122" t="n"/>
-      <c r="N5" s="122" t="n"/>
-      <c r="O5" s="122" t="n"/>
-      <c r="P5" s="122" t="n"/>
-      <c r="Q5" s="122" t="n"/>
-      <c r="R5" s="122" t="n"/>
-      <c r="S5" s="122" t="n"/>
-      <c r="T5" s="122" t="n"/>
-      <c r="U5" s="122" t="n"/>
-      <c r="V5" s="122" t="n"/>
-      <c r="W5" s="122" t="n"/>
-      <c r="X5" s="122" t="n"/>
-      <c r="Y5" s="122" t="n"/>
-      <c r="Z5" s="122" t="n"/>
-      <c r="AA5" s="122" t="n"/>
-      <c r="AB5" s="122" t="n"/>
-      <c r="AC5" s="122" t="n"/>
-      <c r="AD5" s="122" t="n"/>
-      <c r="AE5" s="122" t="n"/>
-      <c r="AF5" s="122" t="n"/>
-      <c r="AG5" s="122" t="n"/>
-      <c r="AH5" s="122" t="n"/>
-      <c r="AI5" s="122" t="n"/>
-      <c r="AJ5" s="122" t="n"/>
-      <c r="AK5" s="122" t="n"/>
-      <c r="AL5" s="122" t="n"/>
-      <c r="AM5" s="122" t="n"/>
-      <c r="AN5" s="122" t="n"/>
-      <c r="AO5" s="122" t="n"/>
-      <c r="AP5" s="122" t="n"/>
-      <c r="AQ5" s="63" t="inlineStr">
+      <c r="M5" s="155" t="n"/>
+      <c r="N5" s="155" t="n"/>
+      <c r="O5" s="155" t="n"/>
+      <c r="P5" s="155" t="n"/>
+      <c r="Q5" s="155" t="n"/>
+      <c r="R5" s="155" t="n"/>
+      <c r="S5" s="155" t="n"/>
+      <c r="T5" s="155" t="n"/>
+      <c r="U5" s="155" t="n"/>
+      <c r="V5" s="155" t="n"/>
+      <c r="W5" s="155" t="n"/>
+      <c r="X5" s="155" t="n"/>
+      <c r="Y5" s="155" t="n"/>
+      <c r="Z5" s="155" t="n"/>
+      <c r="AA5" s="155" t="n"/>
+      <c r="AB5" s="155" t="n"/>
+      <c r="AC5" s="155" t="n"/>
+      <c r="AD5" s="155" t="n"/>
+      <c r="AE5" s="155" t="n"/>
+      <c r="AF5" s="155" t="n"/>
+      <c r="AG5" s="155" t="n"/>
+      <c r="AH5" s="155" t="n"/>
+      <c r="AI5" s="155" t="n"/>
+      <c r="AJ5" s="155" t="n"/>
+      <c r="AK5" s="155" t="n"/>
+      <c r="AL5" s="155" t="n"/>
+      <c r="AM5" s="155" t="n"/>
+      <c r="AN5" s="155" t="n"/>
+      <c r="AO5" s="155" t="n"/>
+      <c r="AP5" s="156" t="n"/>
+      <c r="AQ5" s="157" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="122" t="n"/>
-      <c r="AS5" s="122" t="n"/>
-      <c r="AT5" s="122" t="n"/>
-      <c r="AU5" s="122" t="n"/>
-      <c r="AV5" s="123" t="n"/>
-      <c r="AW5" s="66" t="inlineStr">
+      <c r="AR5" s="158" t="n"/>
+      <c r="AS5" s="158" t="n"/>
+      <c r="AT5" s="158" t="n"/>
+      <c r="AU5" s="158" t="n"/>
+      <c r="AV5" s="159" t="n"/>
+      <c r="AW5" s="160" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="122" t="n"/>
-      <c r="AY5" s="122" t="n"/>
-      <c r="AZ5" s="122" t="n"/>
-      <c r="BA5" s="122" t="n"/>
-      <c r="BB5" s="122" t="n"/>
-      <c r="BC5" s="122" t="n"/>
-      <c r="BD5" s="123" t="n"/>
+      <c r="AX5" s="161" t="n"/>
+      <c r="AY5" s="161" t="n"/>
+      <c r="AZ5" s="161" t="n"/>
+      <c r="BA5" s="161" t="n"/>
+      <c r="BB5" s="161" t="n"/>
+      <c r="BC5" s="161" t="n"/>
+      <c r="BD5" s="162" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="70" t="n"/>
-      <c r="B6" s="117" t="n"/>
-      <c r="C6" s="117" t="n"/>
-      <c r="D6" s="117" t="n"/>
-      <c r="E6" s="117" t="n"/>
-      <c r="F6" s="117" t="n"/>
-      <c r="G6" s="117" t="n"/>
-      <c r="H6" s="117" t="n"/>
-      <c r="I6" s="117" t="n"/>
-      <c r="J6" s="117" t="n"/>
-      <c r="K6" s="117" t="n"/>
-      <c r="L6" s="117" t="n"/>
-      <c r="M6" s="117" t="n"/>
-      <c r="N6" s="117" t="n"/>
-      <c r="O6" s="117" t="n"/>
-      <c r="P6" s="117" t="n"/>
-      <c r="Q6" s="117" t="n"/>
-      <c r="R6" s="117" t="n"/>
-      <c r="S6" s="117" t="n"/>
-      <c r="T6" s="117" t="n"/>
-      <c r="U6" s="117" t="n"/>
-      <c r="V6" s="117" t="n"/>
-      <c r="W6" s="117" t="n"/>
-      <c r="X6" s="117" t="n"/>
-      <c r="Y6" s="117" t="n"/>
-      <c r="Z6" s="117" t="n"/>
-      <c r="AA6" s="117" t="n"/>
-      <c r="AB6" s="117" t="n"/>
-      <c r="AC6" s="117" t="n"/>
-      <c r="AD6" s="117" t="n"/>
-      <c r="AE6" s="117" t="n"/>
-      <c r="AF6" s="117" t="n"/>
-      <c r="AG6" s="117" t="n"/>
-      <c r="AH6" s="117" t="n"/>
-      <c r="AI6" s="117" t="n"/>
-      <c r="AJ6" s="117" t="n"/>
-      <c r="AK6" s="117" t="n"/>
-      <c r="AL6" s="117" t="n"/>
-      <c r="AM6" s="117" t="n"/>
-      <c r="AN6" s="117" t="n"/>
-      <c r="AO6" s="117" t="n"/>
-      <c r="AP6" s="117" t="n"/>
-      <c r="AQ6" s="117" t="n"/>
-      <c r="AR6" s="117" t="n"/>
-      <c r="AS6" s="117" t="n"/>
-      <c r="AT6" s="117" t="n"/>
-      <c r="AU6" s="117" t="n"/>
-      <c r="AV6" s="117" t="n"/>
-      <c r="AW6" s="117" t="n"/>
-      <c r="AX6" s="117" t="n"/>
-      <c r="AY6" s="117" t="n"/>
-      <c r="AZ6" s="117" t="n"/>
-      <c r="BA6" s="117" t="n"/>
-      <c r="BB6" s="117" t="n"/>
-      <c r="BC6" s="117" t="n"/>
-      <c r="BD6" s="117" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="163" t="n"/>
+      <c r="B6" s="163" t="n"/>
+      <c r="C6" s="163" t="n"/>
+      <c r="D6" s="163" t="n"/>
+      <c r="E6" s="163" t="n"/>
+      <c r="F6" s="163" t="n"/>
+      <c r="G6" s="163" t="n"/>
+      <c r="H6" s="163" t="n"/>
+      <c r="I6" s="163" t="n"/>
+      <c r="J6" s="163" t="n"/>
+      <c r="K6" s="163" t="n"/>
+      <c r="L6" s="163" t="n"/>
+      <c r="M6" s="163" t="n"/>
+      <c r="N6" s="163" t="n"/>
+      <c r="O6" s="163" t="n"/>
+      <c r="P6" s="163" t="n"/>
+      <c r="Q6" s="163" t="n"/>
+      <c r="R6" s="163" t="n"/>
+      <c r="S6" s="163" t="n"/>
+      <c r="T6" s="163" t="n"/>
+      <c r="U6" s="163" t="n"/>
+      <c r="V6" s="163" t="n"/>
+      <c r="W6" s="163" t="n"/>
+      <c r="X6" s="163" t="n"/>
+      <c r="Y6" s="163" t="n"/>
+      <c r="Z6" s="163" t="n"/>
+      <c r="AA6" s="163" t="n"/>
+      <c r="AB6" s="163" t="n"/>
+      <c r="AC6" s="163" t="n"/>
+      <c r="AD6" s="163" t="n"/>
+      <c r="AE6" s="163" t="n"/>
+      <c r="AF6" s="163" t="n"/>
+      <c r="AG6" s="163" t="n"/>
+      <c r="AH6" s="163" t="n"/>
+      <c r="AI6" s="163" t="n"/>
+      <c r="AJ6" s="163" t="n"/>
+      <c r="AK6" s="163" t="n"/>
+      <c r="AL6" s="163" t="n"/>
+      <c r="AM6" s="163" t="n"/>
+      <c r="AN6" s="163" t="n"/>
+      <c r="AO6" s="163" t="n"/>
+      <c r="AP6" s="163" t="n"/>
+      <c r="AQ6" s="163" t="n"/>
+      <c r="AR6" s="163" t="n"/>
+      <c r="AS6" s="163" t="n"/>
+      <c r="AT6" s="163" t="n"/>
+      <c r="AU6" s="163" t="n"/>
+      <c r="AV6" s="163" t="n"/>
+      <c r="AW6" s="163" t="n"/>
+      <c r="AX6" s="163" t="n"/>
+      <c r="AY6" s="163" t="n"/>
+      <c r="AZ6" s="163" t="n"/>
+      <c r="BA6" s="163" t="n"/>
+      <c r="BB6" s="163" t="n"/>
+      <c r="BC6" s="163" t="n"/>
+      <c r="BD6" s="163" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="71" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="119" t="n"/>
-      <c r="C7" s="119" t="n"/>
-      <c r="D7" s="119" t="n"/>
-      <c r="E7" s="119" t="n"/>
-      <c r="F7" s="119" t="n"/>
-      <c r="G7" s="119" t="n"/>
-      <c r="H7" s="119" t="n"/>
-      <c r="I7" s="119" t="n"/>
-      <c r="J7" s="119" t="n"/>
-      <c r="K7" s="119" t="n"/>
-      <c r="L7" s="119" t="n"/>
-      <c r="M7" s="119" t="n"/>
-      <c r="N7" s="119" t="n"/>
-      <c r="O7" s="119" t="n"/>
-      <c r="P7" s="119" t="n"/>
-      <c r="Q7" s="119" t="n"/>
-      <c r="R7" s="119" t="n"/>
-      <c r="S7" s="119" t="n"/>
-      <c r="T7" s="119" t="n"/>
-      <c r="U7" s="119" t="n"/>
-      <c r="V7" s="119" t="n"/>
-      <c r="W7" s="119" t="n"/>
-      <c r="X7" s="119" t="n"/>
-      <c r="Y7" s="119" t="n"/>
-      <c r="Z7" s="119" t="n"/>
-      <c r="AA7" s="119" t="n"/>
-      <c r="AB7" s="119" t="n"/>
-      <c r="AC7" s="119" t="n"/>
-      <c r="AD7" s="119" t="n"/>
-      <c r="AE7" s="119" t="n"/>
-      <c r="AF7" s="119" t="n"/>
-      <c r="AG7" s="119" t="n"/>
-      <c r="AH7" s="119" t="n"/>
-      <c r="AI7" s="119" t="n"/>
-      <c r="AJ7" s="119" t="n"/>
-      <c r="AK7" s="119" t="n"/>
-      <c r="AL7" s="119" t="n"/>
-      <c r="AM7" s="119" t="n"/>
-      <c r="AN7" s="119" t="n"/>
-      <c r="AO7" s="119" t="n"/>
-      <c r="AP7" s="119" t="n"/>
-      <c r="AQ7" s="119" t="n"/>
-      <c r="AR7" s="119" t="n"/>
-      <c r="AS7" s="119" t="n"/>
-      <c r="AT7" s="119" t="n"/>
-      <c r="AU7" s="119" t="n"/>
-      <c r="AV7" s="119" t="n"/>
-      <c r="AW7" s="119" t="n"/>
-      <c r="AX7" s="119" t="n"/>
-      <c r="AY7" s="119" t="n"/>
-      <c r="AZ7" s="119" t="n"/>
-      <c r="BA7" s="119" t="n"/>
-      <c r="BB7" s="119" t="n"/>
-      <c r="BC7" s="119" t="n"/>
-      <c r="BD7" s="120" t="n"/>
+      <c r="B7" s="165" t="n"/>
+      <c r="C7" s="165" t="n"/>
+      <c r="D7" s="165" t="n"/>
+      <c r="E7" s="165" t="n"/>
+      <c r="F7" s="165" t="n"/>
+      <c r="G7" s="165" t="n"/>
+      <c r="H7" s="165" t="n"/>
+      <c r="I7" s="165" t="n"/>
+      <c r="J7" s="165" t="n"/>
+      <c r="K7" s="165" t="n"/>
+      <c r="L7" s="165" t="n"/>
+      <c r="M7" s="165" t="n"/>
+      <c r="N7" s="165" t="n"/>
+      <c r="O7" s="165" t="n"/>
+      <c r="P7" s="165" t="n"/>
+      <c r="Q7" s="165" t="n"/>
+      <c r="R7" s="165" t="n"/>
+      <c r="S7" s="165" t="n"/>
+      <c r="T7" s="165" t="n"/>
+      <c r="U7" s="165" t="n"/>
+      <c r="V7" s="165" t="n"/>
+      <c r="W7" s="165" t="n"/>
+      <c r="X7" s="165" t="n"/>
+      <c r="Y7" s="165" t="n"/>
+      <c r="Z7" s="165" t="n"/>
+      <c r="AA7" s="165" t="n"/>
+      <c r="AB7" s="165" t="n"/>
+      <c r="AC7" s="165" t="n"/>
+      <c r="AD7" s="165" t="n"/>
+      <c r="AE7" s="165" t="n"/>
+      <c r="AF7" s="165" t="n"/>
+      <c r="AG7" s="165" t="n"/>
+      <c r="AH7" s="165" t="n"/>
+      <c r="AI7" s="165" t="n"/>
+      <c r="AJ7" s="165" t="n"/>
+      <c r="AK7" s="165" t="n"/>
+      <c r="AL7" s="165" t="n"/>
+      <c r="AM7" s="165" t="n"/>
+      <c r="AN7" s="165" t="n"/>
+      <c r="AO7" s="165" t="n"/>
+      <c r="AP7" s="165" t="n"/>
+      <c r="AQ7" s="165" t="n"/>
+      <c r="AR7" s="165" t="n"/>
+      <c r="AS7" s="165" t="n"/>
+      <c r="AT7" s="165" t="n"/>
+      <c r="AU7" s="165" t="n"/>
+      <c r="AV7" s="165" t="n"/>
+      <c r="AW7" s="165" t="n"/>
+      <c r="AX7" s="165" t="n"/>
+      <c r="AY7" s="165" t="n"/>
+      <c r="AZ7" s="165" t="n"/>
+      <c r="BA7" s="165" t="n"/>
+      <c r="BB7" s="165" t="n"/>
+      <c r="BC7" s="165" t="n"/>
+      <c r="BD7" s="166" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="72" t="inlineStr">
+      <c r="A8" s="167" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="105" t="n"/>
-      <c r="C8" s="105" t="n"/>
-      <c r="D8" s="105" t="n"/>
-      <c r="E8" s="105" t="n"/>
-      <c r="F8" s="105" t="n"/>
-      <c r="G8" s="105" t="n"/>
-      <c r="H8" s="105" t="n"/>
-      <c r="I8" s="105" t="n"/>
-      <c r="J8" s="106" t="n"/>
-      <c r="K8" s="89" t="inlineStr">
+      <c r="B8" s="168" t="n"/>
+      <c r="C8" s="168" t="n"/>
+      <c r="D8" s="168" t="n"/>
+      <c r="E8" s="168" t="n"/>
+      <c r="F8" s="168" t="n"/>
+      <c r="G8" s="168" t="n"/>
+      <c r="H8" s="168" t="n"/>
+      <c r="I8" s="168" t="n"/>
+      <c r="J8" s="168" t="n"/>
+      <c r="K8" s="196" t="inlineStr">
         <is>
           <t>M365 evidence stays SSOT; workbook captures the formal study / gate / decision record while annex rules, criteria dictionaries and authority matrices are referenced, not re-keyed.</t>
         </is>
       </c>
-      <c r="L8" s="105" t="n"/>
-      <c r="M8" s="105" t="n"/>
-      <c r="N8" s="105" t="n"/>
-      <c r="O8" s="105" t="n"/>
-      <c r="P8" s="105" t="n"/>
-      <c r="Q8" s="105" t="n"/>
-      <c r="R8" s="105" t="n"/>
-      <c r="S8" s="105" t="n"/>
-      <c r="T8" s="105" t="n"/>
-      <c r="U8" s="105" t="n"/>
-      <c r="V8" s="105" t="n"/>
-      <c r="W8" s="105" t="n"/>
-      <c r="X8" s="105" t="n"/>
-      <c r="Y8" s="105" t="n"/>
-      <c r="Z8" s="105" t="n"/>
-      <c r="AA8" s="105" t="n"/>
-      <c r="AB8" s="106" t="n"/>
-      <c r="AC8" s="20" t="inlineStr"/>
-      <c r="AD8" s="90" t="n"/>
-      <c r="AE8" s="90" t="n"/>
-      <c r="AF8" s="90" t="n"/>
-      <c r="AG8" s="90" t="n"/>
-      <c r="AH8" s="90" t="n"/>
-      <c r="AI8" s="90" t="n"/>
-      <c r="AJ8" s="90" t="n"/>
-      <c r="AK8" s="90" t="n"/>
-      <c r="AL8" s="90" t="n"/>
-      <c r="AM8" s="20" t="inlineStr"/>
-      <c r="AN8" s="90" t="n"/>
-      <c r="AO8" s="90" t="n"/>
-      <c r="AP8" s="90" t="n"/>
-      <c r="AQ8" s="90" t="n"/>
-      <c r="AR8" s="90" t="n"/>
-      <c r="AS8" s="90" t="n"/>
-      <c r="AT8" s="90" t="n"/>
-      <c r="AU8" s="90" t="n"/>
-      <c r="AV8" s="90" t="n"/>
-      <c r="AW8" s="90" t="n"/>
-      <c r="AX8" s="90" t="n"/>
-      <c r="AY8" s="90" t="n"/>
-      <c r="AZ8" s="90" t="n"/>
-      <c r="BA8" s="90" t="n"/>
-      <c r="BB8" s="90" t="n"/>
-      <c r="BC8" s="90" t="n"/>
-      <c r="BD8" s="90" t="n"/>
+      <c r="L8" s="168" t="n"/>
+      <c r="M8" s="168" t="n"/>
+      <c r="N8" s="168" t="n"/>
+      <c r="O8" s="168" t="n"/>
+      <c r="P8" s="168" t="n"/>
+      <c r="Q8" s="168" t="n"/>
+      <c r="R8" s="168" t="n"/>
+      <c r="S8" s="168" t="n"/>
+      <c r="T8" s="168" t="n"/>
+      <c r="U8" s="168" t="n"/>
+      <c r="V8" s="168" t="n"/>
+      <c r="W8" s="168" t="n"/>
+      <c r="X8" s="168" t="n"/>
+      <c r="Y8" s="168" t="n"/>
+      <c r="Z8" s="168" t="n"/>
+      <c r="AA8" s="168" t="n"/>
+      <c r="AB8" s="168" t="n"/>
+      <c r="AC8" s="197" t="inlineStr"/>
+      <c r="AD8" s="168" t="n"/>
+      <c r="AE8" s="168" t="n"/>
+      <c r="AF8" s="168" t="n"/>
+      <c r="AG8" s="168" t="n"/>
+      <c r="AH8" s="168" t="n"/>
+      <c r="AI8" s="168" t="n"/>
+      <c r="AJ8" s="168" t="n"/>
+      <c r="AK8" s="168" t="n"/>
+      <c r="AL8" s="168" t="n"/>
+      <c r="AM8" s="197" t="inlineStr"/>
+      <c r="AN8" s="168" t="n"/>
+      <c r="AO8" s="168" t="n"/>
+      <c r="AP8" s="168" t="n"/>
+      <c r="AQ8" s="168" t="n"/>
+      <c r="AR8" s="168" t="n"/>
+      <c r="AS8" s="168" t="n"/>
+      <c r="AT8" s="168" t="n"/>
+      <c r="AU8" s="168" t="n"/>
+      <c r="AV8" s="168" t="n"/>
+      <c r="AW8" s="168" t="n"/>
+      <c r="AX8" s="168" t="n"/>
+      <c r="AY8" s="168" t="n"/>
+      <c r="AZ8" s="168" t="n"/>
+      <c r="BA8" s="168" t="n"/>
+      <c r="BB8" s="168" t="n"/>
+      <c r="BC8" s="168" t="n"/>
+      <c r="BD8" s="198" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="173" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="105" t="n"/>
-      <c r="C9" s="105" t="n"/>
-      <c r="D9" s="105" t="n"/>
-      <c r="E9" s="105" t="n"/>
-      <c r="F9" s="105" t="n"/>
-      <c r="G9" s="105" t="n"/>
-      <c r="H9" s="105" t="n"/>
-      <c r="I9" s="105" t="n"/>
-      <c r="J9" s="106" t="n"/>
-      <c r="K9" s="89" t="inlineStr">
+      <c r="B9" s="174" t="n"/>
+      <c r="C9" s="174" t="n"/>
+      <c r="D9" s="174" t="n"/>
+      <c r="E9" s="174" t="n"/>
+      <c r="F9" s="174" t="n"/>
+      <c r="G9" s="174" t="n"/>
+      <c r="H9" s="174" t="n"/>
+      <c r="I9" s="174" t="n"/>
+      <c r="J9" s="174" t="n"/>
+      <c r="K9" s="199" t="inlineStr">
         <is>
           <t>Reference / code-support sheet for controlled vocabulary or approved code mappings.</t>
         </is>
       </c>
-      <c r="L9" s="105" t="n"/>
-      <c r="M9" s="105" t="n"/>
-      <c r="N9" s="105" t="n"/>
-      <c r="O9" s="105" t="n"/>
-      <c r="P9" s="105" t="n"/>
-      <c r="Q9" s="105" t="n"/>
-      <c r="R9" s="105" t="n"/>
-      <c r="S9" s="105" t="n"/>
-      <c r="T9" s="105" t="n"/>
-      <c r="U9" s="105" t="n"/>
-      <c r="V9" s="105" t="n"/>
-      <c r="W9" s="105" t="n"/>
-      <c r="X9" s="105" t="n"/>
-      <c r="Y9" s="105" t="n"/>
-      <c r="Z9" s="105" t="n"/>
-      <c r="AA9" s="105" t="n"/>
-      <c r="AB9" s="106" t="n"/>
-      <c r="AC9" s="20" t="inlineStr"/>
-      <c r="AD9" s="90" t="n"/>
-      <c r="AE9" s="90" t="n"/>
-      <c r="AF9" s="90" t="n"/>
-      <c r="AG9" s="90" t="n"/>
-      <c r="AH9" s="90" t="n"/>
-      <c r="AI9" s="90" t="n"/>
-      <c r="AJ9" s="90" t="n"/>
-      <c r="AK9" s="90" t="n"/>
-      <c r="AL9" s="90" t="n"/>
-      <c r="AM9" s="20" t="inlineStr"/>
-      <c r="AN9" s="90" t="n"/>
-      <c r="AO9" s="90" t="n"/>
-      <c r="AP9" s="90" t="n"/>
-      <c r="AQ9" s="90" t="n"/>
-      <c r="AR9" s="90" t="n"/>
-      <c r="AS9" s="90" t="n"/>
-      <c r="AT9" s="90" t="n"/>
-      <c r="AU9" s="90" t="n"/>
-      <c r="AV9" s="90" t="n"/>
-      <c r="AW9" s="90" t="n"/>
-      <c r="AX9" s="90" t="n"/>
-      <c r="AY9" s="90" t="n"/>
-      <c r="AZ9" s="90" t="n"/>
-      <c r="BA9" s="90" t="n"/>
-      <c r="BB9" s="90" t="n"/>
-      <c r="BC9" s="90" t="n"/>
-      <c r="BD9" s="90" t="n"/>
+      <c r="L9" s="174" t="n"/>
+      <c r="M9" s="174" t="n"/>
+      <c r="N9" s="174" t="n"/>
+      <c r="O9" s="174" t="n"/>
+      <c r="P9" s="174" t="n"/>
+      <c r="Q9" s="174" t="n"/>
+      <c r="R9" s="174" t="n"/>
+      <c r="S9" s="174" t="n"/>
+      <c r="T9" s="174" t="n"/>
+      <c r="U9" s="174" t="n"/>
+      <c r="V9" s="174" t="n"/>
+      <c r="W9" s="174" t="n"/>
+      <c r="X9" s="174" t="n"/>
+      <c r="Y9" s="174" t="n"/>
+      <c r="Z9" s="174" t="n"/>
+      <c r="AA9" s="174" t="n"/>
+      <c r="AB9" s="174" t="n"/>
+      <c r="AC9" s="200" t="inlineStr"/>
+      <c r="AD9" s="174" t="n"/>
+      <c r="AE9" s="174" t="n"/>
+      <c r="AF9" s="174" t="n"/>
+      <c r="AG9" s="174" t="n"/>
+      <c r="AH9" s="174" t="n"/>
+      <c r="AI9" s="174" t="n"/>
+      <c r="AJ9" s="174" t="n"/>
+      <c r="AK9" s="174" t="n"/>
+      <c r="AL9" s="174" t="n"/>
+      <c r="AM9" s="200" t="inlineStr"/>
+      <c r="AN9" s="174" t="n"/>
+      <c r="AO9" s="174" t="n"/>
+      <c r="AP9" s="174" t="n"/>
+      <c r="AQ9" s="174" t="n"/>
+      <c r="AR9" s="174" t="n"/>
+      <c r="AS9" s="174" t="n"/>
+      <c r="AT9" s="174" t="n"/>
+      <c r="AU9" s="174" t="n"/>
+      <c r="AV9" s="174" t="n"/>
+      <c r="AW9" s="174" t="n"/>
+      <c r="AX9" s="174" t="n"/>
+      <c r="AY9" s="174" t="n"/>
+      <c r="AZ9" s="174" t="n"/>
+      <c r="BA9" s="174" t="n"/>
+      <c r="BB9" s="174" t="n"/>
+      <c r="BC9" s="174" t="n"/>
+      <c r="BD9" s="201" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="71" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B10" s="105" t="n"/>
-      <c r="C10" s="105" t="n"/>
-      <c r="D10" s="105" t="n"/>
-      <c r="E10" s="105" t="n"/>
-      <c r="F10" s="105" t="n"/>
-      <c r="G10" s="105" t="n"/>
-      <c r="H10" s="105" t="n"/>
-      <c r="I10" s="105" t="n"/>
-      <c r="J10" s="105" t="n"/>
-      <c r="K10" s="105" t="n"/>
-      <c r="L10" s="105" t="n"/>
-      <c r="M10" s="105" t="n"/>
-      <c r="N10" s="105" t="n"/>
-      <c r="O10" s="105" t="n"/>
-      <c r="P10" s="105" t="n"/>
-      <c r="Q10" s="105" t="n"/>
-      <c r="R10" s="105" t="n"/>
-      <c r="S10" s="105" t="n"/>
-      <c r="T10" s="105" t="n"/>
-      <c r="U10" s="105" t="n"/>
-      <c r="V10" s="105" t="n"/>
-      <c r="W10" s="105" t="n"/>
-      <c r="X10" s="105" t="n"/>
-      <c r="Y10" s="105" t="n"/>
-      <c r="Z10" s="105" t="n"/>
-      <c r="AA10" s="105" t="n"/>
-      <c r="AB10" s="105" t="n"/>
-      <c r="AC10" s="105" t="n"/>
-      <c r="AD10" s="105" t="n"/>
-      <c r="AE10" s="105" t="n"/>
-      <c r="AF10" s="105" t="n"/>
-      <c r="AG10" s="105" t="n"/>
-      <c r="AH10" s="105" t="n"/>
-      <c r="AI10" s="105" t="n"/>
-      <c r="AJ10" s="105" t="n"/>
-      <c r="AK10" s="105" t="n"/>
-      <c r="AL10" s="105" t="n"/>
-      <c r="AM10" s="105" t="n"/>
-      <c r="AN10" s="105" t="n"/>
-      <c r="AO10" s="105" t="n"/>
-      <c r="AP10" s="105" t="n"/>
-      <c r="AQ10" s="105" t="n"/>
-      <c r="AR10" s="105" t="n"/>
-      <c r="AS10" s="105" t="n"/>
-      <c r="AT10" s="105" t="n"/>
-      <c r="AU10" s="105" t="n"/>
-      <c r="AV10" s="105" t="n"/>
-      <c r="AW10" s="105" t="n"/>
-      <c r="AX10" s="105" t="n"/>
-      <c r="AY10" s="105" t="n"/>
-      <c r="AZ10" s="105" t="n"/>
-      <c r="BA10" s="105" t="n"/>
-      <c r="BB10" s="105" t="n"/>
-      <c r="BC10" s="105" t="n"/>
-      <c r="BD10" s="106" t="n"/>
+      <c r="B10" s="165" t="n"/>
+      <c r="C10" s="165" t="n"/>
+      <c r="D10" s="165" t="n"/>
+      <c r="E10" s="165" t="n"/>
+      <c r="F10" s="165" t="n"/>
+      <c r="G10" s="165" t="n"/>
+      <c r="H10" s="165" t="n"/>
+      <c r="I10" s="165" t="n"/>
+      <c r="J10" s="165" t="n"/>
+      <c r="K10" s="165" t="n"/>
+      <c r="L10" s="165" t="n"/>
+      <c r="M10" s="165" t="n"/>
+      <c r="N10" s="165" t="n"/>
+      <c r="O10" s="165" t="n"/>
+      <c r="P10" s="165" t="n"/>
+      <c r="Q10" s="165" t="n"/>
+      <c r="R10" s="165" t="n"/>
+      <c r="S10" s="165" t="n"/>
+      <c r="T10" s="165" t="n"/>
+      <c r="U10" s="165" t="n"/>
+      <c r="V10" s="165" t="n"/>
+      <c r="W10" s="165" t="n"/>
+      <c r="X10" s="165" t="n"/>
+      <c r="Y10" s="165" t="n"/>
+      <c r="Z10" s="165" t="n"/>
+      <c r="AA10" s="165" t="n"/>
+      <c r="AB10" s="165" t="n"/>
+      <c r="AC10" s="165" t="n"/>
+      <c r="AD10" s="165" t="n"/>
+      <c r="AE10" s="165" t="n"/>
+      <c r="AF10" s="165" t="n"/>
+      <c r="AG10" s="165" t="n"/>
+      <c r="AH10" s="165" t="n"/>
+      <c r="AI10" s="165" t="n"/>
+      <c r="AJ10" s="165" t="n"/>
+      <c r="AK10" s="165" t="n"/>
+      <c r="AL10" s="165" t="n"/>
+      <c r="AM10" s="165" t="n"/>
+      <c r="AN10" s="165" t="n"/>
+      <c r="AO10" s="165" t="n"/>
+      <c r="AP10" s="165" t="n"/>
+      <c r="AQ10" s="165" t="n"/>
+      <c r="AR10" s="165" t="n"/>
+      <c r="AS10" s="165" t="n"/>
+      <c r="AT10" s="165" t="n"/>
+      <c r="AU10" s="165" t="n"/>
+      <c r="AV10" s="165" t="n"/>
+      <c r="AW10" s="165" t="n"/>
+      <c r="AX10" s="165" t="n"/>
+      <c r="AY10" s="165" t="n"/>
+      <c r="AZ10" s="165" t="n"/>
+      <c r="BA10" s="165" t="n"/>
+      <c r="BB10" s="165" t="n"/>
+      <c r="BC10" s="165" t="n"/>
+      <c r="BD10" s="166" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="91" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="202" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="B11" s="105" t="n"/>
-      <c r="C11" s="105" t="n"/>
-      <c r="D11" s="105" t="n"/>
-      <c r="E11" s="105" t="n"/>
-      <c r="F11" s="105" t="n"/>
-      <c r="G11" s="105" t="n"/>
-      <c r="H11" s="105" t="n"/>
-      <c r="I11" s="106" t="n"/>
-      <c r="J11" s="91" t="inlineStr">
+      <c r="B11" s="203" t="n"/>
+      <c r="C11" s="203" t="n"/>
+      <c r="D11" s="203" t="n"/>
+      <c r="E11" s="203" t="n"/>
+      <c r="F11" s="203" t="n"/>
+      <c r="G11" s="203" t="n"/>
+      <c r="H11" s="203" t="n"/>
+      <c r="I11" s="203" t="n"/>
+      <c r="J11" s="204" t="inlineStr">
         <is>
           <t>Expected Standard</t>
         </is>
       </c>
-      <c r="K11" s="105" t="n"/>
-      <c r="L11" s="105" t="n"/>
-      <c r="M11" s="105" t="n"/>
-      <c r="N11" s="105" t="n"/>
-      <c r="O11" s="105" t="n"/>
-      <c r="P11" s="105" t="n"/>
-      <c r="Q11" s="105" t="n"/>
-      <c r="R11" s="105" t="n"/>
-      <c r="S11" s="106" t="n"/>
-      <c r="T11" s="91" t="inlineStr">
+      <c r="K11" s="203" t="n"/>
+      <c r="L11" s="203" t="n"/>
+      <c r="M11" s="203" t="n"/>
+      <c r="N11" s="203" t="n"/>
+      <c r="O11" s="203" t="n"/>
+      <c r="P11" s="203" t="n"/>
+      <c r="Q11" s="203" t="n"/>
+      <c r="R11" s="203" t="n"/>
+      <c r="S11" s="203" t="n"/>
+      <c r="T11" s="204" t="inlineStr">
         <is>
           <t>Observed Evidence</t>
         </is>
       </c>
-      <c r="U11" s="105" t="n"/>
-      <c r="V11" s="105" t="n"/>
-      <c r="W11" s="105" t="n"/>
-      <c r="X11" s="105" t="n"/>
-      <c r="Y11" s="105" t="n"/>
-      <c r="Z11" s="105" t="n"/>
-      <c r="AA11" s="105" t="n"/>
-      <c r="AB11" s="105" t="n"/>
-      <c r="AC11" s="105" t="n"/>
-      <c r="AD11" s="105" t="n"/>
-      <c r="AE11" s="106" t="n"/>
-      <c r="AF11" s="91" t="inlineStr">
+      <c r="U11" s="203" t="n"/>
+      <c r="V11" s="203" t="n"/>
+      <c r="W11" s="203" t="n"/>
+      <c r="X11" s="203" t="n"/>
+      <c r="Y11" s="203" t="n"/>
+      <c r="Z11" s="203" t="n"/>
+      <c r="AA11" s="203" t="n"/>
+      <c r="AB11" s="203" t="n"/>
+      <c r="AC11" s="203" t="n"/>
+      <c r="AD11" s="203" t="n"/>
+      <c r="AE11" s="203" t="n"/>
+      <c r="AF11" s="204" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AG11" s="105" t="n"/>
-      <c r="AH11" s="105" t="n"/>
-      <c r="AI11" s="105" t="n"/>
-      <c r="AJ11" s="105" t="n"/>
-      <c r="AK11" s="105" t="n"/>
-      <c r="AL11" s="105" t="n"/>
-      <c r="AM11" s="105" t="n"/>
-      <c r="AN11" s="106" t="n"/>
-      <c r="AO11" s="91" t="inlineStr">
+      <c r="AG11" s="203" t="n"/>
+      <c r="AH11" s="203" t="n"/>
+      <c r="AI11" s="203" t="n"/>
+      <c r="AJ11" s="203" t="n"/>
+      <c r="AK11" s="203" t="n"/>
+      <c r="AL11" s="203" t="n"/>
+      <c r="AM11" s="203" t="n"/>
+      <c r="AN11" s="203" t="n"/>
+      <c r="AO11" s="204" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="AP11" s="105" t="n"/>
-      <c r="AQ11" s="105" t="n"/>
-      <c r="AR11" s="105" t="n"/>
-      <c r="AS11" s="105" t="n"/>
-      <c r="AT11" s="105" t="n"/>
-      <c r="AU11" s="105" t="n"/>
-      <c r="AV11" s="105" t="n"/>
-      <c r="AW11" s="105" t="n"/>
-      <c r="AX11" s="105" t="n"/>
-      <c r="AY11" s="105" t="n"/>
-      <c r="AZ11" s="105" t="n"/>
-      <c r="BA11" s="105" t="n"/>
-      <c r="BB11" s="105" t="n"/>
-      <c r="BC11" s="105" t="n"/>
-      <c r="BD11" s="106" t="n"/>
+      <c r="AP11" s="203" t="n"/>
+      <c r="AQ11" s="203" t="n"/>
+      <c r="AR11" s="203" t="n"/>
+      <c r="AS11" s="203" t="n"/>
+      <c r="AT11" s="203" t="n"/>
+      <c r="AU11" s="203" t="n"/>
+      <c r="AV11" s="203" t="n"/>
+      <c r="AW11" s="203" t="n"/>
+      <c r="AX11" s="203" t="n"/>
+      <c r="AY11" s="203" t="n"/>
+      <c r="AZ11" s="203" t="n"/>
+      <c r="BA11" s="203" t="n"/>
+      <c r="BB11" s="203" t="n"/>
+      <c r="BC11" s="203" t="n"/>
+      <c r="BD11" s="205" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="92" t="n"/>
-      <c r="B12" s="115" t="n"/>
-      <c r="C12" s="115" t="n"/>
-      <c r="D12" s="115" t="n"/>
-      <c r="E12" s="115" t="n"/>
-      <c r="F12" s="115" t="n"/>
-      <c r="G12" s="115" t="n"/>
-      <c r="H12" s="115" t="n"/>
-      <c r="I12" s="116" t="n"/>
-      <c r="J12" s="95" t="n"/>
-      <c r="K12" s="113" t="n"/>
-      <c r="L12" s="113" t="n"/>
-      <c r="M12" s="113" t="n"/>
-      <c r="N12" s="113" t="n"/>
-      <c r="O12" s="113" t="n"/>
-      <c r="P12" s="113" t="n"/>
-      <c r="Q12" s="113" t="n"/>
-      <c r="R12" s="113" t="n"/>
-      <c r="S12" s="114" t="n"/>
-      <c r="T12" s="95" t="n"/>
-      <c r="U12" s="113" t="n"/>
-      <c r="V12" s="113" t="n"/>
-      <c r="W12" s="113" t="n"/>
-      <c r="X12" s="113" t="n"/>
-      <c r="Y12" s="113" t="n"/>
-      <c r="Z12" s="113" t="n"/>
-      <c r="AA12" s="113" t="n"/>
-      <c r="AB12" s="113" t="n"/>
-      <c r="AC12" s="113" t="n"/>
-      <c r="AD12" s="113" t="n"/>
-      <c r="AE12" s="114" t="n"/>
-      <c r="AF12" s="96" t="n"/>
-      <c r="AG12" s="113" t="n"/>
-      <c r="AH12" s="113" t="n"/>
-      <c r="AI12" s="113" t="n"/>
-      <c r="AJ12" s="113" t="n"/>
-      <c r="AK12" s="113" t="n"/>
-      <c r="AL12" s="113" t="n"/>
-      <c r="AM12" s="113" t="n"/>
-      <c r="AN12" s="114" t="n"/>
-      <c r="AO12" s="95" t="n"/>
-      <c r="AP12" s="113" t="n"/>
-      <c r="AQ12" s="113" t="n"/>
-      <c r="AR12" s="113" t="n"/>
-      <c r="AS12" s="113" t="n"/>
-      <c r="AT12" s="113" t="n"/>
-      <c r="AU12" s="113" t="n"/>
-      <c r="AV12" s="113" t="n"/>
-      <c r="AW12" s="113" t="n"/>
-      <c r="AX12" s="113" t="n"/>
-      <c r="AY12" s="113" t="n"/>
-      <c r="AZ12" s="113" t="n"/>
-      <c r="BA12" s="113" t="n"/>
-      <c r="BB12" s="113" t="n"/>
-      <c r="BC12" s="113" t="n"/>
-      <c r="BD12" s="114" t="n"/>
+      <c r="A12" s="206" t="n"/>
+      <c r="B12" s="168" t="n"/>
+      <c r="C12" s="168" t="n"/>
+      <c r="D12" s="168" t="n"/>
+      <c r="E12" s="168" t="n"/>
+      <c r="F12" s="168" t="n"/>
+      <c r="G12" s="168" t="n"/>
+      <c r="H12" s="168" t="n"/>
+      <c r="I12" s="168" t="n"/>
+      <c r="J12" s="169" t="n"/>
+      <c r="K12" s="170" t="n"/>
+      <c r="L12" s="170" t="n"/>
+      <c r="M12" s="170" t="n"/>
+      <c r="N12" s="170" t="n"/>
+      <c r="O12" s="170" t="n"/>
+      <c r="P12" s="170" t="n"/>
+      <c r="Q12" s="170" t="n"/>
+      <c r="R12" s="170" t="n"/>
+      <c r="S12" s="170" t="n"/>
+      <c r="T12" s="169" t="n"/>
+      <c r="U12" s="170" t="n"/>
+      <c r="V12" s="170" t="n"/>
+      <c r="W12" s="170" t="n"/>
+      <c r="X12" s="170" t="n"/>
+      <c r="Y12" s="170" t="n"/>
+      <c r="Z12" s="170" t="n"/>
+      <c r="AA12" s="170" t="n"/>
+      <c r="AB12" s="170" t="n"/>
+      <c r="AC12" s="170" t="n"/>
+      <c r="AD12" s="170" t="n"/>
+      <c r="AE12" s="170" t="n"/>
+      <c r="AF12" s="207" t="n"/>
+      <c r="AG12" s="170" t="n"/>
+      <c r="AH12" s="170" t="n"/>
+      <c r="AI12" s="170" t="n"/>
+      <c r="AJ12" s="170" t="n"/>
+      <c r="AK12" s="170" t="n"/>
+      <c r="AL12" s="170" t="n"/>
+      <c r="AM12" s="170" t="n"/>
+      <c r="AN12" s="170" t="n"/>
+      <c r="AO12" s="169" t="n"/>
+      <c r="AP12" s="170" t="n"/>
+      <c r="AQ12" s="170" t="n"/>
+      <c r="AR12" s="170" t="n"/>
+      <c r="AS12" s="170" t="n"/>
+      <c r="AT12" s="170" t="n"/>
+      <c r="AU12" s="170" t="n"/>
+      <c r="AV12" s="170" t="n"/>
+      <c r="AW12" s="170" t="n"/>
+      <c r="AX12" s="170" t="n"/>
+      <c r="AY12" s="170" t="n"/>
+      <c r="AZ12" s="170" t="n"/>
+      <c r="BA12" s="170" t="n"/>
+      <c r="BB12" s="170" t="n"/>
+      <c r="BC12" s="170" t="n"/>
+      <c r="BD12" s="172" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="92" t="n"/>
-      <c r="B13" s="115" t="n"/>
-      <c r="C13" s="115" t="n"/>
-      <c r="D13" s="115" t="n"/>
-      <c r="E13" s="115" t="n"/>
-      <c r="F13" s="115" t="n"/>
-      <c r="G13" s="115" t="n"/>
-      <c r="H13" s="115" t="n"/>
-      <c r="I13" s="116" t="n"/>
-      <c r="J13" s="97" t="n"/>
-      <c r="K13" s="113" t="n"/>
-      <c r="L13" s="113" t="n"/>
-      <c r="M13" s="113" t="n"/>
-      <c r="N13" s="113" t="n"/>
-      <c r="O13" s="113" t="n"/>
-      <c r="P13" s="113" t="n"/>
-      <c r="Q13" s="113" t="n"/>
-      <c r="R13" s="113" t="n"/>
-      <c r="S13" s="114" t="n"/>
-      <c r="T13" s="97" t="n"/>
-      <c r="U13" s="113" t="n"/>
-      <c r="V13" s="113" t="n"/>
-      <c r="W13" s="113" t="n"/>
-      <c r="X13" s="113" t="n"/>
-      <c r="Y13" s="113" t="n"/>
-      <c r="Z13" s="113" t="n"/>
-      <c r="AA13" s="113" t="n"/>
-      <c r="AB13" s="113" t="n"/>
-      <c r="AC13" s="113" t="n"/>
-      <c r="AD13" s="113" t="n"/>
-      <c r="AE13" s="114" t="n"/>
-      <c r="AF13" s="96" t="n"/>
-      <c r="AG13" s="113" t="n"/>
-      <c r="AH13" s="113" t="n"/>
-      <c r="AI13" s="113" t="n"/>
-      <c r="AJ13" s="113" t="n"/>
-      <c r="AK13" s="113" t="n"/>
-      <c r="AL13" s="113" t="n"/>
-      <c r="AM13" s="113" t="n"/>
-      <c r="AN13" s="114" t="n"/>
-      <c r="AO13" s="97" t="n"/>
-      <c r="AP13" s="113" t="n"/>
-      <c r="AQ13" s="113" t="n"/>
-      <c r="AR13" s="113" t="n"/>
-      <c r="AS13" s="113" t="n"/>
-      <c r="AT13" s="113" t="n"/>
-      <c r="AU13" s="113" t="n"/>
-      <c r="AV13" s="113" t="n"/>
-      <c r="AW13" s="113" t="n"/>
-      <c r="AX13" s="113" t="n"/>
-      <c r="AY13" s="113" t="n"/>
-      <c r="AZ13" s="113" t="n"/>
-      <c r="BA13" s="113" t="n"/>
-      <c r="BB13" s="113" t="n"/>
-      <c r="BC13" s="113" t="n"/>
-      <c r="BD13" s="114" t="n"/>
+      <c r="A13" s="208" t="n"/>
+      <c r="B13" s="58" t="n"/>
+      <c r="C13" s="58" t="n"/>
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="58" t="n"/>
+      <c r="F13" s="58" t="n"/>
+      <c r="G13" s="58" t="n"/>
+      <c r="H13" s="58" t="n"/>
+      <c r="I13" s="58" t="n"/>
+      <c r="J13" s="209" t="n"/>
+      <c r="K13" s="183" t="n"/>
+      <c r="L13" s="183" t="n"/>
+      <c r="M13" s="183" t="n"/>
+      <c r="N13" s="183" t="n"/>
+      <c r="O13" s="183" t="n"/>
+      <c r="P13" s="183" t="n"/>
+      <c r="Q13" s="183" t="n"/>
+      <c r="R13" s="183" t="n"/>
+      <c r="S13" s="183" t="n"/>
+      <c r="T13" s="209" t="n"/>
+      <c r="U13" s="183" t="n"/>
+      <c r="V13" s="183" t="n"/>
+      <c r="W13" s="183" t="n"/>
+      <c r="X13" s="183" t="n"/>
+      <c r="Y13" s="183" t="n"/>
+      <c r="Z13" s="183" t="n"/>
+      <c r="AA13" s="183" t="n"/>
+      <c r="AB13" s="183" t="n"/>
+      <c r="AC13" s="183" t="n"/>
+      <c r="AD13" s="183" t="n"/>
+      <c r="AE13" s="183" t="n"/>
+      <c r="AF13" s="210" t="n"/>
+      <c r="AG13" s="183" t="n"/>
+      <c r="AH13" s="183" t="n"/>
+      <c r="AI13" s="183" t="n"/>
+      <c r="AJ13" s="183" t="n"/>
+      <c r="AK13" s="183" t="n"/>
+      <c r="AL13" s="183" t="n"/>
+      <c r="AM13" s="183" t="n"/>
+      <c r="AN13" s="183" t="n"/>
+      <c r="AO13" s="209" t="n"/>
+      <c r="AP13" s="183" t="n"/>
+      <c r="AQ13" s="183" t="n"/>
+      <c r="AR13" s="183" t="n"/>
+      <c r="AS13" s="183" t="n"/>
+      <c r="AT13" s="183" t="n"/>
+      <c r="AU13" s="183" t="n"/>
+      <c r="AV13" s="183" t="n"/>
+      <c r="AW13" s="183" t="n"/>
+      <c r="AX13" s="183" t="n"/>
+      <c r="AY13" s="183" t="n"/>
+      <c r="AZ13" s="183" t="n"/>
+      <c r="BA13" s="183" t="n"/>
+      <c r="BB13" s="183" t="n"/>
+      <c r="BC13" s="183" t="n"/>
+      <c r="BD13" s="187" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="92" t="n"/>
-      <c r="B14" s="115" t="n"/>
-      <c r="C14" s="115" t="n"/>
-      <c r="D14" s="115" t="n"/>
-      <c r="E14" s="115" t="n"/>
-      <c r="F14" s="115" t="n"/>
-      <c r="G14" s="115" t="n"/>
-      <c r="H14" s="115" t="n"/>
-      <c r="I14" s="116" t="n"/>
-      <c r="J14" s="95" t="n"/>
-      <c r="K14" s="113" t="n"/>
-      <c r="L14" s="113" t="n"/>
-      <c r="M14" s="113" t="n"/>
-      <c r="N14" s="113" t="n"/>
-      <c r="O14" s="113" t="n"/>
-      <c r="P14" s="113" t="n"/>
-      <c r="Q14" s="113" t="n"/>
-      <c r="R14" s="113" t="n"/>
-      <c r="S14" s="114" t="n"/>
-      <c r="T14" s="95" t="n"/>
-      <c r="U14" s="113" t="n"/>
-      <c r="V14" s="113" t="n"/>
-      <c r="W14" s="113" t="n"/>
-      <c r="X14" s="113" t="n"/>
-      <c r="Y14" s="113" t="n"/>
-      <c r="Z14" s="113" t="n"/>
-      <c r="AA14" s="113" t="n"/>
-      <c r="AB14" s="113" t="n"/>
-      <c r="AC14" s="113" t="n"/>
-      <c r="AD14" s="113" t="n"/>
-      <c r="AE14" s="114" t="n"/>
-      <c r="AF14" s="96" t="n"/>
-      <c r="AG14" s="113" t="n"/>
-      <c r="AH14" s="113" t="n"/>
-      <c r="AI14" s="113" t="n"/>
-      <c r="AJ14" s="113" t="n"/>
-      <c r="AK14" s="113" t="n"/>
-      <c r="AL14" s="113" t="n"/>
-      <c r="AM14" s="113" t="n"/>
-      <c r="AN14" s="114" t="n"/>
-      <c r="AO14" s="95" t="n"/>
-      <c r="AP14" s="113" t="n"/>
-      <c r="AQ14" s="113" t="n"/>
-      <c r="AR14" s="113" t="n"/>
-      <c r="AS14" s="113" t="n"/>
-      <c r="AT14" s="113" t="n"/>
-      <c r="AU14" s="113" t="n"/>
-      <c r="AV14" s="113" t="n"/>
-      <c r="AW14" s="113" t="n"/>
-      <c r="AX14" s="113" t="n"/>
-      <c r="AY14" s="113" t="n"/>
-      <c r="AZ14" s="113" t="n"/>
-      <c r="BA14" s="113" t="n"/>
-      <c r="BB14" s="113" t="n"/>
-      <c r="BC14" s="113" t="n"/>
-      <c r="BD14" s="114" t="n"/>
+      <c r="A14" s="208" t="n"/>
+      <c r="B14" s="58" t="n"/>
+      <c r="C14" s="58" t="n"/>
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="58" t="n"/>
+      <c r="H14" s="58" t="n"/>
+      <c r="I14" s="58" t="n"/>
+      <c r="J14" s="182" t="n"/>
+      <c r="K14" s="183" t="n"/>
+      <c r="L14" s="183" t="n"/>
+      <c r="M14" s="183" t="n"/>
+      <c r="N14" s="183" t="n"/>
+      <c r="O14" s="183" t="n"/>
+      <c r="P14" s="183" t="n"/>
+      <c r="Q14" s="183" t="n"/>
+      <c r="R14" s="183" t="n"/>
+      <c r="S14" s="183" t="n"/>
+      <c r="T14" s="182" t="n"/>
+      <c r="U14" s="183" t="n"/>
+      <c r="V14" s="183" t="n"/>
+      <c r="W14" s="183" t="n"/>
+      <c r="X14" s="183" t="n"/>
+      <c r="Y14" s="183" t="n"/>
+      <c r="Z14" s="183" t="n"/>
+      <c r="AA14" s="183" t="n"/>
+      <c r="AB14" s="183" t="n"/>
+      <c r="AC14" s="183" t="n"/>
+      <c r="AD14" s="183" t="n"/>
+      <c r="AE14" s="183" t="n"/>
+      <c r="AF14" s="210" t="n"/>
+      <c r="AG14" s="183" t="n"/>
+      <c r="AH14" s="183" t="n"/>
+      <c r="AI14" s="183" t="n"/>
+      <c r="AJ14" s="183" t="n"/>
+      <c r="AK14" s="183" t="n"/>
+      <c r="AL14" s="183" t="n"/>
+      <c r="AM14" s="183" t="n"/>
+      <c r="AN14" s="183" t="n"/>
+      <c r="AO14" s="182" t="n"/>
+      <c r="AP14" s="183" t="n"/>
+      <c r="AQ14" s="183" t="n"/>
+      <c r="AR14" s="183" t="n"/>
+      <c r="AS14" s="183" t="n"/>
+      <c r="AT14" s="183" t="n"/>
+      <c r="AU14" s="183" t="n"/>
+      <c r="AV14" s="183" t="n"/>
+      <c r="AW14" s="183" t="n"/>
+      <c r="AX14" s="183" t="n"/>
+      <c r="AY14" s="183" t="n"/>
+      <c r="AZ14" s="183" t="n"/>
+      <c r="BA14" s="183" t="n"/>
+      <c r="BB14" s="183" t="n"/>
+      <c r="BC14" s="183" t="n"/>
+      <c r="BD14" s="187" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="92" t="n"/>
-      <c r="B15" s="115" t="n"/>
-      <c r="C15" s="115" t="n"/>
-      <c r="D15" s="115" t="n"/>
-      <c r="E15" s="115" t="n"/>
-      <c r="F15" s="115" t="n"/>
-      <c r="G15" s="115" t="n"/>
-      <c r="H15" s="115" t="n"/>
-      <c r="I15" s="116" t="n"/>
-      <c r="J15" s="97" t="n"/>
-      <c r="K15" s="113" t="n"/>
-      <c r="L15" s="113" t="n"/>
-      <c r="M15" s="113" t="n"/>
-      <c r="N15" s="113" t="n"/>
-      <c r="O15" s="113" t="n"/>
-      <c r="P15" s="113" t="n"/>
-      <c r="Q15" s="113" t="n"/>
-      <c r="R15" s="113" t="n"/>
-      <c r="S15" s="114" t="n"/>
-      <c r="T15" s="97" t="n"/>
-      <c r="U15" s="113" t="n"/>
-      <c r="V15" s="113" t="n"/>
-      <c r="W15" s="113" t="n"/>
-      <c r="X15" s="113" t="n"/>
-      <c r="Y15" s="113" t="n"/>
-      <c r="Z15" s="113" t="n"/>
-      <c r="AA15" s="113" t="n"/>
-      <c r="AB15" s="113" t="n"/>
-      <c r="AC15" s="113" t="n"/>
-      <c r="AD15" s="113" t="n"/>
-      <c r="AE15" s="114" t="n"/>
-      <c r="AF15" s="96" t="n"/>
-      <c r="AG15" s="113" t="n"/>
-      <c r="AH15" s="113" t="n"/>
-      <c r="AI15" s="113" t="n"/>
-      <c r="AJ15" s="113" t="n"/>
-      <c r="AK15" s="113" t="n"/>
-      <c r="AL15" s="113" t="n"/>
-      <c r="AM15" s="113" t="n"/>
-      <c r="AN15" s="114" t="n"/>
-      <c r="AO15" s="97" t="n"/>
-      <c r="AP15" s="113" t="n"/>
-      <c r="AQ15" s="113" t="n"/>
-      <c r="AR15" s="113" t="n"/>
-      <c r="AS15" s="113" t="n"/>
-      <c r="AT15" s="113" t="n"/>
-      <c r="AU15" s="113" t="n"/>
-      <c r="AV15" s="113" t="n"/>
-      <c r="AW15" s="113" t="n"/>
-      <c r="AX15" s="113" t="n"/>
-      <c r="AY15" s="113" t="n"/>
-      <c r="AZ15" s="113" t="n"/>
-      <c r="BA15" s="113" t="n"/>
-      <c r="BB15" s="113" t="n"/>
-      <c r="BC15" s="113" t="n"/>
-      <c r="BD15" s="114" t="n"/>
+      <c r="A15" s="208" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="C15" s="58" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="58" t="n"/>
+      <c r="H15" s="58" t="n"/>
+      <c r="I15" s="58" t="n"/>
+      <c r="J15" s="209" t="n"/>
+      <c r="K15" s="183" t="n"/>
+      <c r="L15" s="183" t="n"/>
+      <c r="M15" s="183" t="n"/>
+      <c r="N15" s="183" t="n"/>
+      <c r="O15" s="183" t="n"/>
+      <c r="P15" s="183" t="n"/>
+      <c r="Q15" s="183" t="n"/>
+      <c r="R15" s="183" t="n"/>
+      <c r="S15" s="183" t="n"/>
+      <c r="T15" s="209" t="n"/>
+      <c r="U15" s="183" t="n"/>
+      <c r="V15" s="183" t="n"/>
+      <c r="W15" s="183" t="n"/>
+      <c r="X15" s="183" t="n"/>
+      <c r="Y15" s="183" t="n"/>
+      <c r="Z15" s="183" t="n"/>
+      <c r="AA15" s="183" t="n"/>
+      <c r="AB15" s="183" t="n"/>
+      <c r="AC15" s="183" t="n"/>
+      <c r="AD15" s="183" t="n"/>
+      <c r="AE15" s="183" t="n"/>
+      <c r="AF15" s="210" t="n"/>
+      <c r="AG15" s="183" t="n"/>
+      <c r="AH15" s="183" t="n"/>
+      <c r="AI15" s="183" t="n"/>
+      <c r="AJ15" s="183" t="n"/>
+      <c r="AK15" s="183" t="n"/>
+      <c r="AL15" s="183" t="n"/>
+      <c r="AM15" s="183" t="n"/>
+      <c r="AN15" s="183" t="n"/>
+      <c r="AO15" s="209" t="n"/>
+      <c r="AP15" s="183" t="n"/>
+      <c r="AQ15" s="183" t="n"/>
+      <c r="AR15" s="183" t="n"/>
+      <c r="AS15" s="183" t="n"/>
+      <c r="AT15" s="183" t="n"/>
+      <c r="AU15" s="183" t="n"/>
+      <c r="AV15" s="183" t="n"/>
+      <c r="AW15" s="183" t="n"/>
+      <c r="AX15" s="183" t="n"/>
+      <c r="AY15" s="183" t="n"/>
+      <c r="AZ15" s="183" t="n"/>
+      <c r="BA15" s="183" t="n"/>
+      <c r="BB15" s="183" t="n"/>
+      <c r="BC15" s="183" t="n"/>
+      <c r="BD15" s="187" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="92" t="n"/>
-      <c r="B16" s="115" t="n"/>
-      <c r="C16" s="115" t="n"/>
-      <c r="D16" s="115" t="n"/>
-      <c r="E16" s="115" t="n"/>
-      <c r="F16" s="115" t="n"/>
-      <c r="G16" s="115" t="n"/>
-      <c r="H16" s="115" t="n"/>
-      <c r="I16" s="116" t="n"/>
-      <c r="J16" s="95" t="n"/>
-      <c r="K16" s="113" t="n"/>
-      <c r="L16" s="113" t="n"/>
-      <c r="M16" s="113" t="n"/>
-      <c r="N16" s="113" t="n"/>
-      <c r="O16" s="113" t="n"/>
-      <c r="P16" s="113" t="n"/>
-      <c r="Q16" s="113" t="n"/>
-      <c r="R16" s="113" t="n"/>
-      <c r="S16" s="114" t="n"/>
-      <c r="T16" s="95" t="n"/>
-      <c r="U16" s="113" t="n"/>
-      <c r="V16" s="113" t="n"/>
-      <c r="W16" s="113" t="n"/>
-      <c r="X16" s="113" t="n"/>
-      <c r="Y16" s="113" t="n"/>
-      <c r="Z16" s="113" t="n"/>
-      <c r="AA16" s="113" t="n"/>
-      <c r="AB16" s="113" t="n"/>
-      <c r="AC16" s="113" t="n"/>
-      <c r="AD16" s="113" t="n"/>
-      <c r="AE16" s="114" t="n"/>
-      <c r="AF16" s="96" t="n"/>
-      <c r="AG16" s="113" t="n"/>
-      <c r="AH16" s="113" t="n"/>
-      <c r="AI16" s="113" t="n"/>
-      <c r="AJ16" s="113" t="n"/>
-      <c r="AK16" s="113" t="n"/>
-      <c r="AL16" s="113" t="n"/>
-      <c r="AM16" s="113" t="n"/>
-      <c r="AN16" s="114" t="n"/>
-      <c r="AO16" s="95" t="n"/>
-      <c r="AP16" s="113" t="n"/>
-      <c r="AQ16" s="113" t="n"/>
-      <c r="AR16" s="113" t="n"/>
-      <c r="AS16" s="113" t="n"/>
-      <c r="AT16" s="113" t="n"/>
-      <c r="AU16" s="113" t="n"/>
-      <c r="AV16" s="113" t="n"/>
-      <c r="AW16" s="113" t="n"/>
-      <c r="AX16" s="113" t="n"/>
-      <c r="AY16" s="113" t="n"/>
-      <c r="AZ16" s="113" t="n"/>
-      <c r="BA16" s="113" t="n"/>
-      <c r="BB16" s="113" t="n"/>
-      <c r="BC16" s="113" t="n"/>
-      <c r="BD16" s="114" t="n"/>
+      <c r="A16" s="208" t="n"/>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="58" t="n"/>
+      <c r="I16" s="58" t="n"/>
+      <c r="J16" s="182" t="n"/>
+      <c r="K16" s="183" t="n"/>
+      <c r="L16" s="183" t="n"/>
+      <c r="M16" s="183" t="n"/>
+      <c r="N16" s="183" t="n"/>
+      <c r="O16" s="183" t="n"/>
+      <c r="P16" s="183" t="n"/>
+      <c r="Q16" s="183" t="n"/>
+      <c r="R16" s="183" t="n"/>
+      <c r="S16" s="183" t="n"/>
+      <c r="T16" s="182" t="n"/>
+      <c r="U16" s="183" t="n"/>
+      <c r="V16" s="183" t="n"/>
+      <c r="W16" s="183" t="n"/>
+      <c r="X16" s="183" t="n"/>
+      <c r="Y16" s="183" t="n"/>
+      <c r="Z16" s="183" t="n"/>
+      <c r="AA16" s="183" t="n"/>
+      <c r="AB16" s="183" t="n"/>
+      <c r="AC16" s="183" t="n"/>
+      <c r="AD16" s="183" t="n"/>
+      <c r="AE16" s="183" t="n"/>
+      <c r="AF16" s="210" t="n"/>
+      <c r="AG16" s="183" t="n"/>
+      <c r="AH16" s="183" t="n"/>
+      <c r="AI16" s="183" t="n"/>
+      <c r="AJ16" s="183" t="n"/>
+      <c r="AK16" s="183" t="n"/>
+      <c r="AL16" s="183" t="n"/>
+      <c r="AM16" s="183" t="n"/>
+      <c r="AN16" s="183" t="n"/>
+      <c r="AO16" s="182" t="n"/>
+      <c r="AP16" s="183" t="n"/>
+      <c r="AQ16" s="183" t="n"/>
+      <c r="AR16" s="183" t="n"/>
+      <c r="AS16" s="183" t="n"/>
+      <c r="AT16" s="183" t="n"/>
+      <c r="AU16" s="183" t="n"/>
+      <c r="AV16" s="183" t="n"/>
+      <c r="AW16" s="183" t="n"/>
+      <c r="AX16" s="183" t="n"/>
+      <c r="AY16" s="183" t="n"/>
+      <c r="AZ16" s="183" t="n"/>
+      <c r="BA16" s="183" t="n"/>
+      <c r="BB16" s="183" t="n"/>
+      <c r="BC16" s="183" t="n"/>
+      <c r="BD16" s="187" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="92" t="n"/>
-      <c r="B17" s="115" t="n"/>
-      <c r="C17" s="115" t="n"/>
-      <c r="D17" s="115" t="n"/>
-      <c r="E17" s="115" t="n"/>
-      <c r="F17" s="115" t="n"/>
-      <c r="G17" s="115" t="n"/>
-      <c r="H17" s="115" t="n"/>
-      <c r="I17" s="116" t="n"/>
-      <c r="J17" s="97" t="n"/>
-      <c r="K17" s="113" t="n"/>
-      <c r="L17" s="113" t="n"/>
-      <c r="M17" s="113" t="n"/>
-      <c r="N17" s="113" t="n"/>
-      <c r="O17" s="113" t="n"/>
-      <c r="P17" s="113" t="n"/>
-      <c r="Q17" s="113" t="n"/>
-      <c r="R17" s="113" t="n"/>
-      <c r="S17" s="114" t="n"/>
-      <c r="T17" s="97" t="n"/>
-      <c r="U17" s="113" t="n"/>
-      <c r="V17" s="113" t="n"/>
-      <c r="W17" s="113" t="n"/>
-      <c r="X17" s="113" t="n"/>
-      <c r="Y17" s="113" t="n"/>
-      <c r="Z17" s="113" t="n"/>
-      <c r="AA17" s="113" t="n"/>
-      <c r="AB17" s="113" t="n"/>
-      <c r="AC17" s="113" t="n"/>
-      <c r="AD17" s="113" t="n"/>
-      <c r="AE17" s="114" t="n"/>
-      <c r="AF17" s="96" t="n"/>
-      <c r="AG17" s="113" t="n"/>
-      <c r="AH17" s="113" t="n"/>
-      <c r="AI17" s="113" t="n"/>
-      <c r="AJ17" s="113" t="n"/>
-      <c r="AK17" s="113" t="n"/>
-      <c r="AL17" s="113" t="n"/>
-      <c r="AM17" s="113" t="n"/>
-      <c r="AN17" s="114" t="n"/>
-      <c r="AO17" s="97" t="n"/>
-      <c r="AP17" s="113" t="n"/>
-      <c r="AQ17" s="113" t="n"/>
-      <c r="AR17" s="113" t="n"/>
-      <c r="AS17" s="113" t="n"/>
-      <c r="AT17" s="113" t="n"/>
-      <c r="AU17" s="113" t="n"/>
-      <c r="AV17" s="113" t="n"/>
-      <c r="AW17" s="113" t="n"/>
-      <c r="AX17" s="113" t="n"/>
-      <c r="AY17" s="113" t="n"/>
-      <c r="AZ17" s="113" t="n"/>
-      <c r="BA17" s="113" t="n"/>
-      <c r="BB17" s="113" t="n"/>
-      <c r="BC17" s="113" t="n"/>
-      <c r="BD17" s="114" t="n"/>
+      <c r="A17" s="211" t="n"/>
+      <c r="B17" s="174" t="n"/>
+      <c r="C17" s="174" t="n"/>
+      <c r="D17" s="174" t="n"/>
+      <c r="E17" s="174" t="n"/>
+      <c r="F17" s="174" t="n"/>
+      <c r="G17" s="174" t="n"/>
+      <c r="H17" s="174" t="n"/>
+      <c r="I17" s="174" t="n"/>
+      <c r="J17" s="212" t="n"/>
+      <c r="K17" s="176" t="n"/>
+      <c r="L17" s="176" t="n"/>
+      <c r="M17" s="176" t="n"/>
+      <c r="N17" s="176" t="n"/>
+      <c r="O17" s="176" t="n"/>
+      <c r="P17" s="176" t="n"/>
+      <c r="Q17" s="176" t="n"/>
+      <c r="R17" s="176" t="n"/>
+      <c r="S17" s="176" t="n"/>
+      <c r="T17" s="212" t="n"/>
+      <c r="U17" s="176" t="n"/>
+      <c r="V17" s="176" t="n"/>
+      <c r="W17" s="176" t="n"/>
+      <c r="X17" s="176" t="n"/>
+      <c r="Y17" s="176" t="n"/>
+      <c r="Z17" s="176" t="n"/>
+      <c r="AA17" s="176" t="n"/>
+      <c r="AB17" s="176" t="n"/>
+      <c r="AC17" s="176" t="n"/>
+      <c r="AD17" s="176" t="n"/>
+      <c r="AE17" s="176" t="n"/>
+      <c r="AF17" s="213" t="n"/>
+      <c r="AG17" s="176" t="n"/>
+      <c r="AH17" s="176" t="n"/>
+      <c r="AI17" s="176" t="n"/>
+      <c r="AJ17" s="176" t="n"/>
+      <c r="AK17" s="176" t="n"/>
+      <c r="AL17" s="176" t="n"/>
+      <c r="AM17" s="176" t="n"/>
+      <c r="AN17" s="176" t="n"/>
+      <c r="AO17" s="212" t="n"/>
+      <c r="AP17" s="176" t="n"/>
+      <c r="AQ17" s="176" t="n"/>
+      <c r="AR17" s="176" t="n"/>
+      <c r="AS17" s="176" t="n"/>
+      <c r="AT17" s="176" t="n"/>
+      <c r="AU17" s="176" t="n"/>
+      <c r="AV17" s="176" t="n"/>
+      <c r="AW17" s="176" t="n"/>
+      <c r="AX17" s="176" t="n"/>
+      <c r="AY17" s="176" t="n"/>
+      <c r="AZ17" s="176" t="n"/>
+      <c r="BA17" s="176" t="n"/>
+      <c r="BB17" s="176" t="n"/>
+      <c r="BC17" s="176" t="n"/>
+      <c r="BD17" s="178" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="88" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="164" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B18" s="99" t="n"/>
-      <c r="C18" s="99" t="n"/>
-      <c r="D18" s="99" t="n"/>
-      <c r="E18" s="99" t="n"/>
-      <c r="F18" s="99" t="n"/>
-      <c r="G18" s="99" t="n"/>
-      <c r="H18" s="99" t="n"/>
-      <c r="I18" s="99" t="n"/>
-      <c r="J18" s="99" t="n"/>
-      <c r="K18" s="99" t="n"/>
-      <c r="L18" s="99" t="n"/>
-      <c r="M18" s="99" t="n"/>
-      <c r="N18" s="99" t="n"/>
-      <c r="O18" s="99" t="n"/>
-      <c r="P18" s="99" t="n"/>
-      <c r="Q18" s="99" t="n"/>
-      <c r="R18" s="99" t="n"/>
-      <c r="S18" s="99" t="n"/>
-      <c r="T18" s="99" t="n"/>
-      <c r="U18" s="99" t="n"/>
-      <c r="V18" s="99" t="n"/>
-      <c r="W18" s="99" t="n"/>
-      <c r="X18" s="99" t="n"/>
-      <c r="Y18" s="99" t="n"/>
-      <c r="Z18" s="99" t="n"/>
-      <c r="AA18" s="99" t="n"/>
-      <c r="AB18" s="99" t="n"/>
-      <c r="AC18" s="99" t="n"/>
-      <c r="AD18" s="99" t="n"/>
-      <c r="AE18" s="99" t="n"/>
-      <c r="AF18" s="99" t="n"/>
-      <c r="AG18" s="99" t="n"/>
-      <c r="AH18" s="99" t="n"/>
-      <c r="AI18" s="99" t="n"/>
-      <c r="AJ18" s="99" t="n"/>
-      <c r="AK18" s="99" t="n"/>
-      <c r="AL18" s="99" t="n"/>
-      <c r="AM18" s="99" t="n"/>
-      <c r="AN18" s="99" t="n"/>
-      <c r="AO18" s="99" t="n"/>
-      <c r="AP18" s="99" t="n"/>
-      <c r="AQ18" s="99" t="n"/>
-      <c r="AR18" s="99" t="n"/>
-      <c r="AS18" s="99" t="n"/>
-      <c r="AT18" s="99" t="n"/>
-      <c r="AU18" s="99" t="n"/>
-      <c r="AV18" s="99" t="n"/>
-      <c r="AW18" s="99" t="n"/>
-      <c r="AX18" s="99" t="n"/>
-      <c r="AY18" s="99" t="n"/>
-      <c r="AZ18" s="99" t="n"/>
-      <c r="BA18" s="99" t="n"/>
-      <c r="BB18" s="99" t="n"/>
-      <c r="BC18" s="99" t="n"/>
-      <c r="BD18" s="100" t="n"/>
+      <c r="B18" s="165" t="n"/>
+      <c r="C18" s="165" t="n"/>
+      <c r="D18" s="165" t="n"/>
+      <c r="E18" s="165" t="n"/>
+      <c r="F18" s="165" t="n"/>
+      <c r="G18" s="165" t="n"/>
+      <c r="H18" s="165" t="n"/>
+      <c r="I18" s="165" t="n"/>
+      <c r="J18" s="165" t="n"/>
+      <c r="K18" s="165" t="n"/>
+      <c r="L18" s="165" t="n"/>
+      <c r="M18" s="165" t="n"/>
+      <c r="N18" s="165" t="n"/>
+      <c r="O18" s="165" t="n"/>
+      <c r="P18" s="165" t="n"/>
+      <c r="Q18" s="165" t="n"/>
+      <c r="R18" s="165" t="n"/>
+      <c r="S18" s="165" t="n"/>
+      <c r="T18" s="165" t="n"/>
+      <c r="U18" s="165" t="n"/>
+      <c r="V18" s="165" t="n"/>
+      <c r="W18" s="165" t="n"/>
+      <c r="X18" s="165" t="n"/>
+      <c r="Y18" s="165" t="n"/>
+      <c r="Z18" s="165" t="n"/>
+      <c r="AA18" s="165" t="n"/>
+      <c r="AB18" s="165" t="n"/>
+      <c r="AC18" s="165" t="n"/>
+      <c r="AD18" s="165" t="n"/>
+      <c r="AE18" s="165" t="n"/>
+      <c r="AF18" s="165" t="n"/>
+      <c r="AG18" s="165" t="n"/>
+      <c r="AH18" s="165" t="n"/>
+      <c r="AI18" s="165" t="n"/>
+      <c r="AJ18" s="165" t="n"/>
+      <c r="AK18" s="165" t="n"/>
+      <c r="AL18" s="165" t="n"/>
+      <c r="AM18" s="165" t="n"/>
+      <c r="AN18" s="165" t="n"/>
+      <c r="AO18" s="165" t="n"/>
+      <c r="AP18" s="165" t="n"/>
+      <c r="AQ18" s="165" t="n"/>
+      <c r="AR18" s="165" t="n"/>
+      <c r="AS18" s="165" t="n"/>
+      <c r="AT18" s="165" t="n"/>
+      <c r="AU18" s="165" t="n"/>
+      <c r="AV18" s="165" t="n"/>
+      <c r="AW18" s="165" t="n"/>
+      <c r="AX18" s="165" t="n"/>
+      <c r="AY18" s="165" t="n"/>
+      <c r="AZ18" s="165" t="n"/>
+      <c r="BA18" s="165" t="n"/>
+      <c r="BB18" s="165" t="n"/>
+      <c r="BC18" s="165" t="n"/>
+      <c r="BD18" s="166" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="61">
+  <mergeCells count="60">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="AQ3:AV3"/>
     <mergeCell ref="A8:J8"/>
@@ -4191,7 +5064,6 @@
     <mergeCell ref="AO17:BD17"/>
     <mergeCell ref="J14:S14"/>
     <mergeCell ref="AO11:BD11"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="T16:AE16"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="J13:S13"/>
@@ -4232,6 +5104,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4303,1074 +5176,1164 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="54" t="n"/>
-      <c r="B1" s="118" t="n"/>
-      <c r="C1" s="118" t="n"/>
-      <c r="D1" s="118" t="n"/>
-      <c r="E1" s="118" t="n"/>
-      <c r="F1" s="118" t="n"/>
-      <c r="G1" s="118" t="n"/>
-      <c r="H1" s="118" t="n"/>
-      <c r="I1" s="118" t="n"/>
-      <c r="J1" s="118" t="n"/>
-      <c r="K1" s="118" t="n"/>
-      <c r="L1" s="56" t="inlineStr">
+      <c r="A1" s="125" t="n"/>
+      <c r="B1" s="126" t="n"/>
+      <c r="C1" s="126" t="n"/>
+      <c r="D1" s="126" t="n"/>
+      <c r="E1" s="126" t="n"/>
+      <c r="F1" s="126" t="n"/>
+      <c r="G1" s="126" t="n"/>
+      <c r="H1" s="126" t="n"/>
+      <c r="I1" s="126" t="n"/>
+      <c r="J1" s="126" t="n"/>
+      <c r="K1" s="127" t="n"/>
+      <c r="L1" s="128" t="inlineStr">
         <is>
           <t>COMPETENCE ASSESSMENT — EVIDENCE REFERENCE REGISTER</t>
         </is>
       </c>
-      <c r="M1" s="118" t="n"/>
-      <c r="N1" s="118" t="n"/>
-      <c r="O1" s="118" t="n"/>
-      <c r="P1" s="118" t="n"/>
-      <c r="Q1" s="118" t="n"/>
-      <c r="R1" s="118" t="n"/>
-      <c r="S1" s="118" t="n"/>
-      <c r="T1" s="118" t="n"/>
-      <c r="U1" s="118" t="n"/>
-      <c r="V1" s="118" t="n"/>
-      <c r="W1" s="118" t="n"/>
-      <c r="X1" s="118" t="n"/>
-      <c r="Y1" s="118" t="n"/>
-      <c r="Z1" s="118" t="n"/>
-      <c r="AA1" s="118" t="n"/>
-      <c r="AB1" s="118" t="n"/>
-      <c r="AC1" s="118" t="n"/>
-      <c r="AD1" s="118" t="n"/>
-      <c r="AE1" s="118" t="n"/>
-      <c r="AF1" s="118" t="n"/>
-      <c r="AG1" s="118" t="n"/>
-      <c r="AH1" s="118" t="n"/>
-      <c r="AI1" s="118" t="n"/>
-      <c r="AJ1" s="118" t="n"/>
-      <c r="AK1" s="118" t="n"/>
-      <c r="AL1" s="118" t="n"/>
-      <c r="AM1" s="118" t="n"/>
-      <c r="AN1" s="118" t="n"/>
-      <c r="AO1" s="118" t="n"/>
-      <c r="AP1" s="118" t="n"/>
-      <c r="AQ1" s="57" t="inlineStr">
+      <c r="M1" s="129" t="n"/>
+      <c r="N1" s="129" t="n"/>
+      <c r="O1" s="129" t="n"/>
+      <c r="P1" s="129" t="n"/>
+      <c r="Q1" s="129" t="n"/>
+      <c r="R1" s="129" t="n"/>
+      <c r="S1" s="129" t="n"/>
+      <c r="T1" s="129" t="n"/>
+      <c r="U1" s="129" t="n"/>
+      <c r="V1" s="129" t="n"/>
+      <c r="W1" s="129" t="n"/>
+      <c r="X1" s="129" t="n"/>
+      <c r="Y1" s="129" t="n"/>
+      <c r="Z1" s="129" t="n"/>
+      <c r="AA1" s="129" t="n"/>
+      <c r="AB1" s="129" t="n"/>
+      <c r="AC1" s="129" t="n"/>
+      <c r="AD1" s="129" t="n"/>
+      <c r="AE1" s="129" t="n"/>
+      <c r="AF1" s="129" t="n"/>
+      <c r="AG1" s="129" t="n"/>
+      <c r="AH1" s="129" t="n"/>
+      <c r="AI1" s="129" t="n"/>
+      <c r="AJ1" s="129" t="n"/>
+      <c r="AK1" s="129" t="n"/>
+      <c r="AL1" s="129" t="n"/>
+      <c r="AM1" s="129" t="n"/>
+      <c r="AN1" s="129" t="n"/>
+      <c r="AO1" s="129" t="n"/>
+      <c r="AP1" s="130" t="n"/>
+      <c r="AQ1" s="131" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="119" t="n"/>
-      <c r="AS1" s="119" t="n"/>
-      <c r="AT1" s="119" t="n"/>
-      <c r="AU1" s="119" t="n"/>
-      <c r="AV1" s="120" t="n"/>
-      <c r="AW1" s="60" t="inlineStr">
+      <c r="AR1" s="132" t="n"/>
+      <c r="AS1" s="132" t="n"/>
+      <c r="AT1" s="132" t="n"/>
+      <c r="AU1" s="132" t="n"/>
+      <c r="AV1" s="133" t="n"/>
+      <c r="AW1" s="134" t="inlineStr">
         <is>
           <t>FRM-804</t>
         </is>
       </c>
-      <c r="AX1" s="119" t="n"/>
-      <c r="AY1" s="119" t="n"/>
-      <c r="AZ1" s="119" t="n"/>
-      <c r="BA1" s="119" t="n"/>
-      <c r="BB1" s="119" t="n"/>
-      <c r="BC1" s="119" t="n"/>
-      <c r="BD1" s="120" t="n"/>
+      <c r="AX1" s="135" t="n"/>
+      <c r="AY1" s="135" t="n"/>
+      <c r="AZ1" s="135" t="n"/>
+      <c r="BA1" s="135" t="n"/>
+      <c r="BB1" s="135" t="n"/>
+      <c r="BC1" s="135" t="n"/>
+      <c r="BD1" s="136" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="121" t="n"/>
-      <c r="L2" s="121" t="n"/>
-      <c r="AQ2" s="63" t="inlineStr">
+      <c r="A2" s="137" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
+      <c r="G2" s="53" t="n"/>
+      <c r="H2" s="53" t="n"/>
+      <c r="I2" s="53" t="n"/>
+      <c r="J2" s="53" t="n"/>
+      <c r="K2" s="138" t="n"/>
+      <c r="L2" s="139" t="n"/>
+      <c r="M2" s="140" t="n"/>
+      <c r="N2" s="140" t="n"/>
+      <c r="O2" s="140" t="n"/>
+      <c r="P2" s="140" t="n"/>
+      <c r="Q2" s="140" t="n"/>
+      <c r="R2" s="140" t="n"/>
+      <c r="S2" s="140" t="n"/>
+      <c r="T2" s="140" t="n"/>
+      <c r="U2" s="140" t="n"/>
+      <c r="V2" s="140" t="n"/>
+      <c r="W2" s="140" t="n"/>
+      <c r="X2" s="140" t="n"/>
+      <c r="Y2" s="140" t="n"/>
+      <c r="Z2" s="140" t="n"/>
+      <c r="AA2" s="140" t="n"/>
+      <c r="AB2" s="140" t="n"/>
+      <c r="AC2" s="140" t="n"/>
+      <c r="AD2" s="140" t="n"/>
+      <c r="AE2" s="140" t="n"/>
+      <c r="AF2" s="140" t="n"/>
+      <c r="AG2" s="140" t="n"/>
+      <c r="AH2" s="140" t="n"/>
+      <c r="AI2" s="140" t="n"/>
+      <c r="AJ2" s="140" t="n"/>
+      <c r="AK2" s="140" t="n"/>
+      <c r="AL2" s="140" t="n"/>
+      <c r="AM2" s="140" t="n"/>
+      <c r="AN2" s="140" t="n"/>
+      <c r="AO2" s="140" t="n"/>
+      <c r="AP2" s="141" t="n"/>
+      <c r="AQ2" s="142" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="122" t="n"/>
-      <c r="AS2" s="122" t="n"/>
-      <c r="AT2" s="122" t="n"/>
-      <c r="AU2" s="122" t="n"/>
-      <c r="AV2" s="123" t="n"/>
-      <c r="AW2" s="66" t="inlineStr">
+      <c r="AR2" s="143" t="n"/>
+      <c r="AS2" s="143" t="n"/>
+      <c r="AT2" s="143" t="n"/>
+      <c r="AU2" s="143" t="n"/>
+      <c r="AV2" s="144" t="n"/>
+      <c r="AW2" s="145" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="122" t="n"/>
-      <c r="AY2" s="122" t="n"/>
-      <c r="AZ2" s="122" t="n"/>
-      <c r="BA2" s="122" t="n"/>
-      <c r="BB2" s="122" t="n"/>
-      <c r="BC2" s="122" t="n"/>
-      <c r="BD2" s="123" t="n"/>
+      <c r="AX2" s="146" t="n"/>
+      <c r="AY2" s="146" t="n"/>
+      <c r="AZ2" s="146" t="n"/>
+      <c r="BA2" s="146" t="n"/>
+      <c r="BB2" s="146" t="n"/>
+      <c r="BC2" s="146" t="n"/>
+      <c r="BD2" s="147" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="121" t="n"/>
-      <c r="L3" s="124" t="n"/>
-      <c r="M3" s="122" t="n"/>
-      <c r="N3" s="122" t="n"/>
-      <c r="O3" s="122" t="n"/>
-      <c r="P3" s="122" t="n"/>
-      <c r="Q3" s="122" t="n"/>
-      <c r="R3" s="122" t="n"/>
-      <c r="S3" s="122" t="n"/>
-      <c r="T3" s="122" t="n"/>
-      <c r="U3" s="122" t="n"/>
-      <c r="V3" s="122" t="n"/>
-      <c r="W3" s="122" t="n"/>
-      <c r="X3" s="122" t="n"/>
-      <c r="Y3" s="122" t="n"/>
-      <c r="Z3" s="122" t="n"/>
-      <c r="AA3" s="122" t="n"/>
-      <c r="AB3" s="122" t="n"/>
-      <c r="AC3" s="122" t="n"/>
-      <c r="AD3" s="122" t="n"/>
-      <c r="AE3" s="122" t="n"/>
-      <c r="AF3" s="122" t="n"/>
-      <c r="AG3" s="122" t="n"/>
-      <c r="AH3" s="122" t="n"/>
-      <c r="AI3" s="122" t="n"/>
-      <c r="AJ3" s="122" t="n"/>
-      <c r="AK3" s="122" t="n"/>
-      <c r="AL3" s="122" t="n"/>
-      <c r="AM3" s="122" t="n"/>
-      <c r="AN3" s="122" t="n"/>
-      <c r="AO3" s="122" t="n"/>
-      <c r="AP3" s="122" t="n"/>
-      <c r="AQ3" s="63" t="inlineStr">
+      <c r="A3" s="137" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="138" t="n"/>
+      <c r="L3" s="139" t="n"/>
+      <c r="M3" s="140" t="n"/>
+      <c r="N3" s="140" t="n"/>
+      <c r="O3" s="140" t="n"/>
+      <c r="P3" s="140" t="n"/>
+      <c r="Q3" s="140" t="n"/>
+      <c r="R3" s="140" t="n"/>
+      <c r="S3" s="140" t="n"/>
+      <c r="T3" s="140" t="n"/>
+      <c r="U3" s="140" t="n"/>
+      <c r="V3" s="140" t="n"/>
+      <c r="W3" s="140" t="n"/>
+      <c r="X3" s="140" t="n"/>
+      <c r="Y3" s="140" t="n"/>
+      <c r="Z3" s="140" t="n"/>
+      <c r="AA3" s="140" t="n"/>
+      <c r="AB3" s="140" t="n"/>
+      <c r="AC3" s="140" t="n"/>
+      <c r="AD3" s="140" t="n"/>
+      <c r="AE3" s="140" t="n"/>
+      <c r="AF3" s="140" t="n"/>
+      <c r="AG3" s="140" t="n"/>
+      <c r="AH3" s="140" t="n"/>
+      <c r="AI3" s="140" t="n"/>
+      <c r="AJ3" s="140" t="n"/>
+      <c r="AK3" s="140" t="n"/>
+      <c r="AL3" s="140" t="n"/>
+      <c r="AM3" s="140" t="n"/>
+      <c r="AN3" s="140" t="n"/>
+      <c r="AO3" s="140" t="n"/>
+      <c r="AP3" s="141" t="n"/>
+      <c r="AQ3" s="142" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="122" t="n"/>
-      <c r="AS3" s="122" t="n"/>
-      <c r="AT3" s="122" t="n"/>
-      <c r="AU3" s="122" t="n"/>
-      <c r="AV3" s="123" t="n"/>
-      <c r="AW3" s="66" t="inlineStr">
+      <c r="AR3" s="143" t="n"/>
+      <c r="AS3" s="143" t="n"/>
+      <c r="AT3" s="143" t="n"/>
+      <c r="AU3" s="143" t="n"/>
+      <c r="AV3" s="144" t="n"/>
+      <c r="AW3" s="145" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="122" t="n"/>
-      <c r="AY3" s="122" t="n"/>
-      <c r="AZ3" s="122" t="n"/>
-      <c r="BA3" s="122" t="n"/>
-      <c r="BB3" s="122" t="n"/>
-      <c r="BC3" s="122" t="n"/>
-      <c r="BD3" s="123" t="n"/>
+      <c r="AX3" s="146" t="n"/>
+      <c r="AY3" s="146" t="n"/>
+      <c r="AZ3" s="146" t="n"/>
+      <c r="BA3" s="146" t="n"/>
+      <c r="BB3" s="146" t="n"/>
+      <c r="BC3" s="146" t="n"/>
+      <c r="BD3" s="147" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="121" t="n"/>
-      <c r="L4" s="68" t="inlineStr">
+      <c r="A4" s="137" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="138" t="n"/>
+      <c r="L4" s="148" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="63" t="inlineStr">
+      <c r="M4" s="149" t="n"/>
+      <c r="N4" s="149" t="n"/>
+      <c r="O4" s="149" t="n"/>
+      <c r="P4" s="149" t="n"/>
+      <c r="Q4" s="149" t="n"/>
+      <c r="R4" s="149" t="n"/>
+      <c r="S4" s="149" t="n"/>
+      <c r="T4" s="149" t="n"/>
+      <c r="U4" s="149" t="n"/>
+      <c r="V4" s="149" t="n"/>
+      <c r="W4" s="149" t="n"/>
+      <c r="X4" s="149" t="n"/>
+      <c r="Y4" s="149" t="n"/>
+      <c r="Z4" s="149" t="n"/>
+      <c r="AA4" s="149" t="n"/>
+      <c r="AB4" s="149" t="n"/>
+      <c r="AC4" s="149" t="n"/>
+      <c r="AD4" s="149" t="n"/>
+      <c r="AE4" s="149" t="n"/>
+      <c r="AF4" s="149" t="n"/>
+      <c r="AG4" s="149" t="n"/>
+      <c r="AH4" s="149" t="n"/>
+      <c r="AI4" s="149" t="n"/>
+      <c r="AJ4" s="149" t="n"/>
+      <c r="AK4" s="149" t="n"/>
+      <c r="AL4" s="149" t="n"/>
+      <c r="AM4" s="149" t="n"/>
+      <c r="AN4" s="149" t="n"/>
+      <c r="AO4" s="149" t="n"/>
+      <c r="AP4" s="150" t="n"/>
+      <c r="AQ4" s="142" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="122" t="n"/>
-      <c r="AS4" s="122" t="n"/>
-      <c r="AT4" s="122" t="n"/>
-      <c r="AU4" s="122" t="n"/>
-      <c r="AV4" s="123" t="n"/>
-      <c r="AW4" s="66" t="inlineStr">
+      <c r="AR4" s="143" t="n"/>
+      <c r="AS4" s="143" t="n"/>
+      <c r="AT4" s="143" t="n"/>
+      <c r="AU4" s="143" t="n"/>
+      <c r="AV4" s="144" t="n"/>
+      <c r="AW4" s="145" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="122" t="n"/>
-      <c r="AY4" s="122" t="n"/>
-      <c r="AZ4" s="122" t="n"/>
-      <c r="BA4" s="122" t="n"/>
-      <c r="BB4" s="122" t="n"/>
-      <c r="BC4" s="122" t="n"/>
-      <c r="BD4" s="123" t="n"/>
+      <c r="AX4" s="146" t="n"/>
+      <c r="AY4" s="146" t="n"/>
+      <c r="AZ4" s="146" t="n"/>
+      <c r="BA4" s="146" t="n"/>
+      <c r="BB4" s="146" t="n"/>
+      <c r="BC4" s="146" t="n"/>
+      <c r="BD4" s="147" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="124" t="n"/>
-      <c r="B5" s="122" t="n"/>
-      <c r="C5" s="122" t="n"/>
-      <c r="D5" s="122" t="n"/>
-      <c r="E5" s="122" t="n"/>
-      <c r="F5" s="122" t="n"/>
-      <c r="G5" s="122" t="n"/>
-      <c r="H5" s="122" t="n"/>
-      <c r="I5" s="122" t="n"/>
-      <c r="J5" s="122" t="n"/>
-      <c r="K5" s="122" t="n"/>
-      <c r="L5" s="69" t="inlineStr">
+      <c r="A5" s="151" t="n"/>
+      <c r="B5" s="152" t="n"/>
+      <c r="C5" s="152" t="n"/>
+      <c r="D5" s="152" t="n"/>
+      <c r="E5" s="152" t="n"/>
+      <c r="F5" s="152" t="n"/>
+      <c r="G5" s="152" t="n"/>
+      <c r="H5" s="152" t="n"/>
+      <c r="I5" s="152" t="n"/>
+      <c r="J5" s="152" t="n"/>
+      <c r="K5" s="153" t="n"/>
+      <c r="L5" s="154" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="122" t="n"/>
-      <c r="N5" s="122" t="n"/>
-      <c r="O5" s="122" t="n"/>
-      <c r="P5" s="122" t="n"/>
-      <c r="Q5" s="122" t="n"/>
-      <c r="R5" s="122" t="n"/>
-      <c r="S5" s="122" t="n"/>
-      <c r="T5" s="122" t="n"/>
-      <c r="U5" s="122" t="n"/>
-      <c r="V5" s="122" t="n"/>
-      <c r="W5" s="122" t="n"/>
-      <c r="X5" s="122" t="n"/>
-      <c r="Y5" s="122" t="n"/>
-      <c r="Z5" s="122" t="n"/>
-      <c r="AA5" s="122" t="n"/>
-      <c r="AB5" s="122" t="n"/>
-      <c r="AC5" s="122" t="n"/>
-      <c r="AD5" s="122" t="n"/>
-      <c r="AE5" s="122" t="n"/>
-      <c r="AF5" s="122" t="n"/>
-      <c r="AG5" s="122" t="n"/>
-      <c r="AH5" s="122" t="n"/>
-      <c r="AI5" s="122" t="n"/>
-      <c r="AJ5" s="122" t="n"/>
-      <c r="AK5" s="122" t="n"/>
-      <c r="AL5" s="122" t="n"/>
-      <c r="AM5" s="122" t="n"/>
-      <c r="AN5" s="122" t="n"/>
-      <c r="AO5" s="122" t="n"/>
-      <c r="AP5" s="122" t="n"/>
-      <c r="AQ5" s="63" t="inlineStr">
+      <c r="M5" s="155" t="n"/>
+      <c r="N5" s="155" t="n"/>
+      <c r="O5" s="155" t="n"/>
+      <c r="P5" s="155" t="n"/>
+      <c r="Q5" s="155" t="n"/>
+      <c r="R5" s="155" t="n"/>
+      <c r="S5" s="155" t="n"/>
+      <c r="T5" s="155" t="n"/>
+      <c r="U5" s="155" t="n"/>
+      <c r="V5" s="155" t="n"/>
+      <c r="W5" s="155" t="n"/>
+      <c r="X5" s="155" t="n"/>
+      <c r="Y5" s="155" t="n"/>
+      <c r="Z5" s="155" t="n"/>
+      <c r="AA5" s="155" t="n"/>
+      <c r="AB5" s="155" t="n"/>
+      <c r="AC5" s="155" t="n"/>
+      <c r="AD5" s="155" t="n"/>
+      <c r="AE5" s="155" t="n"/>
+      <c r="AF5" s="155" t="n"/>
+      <c r="AG5" s="155" t="n"/>
+      <c r="AH5" s="155" t="n"/>
+      <c r="AI5" s="155" t="n"/>
+      <c r="AJ5" s="155" t="n"/>
+      <c r="AK5" s="155" t="n"/>
+      <c r="AL5" s="155" t="n"/>
+      <c r="AM5" s="155" t="n"/>
+      <c r="AN5" s="155" t="n"/>
+      <c r="AO5" s="155" t="n"/>
+      <c r="AP5" s="156" t="n"/>
+      <c r="AQ5" s="157" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="122" t="n"/>
-      <c r="AS5" s="122" t="n"/>
-      <c r="AT5" s="122" t="n"/>
-      <c r="AU5" s="122" t="n"/>
-      <c r="AV5" s="123" t="n"/>
-      <c r="AW5" s="66" t="inlineStr">
+      <c r="AR5" s="158" t="n"/>
+      <c r="AS5" s="158" t="n"/>
+      <c r="AT5" s="158" t="n"/>
+      <c r="AU5" s="158" t="n"/>
+      <c r="AV5" s="159" t="n"/>
+      <c r="AW5" s="160" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="122" t="n"/>
-      <c r="AY5" s="122" t="n"/>
-      <c r="AZ5" s="122" t="n"/>
-      <c r="BA5" s="122" t="n"/>
-      <c r="BB5" s="122" t="n"/>
-      <c r="BC5" s="122" t="n"/>
-      <c r="BD5" s="123" t="n"/>
+      <c r="AX5" s="161" t="n"/>
+      <c r="AY5" s="161" t="n"/>
+      <c r="AZ5" s="161" t="n"/>
+      <c r="BA5" s="161" t="n"/>
+      <c r="BB5" s="161" t="n"/>
+      <c r="BC5" s="161" t="n"/>
+      <c r="BD5" s="162" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="70" t="n"/>
-      <c r="B6" s="117" t="n"/>
-      <c r="C6" s="117" t="n"/>
-      <c r="D6" s="117" t="n"/>
-      <c r="E6" s="117" t="n"/>
-      <c r="F6" s="117" t="n"/>
-      <c r="G6" s="117" t="n"/>
-      <c r="H6" s="117" t="n"/>
-      <c r="I6" s="117" t="n"/>
-      <c r="J6" s="117" t="n"/>
-      <c r="K6" s="117" t="n"/>
-      <c r="L6" s="117" t="n"/>
-      <c r="M6" s="117" t="n"/>
-      <c r="N6" s="117" t="n"/>
-      <c r="O6" s="117" t="n"/>
-      <c r="P6" s="117" t="n"/>
-      <c r="Q6" s="117" t="n"/>
-      <c r="R6" s="117" t="n"/>
-      <c r="S6" s="117" t="n"/>
-      <c r="T6" s="117" t="n"/>
-      <c r="U6" s="117" t="n"/>
-      <c r="V6" s="117" t="n"/>
-      <c r="W6" s="117" t="n"/>
-      <c r="X6" s="117" t="n"/>
-      <c r="Y6" s="117" t="n"/>
-      <c r="Z6" s="117" t="n"/>
-      <c r="AA6" s="117" t="n"/>
-      <c r="AB6" s="117" t="n"/>
-      <c r="AC6" s="117" t="n"/>
-      <c r="AD6" s="117" t="n"/>
-      <c r="AE6" s="117" t="n"/>
-      <c r="AF6" s="117" t="n"/>
-      <c r="AG6" s="117" t="n"/>
-      <c r="AH6" s="117" t="n"/>
-      <c r="AI6" s="117" t="n"/>
-      <c r="AJ6" s="117" t="n"/>
-      <c r="AK6" s="117" t="n"/>
-      <c r="AL6" s="117" t="n"/>
-      <c r="AM6" s="117" t="n"/>
-      <c r="AN6" s="117" t="n"/>
-      <c r="AO6" s="117" t="n"/>
-      <c r="AP6" s="117" t="n"/>
-      <c r="AQ6" s="117" t="n"/>
-      <c r="AR6" s="117" t="n"/>
-      <c r="AS6" s="117" t="n"/>
-      <c r="AT6" s="117" t="n"/>
-      <c r="AU6" s="117" t="n"/>
-      <c r="AV6" s="117" t="n"/>
-      <c r="AW6" s="117" t="n"/>
-      <c r="AX6" s="117" t="n"/>
-      <c r="AY6" s="117" t="n"/>
-      <c r="AZ6" s="117" t="n"/>
-      <c r="BA6" s="117" t="n"/>
-      <c r="BB6" s="117" t="n"/>
-      <c r="BC6" s="117" t="n"/>
-      <c r="BD6" s="117" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="163" t="n"/>
+      <c r="B6" s="163" t="n"/>
+      <c r="C6" s="163" t="n"/>
+      <c r="D6" s="163" t="n"/>
+      <c r="E6" s="163" t="n"/>
+      <c r="F6" s="163" t="n"/>
+      <c r="G6" s="163" t="n"/>
+      <c r="H6" s="163" t="n"/>
+      <c r="I6" s="163" t="n"/>
+      <c r="J6" s="163" t="n"/>
+      <c r="K6" s="163" t="n"/>
+      <c r="L6" s="163" t="n"/>
+      <c r="M6" s="163" t="n"/>
+      <c r="N6" s="163" t="n"/>
+      <c r="O6" s="163" t="n"/>
+      <c r="P6" s="163" t="n"/>
+      <c r="Q6" s="163" t="n"/>
+      <c r="R6" s="163" t="n"/>
+      <c r="S6" s="163" t="n"/>
+      <c r="T6" s="163" t="n"/>
+      <c r="U6" s="163" t="n"/>
+      <c r="V6" s="163" t="n"/>
+      <c r="W6" s="163" t="n"/>
+      <c r="X6" s="163" t="n"/>
+      <c r="Y6" s="163" t="n"/>
+      <c r="Z6" s="163" t="n"/>
+      <c r="AA6" s="163" t="n"/>
+      <c r="AB6" s="163" t="n"/>
+      <c r="AC6" s="163" t="n"/>
+      <c r="AD6" s="163" t="n"/>
+      <c r="AE6" s="163" t="n"/>
+      <c r="AF6" s="163" t="n"/>
+      <c r="AG6" s="163" t="n"/>
+      <c r="AH6" s="163" t="n"/>
+      <c r="AI6" s="163" t="n"/>
+      <c r="AJ6" s="163" t="n"/>
+      <c r="AK6" s="163" t="n"/>
+      <c r="AL6" s="163" t="n"/>
+      <c r="AM6" s="163" t="n"/>
+      <c r="AN6" s="163" t="n"/>
+      <c r="AO6" s="163" t="n"/>
+      <c r="AP6" s="163" t="n"/>
+      <c r="AQ6" s="163" t="n"/>
+      <c r="AR6" s="163" t="n"/>
+      <c r="AS6" s="163" t="n"/>
+      <c r="AT6" s="163" t="n"/>
+      <c r="AU6" s="163" t="n"/>
+      <c r="AV6" s="163" t="n"/>
+      <c r="AW6" s="163" t="n"/>
+      <c r="AX6" s="163" t="n"/>
+      <c r="AY6" s="163" t="n"/>
+      <c r="AZ6" s="163" t="n"/>
+      <c r="BA6" s="163" t="n"/>
+      <c r="BB6" s="163" t="n"/>
+      <c r="BC6" s="163" t="n"/>
+      <c r="BD6" s="163" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="71" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="119" t="n"/>
-      <c r="C7" s="119" t="n"/>
-      <c r="D7" s="119" t="n"/>
-      <c r="E7" s="119" t="n"/>
-      <c r="F7" s="119" t="n"/>
-      <c r="G7" s="119" t="n"/>
-      <c r="H7" s="119" t="n"/>
-      <c r="I7" s="119" t="n"/>
-      <c r="J7" s="119" t="n"/>
-      <c r="K7" s="119" t="n"/>
-      <c r="L7" s="119" t="n"/>
-      <c r="M7" s="119" t="n"/>
-      <c r="N7" s="119" t="n"/>
-      <c r="O7" s="119" t="n"/>
-      <c r="P7" s="119" t="n"/>
-      <c r="Q7" s="119" t="n"/>
-      <c r="R7" s="119" t="n"/>
-      <c r="S7" s="119" t="n"/>
-      <c r="T7" s="119" t="n"/>
-      <c r="U7" s="119" t="n"/>
-      <c r="V7" s="119" t="n"/>
-      <c r="W7" s="119" t="n"/>
-      <c r="X7" s="119" t="n"/>
-      <c r="Y7" s="119" t="n"/>
-      <c r="Z7" s="119" t="n"/>
-      <c r="AA7" s="119" t="n"/>
-      <c r="AB7" s="119" t="n"/>
-      <c r="AC7" s="119" t="n"/>
-      <c r="AD7" s="119" t="n"/>
-      <c r="AE7" s="119" t="n"/>
-      <c r="AF7" s="119" t="n"/>
-      <c r="AG7" s="119" t="n"/>
-      <c r="AH7" s="119" t="n"/>
-      <c r="AI7" s="119" t="n"/>
-      <c r="AJ7" s="119" t="n"/>
-      <c r="AK7" s="119" t="n"/>
-      <c r="AL7" s="119" t="n"/>
-      <c r="AM7" s="119" t="n"/>
-      <c r="AN7" s="119" t="n"/>
-      <c r="AO7" s="119" t="n"/>
-      <c r="AP7" s="119" t="n"/>
-      <c r="AQ7" s="119" t="n"/>
-      <c r="AR7" s="119" t="n"/>
-      <c r="AS7" s="119" t="n"/>
-      <c r="AT7" s="119" t="n"/>
-      <c r="AU7" s="119" t="n"/>
-      <c r="AV7" s="119" t="n"/>
-      <c r="AW7" s="119" t="n"/>
-      <c r="AX7" s="119" t="n"/>
-      <c r="AY7" s="119" t="n"/>
-      <c r="AZ7" s="119" t="n"/>
-      <c r="BA7" s="119" t="n"/>
-      <c r="BB7" s="119" t="n"/>
-      <c r="BC7" s="119" t="n"/>
-      <c r="BD7" s="120" t="n"/>
+      <c r="B7" s="165" t="n"/>
+      <c r="C7" s="165" t="n"/>
+      <c r="D7" s="165" t="n"/>
+      <c r="E7" s="165" t="n"/>
+      <c r="F7" s="165" t="n"/>
+      <c r="G7" s="165" t="n"/>
+      <c r="H7" s="165" t="n"/>
+      <c r="I7" s="165" t="n"/>
+      <c r="J7" s="165" t="n"/>
+      <c r="K7" s="165" t="n"/>
+      <c r="L7" s="165" t="n"/>
+      <c r="M7" s="165" t="n"/>
+      <c r="N7" s="165" t="n"/>
+      <c r="O7" s="165" t="n"/>
+      <c r="P7" s="165" t="n"/>
+      <c r="Q7" s="165" t="n"/>
+      <c r="R7" s="165" t="n"/>
+      <c r="S7" s="165" t="n"/>
+      <c r="T7" s="165" t="n"/>
+      <c r="U7" s="165" t="n"/>
+      <c r="V7" s="165" t="n"/>
+      <c r="W7" s="165" t="n"/>
+      <c r="X7" s="165" t="n"/>
+      <c r="Y7" s="165" t="n"/>
+      <c r="Z7" s="165" t="n"/>
+      <c r="AA7" s="165" t="n"/>
+      <c r="AB7" s="165" t="n"/>
+      <c r="AC7" s="165" t="n"/>
+      <c r="AD7" s="165" t="n"/>
+      <c r="AE7" s="165" t="n"/>
+      <c r="AF7" s="165" t="n"/>
+      <c r="AG7" s="165" t="n"/>
+      <c r="AH7" s="165" t="n"/>
+      <c r="AI7" s="165" t="n"/>
+      <c r="AJ7" s="165" t="n"/>
+      <c r="AK7" s="165" t="n"/>
+      <c r="AL7" s="165" t="n"/>
+      <c r="AM7" s="165" t="n"/>
+      <c r="AN7" s="165" t="n"/>
+      <c r="AO7" s="165" t="n"/>
+      <c r="AP7" s="165" t="n"/>
+      <c r="AQ7" s="165" t="n"/>
+      <c r="AR7" s="165" t="n"/>
+      <c r="AS7" s="165" t="n"/>
+      <c r="AT7" s="165" t="n"/>
+      <c r="AU7" s="165" t="n"/>
+      <c r="AV7" s="165" t="n"/>
+      <c r="AW7" s="165" t="n"/>
+      <c r="AX7" s="165" t="n"/>
+      <c r="AY7" s="165" t="n"/>
+      <c r="AZ7" s="165" t="n"/>
+      <c r="BA7" s="165" t="n"/>
+      <c r="BB7" s="165" t="n"/>
+      <c r="BC7" s="165" t="n"/>
+      <c r="BD7" s="166" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="72" t="inlineStr">
+      <c r="A8" s="167" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="105" t="n"/>
-      <c r="C8" s="105" t="n"/>
-      <c r="D8" s="105" t="n"/>
-      <c r="E8" s="105" t="n"/>
-      <c r="F8" s="105" t="n"/>
-      <c r="G8" s="105" t="n"/>
-      <c r="H8" s="105" t="n"/>
-      <c r="I8" s="105" t="n"/>
-      <c r="J8" s="106" t="n"/>
-      <c r="K8" s="89" t="inlineStr">
+      <c r="B8" s="168" t="n"/>
+      <c r="C8" s="168" t="n"/>
+      <c r="D8" s="168" t="n"/>
+      <c r="E8" s="168" t="n"/>
+      <c r="F8" s="168" t="n"/>
+      <c r="G8" s="168" t="n"/>
+      <c r="H8" s="168" t="n"/>
+      <c r="I8" s="168" t="n"/>
+      <c r="J8" s="168" t="n"/>
+      <c r="K8" s="196" t="inlineStr">
         <is>
           <t>M365 evidence stays SSOT; workbook captures the formal study / gate / decision record while annex rules, criteria dictionaries and authority matrices are referenced, not re-keyed.</t>
         </is>
       </c>
-      <c r="L8" s="105" t="n"/>
-      <c r="M8" s="105" t="n"/>
-      <c r="N8" s="105" t="n"/>
-      <c r="O8" s="105" t="n"/>
-      <c r="P8" s="105" t="n"/>
-      <c r="Q8" s="105" t="n"/>
-      <c r="R8" s="105" t="n"/>
-      <c r="S8" s="105" t="n"/>
-      <c r="T8" s="105" t="n"/>
-      <c r="U8" s="105" t="n"/>
-      <c r="V8" s="105" t="n"/>
-      <c r="W8" s="105" t="n"/>
-      <c r="X8" s="105" t="n"/>
-      <c r="Y8" s="105" t="n"/>
-      <c r="Z8" s="105" t="n"/>
-      <c r="AA8" s="105" t="n"/>
-      <c r="AB8" s="106" t="n"/>
-      <c r="AC8" s="20" t="inlineStr"/>
-      <c r="AD8" s="90" t="n"/>
-      <c r="AE8" s="90" t="n"/>
-      <c r="AF8" s="90" t="n"/>
-      <c r="AG8" s="90" t="n"/>
-      <c r="AH8" s="90" t="n"/>
-      <c r="AI8" s="90" t="n"/>
-      <c r="AJ8" s="90" t="n"/>
-      <c r="AK8" s="90" t="n"/>
-      <c r="AL8" s="90" t="n"/>
-      <c r="AM8" s="20" t="inlineStr"/>
-      <c r="AN8" s="90" t="n"/>
-      <c r="AO8" s="90" t="n"/>
-      <c r="AP8" s="90" t="n"/>
-      <c r="AQ8" s="90" t="n"/>
-      <c r="AR8" s="90" t="n"/>
-      <c r="AS8" s="90" t="n"/>
-      <c r="AT8" s="90" t="n"/>
-      <c r="AU8" s="90" t="n"/>
-      <c r="AV8" s="90" t="n"/>
-      <c r="AW8" s="90" t="n"/>
-      <c r="AX8" s="90" t="n"/>
-      <c r="AY8" s="90" t="n"/>
-      <c r="AZ8" s="90" t="n"/>
-      <c r="BA8" s="90" t="n"/>
-      <c r="BB8" s="90" t="n"/>
-      <c r="BC8" s="90" t="n"/>
-      <c r="BD8" s="90" t="n"/>
+      <c r="L8" s="168" t="n"/>
+      <c r="M8" s="168" t="n"/>
+      <c r="N8" s="168" t="n"/>
+      <c r="O8" s="168" t="n"/>
+      <c r="P8" s="168" t="n"/>
+      <c r="Q8" s="168" t="n"/>
+      <c r="R8" s="168" t="n"/>
+      <c r="S8" s="168" t="n"/>
+      <c r="T8" s="168" t="n"/>
+      <c r="U8" s="168" t="n"/>
+      <c r="V8" s="168" t="n"/>
+      <c r="W8" s="168" t="n"/>
+      <c r="X8" s="168" t="n"/>
+      <c r="Y8" s="168" t="n"/>
+      <c r="Z8" s="168" t="n"/>
+      <c r="AA8" s="168" t="n"/>
+      <c r="AB8" s="168" t="n"/>
+      <c r="AC8" s="197" t="inlineStr"/>
+      <c r="AD8" s="168" t="n"/>
+      <c r="AE8" s="168" t="n"/>
+      <c r="AF8" s="168" t="n"/>
+      <c r="AG8" s="168" t="n"/>
+      <c r="AH8" s="168" t="n"/>
+      <c r="AI8" s="168" t="n"/>
+      <c r="AJ8" s="168" t="n"/>
+      <c r="AK8" s="168" t="n"/>
+      <c r="AL8" s="168" t="n"/>
+      <c r="AM8" s="197" t="inlineStr"/>
+      <c r="AN8" s="168" t="n"/>
+      <c r="AO8" s="168" t="n"/>
+      <c r="AP8" s="168" t="n"/>
+      <c r="AQ8" s="168" t="n"/>
+      <c r="AR8" s="168" t="n"/>
+      <c r="AS8" s="168" t="n"/>
+      <c r="AT8" s="168" t="n"/>
+      <c r="AU8" s="168" t="n"/>
+      <c r="AV8" s="168" t="n"/>
+      <c r="AW8" s="168" t="n"/>
+      <c r="AX8" s="168" t="n"/>
+      <c r="AY8" s="168" t="n"/>
+      <c r="AZ8" s="168" t="n"/>
+      <c r="BA8" s="168" t="n"/>
+      <c r="BB8" s="168" t="n"/>
+      <c r="BC8" s="168" t="n"/>
+      <c r="BD8" s="198" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+      <c r="A9" s="173" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="105" t="n"/>
-      <c r="C9" s="105" t="n"/>
-      <c r="D9" s="105" t="n"/>
-      <c r="E9" s="105" t="n"/>
-      <c r="F9" s="105" t="n"/>
-      <c r="G9" s="105" t="n"/>
-      <c r="H9" s="105" t="n"/>
-      <c r="I9" s="105" t="n"/>
-      <c r="J9" s="106" t="n"/>
-      <c r="K9" s="89" t="inlineStr">
+      <c r="B9" s="174" t="n"/>
+      <c r="C9" s="174" t="n"/>
+      <c r="D9" s="174" t="n"/>
+      <c r="E9" s="174" t="n"/>
+      <c r="F9" s="174" t="n"/>
+      <c r="G9" s="174" t="n"/>
+      <c r="H9" s="174" t="n"/>
+      <c r="I9" s="174" t="n"/>
+      <c r="J9" s="174" t="n"/>
+      <c r="K9" s="199" t="inlineStr">
         <is>
           <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
         </is>
       </c>
-      <c r="L9" s="105" t="n"/>
-      <c r="M9" s="105" t="n"/>
-      <c r="N9" s="105" t="n"/>
-      <c r="O9" s="105" t="n"/>
-      <c r="P9" s="105" t="n"/>
-      <c r="Q9" s="105" t="n"/>
-      <c r="R9" s="105" t="n"/>
-      <c r="S9" s="105" t="n"/>
-      <c r="T9" s="105" t="n"/>
-      <c r="U9" s="105" t="n"/>
-      <c r="V9" s="105" t="n"/>
-      <c r="W9" s="105" t="n"/>
-      <c r="X9" s="105" t="n"/>
-      <c r="Y9" s="105" t="n"/>
-      <c r="Z9" s="105" t="n"/>
-      <c r="AA9" s="105" t="n"/>
-      <c r="AB9" s="106" t="n"/>
-      <c r="AC9" s="20" t="inlineStr"/>
-      <c r="AD9" s="90" t="n"/>
-      <c r="AE9" s="90" t="n"/>
-      <c r="AF9" s="90" t="n"/>
-      <c r="AG9" s="90" t="n"/>
-      <c r="AH9" s="90" t="n"/>
-      <c r="AI9" s="90" t="n"/>
-      <c r="AJ9" s="90" t="n"/>
-      <c r="AK9" s="90" t="n"/>
-      <c r="AL9" s="90" t="n"/>
-      <c r="AM9" s="20" t="inlineStr"/>
-      <c r="AN9" s="90" t="n"/>
-      <c r="AO9" s="90" t="n"/>
-      <c r="AP9" s="90" t="n"/>
-      <c r="AQ9" s="90" t="n"/>
-      <c r="AR9" s="90" t="n"/>
-      <c r="AS9" s="90" t="n"/>
-      <c r="AT9" s="90" t="n"/>
-      <c r="AU9" s="90" t="n"/>
-      <c r="AV9" s="90" t="n"/>
-      <c r="AW9" s="90" t="n"/>
-      <c r="AX9" s="90" t="n"/>
-      <c r="AY9" s="90" t="n"/>
-      <c r="AZ9" s="90" t="n"/>
-      <c r="BA9" s="90" t="n"/>
-      <c r="BB9" s="90" t="n"/>
-      <c r="BC9" s="90" t="n"/>
-      <c r="BD9" s="90" t="n"/>
+      <c r="L9" s="174" t="n"/>
+      <c r="M9" s="174" t="n"/>
+      <c r="N9" s="174" t="n"/>
+      <c r="O9" s="174" t="n"/>
+      <c r="P9" s="174" t="n"/>
+      <c r="Q9" s="174" t="n"/>
+      <c r="R9" s="174" t="n"/>
+      <c r="S9" s="174" t="n"/>
+      <c r="T9" s="174" t="n"/>
+      <c r="U9" s="174" t="n"/>
+      <c r="V9" s="174" t="n"/>
+      <c r="W9" s="174" t="n"/>
+      <c r="X9" s="174" t="n"/>
+      <c r="Y9" s="174" t="n"/>
+      <c r="Z9" s="174" t="n"/>
+      <c r="AA9" s="174" t="n"/>
+      <c r="AB9" s="174" t="n"/>
+      <c r="AC9" s="200" t="inlineStr"/>
+      <c r="AD9" s="174" t="n"/>
+      <c r="AE9" s="174" t="n"/>
+      <c r="AF9" s="174" t="n"/>
+      <c r="AG9" s="174" t="n"/>
+      <c r="AH9" s="174" t="n"/>
+      <c r="AI9" s="174" t="n"/>
+      <c r="AJ9" s="174" t="n"/>
+      <c r="AK9" s="174" t="n"/>
+      <c r="AL9" s="174" t="n"/>
+      <c r="AM9" s="200" t="inlineStr"/>
+      <c r="AN9" s="174" t="n"/>
+      <c r="AO9" s="174" t="n"/>
+      <c r="AP9" s="174" t="n"/>
+      <c r="AQ9" s="174" t="n"/>
+      <c r="AR9" s="174" t="n"/>
+      <c r="AS9" s="174" t="n"/>
+      <c r="AT9" s="174" t="n"/>
+      <c r="AU9" s="174" t="n"/>
+      <c r="AV9" s="174" t="n"/>
+      <c r="AW9" s="174" t="n"/>
+      <c r="AX9" s="174" t="n"/>
+      <c r="AY9" s="174" t="n"/>
+      <c r="AZ9" s="174" t="n"/>
+      <c r="BA9" s="174" t="n"/>
+      <c r="BB9" s="174" t="n"/>
+      <c r="BC9" s="174" t="n"/>
+      <c r="BD9" s="201" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="71" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="164" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B10" s="105" t="n"/>
-      <c r="C10" s="105" t="n"/>
-      <c r="D10" s="105" t="n"/>
-      <c r="E10" s="105" t="n"/>
-      <c r="F10" s="105" t="n"/>
-      <c r="G10" s="105" t="n"/>
-      <c r="H10" s="105" t="n"/>
-      <c r="I10" s="105" t="n"/>
-      <c r="J10" s="105" t="n"/>
-      <c r="K10" s="105" t="n"/>
-      <c r="L10" s="105" t="n"/>
-      <c r="M10" s="105" t="n"/>
-      <c r="N10" s="105" t="n"/>
-      <c r="O10" s="105" t="n"/>
-      <c r="P10" s="105" t="n"/>
-      <c r="Q10" s="105" t="n"/>
-      <c r="R10" s="105" t="n"/>
-      <c r="S10" s="105" t="n"/>
-      <c r="T10" s="105" t="n"/>
-      <c r="U10" s="105" t="n"/>
-      <c r="V10" s="105" t="n"/>
-      <c r="W10" s="105" t="n"/>
-      <c r="X10" s="105" t="n"/>
-      <c r="Y10" s="105" t="n"/>
-      <c r="Z10" s="105" t="n"/>
-      <c r="AA10" s="105" t="n"/>
-      <c r="AB10" s="105" t="n"/>
-      <c r="AC10" s="105" t="n"/>
-      <c r="AD10" s="105" t="n"/>
-      <c r="AE10" s="105" t="n"/>
-      <c r="AF10" s="105" t="n"/>
-      <c r="AG10" s="105" t="n"/>
-      <c r="AH10" s="105" t="n"/>
-      <c r="AI10" s="105" t="n"/>
-      <c r="AJ10" s="105" t="n"/>
-      <c r="AK10" s="105" t="n"/>
-      <c r="AL10" s="105" t="n"/>
-      <c r="AM10" s="105" t="n"/>
-      <c r="AN10" s="105" t="n"/>
-      <c r="AO10" s="105" t="n"/>
-      <c r="AP10" s="105" t="n"/>
-      <c r="AQ10" s="105" t="n"/>
-      <c r="AR10" s="105" t="n"/>
-      <c r="AS10" s="105" t="n"/>
-      <c r="AT10" s="105" t="n"/>
-      <c r="AU10" s="105" t="n"/>
-      <c r="AV10" s="105" t="n"/>
-      <c r="AW10" s="105" t="n"/>
-      <c r="AX10" s="105" t="n"/>
-      <c r="AY10" s="105" t="n"/>
-      <c r="AZ10" s="105" t="n"/>
-      <c r="BA10" s="105" t="n"/>
-      <c r="BB10" s="105" t="n"/>
-      <c r="BC10" s="105" t="n"/>
-      <c r="BD10" s="106" t="n"/>
+      <c r="B10" s="165" t="n"/>
+      <c r="C10" s="165" t="n"/>
+      <c r="D10" s="165" t="n"/>
+      <c r="E10" s="165" t="n"/>
+      <c r="F10" s="165" t="n"/>
+      <c r="G10" s="165" t="n"/>
+      <c r="H10" s="165" t="n"/>
+      <c r="I10" s="165" t="n"/>
+      <c r="J10" s="165" t="n"/>
+      <c r="K10" s="165" t="n"/>
+      <c r="L10" s="165" t="n"/>
+      <c r="M10" s="165" t="n"/>
+      <c r="N10" s="165" t="n"/>
+      <c r="O10" s="165" t="n"/>
+      <c r="P10" s="165" t="n"/>
+      <c r="Q10" s="165" t="n"/>
+      <c r="R10" s="165" t="n"/>
+      <c r="S10" s="165" t="n"/>
+      <c r="T10" s="165" t="n"/>
+      <c r="U10" s="165" t="n"/>
+      <c r="V10" s="165" t="n"/>
+      <c r="W10" s="165" t="n"/>
+      <c r="X10" s="165" t="n"/>
+      <c r="Y10" s="165" t="n"/>
+      <c r="Z10" s="165" t="n"/>
+      <c r="AA10" s="165" t="n"/>
+      <c r="AB10" s="165" t="n"/>
+      <c r="AC10" s="165" t="n"/>
+      <c r="AD10" s="165" t="n"/>
+      <c r="AE10" s="165" t="n"/>
+      <c r="AF10" s="165" t="n"/>
+      <c r="AG10" s="165" t="n"/>
+      <c r="AH10" s="165" t="n"/>
+      <c r="AI10" s="165" t="n"/>
+      <c r="AJ10" s="165" t="n"/>
+      <c r="AK10" s="165" t="n"/>
+      <c r="AL10" s="165" t="n"/>
+      <c r="AM10" s="165" t="n"/>
+      <c r="AN10" s="165" t="n"/>
+      <c r="AO10" s="165" t="n"/>
+      <c r="AP10" s="165" t="n"/>
+      <c r="AQ10" s="165" t="n"/>
+      <c r="AR10" s="165" t="n"/>
+      <c r="AS10" s="165" t="n"/>
+      <c r="AT10" s="165" t="n"/>
+      <c r="AU10" s="165" t="n"/>
+      <c r="AV10" s="165" t="n"/>
+      <c r="AW10" s="165" t="n"/>
+      <c r="AX10" s="165" t="n"/>
+      <c r="AY10" s="165" t="n"/>
+      <c r="AZ10" s="165" t="n"/>
+      <c r="BA10" s="165" t="n"/>
+      <c r="BB10" s="165" t="n"/>
+      <c r="BC10" s="165" t="n"/>
+      <c r="BD10" s="166" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="91" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="202" t="inlineStr">
         <is>
           <t>Evidence ID</t>
         </is>
       </c>
-      <c r="B11" s="105" t="n"/>
-      <c r="C11" s="105" t="n"/>
-      <c r="D11" s="105" t="n"/>
-      <c r="E11" s="105" t="n"/>
-      <c r="F11" s="105" t="n"/>
-      <c r="G11" s="105" t="n"/>
-      <c r="H11" s="106" t="n"/>
-      <c r="I11" s="91" t="inlineStr">
+      <c r="B11" s="203" t="n"/>
+      <c r="C11" s="203" t="n"/>
+      <c r="D11" s="203" t="n"/>
+      <c r="E11" s="203" t="n"/>
+      <c r="F11" s="203" t="n"/>
+      <c r="G11" s="203" t="n"/>
+      <c r="H11" s="203" t="n"/>
+      <c r="I11" s="204" t="inlineStr">
         <is>
           <t>Related Record</t>
         </is>
       </c>
-      <c r="J11" s="105" t="n"/>
-      <c r="K11" s="105" t="n"/>
-      <c r="L11" s="105" t="n"/>
-      <c r="M11" s="106" t="n"/>
-      <c r="N11" s="91" t="inlineStr">
+      <c r="J11" s="203" t="n"/>
+      <c r="K11" s="203" t="n"/>
+      <c r="L11" s="203" t="n"/>
+      <c r="M11" s="203" t="n"/>
+      <c r="N11" s="204" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O11" s="105" t="n"/>
-      <c r="P11" s="105" t="n"/>
-      <c r="Q11" s="105" t="n"/>
-      <c r="R11" s="105" t="n"/>
-      <c r="S11" s="105" t="n"/>
-      <c r="T11" s="105" t="n"/>
-      <c r="U11" s="105" t="n"/>
-      <c r="V11" s="105" t="n"/>
-      <c r="W11" s="105" t="n"/>
-      <c r="X11" s="106" t="n"/>
-      <c r="Y11" s="91" t="inlineStr">
+      <c r="O11" s="203" t="n"/>
+      <c r="P11" s="203" t="n"/>
+      <c r="Q11" s="203" t="n"/>
+      <c r="R11" s="203" t="n"/>
+      <c r="S11" s="203" t="n"/>
+      <c r="T11" s="203" t="n"/>
+      <c r="U11" s="203" t="n"/>
+      <c r="V11" s="203" t="n"/>
+      <c r="W11" s="203" t="n"/>
+      <c r="X11" s="203" t="n"/>
+      <c r="Y11" s="204" t="inlineStr">
         <is>
           <t>Source System</t>
         </is>
       </c>
-      <c r="Z11" s="105" t="n"/>
-      <c r="AA11" s="105" t="n"/>
-      <c r="AB11" s="105" t="n"/>
-      <c r="AC11" s="106" t="n"/>
-      <c r="AD11" s="91" t="inlineStr">
+      <c r="Z11" s="203" t="n"/>
+      <c r="AA11" s="203" t="n"/>
+      <c r="AB11" s="203" t="n"/>
+      <c r="AC11" s="203" t="n"/>
+      <c r="AD11" s="204" t="inlineStr">
         <is>
           <t>Reference Path or Link</t>
         </is>
       </c>
-      <c r="AE11" s="105" t="n"/>
-      <c r="AF11" s="105" t="n"/>
-      <c r="AG11" s="105" t="n"/>
-      <c r="AH11" s="105" t="n"/>
-      <c r="AI11" s="105" t="n"/>
-      <c r="AJ11" s="106" t="n"/>
-      <c r="AK11" s="91" t="inlineStr">
+      <c r="AE11" s="203" t="n"/>
+      <c r="AF11" s="203" t="n"/>
+      <c r="AG11" s="203" t="n"/>
+      <c r="AH11" s="203" t="n"/>
+      <c r="AI11" s="203" t="n"/>
+      <c r="AJ11" s="203" t="n"/>
+      <c r="AK11" s="204" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AL11" s="105" t="n"/>
-      <c r="AM11" s="105" t="n"/>
-      <c r="AN11" s="105" t="n"/>
-      <c r="AO11" s="105" t="n"/>
-      <c r="AP11" s="106" t="n"/>
-      <c r="AQ11" s="91" t="inlineStr">
+      <c r="AL11" s="203" t="n"/>
+      <c r="AM11" s="203" t="n"/>
+      <c r="AN11" s="203" t="n"/>
+      <c r="AO11" s="203" t="n"/>
+      <c r="AP11" s="203" t="n"/>
+      <c r="AQ11" s="204" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="AR11" s="105" t="n"/>
-      <c r="AS11" s="105" t="n"/>
-      <c r="AT11" s="105" t="n"/>
-      <c r="AU11" s="106" t="n"/>
-      <c r="AV11" s="91" t="inlineStr">
+      <c r="AR11" s="203" t="n"/>
+      <c r="AS11" s="203" t="n"/>
+      <c r="AT11" s="203" t="n"/>
+      <c r="AU11" s="203" t="n"/>
+      <c r="AV11" s="204" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AW11" s="105" t="n"/>
-      <c r="AX11" s="105" t="n"/>
-      <c r="AY11" s="105" t="n"/>
-      <c r="AZ11" s="105" t="n"/>
-      <c r="BA11" s="105" t="n"/>
-      <c r="BB11" s="105" t="n"/>
-      <c r="BC11" s="105" t="n"/>
-      <c r="BD11" s="106" t="n"/>
+      <c r="AW11" s="203" t="n"/>
+      <c r="AX11" s="203" t="n"/>
+      <c r="AY11" s="203" t="n"/>
+      <c r="AZ11" s="203" t="n"/>
+      <c r="BA11" s="203" t="n"/>
+      <c r="BB11" s="203" t="n"/>
+      <c r="BC11" s="203" t="n"/>
+      <c r="BD11" s="205" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="92" t="n"/>
-      <c r="B12" s="115" t="n"/>
-      <c r="C12" s="115" t="n"/>
-      <c r="D12" s="115" t="n"/>
-      <c r="E12" s="115" t="n"/>
-      <c r="F12" s="115" t="n"/>
-      <c r="G12" s="115" t="n"/>
-      <c r="H12" s="116" t="n"/>
-      <c r="I12" s="95" t="n"/>
-      <c r="J12" s="113" t="n"/>
-      <c r="K12" s="113" t="n"/>
-      <c r="L12" s="113" t="n"/>
-      <c r="M12" s="114" t="n"/>
-      <c r="N12" s="95" t="n"/>
-      <c r="O12" s="113" t="n"/>
-      <c r="P12" s="113" t="n"/>
-      <c r="Q12" s="113" t="n"/>
-      <c r="R12" s="113" t="n"/>
-      <c r="S12" s="113" t="n"/>
-      <c r="T12" s="113" t="n"/>
-      <c r="U12" s="113" t="n"/>
-      <c r="V12" s="113" t="n"/>
-      <c r="W12" s="113" t="n"/>
-      <c r="X12" s="114" t="n"/>
-      <c r="Y12" s="95" t="n"/>
-      <c r="Z12" s="113" t="n"/>
-      <c r="AA12" s="113" t="n"/>
-      <c r="AB12" s="113" t="n"/>
-      <c r="AC12" s="114" t="n"/>
-      <c r="AD12" s="95" t="n"/>
-      <c r="AE12" s="113" t="n"/>
-      <c r="AF12" s="113" t="n"/>
-      <c r="AG12" s="113" t="n"/>
-      <c r="AH12" s="113" t="n"/>
-      <c r="AI12" s="113" t="n"/>
-      <c r="AJ12" s="114" t="n"/>
-      <c r="AK12" s="96" t="n"/>
-      <c r="AL12" s="113" t="n"/>
-      <c r="AM12" s="113" t="n"/>
-      <c r="AN12" s="113" t="n"/>
-      <c r="AO12" s="113" t="n"/>
-      <c r="AP12" s="114" t="n"/>
-      <c r="AQ12" s="95" t="n"/>
-      <c r="AR12" s="113" t="n"/>
-      <c r="AS12" s="113" t="n"/>
-      <c r="AT12" s="113" t="n"/>
-      <c r="AU12" s="114" t="n"/>
-      <c r="AV12" s="95" t="n"/>
-      <c r="AW12" s="113" t="n"/>
-      <c r="AX12" s="113" t="n"/>
-      <c r="AY12" s="113" t="n"/>
-      <c r="AZ12" s="113" t="n"/>
-      <c r="BA12" s="113" t="n"/>
-      <c r="BB12" s="113" t="n"/>
-      <c r="BC12" s="113" t="n"/>
-      <c r="BD12" s="114" t="n"/>
+      <c r="A12" s="206" t="n"/>
+      <c r="B12" s="168" t="n"/>
+      <c r="C12" s="168" t="n"/>
+      <c r="D12" s="168" t="n"/>
+      <c r="E12" s="168" t="n"/>
+      <c r="F12" s="168" t="n"/>
+      <c r="G12" s="168" t="n"/>
+      <c r="H12" s="168" t="n"/>
+      <c r="I12" s="169" t="n"/>
+      <c r="J12" s="170" t="n"/>
+      <c r="K12" s="170" t="n"/>
+      <c r="L12" s="170" t="n"/>
+      <c r="M12" s="170" t="n"/>
+      <c r="N12" s="169" t="n"/>
+      <c r="O12" s="170" t="n"/>
+      <c r="P12" s="170" t="n"/>
+      <c r="Q12" s="170" t="n"/>
+      <c r="R12" s="170" t="n"/>
+      <c r="S12" s="170" t="n"/>
+      <c r="T12" s="170" t="n"/>
+      <c r="U12" s="170" t="n"/>
+      <c r="V12" s="170" t="n"/>
+      <c r="W12" s="170" t="n"/>
+      <c r="X12" s="170" t="n"/>
+      <c r="Y12" s="169" t="n"/>
+      <c r="Z12" s="170" t="n"/>
+      <c r="AA12" s="170" t="n"/>
+      <c r="AB12" s="170" t="n"/>
+      <c r="AC12" s="170" t="n"/>
+      <c r="AD12" s="169" t="n"/>
+      <c r="AE12" s="170" t="n"/>
+      <c r="AF12" s="170" t="n"/>
+      <c r="AG12" s="170" t="n"/>
+      <c r="AH12" s="170" t="n"/>
+      <c r="AI12" s="170" t="n"/>
+      <c r="AJ12" s="170" t="n"/>
+      <c r="AK12" s="207" t="n"/>
+      <c r="AL12" s="170" t="n"/>
+      <c r="AM12" s="170" t="n"/>
+      <c r="AN12" s="170" t="n"/>
+      <c r="AO12" s="170" t="n"/>
+      <c r="AP12" s="170" t="n"/>
+      <c r="AQ12" s="169" t="n"/>
+      <c r="AR12" s="170" t="n"/>
+      <c r="AS12" s="170" t="n"/>
+      <c r="AT12" s="170" t="n"/>
+      <c r="AU12" s="170" t="n"/>
+      <c r="AV12" s="169" t="n"/>
+      <c r="AW12" s="170" t="n"/>
+      <c r="AX12" s="170" t="n"/>
+      <c r="AY12" s="170" t="n"/>
+      <c r="AZ12" s="170" t="n"/>
+      <c r="BA12" s="170" t="n"/>
+      <c r="BB12" s="170" t="n"/>
+      <c r="BC12" s="170" t="n"/>
+      <c r="BD12" s="172" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="92" t="n"/>
-      <c r="B13" s="115" t="n"/>
-      <c r="C13" s="115" t="n"/>
-      <c r="D13" s="115" t="n"/>
-      <c r="E13" s="115" t="n"/>
-      <c r="F13" s="115" t="n"/>
-      <c r="G13" s="115" t="n"/>
-      <c r="H13" s="116" t="n"/>
-      <c r="I13" s="97" t="n"/>
-      <c r="J13" s="113" t="n"/>
-      <c r="K13" s="113" t="n"/>
-      <c r="L13" s="113" t="n"/>
-      <c r="M13" s="114" t="n"/>
-      <c r="N13" s="97" t="n"/>
-      <c r="O13" s="113" t="n"/>
-      <c r="P13" s="113" t="n"/>
-      <c r="Q13" s="113" t="n"/>
-      <c r="R13" s="113" t="n"/>
-      <c r="S13" s="113" t="n"/>
-      <c r="T13" s="113" t="n"/>
-      <c r="U13" s="113" t="n"/>
-      <c r="V13" s="113" t="n"/>
-      <c r="W13" s="113" t="n"/>
-      <c r="X13" s="114" t="n"/>
-      <c r="Y13" s="97" t="n"/>
-      <c r="Z13" s="113" t="n"/>
-      <c r="AA13" s="113" t="n"/>
-      <c r="AB13" s="113" t="n"/>
-      <c r="AC13" s="114" t="n"/>
-      <c r="AD13" s="97" t="n"/>
-      <c r="AE13" s="113" t="n"/>
-      <c r="AF13" s="113" t="n"/>
-      <c r="AG13" s="113" t="n"/>
-      <c r="AH13" s="113" t="n"/>
-      <c r="AI13" s="113" t="n"/>
-      <c r="AJ13" s="114" t="n"/>
-      <c r="AK13" s="96" t="n"/>
-      <c r="AL13" s="113" t="n"/>
-      <c r="AM13" s="113" t="n"/>
-      <c r="AN13" s="113" t="n"/>
-      <c r="AO13" s="113" t="n"/>
-      <c r="AP13" s="114" t="n"/>
-      <c r="AQ13" s="97" t="n"/>
-      <c r="AR13" s="113" t="n"/>
-      <c r="AS13" s="113" t="n"/>
-      <c r="AT13" s="113" t="n"/>
-      <c r="AU13" s="114" t="n"/>
-      <c r="AV13" s="97" t="n"/>
-      <c r="AW13" s="113" t="n"/>
-      <c r="AX13" s="113" t="n"/>
-      <c r="AY13" s="113" t="n"/>
-      <c r="AZ13" s="113" t="n"/>
-      <c r="BA13" s="113" t="n"/>
-      <c r="BB13" s="113" t="n"/>
-      <c r="BC13" s="113" t="n"/>
-      <c r="BD13" s="114" t="n"/>
+      <c r="A13" s="208" t="n"/>
+      <c r="B13" s="58" t="n"/>
+      <c r="C13" s="58" t="n"/>
+      <c r="D13" s="58" t="n"/>
+      <c r="E13" s="58" t="n"/>
+      <c r="F13" s="58" t="n"/>
+      <c r="G13" s="58" t="n"/>
+      <c r="H13" s="58" t="n"/>
+      <c r="I13" s="209" t="n"/>
+      <c r="J13" s="183" t="n"/>
+      <c r="K13" s="183" t="n"/>
+      <c r="L13" s="183" t="n"/>
+      <c r="M13" s="183" t="n"/>
+      <c r="N13" s="209" t="n"/>
+      <c r="O13" s="183" t="n"/>
+      <c r="P13" s="183" t="n"/>
+      <c r="Q13" s="183" t="n"/>
+      <c r="R13" s="183" t="n"/>
+      <c r="S13" s="183" t="n"/>
+      <c r="T13" s="183" t="n"/>
+      <c r="U13" s="183" t="n"/>
+      <c r="V13" s="183" t="n"/>
+      <c r="W13" s="183" t="n"/>
+      <c r="X13" s="183" t="n"/>
+      <c r="Y13" s="209" t="n"/>
+      <c r="Z13" s="183" t="n"/>
+      <c r="AA13" s="183" t="n"/>
+      <c r="AB13" s="183" t="n"/>
+      <c r="AC13" s="183" t="n"/>
+      <c r="AD13" s="209" t="n"/>
+      <c r="AE13" s="183" t="n"/>
+      <c r="AF13" s="183" t="n"/>
+      <c r="AG13" s="183" t="n"/>
+      <c r="AH13" s="183" t="n"/>
+      <c r="AI13" s="183" t="n"/>
+      <c r="AJ13" s="183" t="n"/>
+      <c r="AK13" s="210" t="n"/>
+      <c r="AL13" s="183" t="n"/>
+      <c r="AM13" s="183" t="n"/>
+      <c r="AN13" s="183" t="n"/>
+      <c r="AO13" s="183" t="n"/>
+      <c r="AP13" s="183" t="n"/>
+      <c r="AQ13" s="209" t="n"/>
+      <c r="AR13" s="183" t="n"/>
+      <c r="AS13" s="183" t="n"/>
+      <c r="AT13" s="183" t="n"/>
+      <c r="AU13" s="183" t="n"/>
+      <c r="AV13" s="209" t="n"/>
+      <c r="AW13" s="183" t="n"/>
+      <c r="AX13" s="183" t="n"/>
+      <c r="AY13" s="183" t="n"/>
+      <c r="AZ13" s="183" t="n"/>
+      <c r="BA13" s="183" t="n"/>
+      <c r="BB13" s="183" t="n"/>
+      <c r="BC13" s="183" t="n"/>
+      <c r="BD13" s="187" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="92" t="n"/>
-      <c r="B14" s="115" t="n"/>
-      <c r="C14" s="115" t="n"/>
-      <c r="D14" s="115" t="n"/>
-      <c r="E14" s="115" t="n"/>
-      <c r="F14" s="115" t="n"/>
-      <c r="G14" s="115" t="n"/>
-      <c r="H14" s="116" t="n"/>
-      <c r="I14" s="95" t="n"/>
-      <c r="J14" s="113" t="n"/>
-      <c r="K14" s="113" t="n"/>
-      <c r="L14" s="113" t="n"/>
-      <c r="M14" s="114" t="n"/>
-      <c r="N14" s="95" t="n"/>
-      <c r="O14" s="113" t="n"/>
-      <c r="P14" s="113" t="n"/>
-      <c r="Q14" s="113" t="n"/>
-      <c r="R14" s="113" t="n"/>
-      <c r="S14" s="113" t="n"/>
-      <c r="T14" s="113" t="n"/>
-      <c r="U14" s="113" t="n"/>
-      <c r="V14" s="113" t="n"/>
-      <c r="W14" s="113" t="n"/>
-      <c r="X14" s="114" t="n"/>
-      <c r="Y14" s="95" t="n"/>
-      <c r="Z14" s="113" t="n"/>
-      <c r="AA14" s="113" t="n"/>
-      <c r="AB14" s="113" t="n"/>
-      <c r="AC14" s="114" t="n"/>
-      <c r="AD14" s="95" t="n"/>
-      <c r="AE14" s="113" t="n"/>
-      <c r="AF14" s="113" t="n"/>
-      <c r="AG14" s="113" t="n"/>
-      <c r="AH14" s="113" t="n"/>
-      <c r="AI14" s="113" t="n"/>
-      <c r="AJ14" s="114" t="n"/>
-      <c r="AK14" s="96" t="n"/>
-      <c r="AL14" s="113" t="n"/>
-      <c r="AM14" s="113" t="n"/>
-      <c r="AN14" s="113" t="n"/>
-      <c r="AO14" s="113" t="n"/>
-      <c r="AP14" s="114" t="n"/>
-      <c r="AQ14" s="95" t="n"/>
-      <c r="AR14" s="113" t="n"/>
-      <c r="AS14" s="113" t="n"/>
-      <c r="AT14" s="113" t="n"/>
-      <c r="AU14" s="114" t="n"/>
-      <c r="AV14" s="95" t="n"/>
-      <c r="AW14" s="113" t="n"/>
-      <c r="AX14" s="113" t="n"/>
-      <c r="AY14" s="113" t="n"/>
-      <c r="AZ14" s="113" t="n"/>
-      <c r="BA14" s="113" t="n"/>
-      <c r="BB14" s="113" t="n"/>
-      <c r="BC14" s="113" t="n"/>
-      <c r="BD14" s="114" t="n"/>
+      <c r="A14" s="208" t="n"/>
+      <c r="B14" s="58" t="n"/>
+      <c r="C14" s="58" t="n"/>
+      <c r="D14" s="58" t="n"/>
+      <c r="E14" s="58" t="n"/>
+      <c r="F14" s="58" t="n"/>
+      <c r="G14" s="58" t="n"/>
+      <c r="H14" s="58" t="n"/>
+      <c r="I14" s="182" t="n"/>
+      <c r="J14" s="183" t="n"/>
+      <c r="K14" s="183" t="n"/>
+      <c r="L14" s="183" t="n"/>
+      <c r="M14" s="183" t="n"/>
+      <c r="N14" s="182" t="n"/>
+      <c r="O14" s="183" t="n"/>
+      <c r="P14" s="183" t="n"/>
+      <c r="Q14" s="183" t="n"/>
+      <c r="R14" s="183" t="n"/>
+      <c r="S14" s="183" t="n"/>
+      <c r="T14" s="183" t="n"/>
+      <c r="U14" s="183" t="n"/>
+      <c r="V14" s="183" t="n"/>
+      <c r="W14" s="183" t="n"/>
+      <c r="X14" s="183" t="n"/>
+      <c r="Y14" s="182" t="n"/>
+      <c r="Z14" s="183" t="n"/>
+      <c r="AA14" s="183" t="n"/>
+      <c r="AB14" s="183" t="n"/>
+      <c r="AC14" s="183" t="n"/>
+      <c r="AD14" s="182" t="n"/>
+      <c r="AE14" s="183" t="n"/>
+      <c r="AF14" s="183" t="n"/>
+      <c r="AG14" s="183" t="n"/>
+      <c r="AH14" s="183" t="n"/>
+      <c r="AI14" s="183" t="n"/>
+      <c r="AJ14" s="183" t="n"/>
+      <c r="AK14" s="210" t="n"/>
+      <c r="AL14" s="183" t="n"/>
+      <c r="AM14" s="183" t="n"/>
+      <c r="AN14" s="183" t="n"/>
+      <c r="AO14" s="183" t="n"/>
+      <c r="AP14" s="183" t="n"/>
+      <c r="AQ14" s="182" t="n"/>
+      <c r="AR14" s="183" t="n"/>
+      <c r="AS14" s="183" t="n"/>
+      <c r="AT14" s="183" t="n"/>
+      <c r="AU14" s="183" t="n"/>
+      <c r="AV14" s="182" t="n"/>
+      <c r="AW14" s="183" t="n"/>
+      <c r="AX14" s="183" t="n"/>
+      <c r="AY14" s="183" t="n"/>
+      <c r="AZ14" s="183" t="n"/>
+      <c r="BA14" s="183" t="n"/>
+      <c r="BB14" s="183" t="n"/>
+      <c r="BC14" s="183" t="n"/>
+      <c r="BD14" s="187" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="92" t="n"/>
-      <c r="B15" s="115" t="n"/>
-      <c r="C15" s="115" t="n"/>
-      <c r="D15" s="115" t="n"/>
-      <c r="E15" s="115" t="n"/>
-      <c r="F15" s="115" t="n"/>
-      <c r="G15" s="115" t="n"/>
-      <c r="H15" s="116" t="n"/>
-      <c r="I15" s="97" t="n"/>
-      <c r="J15" s="113" t="n"/>
-      <c r="K15" s="113" t="n"/>
-      <c r="L15" s="113" t="n"/>
-      <c r="M15" s="114" t="n"/>
-      <c r="N15" s="97" t="n"/>
-      <c r="O15" s="113" t="n"/>
-      <c r="P15" s="113" t="n"/>
-      <c r="Q15" s="113" t="n"/>
-      <c r="R15" s="113" t="n"/>
-      <c r="S15" s="113" t="n"/>
-      <c r="T15" s="113" t="n"/>
-      <c r="U15" s="113" t="n"/>
-      <c r="V15" s="113" t="n"/>
-      <c r="W15" s="113" t="n"/>
-      <c r="X15" s="114" t="n"/>
-      <c r="Y15" s="97" t="n"/>
-      <c r="Z15" s="113" t="n"/>
-      <c r="AA15" s="113" t="n"/>
-      <c r="AB15" s="113" t="n"/>
-      <c r="AC15" s="114" t="n"/>
-      <c r="AD15" s="97" t="n"/>
-      <c r="AE15" s="113" t="n"/>
-      <c r="AF15" s="113" t="n"/>
-      <c r="AG15" s="113" t="n"/>
-      <c r="AH15" s="113" t="n"/>
-      <c r="AI15" s="113" t="n"/>
-      <c r="AJ15" s="114" t="n"/>
-      <c r="AK15" s="96" t="n"/>
-      <c r="AL15" s="113" t="n"/>
-      <c r="AM15" s="113" t="n"/>
-      <c r="AN15" s="113" t="n"/>
-      <c r="AO15" s="113" t="n"/>
-      <c r="AP15" s="114" t="n"/>
-      <c r="AQ15" s="97" t="n"/>
-      <c r="AR15" s="113" t="n"/>
-      <c r="AS15" s="113" t="n"/>
-      <c r="AT15" s="113" t="n"/>
-      <c r="AU15" s="114" t="n"/>
-      <c r="AV15" s="97" t="n"/>
-      <c r="AW15" s="113" t="n"/>
-      <c r="AX15" s="113" t="n"/>
-      <c r="AY15" s="113" t="n"/>
-      <c r="AZ15" s="113" t="n"/>
-      <c r="BA15" s="113" t="n"/>
-      <c r="BB15" s="113" t="n"/>
-      <c r="BC15" s="113" t="n"/>
-      <c r="BD15" s="114" t="n"/>
+      <c r="A15" s="208" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="C15" s="58" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="58" t="n"/>
+      <c r="H15" s="58" t="n"/>
+      <c r="I15" s="209" t="n"/>
+      <c r="J15" s="183" t="n"/>
+      <c r="K15" s="183" t="n"/>
+      <c r="L15" s="183" t="n"/>
+      <c r="M15" s="183" t="n"/>
+      <c r="N15" s="209" t="n"/>
+      <c r="O15" s="183" t="n"/>
+      <c r="P15" s="183" t="n"/>
+      <c r="Q15" s="183" t="n"/>
+      <c r="R15" s="183" t="n"/>
+      <c r="S15" s="183" t="n"/>
+      <c r="T15" s="183" t="n"/>
+      <c r="U15" s="183" t="n"/>
+      <c r="V15" s="183" t="n"/>
+      <c r="W15" s="183" t="n"/>
+      <c r="X15" s="183" t="n"/>
+      <c r="Y15" s="209" t="n"/>
+      <c r="Z15" s="183" t="n"/>
+      <c r="AA15" s="183" t="n"/>
+      <c r="AB15" s="183" t="n"/>
+      <c r="AC15" s="183" t="n"/>
+      <c r="AD15" s="209" t="n"/>
+      <c r="AE15" s="183" t="n"/>
+      <c r="AF15" s="183" t="n"/>
+      <c r="AG15" s="183" t="n"/>
+      <c r="AH15" s="183" t="n"/>
+      <c r="AI15" s="183" t="n"/>
+      <c r="AJ15" s="183" t="n"/>
+      <c r="AK15" s="210" t="n"/>
+      <c r="AL15" s="183" t="n"/>
+      <c r="AM15" s="183" t="n"/>
+      <c r="AN15" s="183" t="n"/>
+      <c r="AO15" s="183" t="n"/>
+      <c r="AP15" s="183" t="n"/>
+      <c r="AQ15" s="209" t="n"/>
+      <c r="AR15" s="183" t="n"/>
+      <c r="AS15" s="183" t="n"/>
+      <c r="AT15" s="183" t="n"/>
+      <c r="AU15" s="183" t="n"/>
+      <c r="AV15" s="209" t="n"/>
+      <c r="AW15" s="183" t="n"/>
+      <c r="AX15" s="183" t="n"/>
+      <c r="AY15" s="183" t="n"/>
+      <c r="AZ15" s="183" t="n"/>
+      <c r="BA15" s="183" t="n"/>
+      <c r="BB15" s="183" t="n"/>
+      <c r="BC15" s="183" t="n"/>
+      <c r="BD15" s="187" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="92" t="n"/>
-      <c r="B16" s="115" t="n"/>
-      <c r="C16" s="115" t="n"/>
-      <c r="D16" s="115" t="n"/>
-      <c r="E16" s="115" t="n"/>
-      <c r="F16" s="115" t="n"/>
-      <c r="G16" s="115" t="n"/>
-      <c r="H16" s="116" t="n"/>
-      <c r="I16" s="95" t="n"/>
-      <c r="J16" s="113" t="n"/>
-      <c r="K16" s="113" t="n"/>
-      <c r="L16" s="113" t="n"/>
-      <c r="M16" s="114" t="n"/>
-      <c r="N16" s="95" t="n"/>
-      <c r="O16" s="113" t="n"/>
-      <c r="P16" s="113" t="n"/>
-      <c r="Q16" s="113" t="n"/>
-      <c r="R16" s="113" t="n"/>
-      <c r="S16" s="113" t="n"/>
-      <c r="T16" s="113" t="n"/>
-      <c r="U16" s="113" t="n"/>
-      <c r="V16" s="113" t="n"/>
-      <c r="W16" s="113" t="n"/>
-      <c r="X16" s="114" t="n"/>
-      <c r="Y16" s="95" t="n"/>
-      <c r="Z16" s="113" t="n"/>
-      <c r="AA16" s="113" t="n"/>
-      <c r="AB16" s="113" t="n"/>
-      <c r="AC16" s="114" t="n"/>
-      <c r="AD16" s="95" t="n"/>
-      <c r="AE16" s="113" t="n"/>
-      <c r="AF16" s="113" t="n"/>
-      <c r="AG16" s="113" t="n"/>
-      <c r="AH16" s="113" t="n"/>
-      <c r="AI16" s="113" t="n"/>
-      <c r="AJ16" s="114" t="n"/>
-      <c r="AK16" s="96" t="n"/>
-      <c r="AL16" s="113" t="n"/>
-      <c r="AM16" s="113" t="n"/>
-      <c r="AN16" s="113" t="n"/>
-      <c r="AO16" s="113" t="n"/>
-      <c r="AP16" s="114" t="n"/>
-      <c r="AQ16" s="95" t="n"/>
-      <c r="AR16" s="113" t="n"/>
-      <c r="AS16" s="113" t="n"/>
-      <c r="AT16" s="113" t="n"/>
-      <c r="AU16" s="114" t="n"/>
-      <c r="AV16" s="95" t="n"/>
-      <c r="AW16" s="113" t="n"/>
-      <c r="AX16" s="113" t="n"/>
-      <c r="AY16" s="113" t="n"/>
-      <c r="AZ16" s="113" t="n"/>
-      <c r="BA16" s="113" t="n"/>
-      <c r="BB16" s="113" t="n"/>
-      <c r="BC16" s="113" t="n"/>
-      <c r="BD16" s="114" t="n"/>
+      <c r="A16" s="208" t="n"/>
+      <c r="B16" s="58" t="n"/>
+      <c r="C16" s="58" t="n"/>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="58" t="n"/>
+      <c r="I16" s="182" t="n"/>
+      <c r="J16" s="183" t="n"/>
+      <c r="K16" s="183" t="n"/>
+      <c r="L16" s="183" t="n"/>
+      <c r="M16" s="183" t="n"/>
+      <c r="N16" s="182" t="n"/>
+      <c r="O16" s="183" t="n"/>
+      <c r="P16" s="183" t="n"/>
+      <c r="Q16" s="183" t="n"/>
+      <c r="R16" s="183" t="n"/>
+      <c r="S16" s="183" t="n"/>
+      <c r="T16" s="183" t="n"/>
+      <c r="U16" s="183" t="n"/>
+      <c r="V16" s="183" t="n"/>
+      <c r="W16" s="183" t="n"/>
+      <c r="X16" s="183" t="n"/>
+      <c r="Y16" s="182" t="n"/>
+      <c r="Z16" s="183" t="n"/>
+      <c r="AA16" s="183" t="n"/>
+      <c r="AB16" s="183" t="n"/>
+      <c r="AC16" s="183" t="n"/>
+      <c r="AD16" s="182" t="n"/>
+      <c r="AE16" s="183" t="n"/>
+      <c r="AF16" s="183" t="n"/>
+      <c r="AG16" s="183" t="n"/>
+      <c r="AH16" s="183" t="n"/>
+      <c r="AI16" s="183" t="n"/>
+      <c r="AJ16" s="183" t="n"/>
+      <c r="AK16" s="210" t="n"/>
+      <c r="AL16" s="183" t="n"/>
+      <c r="AM16" s="183" t="n"/>
+      <c r="AN16" s="183" t="n"/>
+      <c r="AO16" s="183" t="n"/>
+      <c r="AP16" s="183" t="n"/>
+      <c r="AQ16" s="182" t="n"/>
+      <c r="AR16" s="183" t="n"/>
+      <c r="AS16" s="183" t="n"/>
+      <c r="AT16" s="183" t="n"/>
+      <c r="AU16" s="183" t="n"/>
+      <c r="AV16" s="182" t="n"/>
+      <c r="AW16" s="183" t="n"/>
+      <c r="AX16" s="183" t="n"/>
+      <c r="AY16" s="183" t="n"/>
+      <c r="AZ16" s="183" t="n"/>
+      <c r="BA16" s="183" t="n"/>
+      <c r="BB16" s="183" t="n"/>
+      <c r="BC16" s="183" t="n"/>
+      <c r="BD16" s="187" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="92" t="n"/>
-      <c r="B17" s="115" t="n"/>
-      <c r="C17" s="115" t="n"/>
-      <c r="D17" s="115" t="n"/>
-      <c r="E17" s="115" t="n"/>
-      <c r="F17" s="115" t="n"/>
-      <c r="G17" s="115" t="n"/>
-      <c r="H17" s="116" t="n"/>
-      <c r="I17" s="97" t="n"/>
-      <c r="J17" s="113" t="n"/>
-      <c r="K17" s="113" t="n"/>
-      <c r="L17" s="113" t="n"/>
-      <c r="M17" s="114" t="n"/>
-      <c r="N17" s="97" t="n"/>
-      <c r="O17" s="113" t="n"/>
-      <c r="P17" s="113" t="n"/>
-      <c r="Q17" s="113" t="n"/>
-      <c r="R17" s="113" t="n"/>
-      <c r="S17" s="113" t="n"/>
-      <c r="T17" s="113" t="n"/>
-      <c r="U17" s="113" t="n"/>
-      <c r="V17" s="113" t="n"/>
-      <c r="W17" s="113" t="n"/>
-      <c r="X17" s="114" t="n"/>
-      <c r="Y17" s="97" t="n"/>
-      <c r="Z17" s="113" t="n"/>
-      <c r="AA17" s="113" t="n"/>
-      <c r="AB17" s="113" t="n"/>
-      <c r="AC17" s="114" t="n"/>
-      <c r="AD17" s="97" t="n"/>
-      <c r="AE17" s="113" t="n"/>
-      <c r="AF17" s="113" t="n"/>
-      <c r="AG17" s="113" t="n"/>
-      <c r="AH17" s="113" t="n"/>
-      <c r="AI17" s="113" t="n"/>
-      <c r="AJ17" s="114" t="n"/>
-      <c r="AK17" s="96" t="n"/>
-      <c r="AL17" s="113" t="n"/>
-      <c r="AM17" s="113" t="n"/>
-      <c r="AN17" s="113" t="n"/>
-      <c r="AO17" s="113" t="n"/>
-      <c r="AP17" s="114" t="n"/>
-      <c r="AQ17" s="97" t="n"/>
-      <c r="AR17" s="113" t="n"/>
-      <c r="AS17" s="113" t="n"/>
-      <c r="AT17" s="113" t="n"/>
-      <c r="AU17" s="114" t="n"/>
-      <c r="AV17" s="97" t="n"/>
-      <c r="AW17" s="113" t="n"/>
-      <c r="AX17" s="113" t="n"/>
-      <c r="AY17" s="113" t="n"/>
-      <c r="AZ17" s="113" t="n"/>
-      <c r="BA17" s="113" t="n"/>
-      <c r="BB17" s="113" t="n"/>
-      <c r="BC17" s="113" t="n"/>
-      <c r="BD17" s="114" t="n"/>
+      <c r="A17" s="211" t="n"/>
+      <c r="B17" s="174" t="n"/>
+      <c r="C17" s="174" t="n"/>
+      <c r="D17" s="174" t="n"/>
+      <c r="E17" s="174" t="n"/>
+      <c r="F17" s="174" t="n"/>
+      <c r="G17" s="174" t="n"/>
+      <c r="H17" s="174" t="n"/>
+      <c r="I17" s="212" t="n"/>
+      <c r="J17" s="176" t="n"/>
+      <c r="K17" s="176" t="n"/>
+      <c r="L17" s="176" t="n"/>
+      <c r="M17" s="176" t="n"/>
+      <c r="N17" s="212" t="n"/>
+      <c r="O17" s="176" t="n"/>
+      <c r="P17" s="176" t="n"/>
+      <c r="Q17" s="176" t="n"/>
+      <c r="R17" s="176" t="n"/>
+      <c r="S17" s="176" t="n"/>
+      <c r="T17" s="176" t="n"/>
+      <c r="U17" s="176" t="n"/>
+      <c r="V17" s="176" t="n"/>
+      <c r="W17" s="176" t="n"/>
+      <c r="X17" s="176" t="n"/>
+      <c r="Y17" s="212" t="n"/>
+      <c r="Z17" s="176" t="n"/>
+      <c r="AA17" s="176" t="n"/>
+      <c r="AB17" s="176" t="n"/>
+      <c r="AC17" s="176" t="n"/>
+      <c r="AD17" s="212" t="n"/>
+      <c r="AE17" s="176" t="n"/>
+      <c r="AF17" s="176" t="n"/>
+      <c r="AG17" s="176" t="n"/>
+      <c r="AH17" s="176" t="n"/>
+      <c r="AI17" s="176" t="n"/>
+      <c r="AJ17" s="176" t="n"/>
+      <c r="AK17" s="213" t="n"/>
+      <c r="AL17" s="176" t="n"/>
+      <c r="AM17" s="176" t="n"/>
+      <c r="AN17" s="176" t="n"/>
+      <c r="AO17" s="176" t="n"/>
+      <c r="AP17" s="176" t="n"/>
+      <c r="AQ17" s="212" t="n"/>
+      <c r="AR17" s="176" t="n"/>
+      <c r="AS17" s="176" t="n"/>
+      <c r="AT17" s="176" t="n"/>
+      <c r="AU17" s="176" t="n"/>
+      <c r="AV17" s="212" t="n"/>
+      <c r="AW17" s="176" t="n"/>
+      <c r="AX17" s="176" t="n"/>
+      <c r="AY17" s="176" t="n"/>
+      <c r="AZ17" s="176" t="n"/>
+      <c r="BA17" s="176" t="n"/>
+      <c r="BB17" s="176" t="n"/>
+      <c r="BC17" s="176" t="n"/>
+      <c r="BD17" s="178" t="n"/>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="88" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="164" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B18" s="99" t="n"/>
-      <c r="C18" s="99" t="n"/>
-      <c r="D18" s="99" t="n"/>
-      <c r="E18" s="99" t="n"/>
-      <c r="F18" s="99" t="n"/>
-      <c r="G18" s="99" t="n"/>
-      <c r="H18" s="99" t="n"/>
-      <c r="I18" s="99" t="n"/>
-      <c r="J18" s="99" t="n"/>
-      <c r="K18" s="99" t="n"/>
-      <c r="L18" s="99" t="n"/>
-      <c r="M18" s="99" t="n"/>
-      <c r="N18" s="99" t="n"/>
-      <c r="O18" s="99" t="n"/>
-      <c r="P18" s="99" t="n"/>
-      <c r="Q18" s="99" t="n"/>
-      <c r="R18" s="99" t="n"/>
-      <c r="S18" s="99" t="n"/>
-      <c r="T18" s="99" t="n"/>
-      <c r="U18" s="99" t="n"/>
-      <c r="V18" s="99" t="n"/>
-      <c r="W18" s="99" t="n"/>
-      <c r="X18" s="99" t="n"/>
-      <c r="Y18" s="99" t="n"/>
-      <c r="Z18" s="99" t="n"/>
-      <c r="AA18" s="99" t="n"/>
-      <c r="AB18" s="99" t="n"/>
-      <c r="AC18" s="99" t="n"/>
-      <c r="AD18" s="99" t="n"/>
-      <c r="AE18" s="99" t="n"/>
-      <c r="AF18" s="99" t="n"/>
-      <c r="AG18" s="99" t="n"/>
-      <c r="AH18" s="99" t="n"/>
-      <c r="AI18" s="99" t="n"/>
-      <c r="AJ18" s="99" t="n"/>
-      <c r="AK18" s="99" t="n"/>
-      <c r="AL18" s="99" t="n"/>
-      <c r="AM18" s="99" t="n"/>
-      <c r="AN18" s="99" t="n"/>
-      <c r="AO18" s="99" t="n"/>
-      <c r="AP18" s="99" t="n"/>
-      <c r="AQ18" s="99" t="n"/>
-      <c r="AR18" s="99" t="n"/>
-      <c r="AS18" s="99" t="n"/>
-      <c r="AT18" s="99" t="n"/>
-      <c r="AU18" s="99" t="n"/>
-      <c r="AV18" s="99" t="n"/>
-      <c r="AW18" s="99" t="n"/>
-      <c r="AX18" s="99" t="n"/>
-      <c r="AY18" s="99" t="n"/>
-      <c r="AZ18" s="99" t="n"/>
-      <c r="BA18" s="99" t="n"/>
-      <c r="BB18" s="99" t="n"/>
-      <c r="BC18" s="99" t="n"/>
-      <c r="BD18" s="100" t="n"/>
+      <c r="B18" s="165" t="n"/>
+      <c r="C18" s="165" t="n"/>
+      <c r="D18" s="165" t="n"/>
+      <c r="E18" s="165" t="n"/>
+      <c r="F18" s="165" t="n"/>
+      <c r="G18" s="165" t="n"/>
+      <c r="H18" s="165" t="n"/>
+      <c r="I18" s="165" t="n"/>
+      <c r="J18" s="165" t="n"/>
+      <c r="K18" s="165" t="n"/>
+      <c r="L18" s="165" t="n"/>
+      <c r="M18" s="165" t="n"/>
+      <c r="N18" s="165" t="n"/>
+      <c r="O18" s="165" t="n"/>
+      <c r="P18" s="165" t="n"/>
+      <c r="Q18" s="165" t="n"/>
+      <c r="R18" s="165" t="n"/>
+      <c r="S18" s="165" t="n"/>
+      <c r="T18" s="165" t="n"/>
+      <c r="U18" s="165" t="n"/>
+      <c r="V18" s="165" t="n"/>
+      <c r="W18" s="165" t="n"/>
+      <c r="X18" s="165" t="n"/>
+      <c r="Y18" s="165" t="n"/>
+      <c r="Z18" s="165" t="n"/>
+      <c r="AA18" s="165" t="n"/>
+      <c r="AB18" s="165" t="n"/>
+      <c r="AC18" s="165" t="n"/>
+      <c r="AD18" s="165" t="n"/>
+      <c r="AE18" s="165" t="n"/>
+      <c r="AF18" s="165" t="n"/>
+      <c r="AG18" s="165" t="n"/>
+      <c r="AH18" s="165" t="n"/>
+      <c r="AI18" s="165" t="n"/>
+      <c r="AJ18" s="165" t="n"/>
+      <c r="AK18" s="165" t="n"/>
+      <c r="AL18" s="165" t="n"/>
+      <c r="AM18" s="165" t="n"/>
+      <c r="AN18" s="165" t="n"/>
+      <c r="AO18" s="165" t="n"/>
+      <c r="AP18" s="165" t="n"/>
+      <c r="AQ18" s="165" t="n"/>
+      <c r="AR18" s="165" t="n"/>
+      <c r="AS18" s="165" t="n"/>
+      <c r="AT18" s="165" t="n"/>
+      <c r="AU18" s="165" t="n"/>
+      <c r="AV18" s="165" t="n"/>
+      <c r="AW18" s="165" t="n"/>
+      <c r="AX18" s="165" t="n"/>
+      <c r="AY18" s="165" t="n"/>
+      <c r="AZ18" s="165" t="n"/>
+      <c r="BA18" s="165" t="n"/>
+      <c r="BB18" s="165" t="n"/>
+      <c r="BC18" s="165" t="n"/>
+      <c r="BD18" s="166" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="82">
+  <mergeCells count="81">
     <mergeCell ref="AV17:BD17"/>
     <mergeCell ref="AV11:BD11"/>
     <mergeCell ref="N11:X11"/>
@@ -5385,7 +6348,6 @@
     <mergeCell ref="AQ12:AU12"/>
     <mergeCell ref="AQ4:AV4"/>
     <mergeCell ref="N14:X14"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="AV15:BD15"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="Y13:AC13"/>
@@ -5464,6 +6426,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5788,61 +6751,6 @@
     </row>
     <row r="6" ht="4" customHeight="1">
       <c r="A6" s="70" t="n"/>
-      <c r="B6" s="117" t="n"/>
-      <c r="C6" s="117" t="n"/>
-      <c r="D6" s="117" t="n"/>
-      <c r="E6" s="117" t="n"/>
-      <c r="F6" s="117" t="n"/>
-      <c r="G6" s="117" t="n"/>
-      <c r="H6" s="117" t="n"/>
-      <c r="I6" s="117" t="n"/>
-      <c r="J6" s="117" t="n"/>
-      <c r="K6" s="117" t="n"/>
-      <c r="L6" s="117" t="n"/>
-      <c r="M6" s="117" t="n"/>
-      <c r="N6" s="117" t="n"/>
-      <c r="O6" s="117" t="n"/>
-      <c r="P6" s="117" t="n"/>
-      <c r="Q6" s="117" t="n"/>
-      <c r="R6" s="117" t="n"/>
-      <c r="S6" s="117" t="n"/>
-      <c r="T6" s="117" t="n"/>
-      <c r="U6" s="117" t="n"/>
-      <c r="V6" s="117" t="n"/>
-      <c r="W6" s="117" t="n"/>
-      <c r="X6" s="117" t="n"/>
-      <c r="Y6" s="117" t="n"/>
-      <c r="Z6" s="117" t="n"/>
-      <c r="AA6" s="117" t="n"/>
-      <c r="AB6" s="117" t="n"/>
-      <c r="AC6" s="117" t="n"/>
-      <c r="AD6" s="117" t="n"/>
-      <c r="AE6" s="117" t="n"/>
-      <c r="AF6" s="117" t="n"/>
-      <c r="AG6" s="117" t="n"/>
-      <c r="AH6" s="117" t="n"/>
-      <c r="AI6" s="117" t="n"/>
-      <c r="AJ6" s="117" t="n"/>
-      <c r="AK6" s="117" t="n"/>
-      <c r="AL6" s="117" t="n"/>
-      <c r="AM6" s="117" t="n"/>
-      <c r="AN6" s="117" t="n"/>
-      <c r="AO6" s="117" t="n"/>
-      <c r="AP6" s="117" t="n"/>
-      <c r="AQ6" s="117" t="n"/>
-      <c r="AR6" s="117" t="n"/>
-      <c r="AS6" s="117" t="n"/>
-      <c r="AT6" s="117" t="n"/>
-      <c r="AU6" s="117" t="n"/>
-      <c r="AV6" s="117" t="n"/>
-      <c r="AW6" s="117" t="n"/>
-      <c r="AX6" s="117" t="n"/>
-      <c r="AY6" s="117" t="n"/>
-      <c r="AZ6" s="117" t="n"/>
-      <c r="BA6" s="117" t="n"/>
-      <c r="BB6" s="117" t="n"/>
-      <c r="BC6" s="117" t="n"/>
-      <c r="BD6" s="117" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="71" t="inlineStr">
@@ -5912,61 +6820,61 @@
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="105" t="n"/>
-      <c r="C8" s="105" t="n"/>
-      <c r="D8" s="105" t="n"/>
-      <c r="E8" s="105" t="n"/>
-      <c r="F8" s="105" t="n"/>
-      <c r="G8" s="105" t="n"/>
-      <c r="H8" s="105" t="n"/>
-      <c r="I8" s="105" t="n"/>
-      <c r="J8" s="105" t="n"/>
-      <c r="K8" s="105" t="n"/>
-      <c r="L8" s="105" t="n"/>
-      <c r="M8" s="105" t="n"/>
-      <c r="N8" s="105" t="n"/>
-      <c r="O8" s="105" t="n"/>
-      <c r="P8" s="105" t="n"/>
-      <c r="Q8" s="105" t="n"/>
-      <c r="R8" s="105" t="n"/>
-      <c r="S8" s="105" t="n"/>
-      <c r="T8" s="105" t="n"/>
-      <c r="U8" s="105" t="n"/>
-      <c r="V8" s="105" t="n"/>
-      <c r="W8" s="105" t="n"/>
-      <c r="X8" s="105" t="n"/>
-      <c r="Y8" s="105" t="n"/>
-      <c r="Z8" s="105" t="n"/>
-      <c r="AA8" s="105" t="n"/>
-      <c r="AB8" s="105" t="n"/>
-      <c r="AC8" s="105" t="n"/>
-      <c r="AD8" s="105" t="n"/>
-      <c r="AE8" s="105" t="n"/>
-      <c r="AF8" s="105" t="n"/>
-      <c r="AG8" s="105" t="n"/>
-      <c r="AH8" s="105" t="n"/>
-      <c r="AI8" s="105" t="n"/>
-      <c r="AJ8" s="105" t="n"/>
-      <c r="AK8" s="105" t="n"/>
-      <c r="AL8" s="105" t="n"/>
-      <c r="AM8" s="105" t="n"/>
-      <c r="AN8" s="105" t="n"/>
-      <c r="AO8" s="105" t="n"/>
-      <c r="AP8" s="105" t="n"/>
-      <c r="AQ8" s="105" t="n"/>
-      <c r="AR8" s="105" t="n"/>
-      <c r="AS8" s="105" t="n"/>
-      <c r="AT8" s="105" t="n"/>
-      <c r="AU8" s="105" t="n"/>
-      <c r="AV8" s="105" t="n"/>
-      <c r="AW8" s="105" t="n"/>
-      <c r="AX8" s="105" t="n"/>
-      <c r="AY8" s="105" t="n"/>
-      <c r="AZ8" s="105" t="n"/>
-      <c r="BA8" s="105" t="n"/>
-      <c r="BB8" s="105" t="n"/>
-      <c r="BC8" s="105" t="n"/>
-      <c r="BD8" s="106" t="n"/>
+      <c r="B8" s="119" t="n"/>
+      <c r="C8" s="119" t="n"/>
+      <c r="D8" s="119" t="n"/>
+      <c r="E8" s="119" t="n"/>
+      <c r="F8" s="119" t="n"/>
+      <c r="G8" s="119" t="n"/>
+      <c r="H8" s="119" t="n"/>
+      <c r="I8" s="119" t="n"/>
+      <c r="J8" s="119" t="n"/>
+      <c r="K8" s="119" t="n"/>
+      <c r="L8" s="119" t="n"/>
+      <c r="M8" s="119" t="n"/>
+      <c r="N8" s="119" t="n"/>
+      <c r="O8" s="119" t="n"/>
+      <c r="P8" s="119" t="n"/>
+      <c r="Q8" s="119" t="n"/>
+      <c r="R8" s="119" t="n"/>
+      <c r="S8" s="119" t="n"/>
+      <c r="T8" s="119" t="n"/>
+      <c r="U8" s="119" t="n"/>
+      <c r="V8" s="119" t="n"/>
+      <c r="W8" s="119" t="n"/>
+      <c r="X8" s="119" t="n"/>
+      <c r="Y8" s="119" t="n"/>
+      <c r="Z8" s="119" t="n"/>
+      <c r="AA8" s="119" t="n"/>
+      <c r="AB8" s="119" t="n"/>
+      <c r="AC8" s="119" t="n"/>
+      <c r="AD8" s="119" t="n"/>
+      <c r="AE8" s="119" t="n"/>
+      <c r="AF8" s="119" t="n"/>
+      <c r="AG8" s="119" t="n"/>
+      <c r="AH8" s="119" t="n"/>
+      <c r="AI8" s="119" t="n"/>
+      <c r="AJ8" s="119" t="n"/>
+      <c r="AK8" s="119" t="n"/>
+      <c r="AL8" s="119" t="n"/>
+      <c r="AM8" s="119" t="n"/>
+      <c r="AN8" s="119" t="n"/>
+      <c r="AO8" s="119" t="n"/>
+      <c r="AP8" s="119" t="n"/>
+      <c r="AQ8" s="119" t="n"/>
+      <c r="AR8" s="119" t="n"/>
+      <c r="AS8" s="119" t="n"/>
+      <c r="AT8" s="119" t="n"/>
+      <c r="AU8" s="119" t="n"/>
+      <c r="AV8" s="119" t="n"/>
+      <c r="AW8" s="119" t="n"/>
+      <c r="AX8" s="119" t="n"/>
+      <c r="AY8" s="119" t="n"/>
+      <c r="AZ8" s="119" t="n"/>
+      <c r="BA8" s="119" t="n"/>
+      <c r="BB8" s="119" t="n"/>
+      <c r="BC8" s="119" t="n"/>
+      <c r="BD8" s="120" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="91" t="inlineStr">
@@ -7420,61 +8328,61 @@
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="105" t="n"/>
-      <c r="C20" s="105" t="n"/>
-      <c r="D20" s="105" t="n"/>
-      <c r="E20" s="105" t="n"/>
-      <c r="F20" s="105" t="n"/>
-      <c r="G20" s="105" t="n"/>
-      <c r="H20" s="105" t="n"/>
-      <c r="I20" s="105" t="n"/>
-      <c r="J20" s="105" t="n"/>
-      <c r="K20" s="105" t="n"/>
-      <c r="L20" s="105" t="n"/>
-      <c r="M20" s="105" t="n"/>
-      <c r="N20" s="105" t="n"/>
-      <c r="O20" s="105" t="n"/>
-      <c r="P20" s="105" t="n"/>
-      <c r="Q20" s="105" t="n"/>
-      <c r="R20" s="105" t="n"/>
-      <c r="S20" s="105" t="n"/>
-      <c r="T20" s="105" t="n"/>
-      <c r="U20" s="105" t="n"/>
-      <c r="V20" s="105" t="n"/>
-      <c r="W20" s="105" t="n"/>
-      <c r="X20" s="105" t="n"/>
-      <c r="Y20" s="105" t="n"/>
-      <c r="Z20" s="105" t="n"/>
-      <c r="AA20" s="105" t="n"/>
-      <c r="AB20" s="105" t="n"/>
-      <c r="AC20" s="105" t="n"/>
-      <c r="AD20" s="105" t="n"/>
-      <c r="AE20" s="105" t="n"/>
-      <c r="AF20" s="105" t="n"/>
-      <c r="AG20" s="105" t="n"/>
-      <c r="AH20" s="105" t="n"/>
-      <c r="AI20" s="105" t="n"/>
-      <c r="AJ20" s="105" t="n"/>
-      <c r="AK20" s="105" t="n"/>
-      <c r="AL20" s="105" t="n"/>
-      <c r="AM20" s="105" t="n"/>
-      <c r="AN20" s="105" t="n"/>
-      <c r="AO20" s="105" t="n"/>
-      <c r="AP20" s="105" t="n"/>
-      <c r="AQ20" s="105" t="n"/>
-      <c r="AR20" s="105" t="n"/>
-      <c r="AS20" s="105" t="n"/>
-      <c r="AT20" s="105" t="n"/>
-      <c r="AU20" s="105" t="n"/>
-      <c r="AV20" s="105" t="n"/>
-      <c r="AW20" s="105" t="n"/>
-      <c r="AX20" s="105" t="n"/>
-      <c r="AY20" s="105" t="n"/>
-      <c r="AZ20" s="105" t="n"/>
-      <c r="BA20" s="105" t="n"/>
-      <c r="BB20" s="105" t="n"/>
-      <c r="BC20" s="105" t="n"/>
-      <c r="BD20" s="106" t="n"/>
+      <c r="B20" s="119" t="n"/>
+      <c r="C20" s="119" t="n"/>
+      <c r="D20" s="119" t="n"/>
+      <c r="E20" s="119" t="n"/>
+      <c r="F20" s="119" t="n"/>
+      <c r="G20" s="119" t="n"/>
+      <c r="H20" s="119" t="n"/>
+      <c r="I20" s="119" t="n"/>
+      <c r="J20" s="119" t="n"/>
+      <c r="K20" s="119" t="n"/>
+      <c r="L20" s="119" t="n"/>
+      <c r="M20" s="119" t="n"/>
+      <c r="N20" s="119" t="n"/>
+      <c r="O20" s="119" t="n"/>
+      <c r="P20" s="119" t="n"/>
+      <c r="Q20" s="119" t="n"/>
+      <c r="R20" s="119" t="n"/>
+      <c r="S20" s="119" t="n"/>
+      <c r="T20" s="119" t="n"/>
+      <c r="U20" s="119" t="n"/>
+      <c r="V20" s="119" t="n"/>
+      <c r="W20" s="119" t="n"/>
+      <c r="X20" s="119" t="n"/>
+      <c r="Y20" s="119" t="n"/>
+      <c r="Z20" s="119" t="n"/>
+      <c r="AA20" s="119" t="n"/>
+      <c r="AB20" s="119" t="n"/>
+      <c r="AC20" s="119" t="n"/>
+      <c r="AD20" s="119" t="n"/>
+      <c r="AE20" s="119" t="n"/>
+      <c r="AF20" s="119" t="n"/>
+      <c r="AG20" s="119" t="n"/>
+      <c r="AH20" s="119" t="n"/>
+      <c r="AI20" s="119" t="n"/>
+      <c r="AJ20" s="119" t="n"/>
+      <c r="AK20" s="119" t="n"/>
+      <c r="AL20" s="119" t="n"/>
+      <c r="AM20" s="119" t="n"/>
+      <c r="AN20" s="119" t="n"/>
+      <c r="AO20" s="119" t="n"/>
+      <c r="AP20" s="119" t="n"/>
+      <c r="AQ20" s="119" t="n"/>
+      <c r="AR20" s="119" t="n"/>
+      <c r="AS20" s="119" t="n"/>
+      <c r="AT20" s="119" t="n"/>
+      <c r="AU20" s="119" t="n"/>
+      <c r="AV20" s="119" t="n"/>
+      <c r="AW20" s="119" t="n"/>
+      <c r="AX20" s="119" t="n"/>
+      <c r="AY20" s="119" t="n"/>
+      <c r="AZ20" s="119" t="n"/>
+      <c r="BA20" s="119" t="n"/>
+      <c r="BB20" s="119" t="n"/>
+      <c r="BC20" s="119" t="n"/>
+      <c r="BD20" s="120" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -26,10 +26,714 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
+  <si>
+    <t>  1. ASSESSMENT HEADER</t>
+  </si>
+  <si>
+    <t>  1. CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>  2. EVIDENCE-BASED ASSESSMENT SECTION</t>
+  </si>
+  <si>
+    <t>  3. GAP AND DEVELOPMENT SECTION</t>
+  </si>
+  <si>
+    <t>  4. DECISION SECTION</t>
+  </si>
+  <si>
+    <t>  REFERENCE / SOURCE CONTEXT</t>
+  </si>
+  <si>
+    <t>  SUPPORT TABLE</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>ABSENT</t>
+  </si>
+  <si>
+    <t>ACCESS</t>
+  </si>
+  <si>
+    <t>ACCESS_ACTION_TYPE</t>
+  </si>
+  <si>
+    <t>ADJUST</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>ALL HANDS</t>
+  </si>
+  <si>
+    <t>ANNEX</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>APPROVER</t>
+  </si>
+  <si>
+    <t>ATTENDANCE_STATUS</t>
+  </si>
+  <si>
+    <t>AUDIENCE_CLASS</t>
+  </si>
+  <si>
+    <t>AUDIT_FINDING_SEVERITY</t>
+  </si>
+  <si>
+    <t>AUTHORITY_ROLE</t>
+  </si>
+  <si>
+    <t>AUTHORIZATION_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZED</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>Assessor</t>
+  </si>
+  <si>
+    <t>BACKUP_FLAG</t>
+  </si>
+  <si>
+    <t>CHANGE</t>
+  </si>
+  <si>
+    <t>CHANGE_PRIORITY</t>
+  </si>
+  <si>
+    <t>CHANGE_TYPE</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>COMMERCIAL_REFERENCE</t>
+  </si>
+  <si>
+    <t>COMM_CHANNEL</t>
+  </si>
+  <si>
+    <t>COMPETENCE ASSESSMENT</t>
+  </si>
+  <si>
+    <t>COMPETENCE ASSESSMENT — ASSESSMENT CRITERIA</t>
+  </si>
+  <si>
+    <t>COMPETENCE ASSESSMENT — CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>COMPETENCE ASSESSMENT — EVIDENCE REFERENCE REGISTER</t>
+  </si>
+  <si>
+    <t>COMPETENCY_LEVEL</t>
+  </si>
+  <si>
+    <t>COMPLIANCE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CONFIGURATION</t>
+  </si>
+  <si>
+    <t>CONTAINED</t>
+  </si>
+  <si>
+    <t>CONTEXT_CLASS</t>
+  </si>
+  <si>
+    <t>CONTRACT</t>
+  </si>
+  <si>
+    <t>CONTRACT REVIEW</t>
+  </si>
+  <si>
+    <t>CONTRIBUTOR</t>
+  </si>
+  <si>
+    <t>CONTROL_METHOD</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>CREATE</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>CSR</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Comments By Criterion</t>
+  </si>
+  <si>
+    <t>Criterion</t>
+  </si>
+  <si>
+    <t>DAILY</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>DEPT</t>
+  </si>
+  <si>
+    <t>DETECTION</t>
+  </si>
+  <si>
+    <t>DIMENSIONAL</t>
+  </si>
+  <si>
+    <t>DOCUMENT</t>
+  </si>
+  <si>
+    <t>DOC_STATUS</t>
+  </si>
+  <si>
+    <t>DOC_TYPE</t>
+  </si>
+  <si>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Date And Assessment Type</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>EACH LOT</t>
+  </si>
+  <si>
+    <t>EFFECTIVE</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>ESCALATE</t>
+  </si>
+  <si>
+    <t>ESCALATED</t>
+  </si>
+  <si>
+    <t>ESCALATION</t>
+  </si>
+  <si>
+    <t>EXCUSED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>Evidence ID</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Expected Standard</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>FIRST ARTICLE</t>
+  </si>
+  <si>
+    <t>FIRST OFF</t>
+  </si>
+  <si>
+    <t>FIRST PIECE</t>
+  </si>
+  <si>
+    <t>FMEA_RANK</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t>FRM-804</t>
+  </si>
+  <si>
+    <t>FUNCTION</t>
+  </si>
+  <si>
+    <t>FUNCTIONAL</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>GATE</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HOURLY</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>HR + Department Manager</t>
+  </si>
+  <si>
+    <t>IMPACT_LEVEL</t>
+  </si>
+  <si>
+    <t>IMPACT_SCOPE</t>
+  </si>
+  <si>
+    <t>IN PROCESS</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>IN-PROCESS</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>KPI-COST</t>
+  </si>
+  <si>
+    <t>KPI-DELIVERY</t>
+  </si>
+  <si>
+    <t>KPI-QUALITY</t>
+  </si>
+  <si>
+    <t>KPI-SAFETY</t>
+  </si>
+  <si>
+    <t>KPI-TRAINING</t>
+  </si>
+  <si>
+    <t>KPI_OWNER_SET</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>LESSON_CLASS</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>M365 evidence stays SSOT; workbook captures the formal study / gate / decision record while annex rules, criteria dictionaries and authority matrices are referenced, not re-keyed.</t>
+  </si>
+  <si>
+    <t>MAJOR</t>
+  </si>
+  <si>
+    <t>MANAGEMENT</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MEETING</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MINOR</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Mentoring Or Re-Assessment Requirements</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>NOT AUTHORIZED</t>
+  </si>
+  <si>
+    <t>NOT TRAINED</t>
+  </si>
+  <si>
+    <t>NOTICE</t>
+  </si>
+  <si>
+    <t>NOTICE: Competence decisions shall be evidence-based. Record required tasks or behaviors, observed evidence, pass standard, restrictions, re-training needs and the explicit authorization decision.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
+  </si>
+  <si>
+    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OBSERVED</t>
+  </si>
+  <si>
+    <t>OBSOLETE</t>
+  </si>
+  <si>
+    <t>ON HOLD</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OWNER</t>
+  </si>
+  <si>
+    <t>Observed Evidence</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PEOPLE</t>
+  </si>
+  <si>
+    <t>PESTLE</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>POLICY</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>PRESENT</t>
+  </si>
+  <si>
+    <t>PREVENTION</t>
+  </si>
+  <si>
+    <t>PROCESS</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Pass Standard</t>
+  </si>
+  <si>
+    <t>Per authority matrix</t>
+  </si>
+  <si>
+    <t>Prepared By</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QUALITY</t>
+  </si>
+  <si>
+    <t>QUOTE</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REACTION_CLASS</t>
+  </si>
+  <si>
+    <t>RECHECK</t>
+  </si>
+  <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t>RECOVERING</t>
+  </si>
+  <si>
+    <t>RECOVERY_STATUS</t>
+  </si>
+  <si>
+    <t>REGULATORY</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>REMOVE</t>
+  </si>
+  <si>
+    <t>REQUESTER</t>
+  </si>
+  <si>
+    <t>RESPONSE</t>
+  </si>
+  <si>
+    <t>RESTORED</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>REVIEWER</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>RISK_CATEGORY</t>
+  </si>
+  <si>
+    <t>ROLE</t>
+  </si>
+  <si>
+    <t>ROLE_ACCESS_PROFILE</t>
+  </si>
+  <si>
+    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
+  </si>
+  <si>
+    <t>Reference / code-support sheet for controlled vocabulary or approved code mappings.</t>
+  </si>
+  <si>
+    <t>Reference Path or Link</t>
+  </si>
+  <si>
+    <t>Related Record</t>
+  </si>
+  <si>
+    <t>Required Tasks / Knowledge / Behaviors</t>
+  </si>
+  <si>
+    <t>Restrictions</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Retraining</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>SAFETY</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SAMPLE_FREQUENCY</t>
+  </si>
+  <si>
+    <t>SEGREGATE</t>
+  </si>
+  <si>
+    <t>SHIFT</t>
+  </si>
+  <si>
+    <t>SHIPPING</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>SOP</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>STOP</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>SUPERVISED</t>
+  </si>
+  <si>
+    <t>SUSPENDED</t>
+  </si>
+  <si>
+    <t>SWOT</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>Source Links</t>
+  </si>
+  <si>
+    <t>Source System</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>TRAINER</t>
+  </si>
+  <si>
+    <t>TRAINING</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VIEWER</t>
+  </si>
+  <si>
+    <t>VISUAL</t>
+  </si>
+  <si>
+    <t>WEEKLY</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,8 +844,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -198,8 +907,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="145">
+  <borders count="148">
     <border>
       <left/>
       <right/>
@@ -1757,11 +2471,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="364">
+  <cellXfs count="367">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2717,6 +3465,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4657,67 +5414,67 @@
       <c r="BC23" s="35" t="n"/>
       <c r="BD23" s="336" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="321" t="inlineStr">
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="364" t="inlineStr">
         <is>
           <t>NOTICE: Competence decisions shall be evidence-based. Record required tasks or behaviors, observed evidence, pass standard, restrictions, re-training needs and the explicit authorization decision.</t>
         </is>
       </c>
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="22" t="n"/>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="22" t="n"/>
-      <c r="J24" s="22" t="n"/>
-      <c r="K24" s="22" t="n"/>
-      <c r="L24" s="22" t="n"/>
-      <c r="M24" s="22" t="n"/>
-      <c r="N24" s="22" t="n"/>
-      <c r="O24" s="22" t="n"/>
-      <c r="P24" s="22" t="n"/>
-      <c r="Q24" s="22" t="n"/>
-      <c r="R24" s="22" t="n"/>
-      <c r="S24" s="22" t="n"/>
-      <c r="T24" s="22" t="n"/>
-      <c r="U24" s="22" t="n"/>
-      <c r="V24" s="22" t="n"/>
-      <c r="W24" s="22" t="n"/>
-      <c r="X24" s="22" t="n"/>
-      <c r="Y24" s="22" t="n"/>
-      <c r="Z24" s="22" t="n"/>
-      <c r="AA24" s="22" t="n"/>
-      <c r="AB24" s="22" t="n"/>
-      <c r="AC24" s="22" t="n"/>
-      <c r="AD24" s="22" t="n"/>
-      <c r="AE24" s="22" t="n"/>
-      <c r="AF24" s="22" t="n"/>
-      <c r="AG24" s="22" t="n"/>
-      <c r="AH24" s="22" t="n"/>
-      <c r="AI24" s="22" t="n"/>
-      <c r="AJ24" s="22" t="n"/>
-      <c r="AK24" s="22" t="n"/>
-      <c r="AL24" s="22" t="n"/>
-      <c r="AM24" s="22" t="n"/>
-      <c r="AN24" s="22" t="n"/>
-      <c r="AO24" s="22" t="n"/>
-      <c r="AP24" s="22" t="n"/>
-      <c r="AQ24" s="22" t="n"/>
-      <c r="AR24" s="22" t="n"/>
-      <c r="AS24" s="22" t="n"/>
-      <c r="AT24" s="22" t="n"/>
-      <c r="AU24" s="22" t="n"/>
-      <c r="AV24" s="22" t="n"/>
-      <c r="AW24" s="22" t="n"/>
-      <c r="AX24" s="22" t="n"/>
-      <c r="AY24" s="22" t="n"/>
-      <c r="AZ24" s="22" t="n"/>
-      <c r="BA24" s="22" t="n"/>
-      <c r="BB24" s="22" t="n"/>
-      <c r="BC24" s="22" t="n"/>
-      <c r="BD24" s="23" t="n"/>
+      <c r="B24" s="365" t="n"/>
+      <c r="C24" s="365" t="n"/>
+      <c r="D24" s="365" t="n"/>
+      <c r="E24" s="365" t="n"/>
+      <c r="F24" s="365" t="n"/>
+      <c r="G24" s="365" t="n"/>
+      <c r="H24" s="365" t="n"/>
+      <c r="I24" s="365" t="n"/>
+      <c r="J24" s="365" t="n"/>
+      <c r="K24" s="365" t="n"/>
+      <c r="L24" s="365" t="n"/>
+      <c r="M24" s="365" t="n"/>
+      <c r="N24" s="365" t="n"/>
+      <c r="O24" s="365" t="n"/>
+      <c r="P24" s="365" t="n"/>
+      <c r="Q24" s="365" t="n"/>
+      <c r="R24" s="365" t="n"/>
+      <c r="S24" s="365" t="n"/>
+      <c r="T24" s="365" t="n"/>
+      <c r="U24" s="365" t="n"/>
+      <c r="V24" s="365" t="n"/>
+      <c r="W24" s="365" t="n"/>
+      <c r="X24" s="365" t="n"/>
+      <c r="Y24" s="365" t="n"/>
+      <c r="Z24" s="365" t="n"/>
+      <c r="AA24" s="365" t="n"/>
+      <c r="AB24" s="365" t="n"/>
+      <c r="AC24" s="365" t="n"/>
+      <c r="AD24" s="365" t="n"/>
+      <c r="AE24" s="365" t="n"/>
+      <c r="AF24" s="365" t="n"/>
+      <c r="AG24" s="365" t="n"/>
+      <c r="AH24" s="365" t="n"/>
+      <c r="AI24" s="365" t="n"/>
+      <c r="AJ24" s="365" t="n"/>
+      <c r="AK24" s="365" t="n"/>
+      <c r="AL24" s="365" t="n"/>
+      <c r="AM24" s="365" t="n"/>
+      <c r="AN24" s="365" t="n"/>
+      <c r="AO24" s="365" t="n"/>
+      <c r="AP24" s="365" t="n"/>
+      <c r="AQ24" s="365" t="n"/>
+      <c r="AR24" s="365" t="n"/>
+      <c r="AS24" s="365" t="n"/>
+      <c r="AT24" s="365" t="n"/>
+      <c r="AU24" s="365" t="n"/>
+      <c r="AV24" s="365" t="n"/>
+      <c r="AW24" s="365" t="n"/>
+      <c r="AX24" s="365" t="n"/>
+      <c r="AY24" s="365" t="n"/>
+      <c r="AZ24" s="365" t="n"/>
+      <c r="BA24" s="365" t="n"/>
+      <c r="BB24" s="365" t="n"/>
+      <c r="BC24" s="365" t="n"/>
+      <c r="BD24" s="366" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -913,7 +913,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="148">
+  <borders count="153">
     <border>
       <left/>
       <right/>
@@ -2504,6 +2504,64 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -24,710 +24,6 @@
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" calcOnSave="1" forceFullCalc="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
-  <si>
-    <t>  1. ASSESSMENT HEADER</t>
-  </si>
-  <si>
-    <t>  1. CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>  2. EVIDENCE-BASED ASSESSMENT SECTION</t>
-  </si>
-  <si>
-    <t>  3. GAP AND DEVELOPMENT SECTION</t>
-  </si>
-  <si>
-    <t>  4. DECISION SECTION</t>
-  </si>
-  <si>
-    <t>  REFERENCE / SOURCE CONTEXT</t>
-  </si>
-  <si>
-    <t>  SUPPORT TABLE</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>ACCESS</t>
-  </si>
-  <si>
-    <t>ACCESS_ACTION_TYPE</t>
-  </si>
-  <si>
-    <t>ADJUST</t>
-  </si>
-  <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
-    <t>ALL HANDS</t>
-  </si>
-  <si>
-    <t>ANNEX</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>APPROVER</t>
-  </si>
-  <si>
-    <t>ATTENDANCE_STATUS</t>
-  </si>
-  <si>
-    <t>AUDIENCE_CLASS</t>
-  </si>
-  <si>
-    <t>AUDIT_FINDING_SEVERITY</t>
-  </si>
-  <si>
-    <t>AUTHORITY_ROLE</t>
-  </si>
-  <si>
-    <t>AUTHORIZATION_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZED</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>Assessor</t>
-  </si>
-  <si>
-    <t>BACKUP_FLAG</t>
-  </si>
-  <si>
-    <t>CHANGE</t>
-  </si>
-  <si>
-    <t>CHANGE_PRIORITY</t>
-  </si>
-  <si>
-    <t>CHANGE_TYPE</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>COMMERCIAL_REFERENCE</t>
-  </si>
-  <si>
-    <t>COMM_CHANNEL</t>
-  </si>
-  <si>
-    <t>COMPETENCE ASSESSMENT</t>
-  </si>
-  <si>
-    <t>COMPETENCE ASSESSMENT — ASSESSMENT CRITERIA</t>
-  </si>
-  <si>
-    <t>COMPETENCE ASSESSMENT — CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>COMPETENCE ASSESSMENT — EVIDENCE REFERENCE REGISTER</t>
-  </si>
-  <si>
-    <t>COMPETENCY_LEVEL</t>
-  </si>
-  <si>
-    <t>COMPLIANCE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CONFIGURATION</t>
-  </si>
-  <si>
-    <t>CONTAINED</t>
-  </si>
-  <si>
-    <t>CONTEXT_CLASS</t>
-  </si>
-  <si>
-    <t>CONTRACT</t>
-  </si>
-  <si>
-    <t>CONTRACT REVIEW</t>
-  </si>
-  <si>
-    <t>CONTRIBUTOR</t>
-  </si>
-  <si>
-    <t>CONTROL_METHOD</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>CREATE</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>CSR</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Comments By Criterion</t>
-  </si>
-  <si>
-    <t>Criterion</t>
-  </si>
-  <si>
-    <t>DAILY</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>DELIVERY</t>
-  </si>
-  <si>
-    <t>DEPT</t>
-  </si>
-  <si>
-    <t>DETECTION</t>
-  </si>
-  <si>
-    <t>DIMENSIONAL</t>
-  </si>
-  <si>
-    <t>DOCUMENT</t>
-  </si>
-  <si>
-    <t>DOC_STATUS</t>
-  </si>
-  <si>
-    <t>DOC_TYPE</t>
-  </si>
-  <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Date And Assessment Type</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>EACH LOT</t>
-  </si>
-  <si>
-    <t>EFFECTIVE</t>
-  </si>
-  <si>
-    <t>EMAIL</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>ESCALATE</t>
-  </si>
-  <si>
-    <t>ESCALATED</t>
-  </si>
-  <si>
-    <t>ESCALATION</t>
-  </si>
-  <si>
-    <t>EXCUSED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Employee</t>
-  </si>
-  <si>
-    <t>Evidence ID</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Expected Standard</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FINAL</t>
-  </si>
-  <si>
-    <t>FIRST ARTICLE</t>
-  </si>
-  <si>
-    <t>FIRST OFF</t>
-  </si>
-  <si>
-    <t>FIRST PIECE</t>
-  </si>
-  <si>
-    <t>FMEA_RANK</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>FRM-804</t>
-  </si>
-  <si>
-    <t>FUNCTION</t>
-  </si>
-  <si>
-    <t>FUNCTIONAL</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>GATE</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HOURLY</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>HR + Department Manager</t>
-  </si>
-  <si>
-    <t>IMPACT_LEVEL</t>
-  </si>
-  <si>
-    <t>IMPACT_SCOPE</t>
-  </si>
-  <si>
-    <t>IN PROCESS</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>IN-PROCESS</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>KPI-COST</t>
-  </si>
-  <si>
-    <t>KPI-DELIVERY</t>
-  </si>
-  <si>
-    <t>KPI-QUALITY</t>
-  </si>
-  <si>
-    <t>KPI-SAFETY</t>
-  </si>
-  <si>
-    <t>KPI-TRAINING</t>
-  </si>
-  <si>
-    <t>KPI_OWNER_SET</t>
-  </si>
-  <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>LESSON_CLASS</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>M365 evidence stays SSOT; workbook captures the formal study / gate / decision record while annex rules, criteria dictionaries and authority matrices are referenced, not re-keyed.</t>
-  </si>
-  <si>
-    <t>MAJOR</t>
-  </si>
-  <si>
-    <t>MANAGEMENT</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MEETING</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MINOR</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Mentoring Or Re-Assessment Requirements</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>NOT AUTHORIZED</t>
-  </si>
-  <si>
-    <t>NOT TRAINED</t>
-  </si>
-  <si>
-    <t>NOTICE</t>
-  </si>
-  <si>
-    <t>NOTICE: Competence decisions shall be evidence-based. Record required tasks or behaviors, observed evidence, pass standard, restrictions, re-training needs and the explicit authorization decision.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
-  </si>
-  <si>
-    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>OBSERVED</t>
-  </si>
-  <si>
-    <t>OBSOLETE</t>
-  </si>
-  <si>
-    <t>ON HOLD</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OWNER</t>
-  </si>
-  <si>
-    <t>Observed Evidence</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PEOPLE</t>
-  </si>
-  <si>
-    <t>PESTLE</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>POLICY</t>
-  </si>
-  <si>
-    <t>PORTAL</t>
-  </si>
-  <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
-    <t>PREVENTION</t>
-  </si>
-  <si>
-    <t>PROCESS</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Pass Standard</t>
-  </si>
-  <si>
-    <t>Per authority matrix</t>
-  </si>
-  <si>
-    <t>Prepared By</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>QUALITY</t>
-  </si>
-  <si>
-    <t>QUOTE</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>REACTION_CLASS</t>
-  </si>
-  <si>
-    <t>RECHECK</t>
-  </si>
-  <si>
-    <t>RECORD</t>
-  </si>
-  <si>
-    <t>RECOVERING</t>
-  </si>
-  <si>
-    <t>RECOVERY_STATUS</t>
-  </si>
-  <si>
-    <t>REGULATORY</t>
-  </si>
-  <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
-    <t>REMOVE</t>
-  </si>
-  <si>
-    <t>REQUESTER</t>
-  </si>
-  <si>
-    <t>RESPONSE</t>
-  </si>
-  <si>
-    <t>RESTORED</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>REVIEWER</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>RISK_CATEGORY</t>
-  </si>
-  <si>
-    <t>ROLE</t>
-  </si>
-  <si>
-    <t>ROLE_ACCESS_PROFILE</t>
-  </si>
-  <si>
-    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
-  </si>
-  <si>
-    <t>Reference / code-support sheet for controlled vocabulary or approved code mappings.</t>
-  </si>
-  <si>
-    <t>Reference Path or Link</t>
-  </si>
-  <si>
-    <t>Related Record</t>
-  </si>
-  <si>
-    <t>Required Tasks / Knowledge / Behaviors</t>
-  </si>
-  <si>
-    <t>Restrictions</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Retraining</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>SAFETY</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SAMPLE_FREQUENCY</t>
-  </si>
-  <si>
-    <t>SEGREGATE</t>
-  </si>
-  <si>
-    <t>SHIFT</t>
-  </si>
-  <si>
-    <t>SHIPPING</t>
-  </si>
-  <si>
-    <t>SO</t>
-  </si>
-  <si>
-    <t>SOP</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>STOP</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>SUPERVISED</t>
-  </si>
-  <si>
-    <t>SUSPENDED</t>
-  </si>
-  <si>
-    <t>SWOT</t>
-  </si>
-  <si>
-    <t>SYSTEM</t>
-  </si>
-  <si>
-    <t>Source Links</t>
-  </si>
-  <si>
-    <t>Source System</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>TRAINER</t>
-  </si>
-  <si>
-    <t>TRAINING</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VIEWER</t>
-  </si>
-  <si>
-    <t>VISUAL</t>
-  </si>
-  <si>
-    <t>WEEKLY</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="153">
+  <borders count="155">
     <border>
       <left/>
       <right/>
@@ -2563,11 +1859,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="367">
+  <cellXfs count="405">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3532,6 +2852,98 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3614,11 +3026,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3632,9 +3044,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3647,11 +3056,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3665,9 +3074,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3680,11 +3086,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3698,9 +3104,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3713,11 +3116,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3731,9 +3134,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4091,7 +3491,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="307" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -4103,7 +3503,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="217" t="inlineStr">
+      <c r="L1" s="403" t="inlineStr">
         <is>
           <t>COMPETENCE ASSESSMENT</t>
         </is>
@@ -4137,7 +3537,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="308" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -4162,279 +3562,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="311" t="inlineStr">
+      <c r="A2" s="367" t="n"/>
+      <c r="B2" s="368" t="n"/>
+      <c r="C2" s="368" t="n"/>
+      <c r="D2" s="368" t="n"/>
+      <c r="E2" s="368" t="n"/>
+      <c r="F2" s="368" t="n"/>
+      <c r="G2" s="368" t="n"/>
+      <c r="H2" s="368" t="n"/>
+      <c r="I2" s="368" t="n"/>
+      <c r="J2" s="368" t="n"/>
+      <c r="K2" s="369" t="n"/>
+      <c r="L2" s="368" t="n"/>
+      <c r="M2" s="368" t="n"/>
+      <c r="N2" s="368" t="n"/>
+      <c r="O2" s="368" t="n"/>
+      <c r="P2" s="368" t="n"/>
+      <c r="Q2" s="368" t="n"/>
+      <c r="R2" s="368" t="n"/>
+      <c r="S2" s="368" t="n"/>
+      <c r="T2" s="368" t="n"/>
+      <c r="U2" s="368" t="n"/>
+      <c r="V2" s="368" t="n"/>
+      <c r="W2" s="368" t="n"/>
+      <c r="X2" s="368" t="n"/>
+      <c r="Y2" s="368" t="n"/>
+      <c r="Z2" s="368" t="n"/>
+      <c r="AA2" s="368" t="n"/>
+      <c r="AB2" s="368" t="n"/>
+      <c r="AC2" s="368" t="n"/>
+      <c r="AD2" s="368" t="n"/>
+      <c r="AE2" s="368" t="n"/>
+      <c r="AF2" s="368" t="n"/>
+      <c r="AG2" s="368" t="n"/>
+      <c r="AH2" s="368" t="n"/>
+      <c r="AI2" s="368" t="n"/>
+      <c r="AJ2" s="368" t="n"/>
+      <c r="AK2" s="368" t="n"/>
+      <c r="AL2" s="368" t="n"/>
+      <c r="AM2" s="368" t="n"/>
+      <c r="AN2" s="368" t="n"/>
+      <c r="AO2" s="368" t="n"/>
+      <c r="AP2" s="369" t="n"/>
+      <c r="AQ2" s="370" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="312" t="n"/>
-      <c r="AS2" s="312" t="n"/>
-      <c r="AT2" s="312" t="n"/>
-      <c r="AU2" s="312" t="n"/>
-      <c r="AV2" s="313" t="n"/>
-      <c r="AW2" s="314" t="inlineStr">
+      <c r="AR2" s="371" t="n"/>
+      <c r="AS2" s="371" t="n"/>
+      <c r="AT2" s="371" t="n"/>
+      <c r="AU2" s="371" t="n"/>
+      <c r="AV2" s="372" t="n"/>
+      <c r="AW2" s="373" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="312" t="n"/>
-      <c r="AY2" s="312" t="n"/>
-      <c r="AZ2" s="312" t="n"/>
-      <c r="BA2" s="312" t="n"/>
-      <c r="BB2" s="312" t="n"/>
-      <c r="BC2" s="312" t="n"/>
-      <c r="BD2" s="315" t="n"/>
+      <c r="AX2" s="374" t="n"/>
+      <c r="AY2" s="374" t="n"/>
+      <c r="AZ2" s="374" t="n"/>
+      <c r="BA2" s="374" t="n"/>
+      <c r="BB2" s="374" t="n"/>
+      <c r="BC2" s="374" t="n"/>
+      <c r="BD2" s="375" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="311" t="inlineStr">
+      <c r="A3" s="376" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="377" t="n"/>
+      <c r="L3" s="53" t="n"/>
+      <c r="M3" s="53" t="n"/>
+      <c r="N3" s="53" t="n"/>
+      <c r="O3" s="53" t="n"/>
+      <c r="P3" s="53" t="n"/>
+      <c r="Q3" s="53" t="n"/>
+      <c r="R3" s="53" t="n"/>
+      <c r="S3" s="53" t="n"/>
+      <c r="T3" s="53" t="n"/>
+      <c r="U3" s="53" t="n"/>
+      <c r="V3" s="53" t="n"/>
+      <c r="W3" s="53" t="n"/>
+      <c r="X3" s="53" t="n"/>
+      <c r="Y3" s="53" t="n"/>
+      <c r="Z3" s="53" t="n"/>
+      <c r="AA3" s="53" t="n"/>
+      <c r="AB3" s="53" t="n"/>
+      <c r="AC3" s="53" t="n"/>
+      <c r="AD3" s="53" t="n"/>
+      <c r="AE3" s="53" t="n"/>
+      <c r="AF3" s="53" t="n"/>
+      <c r="AG3" s="53" t="n"/>
+      <c r="AH3" s="53" t="n"/>
+      <c r="AI3" s="53" t="n"/>
+      <c r="AJ3" s="53" t="n"/>
+      <c r="AK3" s="53" t="n"/>
+      <c r="AL3" s="53" t="n"/>
+      <c r="AM3" s="53" t="n"/>
+      <c r="AN3" s="53" t="n"/>
+      <c r="AO3" s="53" t="n"/>
+      <c r="AP3" s="377" t="n"/>
+      <c r="AQ3" s="378" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="312" t="n"/>
-      <c r="AS3" s="312" t="n"/>
-      <c r="AT3" s="312" t="n"/>
-      <c r="AU3" s="312" t="n"/>
-      <c r="AV3" s="313" t="n"/>
-      <c r="AW3" s="314" t="inlineStr">
+      <c r="AR3" s="379" t="n"/>
+      <c r="AS3" s="379" t="n"/>
+      <c r="AT3" s="379" t="n"/>
+      <c r="AU3" s="379" t="n"/>
+      <c r="AV3" s="380" t="n"/>
+      <c r="AW3" s="301" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="312" t="n"/>
-      <c r="AY3" s="312" t="n"/>
-      <c r="AZ3" s="312" t="n"/>
-      <c r="BA3" s="312" t="n"/>
-      <c r="BB3" s="312" t="n"/>
-      <c r="BC3" s="312" t="n"/>
-      <c r="BD3" s="315" t="n"/>
+      <c r="AX3" s="381" t="n"/>
+      <c r="AY3" s="381" t="n"/>
+      <c r="AZ3" s="381" t="n"/>
+      <c r="BA3" s="381" t="n"/>
+      <c r="BB3" s="381" t="n"/>
+      <c r="BC3" s="381" t="n"/>
+      <c r="BD3" s="382" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="229" t="inlineStr">
+      <c r="A4" s="376" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="377" t="n"/>
+      <c r="L4" s="383" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="311" t="inlineStr">
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n"/>
+      <c r="O4" s="53" t="n"/>
+      <c r="P4" s="53" t="n"/>
+      <c r="Q4" s="53" t="n"/>
+      <c r="R4" s="53" t="n"/>
+      <c r="S4" s="53" t="n"/>
+      <c r="T4" s="53" t="n"/>
+      <c r="U4" s="53" t="n"/>
+      <c r="V4" s="53" t="n"/>
+      <c r="W4" s="53" t="n"/>
+      <c r="X4" s="53" t="n"/>
+      <c r="Y4" s="53" t="n"/>
+      <c r="Z4" s="53" t="n"/>
+      <c r="AA4" s="53" t="n"/>
+      <c r="AB4" s="53" t="n"/>
+      <c r="AC4" s="53" t="n"/>
+      <c r="AD4" s="53" t="n"/>
+      <c r="AE4" s="53" t="n"/>
+      <c r="AF4" s="53" t="n"/>
+      <c r="AG4" s="53" t="n"/>
+      <c r="AH4" s="53" t="n"/>
+      <c r="AI4" s="53" t="n"/>
+      <c r="AJ4" s="53" t="n"/>
+      <c r="AK4" s="53" t="n"/>
+      <c r="AL4" s="53" t="n"/>
+      <c r="AM4" s="53" t="n"/>
+      <c r="AN4" s="53" t="n"/>
+      <c r="AO4" s="53" t="n"/>
+      <c r="AP4" s="377" t="n"/>
+      <c r="AQ4" s="378" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="312" t="n"/>
-      <c r="AS4" s="312" t="n"/>
-      <c r="AT4" s="312" t="n"/>
-      <c r="AU4" s="312" t="n"/>
-      <c r="AV4" s="313" t="n"/>
-      <c r="AW4" s="314" t="inlineStr">
+      <c r="AR4" s="379" t="n"/>
+      <c r="AS4" s="379" t="n"/>
+      <c r="AT4" s="379" t="n"/>
+      <c r="AU4" s="379" t="n"/>
+      <c r="AV4" s="380" t="n"/>
+      <c r="AW4" s="301" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="312" t="n"/>
-      <c r="AY4" s="312" t="n"/>
-      <c r="AZ4" s="312" t="n"/>
-      <c r="BA4" s="312" t="n"/>
-      <c r="BB4" s="312" t="n"/>
-      <c r="BC4" s="312" t="n"/>
-      <c r="BD4" s="315" t="n"/>
+      <c r="AX4" s="381" t="n"/>
+      <c r="AY4" s="381" t="n"/>
+      <c r="AZ4" s="381" t="n"/>
+      <c r="BA4" s="381" t="n"/>
+      <c r="BB4" s="381" t="n"/>
+      <c r="BC4" s="381" t="n"/>
+      <c r="BD4" s="382" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="49" t="inlineStr">
+      <c r="A5" s="376" t="n"/>
+      <c r="B5" s="53" t="n"/>
+      <c r="C5" s="53" t="n"/>
+      <c r="D5" s="53" t="n"/>
+      <c r="E5" s="53" t="n"/>
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="53" t="n"/>
+      <c r="I5" s="53" t="n"/>
+      <c r="J5" s="53" t="n"/>
+      <c r="K5" s="377" t="n"/>
+      <c r="L5" s="384" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="316" t="inlineStr">
+      <c r="M5" s="53" t="n"/>
+      <c r="N5" s="53" t="n"/>
+      <c r="O5" s="53" t="n"/>
+      <c r="P5" s="53" t="n"/>
+      <c r="Q5" s="53" t="n"/>
+      <c r="R5" s="53" t="n"/>
+      <c r="S5" s="53" t="n"/>
+      <c r="T5" s="53" t="n"/>
+      <c r="U5" s="53" t="n"/>
+      <c r="V5" s="53" t="n"/>
+      <c r="W5" s="53" t="n"/>
+      <c r="X5" s="53" t="n"/>
+      <c r="Y5" s="53" t="n"/>
+      <c r="Z5" s="53" t="n"/>
+      <c r="AA5" s="53" t="n"/>
+      <c r="AB5" s="53" t="n"/>
+      <c r="AC5" s="53" t="n"/>
+      <c r="AD5" s="53" t="n"/>
+      <c r="AE5" s="53" t="n"/>
+      <c r="AF5" s="53" t="n"/>
+      <c r="AG5" s="53" t="n"/>
+      <c r="AH5" s="53" t="n"/>
+      <c r="AI5" s="53" t="n"/>
+      <c r="AJ5" s="53" t="n"/>
+      <c r="AK5" s="53" t="n"/>
+      <c r="AL5" s="53" t="n"/>
+      <c r="AM5" s="53" t="n"/>
+      <c r="AN5" s="53" t="n"/>
+      <c r="AO5" s="53" t="n"/>
+      <c r="AP5" s="377" t="n"/>
+      <c r="AQ5" s="378" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="317" t="n"/>
-      <c r="AS5" s="317" t="n"/>
-      <c r="AT5" s="317" t="n"/>
-      <c r="AU5" s="317" t="n"/>
-      <c r="AV5" s="318" t="n"/>
-      <c r="AW5" s="319" t="inlineStr">
+      <c r="AR5" s="379" t="n"/>
+      <c r="AS5" s="379" t="n"/>
+      <c r="AT5" s="379" t="n"/>
+      <c r="AU5" s="379" t="n"/>
+      <c r="AV5" s="380" t="n"/>
+      <c r="AW5" s="301" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="317" t="n"/>
-      <c r="AY5" s="317" t="n"/>
-      <c r="AZ5" s="317" t="n"/>
-      <c r="BA5" s="317" t="n"/>
-      <c r="BB5" s="317" t="n"/>
-      <c r="BC5" s="317" t="n"/>
-      <c r="BD5" s="320" t="n"/>
+      <c r="AX5" s="381" t="n"/>
+      <c r="AY5" s="381" t="n"/>
+      <c r="AZ5" s="381" t="n"/>
+      <c r="BA5" s="381" t="n"/>
+      <c r="BB5" s="381" t="n"/>
+      <c r="BC5" s="381" t="n"/>
+      <c r="BD5" s="382" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="238" t="n"/>
-      <c r="B6" s="238" t="n"/>
-      <c r="C6" s="238" t="n"/>
-      <c r="D6" s="238" t="n"/>
-      <c r="E6" s="238" t="n"/>
-      <c r="F6" s="238" t="n"/>
-      <c r="G6" s="238" t="n"/>
-      <c r="H6" s="238" t="n"/>
-      <c r="I6" s="238" t="n"/>
-      <c r="J6" s="238" t="n"/>
-      <c r="K6" s="238" t="n"/>
-      <c r="L6" s="238" t="n"/>
-      <c r="M6" s="238" t="n"/>
-      <c r="N6" s="238" t="n"/>
-      <c r="O6" s="238" t="n"/>
-      <c r="P6" s="238" t="n"/>
-      <c r="Q6" s="238" t="n"/>
-      <c r="R6" s="238" t="n"/>
-      <c r="S6" s="238" t="n"/>
-      <c r="T6" s="238" t="n"/>
-      <c r="U6" s="238" t="n"/>
-      <c r="V6" s="238" t="n"/>
-      <c r="W6" s="238" t="n"/>
-      <c r="X6" s="238" t="n"/>
-      <c r="Y6" s="238" t="n"/>
-      <c r="Z6" s="238" t="n"/>
-      <c r="AA6" s="238" t="n"/>
-      <c r="AB6" s="238" t="n"/>
-      <c r="AC6" s="238" t="n"/>
-      <c r="AD6" s="238" t="n"/>
-      <c r="AE6" s="238" t="n"/>
-      <c r="AF6" s="238" t="n"/>
-      <c r="AG6" s="238" t="n"/>
-      <c r="AH6" s="238" t="n"/>
-      <c r="AI6" s="238" t="n"/>
-      <c r="AJ6" s="238" t="n"/>
-      <c r="AK6" s="238" t="n"/>
-      <c r="AL6" s="238" t="n"/>
-      <c r="AM6" s="238" t="n"/>
-      <c r="AN6" s="238" t="n"/>
-      <c r="AO6" s="238" t="n"/>
-      <c r="AP6" s="238" t="n"/>
-      <c r="AQ6" s="238" t="n"/>
-      <c r="AR6" s="238" t="n"/>
-      <c r="AS6" s="238" t="n"/>
-      <c r="AT6" s="238" t="n"/>
-      <c r="AU6" s="238" t="n"/>
-      <c r="AV6" s="238" t="n"/>
-      <c r="AW6" s="238" t="n"/>
-      <c r="AX6" s="238" t="n"/>
-      <c r="AY6" s="238" t="n"/>
-      <c r="AZ6" s="238" t="n"/>
-      <c r="BA6" s="238" t="n"/>
-      <c r="BB6" s="238" t="n"/>
-      <c r="BC6" s="238" t="n"/>
-      <c r="BD6" s="238" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="385" t="n"/>
+      <c r="B6" s="386" t="n"/>
+      <c r="C6" s="386" t="n"/>
+      <c r="D6" s="386" t="n"/>
+      <c r="E6" s="386" t="n"/>
+      <c r="F6" s="386" t="n"/>
+      <c r="G6" s="386" t="n"/>
+      <c r="H6" s="386" t="n"/>
+      <c r="I6" s="386" t="n"/>
+      <c r="J6" s="386" t="n"/>
+      <c r="K6" s="387" t="n"/>
+      <c r="L6" s="386" t="n"/>
+      <c r="M6" s="386" t="n"/>
+      <c r="N6" s="386" t="n"/>
+      <c r="O6" s="386" t="n"/>
+      <c r="P6" s="386" t="n"/>
+      <c r="Q6" s="386" t="n"/>
+      <c r="R6" s="386" t="n"/>
+      <c r="S6" s="386" t="n"/>
+      <c r="T6" s="386" t="n"/>
+      <c r="U6" s="386" t="n"/>
+      <c r="V6" s="386" t="n"/>
+      <c r="W6" s="386" t="n"/>
+      <c r="X6" s="386" t="n"/>
+      <c r="Y6" s="386" t="n"/>
+      <c r="Z6" s="386" t="n"/>
+      <c r="AA6" s="386" t="n"/>
+      <c r="AB6" s="386" t="n"/>
+      <c r="AC6" s="386" t="n"/>
+      <c r="AD6" s="386" t="n"/>
+      <c r="AE6" s="386" t="n"/>
+      <c r="AF6" s="386" t="n"/>
+      <c r="AG6" s="386" t="n"/>
+      <c r="AH6" s="386" t="n"/>
+      <c r="AI6" s="386" t="n"/>
+      <c r="AJ6" s="386" t="n"/>
+      <c r="AK6" s="386" t="n"/>
+      <c r="AL6" s="386" t="n"/>
+      <c r="AM6" s="386" t="n"/>
+      <c r="AN6" s="386" t="n"/>
+      <c r="AO6" s="386" t="n"/>
+      <c r="AP6" s="387" t="n"/>
+      <c r="AQ6" s="388" t="n"/>
+      <c r="AR6" s="388" t="n"/>
+      <c r="AS6" s="388" t="n"/>
+      <c r="AT6" s="388" t="n"/>
+      <c r="AU6" s="388" t="n"/>
+      <c r="AV6" s="389" t="n"/>
+      <c r="AW6" s="390" t="n"/>
+      <c r="AX6" s="390" t="n"/>
+      <c r="AY6" s="390" t="n"/>
+      <c r="AZ6" s="390" t="n"/>
+      <c r="BA6" s="390" t="n"/>
+      <c r="BB6" s="390" t="n"/>
+      <c r="BC6" s="390" t="n"/>
+      <c r="BD6" s="391" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. ASSESSMENT HEADER</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="392" t="n"/>
+      <c r="B7" s="393" t="n"/>
+      <c r="C7" s="393" t="n"/>
+      <c r="D7" s="393" t="n"/>
+      <c r="E7" s="393" t="n"/>
+      <c r="F7" s="393" t="n"/>
+      <c r="G7" s="393" t="n"/>
+      <c r="H7" s="393" t="n"/>
+      <c r="I7" s="393" t="n"/>
+      <c r="J7" s="393" t="n"/>
+      <c r="K7" s="393" t="n"/>
+      <c r="L7" s="393" t="n"/>
+      <c r="M7" s="393" t="n"/>
+      <c r="N7" s="393" t="n"/>
+      <c r="O7" s="393" t="n"/>
+      <c r="P7" s="393" t="n"/>
+      <c r="Q7" s="393" t="n"/>
+      <c r="R7" s="393" t="n"/>
+      <c r="S7" s="393" t="n"/>
+      <c r="T7" s="393" t="n"/>
+      <c r="U7" s="393" t="n"/>
+      <c r="V7" s="393" t="n"/>
+      <c r="W7" s="393" t="n"/>
+      <c r="X7" s="393" t="n"/>
+      <c r="Y7" s="393" t="n"/>
+      <c r="Z7" s="393" t="n"/>
+      <c r="AA7" s="393" t="n"/>
+      <c r="AB7" s="393" t="n"/>
+      <c r="AC7" s="393" t="n"/>
+      <c r="AD7" s="393" t="n"/>
+      <c r="AE7" s="393" t="n"/>
+      <c r="AF7" s="393" t="n"/>
+      <c r="AG7" s="393" t="n"/>
+      <c r="AH7" s="393" t="n"/>
+      <c r="AI7" s="393" t="n"/>
+      <c r="AJ7" s="393" t="n"/>
+      <c r="AK7" s="393" t="n"/>
+      <c r="AL7" s="393" t="n"/>
+      <c r="AM7" s="393" t="n"/>
+      <c r="AN7" s="393" t="n"/>
+      <c r="AO7" s="393" t="n"/>
+      <c r="AP7" s="393" t="n"/>
+      <c r="AQ7" s="393" t="n"/>
+      <c r="AR7" s="393" t="n"/>
+      <c r="AS7" s="393" t="n"/>
+      <c r="AT7" s="393" t="n"/>
+      <c r="AU7" s="393" t="n"/>
+      <c r="AV7" s="393" t="n"/>
+      <c r="AW7" s="393" t="n"/>
+      <c r="AX7" s="393" t="n"/>
+      <c r="AY7" s="393" t="n"/>
+      <c r="AZ7" s="393" t="n"/>
+      <c r="BA7" s="393" t="n"/>
+      <c r="BB7" s="393" t="n"/>
+      <c r="BC7" s="393" t="n"/>
+      <c r="BD7" s="393" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="322" t="inlineStr">
@@ -5473,66 +4986,66 @@
       <c r="BD23" s="336" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="364" t="inlineStr">
+      <c r="A24" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Competence decisions shall be evidence-based. Record required tasks or behaviors, observed evidence, pass standard, restrictions, re-training needs and the explicit authorization decision.</t>
         </is>
       </c>
-      <c r="B24" s="365" t="n"/>
-      <c r="C24" s="365" t="n"/>
-      <c r="D24" s="365" t="n"/>
-      <c r="E24" s="365" t="n"/>
-      <c r="F24" s="365" t="n"/>
-      <c r="G24" s="365" t="n"/>
-      <c r="H24" s="365" t="n"/>
-      <c r="I24" s="365" t="n"/>
-      <c r="J24" s="365" t="n"/>
-      <c r="K24" s="365" t="n"/>
-      <c r="L24" s="365" t="n"/>
-      <c r="M24" s="365" t="n"/>
-      <c r="N24" s="365" t="n"/>
-      <c r="O24" s="365" t="n"/>
-      <c r="P24" s="365" t="n"/>
-      <c r="Q24" s="365" t="n"/>
-      <c r="R24" s="365" t="n"/>
-      <c r="S24" s="365" t="n"/>
-      <c r="T24" s="365" t="n"/>
-      <c r="U24" s="365" t="n"/>
-      <c r="V24" s="365" t="n"/>
-      <c r="W24" s="365" t="n"/>
-      <c r="X24" s="365" t="n"/>
-      <c r="Y24" s="365" t="n"/>
-      <c r="Z24" s="365" t="n"/>
-      <c r="AA24" s="365" t="n"/>
-      <c r="AB24" s="365" t="n"/>
-      <c r="AC24" s="365" t="n"/>
-      <c r="AD24" s="365" t="n"/>
-      <c r="AE24" s="365" t="n"/>
-      <c r="AF24" s="365" t="n"/>
-      <c r="AG24" s="365" t="n"/>
-      <c r="AH24" s="365" t="n"/>
-      <c r="AI24" s="365" t="n"/>
-      <c r="AJ24" s="365" t="n"/>
-      <c r="AK24" s="365" t="n"/>
-      <c r="AL24" s="365" t="n"/>
-      <c r="AM24" s="365" t="n"/>
-      <c r="AN24" s="365" t="n"/>
-      <c r="AO24" s="365" t="n"/>
-      <c r="AP24" s="365" t="n"/>
-      <c r="AQ24" s="365" t="n"/>
-      <c r="AR24" s="365" t="n"/>
-      <c r="AS24" s="365" t="n"/>
-      <c r="AT24" s="365" t="n"/>
-      <c r="AU24" s="365" t="n"/>
-      <c r="AV24" s="365" t="n"/>
-      <c r="AW24" s="365" t="n"/>
-      <c r="AX24" s="365" t="n"/>
-      <c r="AY24" s="365" t="n"/>
-      <c r="AZ24" s="365" t="n"/>
-      <c r="BA24" s="365" t="n"/>
-      <c r="BB24" s="365" t="n"/>
-      <c r="BC24" s="365" t="n"/>
-      <c r="BD24" s="366" t="n"/>
+      <c r="B24" s="394" t="n"/>
+      <c r="C24" s="394" t="n"/>
+      <c r="D24" s="394" t="n"/>
+      <c r="E24" s="394" t="n"/>
+      <c r="F24" s="394" t="n"/>
+      <c r="G24" s="394" t="n"/>
+      <c r="H24" s="394" t="n"/>
+      <c r="I24" s="394" t="n"/>
+      <c r="J24" s="394" t="n"/>
+      <c r="K24" s="394" t="n"/>
+      <c r="L24" s="394" t="n"/>
+      <c r="M24" s="394" t="n"/>
+      <c r="N24" s="394" t="n"/>
+      <c r="O24" s="394" t="n"/>
+      <c r="P24" s="394" t="n"/>
+      <c r="Q24" s="394" t="n"/>
+      <c r="R24" s="394" t="n"/>
+      <c r="S24" s="394" t="n"/>
+      <c r="T24" s="394" t="n"/>
+      <c r="U24" s="394" t="n"/>
+      <c r="V24" s="394" t="n"/>
+      <c r="W24" s="394" t="n"/>
+      <c r="X24" s="394" t="n"/>
+      <c r="Y24" s="394" t="n"/>
+      <c r="Z24" s="394" t="n"/>
+      <c r="AA24" s="394" t="n"/>
+      <c r="AB24" s="394" t="n"/>
+      <c r="AC24" s="394" t="n"/>
+      <c r="AD24" s="394" t="n"/>
+      <c r="AE24" s="394" t="n"/>
+      <c r="AF24" s="394" t="n"/>
+      <c r="AG24" s="394" t="n"/>
+      <c r="AH24" s="394" t="n"/>
+      <c r="AI24" s="394" t="n"/>
+      <c r="AJ24" s="394" t="n"/>
+      <c r="AK24" s="394" t="n"/>
+      <c r="AL24" s="394" t="n"/>
+      <c r="AM24" s="394" t="n"/>
+      <c r="AN24" s="394" t="n"/>
+      <c r="AO24" s="394" t="n"/>
+      <c r="AP24" s="394" t="n"/>
+      <c r="AQ24" s="394" t="n"/>
+      <c r="AR24" s="394" t="n"/>
+      <c r="AS24" s="394" t="n"/>
+      <c r="AT24" s="394" t="n"/>
+      <c r="AU24" s="394" t="n"/>
+      <c r="AV24" s="394" t="n"/>
+      <c r="AW24" s="394" t="n"/>
+      <c r="AX24" s="394" t="n"/>
+      <c r="AY24" s="394" t="n"/>
+      <c r="AZ24" s="394" t="n"/>
+      <c r="BA24" s="394" t="n"/>
+      <c r="BB24" s="394" t="n"/>
+      <c r="BC24" s="394" t="n"/>
+      <c r="BD24" s="395" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -5699,7 +5212,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="307" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -5711,7 +5224,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="217" t="inlineStr">
+      <c r="L1" s="403" t="inlineStr">
         <is>
           <t>COMPETENCE ASSESSMENT — ASSESSMENT CRITERIA</t>
         </is>
@@ -5745,7 +5258,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="308" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -5770,279 +5283,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="311" t="inlineStr">
+      <c r="A2" s="367" t="n"/>
+      <c r="B2" s="368" t="n"/>
+      <c r="C2" s="368" t="n"/>
+      <c r="D2" s="368" t="n"/>
+      <c r="E2" s="368" t="n"/>
+      <c r="F2" s="368" t="n"/>
+      <c r="G2" s="368" t="n"/>
+      <c r="H2" s="368" t="n"/>
+      <c r="I2" s="368" t="n"/>
+      <c r="J2" s="368" t="n"/>
+      <c r="K2" s="369" t="n"/>
+      <c r="L2" s="368" t="n"/>
+      <c r="M2" s="368" t="n"/>
+      <c r="N2" s="368" t="n"/>
+      <c r="O2" s="368" t="n"/>
+      <c r="P2" s="368" t="n"/>
+      <c r="Q2" s="368" t="n"/>
+      <c r="R2" s="368" t="n"/>
+      <c r="S2" s="368" t="n"/>
+      <c r="T2" s="368" t="n"/>
+      <c r="U2" s="368" t="n"/>
+      <c r="V2" s="368" t="n"/>
+      <c r="W2" s="368" t="n"/>
+      <c r="X2" s="368" t="n"/>
+      <c r="Y2" s="368" t="n"/>
+      <c r="Z2" s="368" t="n"/>
+      <c r="AA2" s="368" t="n"/>
+      <c r="AB2" s="368" t="n"/>
+      <c r="AC2" s="368" t="n"/>
+      <c r="AD2" s="368" t="n"/>
+      <c r="AE2" s="368" t="n"/>
+      <c r="AF2" s="368" t="n"/>
+      <c r="AG2" s="368" t="n"/>
+      <c r="AH2" s="368" t="n"/>
+      <c r="AI2" s="368" t="n"/>
+      <c r="AJ2" s="368" t="n"/>
+      <c r="AK2" s="368" t="n"/>
+      <c r="AL2" s="368" t="n"/>
+      <c r="AM2" s="368" t="n"/>
+      <c r="AN2" s="368" t="n"/>
+      <c r="AO2" s="368" t="n"/>
+      <c r="AP2" s="369" t="n"/>
+      <c r="AQ2" s="370" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="312" t="n"/>
-      <c r="AS2" s="312" t="n"/>
-      <c r="AT2" s="312" t="n"/>
-      <c r="AU2" s="312" t="n"/>
-      <c r="AV2" s="313" t="n"/>
-      <c r="AW2" s="314" t="inlineStr">
+      <c r="AR2" s="371" t="n"/>
+      <c r="AS2" s="371" t="n"/>
+      <c r="AT2" s="371" t="n"/>
+      <c r="AU2" s="371" t="n"/>
+      <c r="AV2" s="372" t="n"/>
+      <c r="AW2" s="373" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="312" t="n"/>
-      <c r="AY2" s="312" t="n"/>
-      <c r="AZ2" s="312" t="n"/>
-      <c r="BA2" s="312" t="n"/>
-      <c r="BB2" s="312" t="n"/>
-      <c r="BC2" s="312" t="n"/>
-      <c r="BD2" s="315" t="n"/>
+      <c r="AX2" s="374" t="n"/>
+      <c r="AY2" s="374" t="n"/>
+      <c r="AZ2" s="374" t="n"/>
+      <c r="BA2" s="374" t="n"/>
+      <c r="BB2" s="374" t="n"/>
+      <c r="BC2" s="374" t="n"/>
+      <c r="BD2" s="375" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="311" t="inlineStr">
+      <c r="A3" s="376" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="377" t="n"/>
+      <c r="L3" s="53" t="n"/>
+      <c r="M3" s="53" t="n"/>
+      <c r="N3" s="53" t="n"/>
+      <c r="O3" s="53" t="n"/>
+      <c r="P3" s="53" t="n"/>
+      <c r="Q3" s="53" t="n"/>
+      <c r="R3" s="53" t="n"/>
+      <c r="S3" s="53" t="n"/>
+      <c r="T3" s="53" t="n"/>
+      <c r="U3" s="53" t="n"/>
+      <c r="V3" s="53" t="n"/>
+      <c r="W3" s="53" t="n"/>
+      <c r="X3" s="53" t="n"/>
+      <c r="Y3" s="53" t="n"/>
+      <c r="Z3" s="53" t="n"/>
+      <c r="AA3" s="53" t="n"/>
+      <c r="AB3" s="53" t="n"/>
+      <c r="AC3" s="53" t="n"/>
+      <c r="AD3" s="53" t="n"/>
+      <c r="AE3" s="53" t="n"/>
+      <c r="AF3" s="53" t="n"/>
+      <c r="AG3" s="53" t="n"/>
+      <c r="AH3" s="53" t="n"/>
+      <c r="AI3" s="53" t="n"/>
+      <c r="AJ3" s="53" t="n"/>
+      <c r="AK3" s="53" t="n"/>
+      <c r="AL3" s="53" t="n"/>
+      <c r="AM3" s="53" t="n"/>
+      <c r="AN3" s="53" t="n"/>
+      <c r="AO3" s="53" t="n"/>
+      <c r="AP3" s="377" t="n"/>
+      <c r="AQ3" s="378" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="312" t="n"/>
-      <c r="AS3" s="312" t="n"/>
-      <c r="AT3" s="312" t="n"/>
-      <c r="AU3" s="312" t="n"/>
-      <c r="AV3" s="313" t="n"/>
-      <c r="AW3" s="314" t="inlineStr">
+      <c r="AR3" s="379" t="n"/>
+      <c r="AS3" s="379" t="n"/>
+      <c r="AT3" s="379" t="n"/>
+      <c r="AU3" s="379" t="n"/>
+      <c r="AV3" s="380" t="n"/>
+      <c r="AW3" s="301" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="312" t="n"/>
-      <c r="AY3" s="312" t="n"/>
-      <c r="AZ3" s="312" t="n"/>
-      <c r="BA3" s="312" t="n"/>
-      <c r="BB3" s="312" t="n"/>
-      <c r="BC3" s="312" t="n"/>
-      <c r="BD3" s="315" t="n"/>
+      <c r="AX3" s="381" t="n"/>
+      <c r="AY3" s="381" t="n"/>
+      <c r="AZ3" s="381" t="n"/>
+      <c r="BA3" s="381" t="n"/>
+      <c r="BB3" s="381" t="n"/>
+      <c r="BC3" s="381" t="n"/>
+      <c r="BD3" s="382" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="229" t="inlineStr">
+      <c r="A4" s="376" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="377" t="n"/>
+      <c r="L4" s="383" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="311" t="inlineStr">
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n"/>
+      <c r="O4" s="53" t="n"/>
+      <c r="P4" s="53" t="n"/>
+      <c r="Q4" s="53" t="n"/>
+      <c r="R4" s="53" t="n"/>
+      <c r="S4" s="53" t="n"/>
+      <c r="T4" s="53" t="n"/>
+      <c r="U4" s="53" t="n"/>
+      <c r="V4" s="53" t="n"/>
+      <c r="W4" s="53" t="n"/>
+      <c r="X4" s="53" t="n"/>
+      <c r="Y4" s="53" t="n"/>
+      <c r="Z4" s="53" t="n"/>
+      <c r="AA4" s="53" t="n"/>
+      <c r="AB4" s="53" t="n"/>
+      <c r="AC4" s="53" t="n"/>
+      <c r="AD4" s="53" t="n"/>
+      <c r="AE4" s="53" t="n"/>
+      <c r="AF4" s="53" t="n"/>
+      <c r="AG4" s="53" t="n"/>
+      <c r="AH4" s="53" t="n"/>
+      <c r="AI4" s="53" t="n"/>
+      <c r="AJ4" s="53" t="n"/>
+      <c r="AK4" s="53" t="n"/>
+      <c r="AL4" s="53" t="n"/>
+      <c r="AM4" s="53" t="n"/>
+      <c r="AN4" s="53" t="n"/>
+      <c r="AO4" s="53" t="n"/>
+      <c r="AP4" s="377" t="n"/>
+      <c r="AQ4" s="378" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="312" t="n"/>
-      <c r="AS4" s="312" t="n"/>
-      <c r="AT4" s="312" t="n"/>
-      <c r="AU4" s="312" t="n"/>
-      <c r="AV4" s="313" t="n"/>
-      <c r="AW4" s="314" t="inlineStr">
+      <c r="AR4" s="379" t="n"/>
+      <c r="AS4" s="379" t="n"/>
+      <c r="AT4" s="379" t="n"/>
+      <c r="AU4" s="379" t="n"/>
+      <c r="AV4" s="380" t="n"/>
+      <c r="AW4" s="301" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="312" t="n"/>
-      <c r="AY4" s="312" t="n"/>
-      <c r="AZ4" s="312" t="n"/>
-      <c r="BA4" s="312" t="n"/>
-      <c r="BB4" s="312" t="n"/>
-      <c r="BC4" s="312" t="n"/>
-      <c r="BD4" s="315" t="n"/>
+      <c r="AX4" s="381" t="n"/>
+      <c r="AY4" s="381" t="n"/>
+      <c r="AZ4" s="381" t="n"/>
+      <c r="BA4" s="381" t="n"/>
+      <c r="BB4" s="381" t="n"/>
+      <c r="BC4" s="381" t="n"/>
+      <c r="BD4" s="382" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="49" t="inlineStr">
+      <c r="A5" s="376" t="n"/>
+      <c r="B5" s="53" t="n"/>
+      <c r="C5" s="53" t="n"/>
+      <c r="D5" s="53" t="n"/>
+      <c r="E5" s="53" t="n"/>
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="53" t="n"/>
+      <c r="I5" s="53" t="n"/>
+      <c r="J5" s="53" t="n"/>
+      <c r="K5" s="377" t="n"/>
+      <c r="L5" s="384" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="316" t="inlineStr">
+      <c r="M5" s="53" t="n"/>
+      <c r="N5" s="53" t="n"/>
+      <c r="O5" s="53" t="n"/>
+      <c r="P5" s="53" t="n"/>
+      <c r="Q5" s="53" t="n"/>
+      <c r="R5" s="53" t="n"/>
+      <c r="S5" s="53" t="n"/>
+      <c r="T5" s="53" t="n"/>
+      <c r="U5" s="53" t="n"/>
+      <c r="V5" s="53" t="n"/>
+      <c r="W5" s="53" t="n"/>
+      <c r="X5" s="53" t="n"/>
+      <c r="Y5" s="53" t="n"/>
+      <c r="Z5" s="53" t="n"/>
+      <c r="AA5" s="53" t="n"/>
+      <c r="AB5" s="53" t="n"/>
+      <c r="AC5" s="53" t="n"/>
+      <c r="AD5" s="53" t="n"/>
+      <c r="AE5" s="53" t="n"/>
+      <c r="AF5" s="53" t="n"/>
+      <c r="AG5" s="53" t="n"/>
+      <c r="AH5" s="53" t="n"/>
+      <c r="AI5" s="53" t="n"/>
+      <c r="AJ5" s="53" t="n"/>
+      <c r="AK5" s="53" t="n"/>
+      <c r="AL5" s="53" t="n"/>
+      <c r="AM5" s="53" t="n"/>
+      <c r="AN5" s="53" t="n"/>
+      <c r="AO5" s="53" t="n"/>
+      <c r="AP5" s="377" t="n"/>
+      <c r="AQ5" s="378" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="317" t="n"/>
-      <c r="AS5" s="317" t="n"/>
-      <c r="AT5" s="317" t="n"/>
-      <c r="AU5" s="317" t="n"/>
-      <c r="AV5" s="318" t="n"/>
-      <c r="AW5" s="319" t="inlineStr">
+      <c r="AR5" s="379" t="n"/>
+      <c r="AS5" s="379" t="n"/>
+      <c r="AT5" s="379" t="n"/>
+      <c r="AU5" s="379" t="n"/>
+      <c r="AV5" s="380" t="n"/>
+      <c r="AW5" s="301" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="317" t="n"/>
-      <c r="AY5" s="317" t="n"/>
-      <c r="AZ5" s="317" t="n"/>
-      <c r="BA5" s="317" t="n"/>
-      <c r="BB5" s="317" t="n"/>
-      <c r="BC5" s="317" t="n"/>
-      <c r="BD5" s="320" t="n"/>
+      <c r="AX5" s="381" t="n"/>
+      <c r="AY5" s="381" t="n"/>
+      <c r="AZ5" s="381" t="n"/>
+      <c r="BA5" s="381" t="n"/>
+      <c r="BB5" s="381" t="n"/>
+      <c r="BC5" s="381" t="n"/>
+      <c r="BD5" s="382" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="238" t="n"/>
-      <c r="B6" s="238" t="n"/>
-      <c r="C6" s="238" t="n"/>
-      <c r="D6" s="238" t="n"/>
-      <c r="E6" s="238" t="n"/>
-      <c r="F6" s="238" t="n"/>
-      <c r="G6" s="238" t="n"/>
-      <c r="H6" s="238" t="n"/>
-      <c r="I6" s="238" t="n"/>
-      <c r="J6" s="238" t="n"/>
-      <c r="K6" s="238" t="n"/>
-      <c r="L6" s="238" t="n"/>
-      <c r="M6" s="238" t="n"/>
-      <c r="N6" s="238" t="n"/>
-      <c r="O6" s="238" t="n"/>
-      <c r="P6" s="238" t="n"/>
-      <c r="Q6" s="238" t="n"/>
-      <c r="R6" s="238" t="n"/>
-      <c r="S6" s="238" t="n"/>
-      <c r="T6" s="238" t="n"/>
-      <c r="U6" s="238" t="n"/>
-      <c r="V6" s="238" t="n"/>
-      <c r="W6" s="238" t="n"/>
-      <c r="X6" s="238" t="n"/>
-      <c r="Y6" s="238" t="n"/>
-      <c r="Z6" s="238" t="n"/>
-      <c r="AA6" s="238" t="n"/>
-      <c r="AB6" s="238" t="n"/>
-      <c r="AC6" s="238" t="n"/>
-      <c r="AD6" s="238" t="n"/>
-      <c r="AE6" s="238" t="n"/>
-      <c r="AF6" s="238" t="n"/>
-      <c r="AG6" s="238" t="n"/>
-      <c r="AH6" s="238" t="n"/>
-      <c r="AI6" s="238" t="n"/>
-      <c r="AJ6" s="238" t="n"/>
-      <c r="AK6" s="238" t="n"/>
-      <c r="AL6" s="238" t="n"/>
-      <c r="AM6" s="238" t="n"/>
-      <c r="AN6" s="238" t="n"/>
-      <c r="AO6" s="238" t="n"/>
-      <c r="AP6" s="238" t="n"/>
-      <c r="AQ6" s="238" t="n"/>
-      <c r="AR6" s="238" t="n"/>
-      <c r="AS6" s="238" t="n"/>
-      <c r="AT6" s="238" t="n"/>
-      <c r="AU6" s="238" t="n"/>
-      <c r="AV6" s="238" t="n"/>
-      <c r="AW6" s="238" t="n"/>
-      <c r="AX6" s="238" t="n"/>
-      <c r="AY6" s="238" t="n"/>
-      <c r="AZ6" s="238" t="n"/>
-      <c r="BA6" s="238" t="n"/>
-      <c r="BB6" s="238" t="n"/>
-      <c r="BC6" s="238" t="n"/>
-      <c r="BD6" s="238" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="385" t="n"/>
+      <c r="B6" s="386" t="n"/>
+      <c r="C6" s="386" t="n"/>
+      <c r="D6" s="386" t="n"/>
+      <c r="E6" s="386" t="n"/>
+      <c r="F6" s="386" t="n"/>
+      <c r="G6" s="386" t="n"/>
+      <c r="H6" s="386" t="n"/>
+      <c r="I6" s="386" t="n"/>
+      <c r="J6" s="386" t="n"/>
+      <c r="K6" s="387" t="n"/>
+      <c r="L6" s="386" t="n"/>
+      <c r="M6" s="386" t="n"/>
+      <c r="N6" s="386" t="n"/>
+      <c r="O6" s="386" t="n"/>
+      <c r="P6" s="386" t="n"/>
+      <c r="Q6" s="386" t="n"/>
+      <c r="R6" s="386" t="n"/>
+      <c r="S6" s="386" t="n"/>
+      <c r="T6" s="386" t="n"/>
+      <c r="U6" s="386" t="n"/>
+      <c r="V6" s="386" t="n"/>
+      <c r="W6" s="386" t="n"/>
+      <c r="X6" s="386" t="n"/>
+      <c r="Y6" s="386" t="n"/>
+      <c r="Z6" s="386" t="n"/>
+      <c r="AA6" s="386" t="n"/>
+      <c r="AB6" s="386" t="n"/>
+      <c r="AC6" s="386" t="n"/>
+      <c r="AD6" s="386" t="n"/>
+      <c r="AE6" s="386" t="n"/>
+      <c r="AF6" s="386" t="n"/>
+      <c r="AG6" s="386" t="n"/>
+      <c r="AH6" s="386" t="n"/>
+      <c r="AI6" s="386" t="n"/>
+      <c r="AJ6" s="386" t="n"/>
+      <c r="AK6" s="386" t="n"/>
+      <c r="AL6" s="386" t="n"/>
+      <c r="AM6" s="386" t="n"/>
+      <c r="AN6" s="386" t="n"/>
+      <c r="AO6" s="386" t="n"/>
+      <c r="AP6" s="387" t="n"/>
+      <c r="AQ6" s="388" t="n"/>
+      <c r="AR6" s="388" t="n"/>
+      <c r="AS6" s="388" t="n"/>
+      <c r="AT6" s="388" t="n"/>
+      <c r="AU6" s="388" t="n"/>
+      <c r="AV6" s="389" t="n"/>
+      <c r="AW6" s="390" t="n"/>
+      <c r="AX6" s="390" t="n"/>
+      <c r="AY6" s="390" t="n"/>
+      <c r="AZ6" s="390" t="n"/>
+      <c r="BA6" s="390" t="n"/>
+      <c r="BB6" s="390" t="n"/>
+      <c r="BC6" s="390" t="n"/>
+      <c r="BD6" s="391" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="392" t="n"/>
+      <c r="B7" s="393" t="n"/>
+      <c r="C7" s="393" t="n"/>
+      <c r="D7" s="393" t="n"/>
+      <c r="E7" s="393" t="n"/>
+      <c r="F7" s="393" t="n"/>
+      <c r="G7" s="393" t="n"/>
+      <c r="H7" s="393" t="n"/>
+      <c r="I7" s="393" t="n"/>
+      <c r="J7" s="393" t="n"/>
+      <c r="K7" s="393" t="n"/>
+      <c r="L7" s="393" t="n"/>
+      <c r="M7" s="393" t="n"/>
+      <c r="N7" s="393" t="n"/>
+      <c r="O7" s="393" t="n"/>
+      <c r="P7" s="393" t="n"/>
+      <c r="Q7" s="393" t="n"/>
+      <c r="R7" s="393" t="n"/>
+      <c r="S7" s="393" t="n"/>
+      <c r="T7" s="393" t="n"/>
+      <c r="U7" s="393" t="n"/>
+      <c r="V7" s="393" t="n"/>
+      <c r="W7" s="393" t="n"/>
+      <c r="X7" s="393" t="n"/>
+      <c r="Y7" s="393" t="n"/>
+      <c r="Z7" s="393" t="n"/>
+      <c r="AA7" s="393" t="n"/>
+      <c r="AB7" s="393" t="n"/>
+      <c r="AC7" s="393" t="n"/>
+      <c r="AD7" s="393" t="n"/>
+      <c r="AE7" s="393" t="n"/>
+      <c r="AF7" s="393" t="n"/>
+      <c r="AG7" s="393" t="n"/>
+      <c r="AH7" s="393" t="n"/>
+      <c r="AI7" s="393" t="n"/>
+      <c r="AJ7" s="393" t="n"/>
+      <c r="AK7" s="393" t="n"/>
+      <c r="AL7" s="393" t="n"/>
+      <c r="AM7" s="393" t="n"/>
+      <c r="AN7" s="393" t="n"/>
+      <c r="AO7" s="393" t="n"/>
+      <c r="AP7" s="393" t="n"/>
+      <c r="AQ7" s="393" t="n"/>
+      <c r="AR7" s="393" t="n"/>
+      <c r="AS7" s="393" t="n"/>
+      <c r="AT7" s="393" t="n"/>
+      <c r="AU7" s="393" t="n"/>
+      <c r="AV7" s="393" t="n"/>
+      <c r="AW7" s="393" t="n"/>
+      <c r="AX7" s="393" t="n"/>
+      <c r="AY7" s="393" t="n"/>
+      <c r="AZ7" s="393" t="n"/>
+      <c r="BA7" s="393" t="n"/>
+      <c r="BB7" s="393" t="n"/>
+      <c r="BC7" s="393" t="n"/>
+      <c r="BD7" s="393" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="322" t="inlineStr">
@@ -6664,67 +6290,67 @@
       <c r="BC17" s="328" t="n"/>
       <c r="BD17" s="332" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="321" t="inlineStr">
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="22" t="n"/>
-      <c r="R18" s="22" t="n"/>
-      <c r="S18" s="22" t="n"/>
-      <c r="T18" s="22" t="n"/>
-      <c r="U18" s="22" t="n"/>
-      <c r="V18" s="22" t="n"/>
-      <c r="W18" s="22" t="n"/>
-      <c r="X18" s="22" t="n"/>
-      <c r="Y18" s="22" t="n"/>
-      <c r="Z18" s="22" t="n"/>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="22" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="22" t="n"/>
-      <c r="AE18" s="22" t="n"/>
-      <c r="AF18" s="22" t="n"/>
-      <c r="AG18" s="22" t="n"/>
-      <c r="AH18" s="22" t="n"/>
-      <c r="AI18" s="22" t="n"/>
-      <c r="AJ18" s="22" t="n"/>
-      <c r="AK18" s="22" t="n"/>
-      <c r="AL18" s="22" t="n"/>
-      <c r="AM18" s="22" t="n"/>
-      <c r="AN18" s="22" t="n"/>
-      <c r="AO18" s="22" t="n"/>
-      <c r="AP18" s="22" t="n"/>
-      <c r="AQ18" s="22" t="n"/>
-      <c r="AR18" s="22" t="n"/>
-      <c r="AS18" s="22" t="n"/>
-      <c r="AT18" s="22" t="n"/>
-      <c r="AU18" s="22" t="n"/>
-      <c r="AV18" s="22" t="n"/>
-      <c r="AW18" s="22" t="n"/>
-      <c r="AX18" s="22" t="n"/>
-      <c r="AY18" s="22" t="n"/>
-      <c r="AZ18" s="22" t="n"/>
-      <c r="BA18" s="22" t="n"/>
-      <c r="BB18" s="22" t="n"/>
-      <c r="BC18" s="22" t="n"/>
-      <c r="BD18" s="23" t="n"/>
+      <c r="B18" s="394" t="n"/>
+      <c r="C18" s="394" t="n"/>
+      <c r="D18" s="394" t="n"/>
+      <c r="E18" s="394" t="n"/>
+      <c r="F18" s="394" t="n"/>
+      <c r="G18" s="394" t="n"/>
+      <c r="H18" s="394" t="n"/>
+      <c r="I18" s="394" t="n"/>
+      <c r="J18" s="394" t="n"/>
+      <c r="K18" s="394" t="n"/>
+      <c r="L18" s="394" t="n"/>
+      <c r="M18" s="394" t="n"/>
+      <c r="N18" s="394" t="n"/>
+      <c r="O18" s="394" t="n"/>
+      <c r="P18" s="394" t="n"/>
+      <c r="Q18" s="394" t="n"/>
+      <c r="R18" s="394" t="n"/>
+      <c r="S18" s="394" t="n"/>
+      <c r="T18" s="394" t="n"/>
+      <c r="U18" s="394" t="n"/>
+      <c r="V18" s="394" t="n"/>
+      <c r="W18" s="394" t="n"/>
+      <c r="X18" s="394" t="n"/>
+      <c r="Y18" s="394" t="n"/>
+      <c r="Z18" s="394" t="n"/>
+      <c r="AA18" s="394" t="n"/>
+      <c r="AB18" s="394" t="n"/>
+      <c r="AC18" s="394" t="n"/>
+      <c r="AD18" s="394" t="n"/>
+      <c r="AE18" s="394" t="n"/>
+      <c r="AF18" s="394" t="n"/>
+      <c r="AG18" s="394" t="n"/>
+      <c r="AH18" s="394" t="n"/>
+      <c r="AI18" s="394" t="n"/>
+      <c r="AJ18" s="394" t="n"/>
+      <c r="AK18" s="394" t="n"/>
+      <c r="AL18" s="394" t="n"/>
+      <c r="AM18" s="394" t="n"/>
+      <c r="AN18" s="394" t="n"/>
+      <c r="AO18" s="394" t="n"/>
+      <c r="AP18" s="394" t="n"/>
+      <c r="AQ18" s="394" t="n"/>
+      <c r="AR18" s="394" t="n"/>
+      <c r="AS18" s="394" t="n"/>
+      <c r="AT18" s="394" t="n"/>
+      <c r="AU18" s="394" t="n"/>
+      <c r="AV18" s="394" t="n"/>
+      <c r="AW18" s="394" t="n"/>
+      <c r="AX18" s="394" t="n"/>
+      <c r="AY18" s="394" t="n"/>
+      <c r="AZ18" s="394" t="n"/>
+      <c r="BA18" s="394" t="n"/>
+      <c r="BB18" s="394" t="n"/>
+      <c r="BC18" s="394" t="n"/>
+      <c r="BD18" s="395" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -6876,7 +6502,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="307" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -6888,7 +6514,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="217" t="inlineStr">
+      <c r="L1" s="403" t="inlineStr">
         <is>
           <t>COMPETENCE ASSESSMENT — EVIDENCE REFERENCE REGISTER</t>
         </is>
@@ -6922,7 +6548,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="308" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6947,279 +6573,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="311" t="inlineStr">
+      <c r="A2" s="367" t="n"/>
+      <c r="B2" s="368" t="n"/>
+      <c r="C2" s="368" t="n"/>
+      <c r="D2" s="368" t="n"/>
+      <c r="E2" s="368" t="n"/>
+      <c r="F2" s="368" t="n"/>
+      <c r="G2" s="368" t="n"/>
+      <c r="H2" s="368" t="n"/>
+      <c r="I2" s="368" t="n"/>
+      <c r="J2" s="368" t="n"/>
+      <c r="K2" s="369" t="n"/>
+      <c r="L2" s="368" t="n"/>
+      <c r="M2" s="368" t="n"/>
+      <c r="N2" s="368" t="n"/>
+      <c r="O2" s="368" t="n"/>
+      <c r="P2" s="368" t="n"/>
+      <c r="Q2" s="368" t="n"/>
+      <c r="R2" s="368" t="n"/>
+      <c r="S2" s="368" t="n"/>
+      <c r="T2" s="368" t="n"/>
+      <c r="U2" s="368" t="n"/>
+      <c r="V2" s="368" t="n"/>
+      <c r="W2" s="368" t="n"/>
+      <c r="X2" s="368" t="n"/>
+      <c r="Y2" s="368" t="n"/>
+      <c r="Z2" s="368" t="n"/>
+      <c r="AA2" s="368" t="n"/>
+      <c r="AB2" s="368" t="n"/>
+      <c r="AC2" s="368" t="n"/>
+      <c r="AD2" s="368" t="n"/>
+      <c r="AE2" s="368" t="n"/>
+      <c r="AF2" s="368" t="n"/>
+      <c r="AG2" s="368" t="n"/>
+      <c r="AH2" s="368" t="n"/>
+      <c r="AI2" s="368" t="n"/>
+      <c r="AJ2" s="368" t="n"/>
+      <c r="AK2" s="368" t="n"/>
+      <c r="AL2" s="368" t="n"/>
+      <c r="AM2" s="368" t="n"/>
+      <c r="AN2" s="368" t="n"/>
+      <c r="AO2" s="368" t="n"/>
+      <c r="AP2" s="369" t="n"/>
+      <c r="AQ2" s="370" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="312" t="n"/>
-      <c r="AS2" s="312" t="n"/>
-      <c r="AT2" s="312" t="n"/>
-      <c r="AU2" s="312" t="n"/>
-      <c r="AV2" s="313" t="n"/>
-      <c r="AW2" s="314" t="inlineStr">
+      <c r="AR2" s="371" t="n"/>
+      <c r="AS2" s="371" t="n"/>
+      <c r="AT2" s="371" t="n"/>
+      <c r="AU2" s="371" t="n"/>
+      <c r="AV2" s="372" t="n"/>
+      <c r="AW2" s="373" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="312" t="n"/>
-      <c r="AY2" s="312" t="n"/>
-      <c r="AZ2" s="312" t="n"/>
-      <c r="BA2" s="312" t="n"/>
-      <c r="BB2" s="312" t="n"/>
-      <c r="BC2" s="312" t="n"/>
-      <c r="BD2" s="315" t="n"/>
+      <c r="AX2" s="374" t="n"/>
+      <c r="AY2" s="374" t="n"/>
+      <c r="AZ2" s="374" t="n"/>
+      <c r="BA2" s="374" t="n"/>
+      <c r="BB2" s="374" t="n"/>
+      <c r="BC2" s="374" t="n"/>
+      <c r="BD2" s="375" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="311" t="inlineStr">
+      <c r="A3" s="376" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="377" t="n"/>
+      <c r="L3" s="53" t="n"/>
+      <c r="M3" s="53" t="n"/>
+      <c r="N3" s="53" t="n"/>
+      <c r="O3" s="53" t="n"/>
+      <c r="P3" s="53" t="n"/>
+      <c r="Q3" s="53" t="n"/>
+      <c r="R3" s="53" t="n"/>
+      <c r="S3" s="53" t="n"/>
+      <c r="T3" s="53" t="n"/>
+      <c r="U3" s="53" t="n"/>
+      <c r="V3" s="53" t="n"/>
+      <c r="W3" s="53" t="n"/>
+      <c r="X3" s="53" t="n"/>
+      <c r="Y3" s="53" t="n"/>
+      <c r="Z3" s="53" t="n"/>
+      <c r="AA3" s="53" t="n"/>
+      <c r="AB3" s="53" t="n"/>
+      <c r="AC3" s="53" t="n"/>
+      <c r="AD3" s="53" t="n"/>
+      <c r="AE3" s="53" t="n"/>
+      <c r="AF3" s="53" t="n"/>
+      <c r="AG3" s="53" t="n"/>
+      <c r="AH3" s="53" t="n"/>
+      <c r="AI3" s="53" t="n"/>
+      <c r="AJ3" s="53" t="n"/>
+      <c r="AK3" s="53" t="n"/>
+      <c r="AL3" s="53" t="n"/>
+      <c r="AM3" s="53" t="n"/>
+      <c r="AN3" s="53" t="n"/>
+      <c r="AO3" s="53" t="n"/>
+      <c r="AP3" s="377" t="n"/>
+      <c r="AQ3" s="378" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="312" t="n"/>
-      <c r="AS3" s="312" t="n"/>
-      <c r="AT3" s="312" t="n"/>
-      <c r="AU3" s="312" t="n"/>
-      <c r="AV3" s="313" t="n"/>
-      <c r="AW3" s="314" t="inlineStr">
+      <c r="AR3" s="379" t="n"/>
+      <c r="AS3" s="379" t="n"/>
+      <c r="AT3" s="379" t="n"/>
+      <c r="AU3" s="379" t="n"/>
+      <c r="AV3" s="380" t="n"/>
+      <c r="AW3" s="301" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="312" t="n"/>
-      <c r="AY3" s="312" t="n"/>
-      <c r="AZ3" s="312" t="n"/>
-      <c r="BA3" s="312" t="n"/>
-      <c r="BB3" s="312" t="n"/>
-      <c r="BC3" s="312" t="n"/>
-      <c r="BD3" s="315" t="n"/>
+      <c r="AX3" s="381" t="n"/>
+      <c r="AY3" s="381" t="n"/>
+      <c r="AZ3" s="381" t="n"/>
+      <c r="BA3" s="381" t="n"/>
+      <c r="BB3" s="381" t="n"/>
+      <c r="BC3" s="381" t="n"/>
+      <c r="BD3" s="382" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="229" t="inlineStr">
+      <c r="A4" s="376" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="377" t="n"/>
+      <c r="L4" s="383" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="311" t="inlineStr">
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n"/>
+      <c r="O4" s="53" t="n"/>
+      <c r="P4" s="53" t="n"/>
+      <c r="Q4" s="53" t="n"/>
+      <c r="R4" s="53" t="n"/>
+      <c r="S4" s="53" t="n"/>
+      <c r="T4" s="53" t="n"/>
+      <c r="U4" s="53" t="n"/>
+      <c r="V4" s="53" t="n"/>
+      <c r="W4" s="53" t="n"/>
+      <c r="X4" s="53" t="n"/>
+      <c r="Y4" s="53" t="n"/>
+      <c r="Z4" s="53" t="n"/>
+      <c r="AA4" s="53" t="n"/>
+      <c r="AB4" s="53" t="n"/>
+      <c r="AC4" s="53" t="n"/>
+      <c r="AD4" s="53" t="n"/>
+      <c r="AE4" s="53" t="n"/>
+      <c r="AF4" s="53" t="n"/>
+      <c r="AG4" s="53" t="n"/>
+      <c r="AH4" s="53" t="n"/>
+      <c r="AI4" s="53" t="n"/>
+      <c r="AJ4" s="53" t="n"/>
+      <c r="AK4" s="53" t="n"/>
+      <c r="AL4" s="53" t="n"/>
+      <c r="AM4" s="53" t="n"/>
+      <c r="AN4" s="53" t="n"/>
+      <c r="AO4" s="53" t="n"/>
+      <c r="AP4" s="377" t="n"/>
+      <c r="AQ4" s="378" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="312" t="n"/>
-      <c r="AS4" s="312" t="n"/>
-      <c r="AT4" s="312" t="n"/>
-      <c r="AU4" s="312" t="n"/>
-      <c r="AV4" s="313" t="n"/>
-      <c r="AW4" s="314" t="inlineStr">
+      <c r="AR4" s="379" t="n"/>
+      <c r="AS4" s="379" t="n"/>
+      <c r="AT4" s="379" t="n"/>
+      <c r="AU4" s="379" t="n"/>
+      <c r="AV4" s="380" t="n"/>
+      <c r="AW4" s="301" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="312" t="n"/>
-      <c r="AY4" s="312" t="n"/>
-      <c r="AZ4" s="312" t="n"/>
-      <c r="BA4" s="312" t="n"/>
-      <c r="BB4" s="312" t="n"/>
-      <c r="BC4" s="312" t="n"/>
-      <c r="BD4" s="315" t="n"/>
+      <c r="AX4" s="381" t="n"/>
+      <c r="AY4" s="381" t="n"/>
+      <c r="AZ4" s="381" t="n"/>
+      <c r="BA4" s="381" t="n"/>
+      <c r="BB4" s="381" t="n"/>
+      <c r="BC4" s="381" t="n"/>
+      <c r="BD4" s="382" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="49" t="inlineStr">
+      <c r="A5" s="376" t="n"/>
+      <c r="B5" s="53" t="n"/>
+      <c r="C5" s="53" t="n"/>
+      <c r="D5" s="53" t="n"/>
+      <c r="E5" s="53" t="n"/>
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="53" t="n"/>
+      <c r="I5" s="53" t="n"/>
+      <c r="J5" s="53" t="n"/>
+      <c r="K5" s="377" t="n"/>
+      <c r="L5" s="384" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="316" t="inlineStr">
+      <c r="M5" s="53" t="n"/>
+      <c r="N5" s="53" t="n"/>
+      <c r="O5" s="53" t="n"/>
+      <c r="P5" s="53" t="n"/>
+      <c r="Q5" s="53" t="n"/>
+      <c r="R5" s="53" t="n"/>
+      <c r="S5" s="53" t="n"/>
+      <c r="T5" s="53" t="n"/>
+      <c r="U5" s="53" t="n"/>
+      <c r="V5" s="53" t="n"/>
+      <c r="W5" s="53" t="n"/>
+      <c r="X5" s="53" t="n"/>
+      <c r="Y5" s="53" t="n"/>
+      <c r="Z5" s="53" t="n"/>
+      <c r="AA5" s="53" t="n"/>
+      <c r="AB5" s="53" t="n"/>
+      <c r="AC5" s="53" t="n"/>
+      <c r="AD5" s="53" t="n"/>
+      <c r="AE5" s="53" t="n"/>
+      <c r="AF5" s="53" t="n"/>
+      <c r="AG5" s="53" t="n"/>
+      <c r="AH5" s="53" t="n"/>
+      <c r="AI5" s="53" t="n"/>
+      <c r="AJ5" s="53" t="n"/>
+      <c r="AK5" s="53" t="n"/>
+      <c r="AL5" s="53" t="n"/>
+      <c r="AM5" s="53" t="n"/>
+      <c r="AN5" s="53" t="n"/>
+      <c r="AO5" s="53" t="n"/>
+      <c r="AP5" s="377" t="n"/>
+      <c r="AQ5" s="378" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="317" t="n"/>
-      <c r="AS5" s="317" t="n"/>
-      <c r="AT5" s="317" t="n"/>
-      <c r="AU5" s="317" t="n"/>
-      <c r="AV5" s="318" t="n"/>
-      <c r="AW5" s="319" t="inlineStr">
+      <c r="AR5" s="379" t="n"/>
+      <c r="AS5" s="379" t="n"/>
+      <c r="AT5" s="379" t="n"/>
+      <c r="AU5" s="379" t="n"/>
+      <c r="AV5" s="380" t="n"/>
+      <c r="AW5" s="301" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="317" t="n"/>
-      <c r="AY5" s="317" t="n"/>
-      <c r="AZ5" s="317" t="n"/>
-      <c r="BA5" s="317" t="n"/>
-      <c r="BB5" s="317" t="n"/>
-      <c r="BC5" s="317" t="n"/>
-      <c r="BD5" s="320" t="n"/>
+      <c r="AX5" s="381" t="n"/>
+      <c r="AY5" s="381" t="n"/>
+      <c r="AZ5" s="381" t="n"/>
+      <c r="BA5" s="381" t="n"/>
+      <c r="BB5" s="381" t="n"/>
+      <c r="BC5" s="381" t="n"/>
+      <c r="BD5" s="382" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="238" t="n"/>
-      <c r="B6" s="238" t="n"/>
-      <c r="C6" s="238" t="n"/>
-      <c r="D6" s="238" t="n"/>
-      <c r="E6" s="238" t="n"/>
-      <c r="F6" s="238" t="n"/>
-      <c r="G6" s="238" t="n"/>
-      <c r="H6" s="238" t="n"/>
-      <c r="I6" s="238" t="n"/>
-      <c r="J6" s="238" t="n"/>
-      <c r="K6" s="238" t="n"/>
-      <c r="L6" s="238" t="n"/>
-      <c r="M6" s="238" t="n"/>
-      <c r="N6" s="238" t="n"/>
-      <c r="O6" s="238" t="n"/>
-      <c r="P6" s="238" t="n"/>
-      <c r="Q6" s="238" t="n"/>
-      <c r="R6" s="238" t="n"/>
-      <c r="S6" s="238" t="n"/>
-      <c r="T6" s="238" t="n"/>
-      <c r="U6" s="238" t="n"/>
-      <c r="V6" s="238" t="n"/>
-      <c r="W6" s="238" t="n"/>
-      <c r="X6" s="238" t="n"/>
-      <c r="Y6" s="238" t="n"/>
-      <c r="Z6" s="238" t="n"/>
-      <c r="AA6" s="238" t="n"/>
-      <c r="AB6" s="238" t="n"/>
-      <c r="AC6" s="238" t="n"/>
-      <c r="AD6" s="238" t="n"/>
-      <c r="AE6" s="238" t="n"/>
-      <c r="AF6" s="238" t="n"/>
-      <c r="AG6" s="238" t="n"/>
-      <c r="AH6" s="238" t="n"/>
-      <c r="AI6" s="238" t="n"/>
-      <c r="AJ6" s="238" t="n"/>
-      <c r="AK6" s="238" t="n"/>
-      <c r="AL6" s="238" t="n"/>
-      <c r="AM6" s="238" t="n"/>
-      <c r="AN6" s="238" t="n"/>
-      <c r="AO6" s="238" t="n"/>
-      <c r="AP6" s="238" t="n"/>
-      <c r="AQ6" s="238" t="n"/>
-      <c r="AR6" s="238" t="n"/>
-      <c r="AS6" s="238" t="n"/>
-      <c r="AT6" s="238" t="n"/>
-      <c r="AU6" s="238" t="n"/>
-      <c r="AV6" s="238" t="n"/>
-      <c r="AW6" s="238" t="n"/>
-      <c r="AX6" s="238" t="n"/>
-      <c r="AY6" s="238" t="n"/>
-      <c r="AZ6" s="238" t="n"/>
-      <c r="BA6" s="238" t="n"/>
-      <c r="BB6" s="238" t="n"/>
-      <c r="BC6" s="238" t="n"/>
-      <c r="BD6" s="238" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="385" t="n"/>
+      <c r="B6" s="386" t="n"/>
+      <c r="C6" s="386" t="n"/>
+      <c r="D6" s="386" t="n"/>
+      <c r="E6" s="386" t="n"/>
+      <c r="F6" s="386" t="n"/>
+      <c r="G6" s="386" t="n"/>
+      <c r="H6" s="386" t="n"/>
+      <c r="I6" s="386" t="n"/>
+      <c r="J6" s="386" t="n"/>
+      <c r="K6" s="387" t="n"/>
+      <c r="L6" s="386" t="n"/>
+      <c r="M6" s="386" t="n"/>
+      <c r="N6" s="386" t="n"/>
+      <c r="O6" s="386" t="n"/>
+      <c r="P6" s="386" t="n"/>
+      <c r="Q6" s="386" t="n"/>
+      <c r="R6" s="386" t="n"/>
+      <c r="S6" s="386" t="n"/>
+      <c r="T6" s="386" t="n"/>
+      <c r="U6" s="386" t="n"/>
+      <c r="V6" s="386" t="n"/>
+      <c r="W6" s="386" t="n"/>
+      <c r="X6" s="386" t="n"/>
+      <c r="Y6" s="386" t="n"/>
+      <c r="Z6" s="386" t="n"/>
+      <c r="AA6" s="386" t="n"/>
+      <c r="AB6" s="386" t="n"/>
+      <c r="AC6" s="386" t="n"/>
+      <c r="AD6" s="386" t="n"/>
+      <c r="AE6" s="386" t="n"/>
+      <c r="AF6" s="386" t="n"/>
+      <c r="AG6" s="386" t="n"/>
+      <c r="AH6" s="386" t="n"/>
+      <c r="AI6" s="386" t="n"/>
+      <c r="AJ6" s="386" t="n"/>
+      <c r="AK6" s="386" t="n"/>
+      <c r="AL6" s="386" t="n"/>
+      <c r="AM6" s="386" t="n"/>
+      <c r="AN6" s="386" t="n"/>
+      <c r="AO6" s="386" t="n"/>
+      <c r="AP6" s="387" t="n"/>
+      <c r="AQ6" s="388" t="n"/>
+      <c r="AR6" s="388" t="n"/>
+      <c r="AS6" s="388" t="n"/>
+      <c r="AT6" s="388" t="n"/>
+      <c r="AU6" s="388" t="n"/>
+      <c r="AV6" s="389" t="n"/>
+      <c r="AW6" s="390" t="n"/>
+      <c r="AX6" s="390" t="n"/>
+      <c r="AY6" s="390" t="n"/>
+      <c r="AZ6" s="390" t="n"/>
+      <c r="BA6" s="390" t="n"/>
+      <c r="BB6" s="390" t="n"/>
+      <c r="BC6" s="390" t="n"/>
+      <c r="BD6" s="391" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="392" t="n"/>
+      <c r="B7" s="393" t="n"/>
+      <c r="C7" s="393" t="n"/>
+      <c r="D7" s="393" t="n"/>
+      <c r="E7" s="393" t="n"/>
+      <c r="F7" s="393" t="n"/>
+      <c r="G7" s="393" t="n"/>
+      <c r="H7" s="393" t="n"/>
+      <c r="I7" s="393" t="n"/>
+      <c r="J7" s="393" t="n"/>
+      <c r="K7" s="393" t="n"/>
+      <c r="L7" s="393" t="n"/>
+      <c r="M7" s="393" t="n"/>
+      <c r="N7" s="393" t="n"/>
+      <c r="O7" s="393" t="n"/>
+      <c r="P7" s="393" t="n"/>
+      <c r="Q7" s="393" t="n"/>
+      <c r="R7" s="393" t="n"/>
+      <c r="S7" s="393" t="n"/>
+      <c r="T7" s="393" t="n"/>
+      <c r="U7" s="393" t="n"/>
+      <c r="V7" s="393" t="n"/>
+      <c r="W7" s="393" t="n"/>
+      <c r="X7" s="393" t="n"/>
+      <c r="Y7" s="393" t="n"/>
+      <c r="Z7" s="393" t="n"/>
+      <c r="AA7" s="393" t="n"/>
+      <c r="AB7" s="393" t="n"/>
+      <c r="AC7" s="393" t="n"/>
+      <c r="AD7" s="393" t="n"/>
+      <c r="AE7" s="393" t="n"/>
+      <c r="AF7" s="393" t="n"/>
+      <c r="AG7" s="393" t="n"/>
+      <c r="AH7" s="393" t="n"/>
+      <c r="AI7" s="393" t="n"/>
+      <c r="AJ7" s="393" t="n"/>
+      <c r="AK7" s="393" t="n"/>
+      <c r="AL7" s="393" t="n"/>
+      <c r="AM7" s="393" t="n"/>
+      <c r="AN7" s="393" t="n"/>
+      <c r="AO7" s="393" t="n"/>
+      <c r="AP7" s="393" t="n"/>
+      <c r="AQ7" s="393" t="n"/>
+      <c r="AR7" s="393" t="n"/>
+      <c r="AS7" s="393" t="n"/>
+      <c r="AT7" s="393" t="n"/>
+      <c r="AU7" s="393" t="n"/>
+      <c r="AV7" s="393" t="n"/>
+      <c r="AW7" s="393" t="n"/>
+      <c r="AX7" s="393" t="n"/>
+      <c r="AY7" s="393" t="n"/>
+      <c r="AZ7" s="393" t="n"/>
+      <c r="BA7" s="393" t="n"/>
+      <c r="BB7" s="393" t="n"/>
+      <c r="BC7" s="393" t="n"/>
+      <c r="BD7" s="393" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="322" t="inlineStr">
@@ -7853,67 +7592,67 @@
       <c r="BC17" s="328" t="n"/>
       <c r="BD17" s="332" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="321" t="inlineStr">
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="22" t="n"/>
-      <c r="R18" s="22" t="n"/>
-      <c r="S18" s="22" t="n"/>
-      <c r="T18" s="22" t="n"/>
-      <c r="U18" s="22" t="n"/>
-      <c r="V18" s="22" t="n"/>
-      <c r="W18" s="22" t="n"/>
-      <c r="X18" s="22" t="n"/>
-      <c r="Y18" s="22" t="n"/>
-      <c r="Z18" s="22" t="n"/>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="22" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="22" t="n"/>
-      <c r="AE18" s="22" t="n"/>
-      <c r="AF18" s="22" t="n"/>
-      <c r="AG18" s="22" t="n"/>
-      <c r="AH18" s="22" t="n"/>
-      <c r="AI18" s="22" t="n"/>
-      <c r="AJ18" s="22" t="n"/>
-      <c r="AK18" s="22" t="n"/>
-      <c r="AL18" s="22" t="n"/>
-      <c r="AM18" s="22" t="n"/>
-      <c r="AN18" s="22" t="n"/>
-      <c r="AO18" s="22" t="n"/>
-      <c r="AP18" s="22" t="n"/>
-      <c r="AQ18" s="22" t="n"/>
-      <c r="AR18" s="22" t="n"/>
-      <c r="AS18" s="22" t="n"/>
-      <c r="AT18" s="22" t="n"/>
-      <c r="AU18" s="22" t="n"/>
-      <c r="AV18" s="22" t="n"/>
-      <c r="AW18" s="22" t="n"/>
-      <c r="AX18" s="22" t="n"/>
-      <c r="AY18" s="22" t="n"/>
-      <c r="AZ18" s="22" t="n"/>
-      <c r="BA18" s="22" t="n"/>
-      <c r="BB18" s="22" t="n"/>
-      <c r="BC18" s="22" t="n"/>
-      <c r="BD18" s="23" t="n"/>
+      <c r="B18" s="394" t="n"/>
+      <c r="C18" s="394" t="n"/>
+      <c r="D18" s="394" t="n"/>
+      <c r="E18" s="394" t="n"/>
+      <c r="F18" s="394" t="n"/>
+      <c r="G18" s="394" t="n"/>
+      <c r="H18" s="394" t="n"/>
+      <c r="I18" s="394" t="n"/>
+      <c r="J18" s="394" t="n"/>
+      <c r="K18" s="394" t="n"/>
+      <c r="L18" s="394" t="n"/>
+      <c r="M18" s="394" t="n"/>
+      <c r="N18" s="394" t="n"/>
+      <c r="O18" s="394" t="n"/>
+      <c r="P18" s="394" t="n"/>
+      <c r="Q18" s="394" t="n"/>
+      <c r="R18" s="394" t="n"/>
+      <c r="S18" s="394" t="n"/>
+      <c r="T18" s="394" t="n"/>
+      <c r="U18" s="394" t="n"/>
+      <c r="V18" s="394" t="n"/>
+      <c r="W18" s="394" t="n"/>
+      <c r="X18" s="394" t="n"/>
+      <c r="Y18" s="394" t="n"/>
+      <c r="Z18" s="394" t="n"/>
+      <c r="AA18" s="394" t="n"/>
+      <c r="AB18" s="394" t="n"/>
+      <c r="AC18" s="394" t="n"/>
+      <c r="AD18" s="394" t="n"/>
+      <c r="AE18" s="394" t="n"/>
+      <c r="AF18" s="394" t="n"/>
+      <c r="AG18" s="394" t="n"/>
+      <c r="AH18" s="394" t="n"/>
+      <c r="AI18" s="394" t="n"/>
+      <c r="AJ18" s="394" t="n"/>
+      <c r="AK18" s="394" t="n"/>
+      <c r="AL18" s="394" t="n"/>
+      <c r="AM18" s="394" t="n"/>
+      <c r="AN18" s="394" t="n"/>
+      <c r="AO18" s="394" t="n"/>
+      <c r="AP18" s="394" t="n"/>
+      <c r="AQ18" s="394" t="n"/>
+      <c r="AR18" s="394" t="n"/>
+      <c r="AS18" s="394" t="n"/>
+      <c r="AT18" s="394" t="n"/>
+      <c r="AU18" s="394" t="n"/>
+      <c r="AV18" s="394" t="n"/>
+      <c r="AW18" s="394" t="n"/>
+      <c r="AX18" s="394" t="n"/>
+      <c r="AY18" s="394" t="n"/>
+      <c r="AZ18" s="394" t="n"/>
+      <c r="BA18" s="394" t="n"/>
+      <c r="BB18" s="394" t="n"/>
+      <c r="BC18" s="394" t="n"/>
+      <c r="BD18" s="395" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -8081,7 +7820,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="307" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -8093,7 +7832,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="287" t="inlineStr">
+      <c r="L1" s="404" t="inlineStr">
         <is>
           <t>COMPETENCE ASSESSMENT — CONTROLLED LOOKUP LISTS</t>
         </is>
@@ -8127,7 +7866,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="358" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -8152,286 +7891,454 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="360" t="inlineStr">
+      <c r="A2" s="367" t="n"/>
+      <c r="B2" s="368" t="n"/>
+      <c r="C2" s="368" t="n"/>
+      <c r="D2" s="368" t="n"/>
+      <c r="E2" s="368" t="n"/>
+      <c r="F2" s="368" t="n"/>
+      <c r="G2" s="368" t="n"/>
+      <c r="H2" s="368" t="n"/>
+      <c r="I2" s="368" t="n"/>
+      <c r="J2" s="368" t="n"/>
+      <c r="K2" s="369" t="n"/>
+      <c r="L2" s="368" t="n"/>
+      <c r="M2" s="368" t="n"/>
+      <c r="N2" s="368" t="n"/>
+      <c r="O2" s="368" t="n"/>
+      <c r="P2" s="368" t="n"/>
+      <c r="Q2" s="368" t="n"/>
+      <c r="R2" s="368" t="n"/>
+      <c r="S2" s="368" t="n"/>
+      <c r="T2" s="368" t="n"/>
+      <c r="U2" s="368" t="n"/>
+      <c r="V2" s="368" t="n"/>
+      <c r="W2" s="368" t="n"/>
+      <c r="X2" s="368" t="n"/>
+      <c r="Y2" s="368" t="n"/>
+      <c r="Z2" s="368" t="n"/>
+      <c r="AA2" s="368" t="n"/>
+      <c r="AB2" s="368" t="n"/>
+      <c r="AC2" s="368" t="n"/>
+      <c r="AD2" s="368" t="n"/>
+      <c r="AE2" s="368" t="n"/>
+      <c r="AF2" s="368" t="n"/>
+      <c r="AG2" s="368" t="n"/>
+      <c r="AH2" s="368" t="n"/>
+      <c r="AI2" s="368" t="n"/>
+      <c r="AJ2" s="368" t="n"/>
+      <c r="AK2" s="368" t="n"/>
+      <c r="AL2" s="368" t="n"/>
+      <c r="AM2" s="368" t="n"/>
+      <c r="AN2" s="368" t="n"/>
+      <c r="AO2" s="368" t="n"/>
+      <c r="AP2" s="369" t="n"/>
+      <c r="AQ2" s="370" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="312" t="n"/>
-      <c r="AS2" s="312" t="n"/>
-      <c r="AT2" s="312" t="n"/>
-      <c r="AU2" s="312" t="n"/>
-      <c r="AV2" s="313" t="n"/>
-      <c r="AW2" s="361" t="inlineStr">
+      <c r="AR2" s="371" t="n"/>
+      <c r="AS2" s="371" t="n"/>
+      <c r="AT2" s="371" t="n"/>
+      <c r="AU2" s="371" t="n"/>
+      <c r="AV2" s="372" t="n"/>
+      <c r="AW2" s="373" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="312" t="n"/>
-      <c r="AY2" s="312" t="n"/>
-      <c r="AZ2" s="312" t="n"/>
-      <c r="BA2" s="312" t="n"/>
-      <c r="BB2" s="312" t="n"/>
-      <c r="BC2" s="312" t="n"/>
-      <c r="BD2" s="315" t="n"/>
+      <c r="AX2" s="374" t="n"/>
+      <c r="AY2" s="374" t="n"/>
+      <c r="AZ2" s="374" t="n"/>
+      <c r="BA2" s="374" t="n"/>
+      <c r="BB2" s="374" t="n"/>
+      <c r="BC2" s="374" t="n"/>
+      <c r="BD2" s="375" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="360" t="inlineStr">
+      <c r="A3" s="376" t="n"/>
+      <c r="B3" s="53" t="n"/>
+      <c r="C3" s="53" t="n"/>
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="53" t="n"/>
+      <c r="F3" s="53" t="n"/>
+      <c r="G3" s="53" t="n"/>
+      <c r="H3" s="53" t="n"/>
+      <c r="I3" s="53" t="n"/>
+      <c r="J3" s="53" t="n"/>
+      <c r="K3" s="377" t="n"/>
+      <c r="L3" s="53" t="n"/>
+      <c r="M3" s="53" t="n"/>
+      <c r="N3" s="53" t="n"/>
+      <c r="O3" s="53" t="n"/>
+      <c r="P3" s="53" t="n"/>
+      <c r="Q3" s="53" t="n"/>
+      <c r="R3" s="53" t="n"/>
+      <c r="S3" s="53" t="n"/>
+      <c r="T3" s="53" t="n"/>
+      <c r="U3" s="53" t="n"/>
+      <c r="V3" s="53" t="n"/>
+      <c r="W3" s="53" t="n"/>
+      <c r="X3" s="53" t="n"/>
+      <c r="Y3" s="53" t="n"/>
+      <c r="Z3" s="53" t="n"/>
+      <c r="AA3" s="53" t="n"/>
+      <c r="AB3" s="53" t="n"/>
+      <c r="AC3" s="53" t="n"/>
+      <c r="AD3" s="53" t="n"/>
+      <c r="AE3" s="53" t="n"/>
+      <c r="AF3" s="53" t="n"/>
+      <c r="AG3" s="53" t="n"/>
+      <c r="AH3" s="53" t="n"/>
+      <c r="AI3" s="53" t="n"/>
+      <c r="AJ3" s="53" t="n"/>
+      <c r="AK3" s="53" t="n"/>
+      <c r="AL3" s="53" t="n"/>
+      <c r="AM3" s="53" t="n"/>
+      <c r="AN3" s="53" t="n"/>
+      <c r="AO3" s="53" t="n"/>
+      <c r="AP3" s="377" t="n"/>
+      <c r="AQ3" s="378" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="312" t="n"/>
-      <c r="AS3" s="312" t="n"/>
-      <c r="AT3" s="312" t="n"/>
-      <c r="AU3" s="312" t="n"/>
-      <c r="AV3" s="313" t="n"/>
-      <c r="AW3" s="361" t="inlineStr">
+      <c r="AR3" s="379" t="n"/>
+      <c r="AS3" s="379" t="n"/>
+      <c r="AT3" s="379" t="n"/>
+      <c r="AU3" s="379" t="n"/>
+      <c r="AV3" s="380" t="n"/>
+      <c r="AW3" s="301" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="312" t="n"/>
-      <c r="AY3" s="312" t="n"/>
-      <c r="AZ3" s="312" t="n"/>
-      <c r="BA3" s="312" t="n"/>
-      <c r="BB3" s="312" t="n"/>
-      <c r="BC3" s="312" t="n"/>
-      <c r="BD3" s="315" t="n"/>
+      <c r="AX3" s="381" t="n"/>
+      <c r="AY3" s="381" t="n"/>
+      <c r="AZ3" s="381" t="n"/>
+      <c r="BA3" s="381" t="n"/>
+      <c r="BB3" s="381" t="n"/>
+      <c r="BC3" s="381" t="n"/>
+      <c r="BD3" s="382" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="A4" s="376" t="n"/>
+      <c r="B4" s="53" t="n"/>
+      <c r="C4" s="53" t="n"/>
+      <c r="D4" s="53" t="n"/>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="53" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="H4" s="53" t="n"/>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="377" t="n"/>
+      <c r="L4" s="383" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="360" t="inlineStr">
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n"/>
+      <c r="O4" s="53" t="n"/>
+      <c r="P4" s="53" t="n"/>
+      <c r="Q4" s="53" t="n"/>
+      <c r="R4" s="53" t="n"/>
+      <c r="S4" s="53" t="n"/>
+      <c r="T4" s="53" t="n"/>
+      <c r="U4" s="53" t="n"/>
+      <c r="V4" s="53" t="n"/>
+      <c r="W4" s="53" t="n"/>
+      <c r="X4" s="53" t="n"/>
+      <c r="Y4" s="53" t="n"/>
+      <c r="Z4" s="53" t="n"/>
+      <c r="AA4" s="53" t="n"/>
+      <c r="AB4" s="53" t="n"/>
+      <c r="AC4" s="53" t="n"/>
+      <c r="AD4" s="53" t="n"/>
+      <c r="AE4" s="53" t="n"/>
+      <c r="AF4" s="53" t="n"/>
+      <c r="AG4" s="53" t="n"/>
+      <c r="AH4" s="53" t="n"/>
+      <c r="AI4" s="53" t="n"/>
+      <c r="AJ4" s="53" t="n"/>
+      <c r="AK4" s="53" t="n"/>
+      <c r="AL4" s="53" t="n"/>
+      <c r="AM4" s="53" t="n"/>
+      <c r="AN4" s="53" t="n"/>
+      <c r="AO4" s="53" t="n"/>
+      <c r="AP4" s="377" t="n"/>
+      <c r="AQ4" s="378" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="312" t="n"/>
-      <c r="AS4" s="312" t="n"/>
-      <c r="AT4" s="312" t="n"/>
-      <c r="AU4" s="312" t="n"/>
-      <c r="AV4" s="313" t="n"/>
-      <c r="AW4" s="361" t="inlineStr">
+      <c r="AR4" s="379" t="n"/>
+      <c r="AS4" s="379" t="n"/>
+      <c r="AT4" s="379" t="n"/>
+      <c r="AU4" s="379" t="n"/>
+      <c r="AV4" s="380" t="n"/>
+      <c r="AW4" s="301" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="312" t="n"/>
-      <c r="AY4" s="312" t="n"/>
-      <c r="AZ4" s="312" t="n"/>
-      <c r="BA4" s="312" t="n"/>
-      <c r="BB4" s="312" t="n"/>
-      <c r="BC4" s="312" t="n"/>
-      <c r="BD4" s="315" t="n"/>
+      <c r="AX4" s="381" t="n"/>
+      <c r="AY4" s="381" t="n"/>
+      <c r="AZ4" s="381" t="n"/>
+      <c r="BA4" s="381" t="n"/>
+      <c r="BB4" s="381" t="n"/>
+      <c r="BC4" s="381" t="n"/>
+      <c r="BD4" s="382" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="49" t="inlineStr">
+      <c r="A5" s="376" t="n"/>
+      <c r="B5" s="53" t="n"/>
+      <c r="C5" s="53" t="n"/>
+      <c r="D5" s="53" t="n"/>
+      <c r="E5" s="53" t="n"/>
+      <c r="F5" s="53" t="n"/>
+      <c r="G5" s="53" t="n"/>
+      <c r="H5" s="53" t="n"/>
+      <c r="I5" s="53" t="n"/>
+      <c r="J5" s="53" t="n"/>
+      <c r="K5" s="377" t="n"/>
+      <c r="L5" s="384" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="362" t="inlineStr">
+      <c r="M5" s="53" t="n"/>
+      <c r="N5" s="53" t="n"/>
+      <c r="O5" s="53" t="n"/>
+      <c r="P5" s="53" t="n"/>
+      <c r="Q5" s="53" t="n"/>
+      <c r="R5" s="53" t="n"/>
+      <c r="S5" s="53" t="n"/>
+      <c r="T5" s="53" t="n"/>
+      <c r="U5" s="53" t="n"/>
+      <c r="V5" s="53" t="n"/>
+      <c r="W5" s="53" t="n"/>
+      <c r="X5" s="53" t="n"/>
+      <c r="Y5" s="53" t="n"/>
+      <c r="Z5" s="53" t="n"/>
+      <c r="AA5" s="53" t="n"/>
+      <c r="AB5" s="53" t="n"/>
+      <c r="AC5" s="53" t="n"/>
+      <c r="AD5" s="53" t="n"/>
+      <c r="AE5" s="53" t="n"/>
+      <c r="AF5" s="53" t="n"/>
+      <c r="AG5" s="53" t="n"/>
+      <c r="AH5" s="53" t="n"/>
+      <c r="AI5" s="53" t="n"/>
+      <c r="AJ5" s="53" t="n"/>
+      <c r="AK5" s="53" t="n"/>
+      <c r="AL5" s="53" t="n"/>
+      <c r="AM5" s="53" t="n"/>
+      <c r="AN5" s="53" t="n"/>
+      <c r="AO5" s="53" t="n"/>
+      <c r="AP5" s="377" t="n"/>
+      <c r="AQ5" s="378" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="317" t="n"/>
-      <c r="AS5" s="317" t="n"/>
-      <c r="AT5" s="317" t="n"/>
-      <c r="AU5" s="317" t="n"/>
-      <c r="AV5" s="318" t="n"/>
-      <c r="AW5" s="363" t="inlineStr">
+      <c r="AR5" s="379" t="n"/>
+      <c r="AS5" s="379" t="n"/>
+      <c r="AT5" s="379" t="n"/>
+      <c r="AU5" s="379" t="n"/>
+      <c r="AV5" s="380" t="n"/>
+      <c r="AW5" s="301" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="317" t="n"/>
-      <c r="AY5" s="317" t="n"/>
-      <c r="AZ5" s="317" t="n"/>
-      <c r="BA5" s="317" t="n"/>
-      <c r="BB5" s="317" t="n"/>
-      <c r="BC5" s="317" t="n"/>
-      <c r="BD5" s="320" t="n"/>
+      <c r="AX5" s="381" t="n"/>
+      <c r="AY5" s="381" t="n"/>
+      <c r="AZ5" s="381" t="n"/>
+      <c r="BA5" s="381" t="n"/>
+      <c r="BB5" s="381" t="n"/>
+      <c r="BC5" s="381" t="n"/>
+      <c r="BD5" s="382" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="294" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="385" t="n"/>
+      <c r="B6" s="396" t="n"/>
+      <c r="C6" s="396" t="n"/>
+      <c r="D6" s="396" t="n"/>
+      <c r="E6" s="396" t="n"/>
+      <c r="F6" s="396" t="n"/>
+      <c r="G6" s="396" t="n"/>
+      <c r="H6" s="396" t="n"/>
+      <c r="I6" s="396" t="n"/>
+      <c r="J6" s="396" t="n"/>
+      <c r="K6" s="397" t="n"/>
+      <c r="L6" s="396" t="n"/>
+      <c r="M6" s="396" t="n"/>
+      <c r="N6" s="396" t="n"/>
+      <c r="O6" s="396" t="n"/>
+      <c r="P6" s="396" t="n"/>
+      <c r="Q6" s="396" t="n"/>
+      <c r="R6" s="396" t="n"/>
+      <c r="S6" s="396" t="n"/>
+      <c r="T6" s="396" t="n"/>
+      <c r="U6" s="396" t="n"/>
+      <c r="V6" s="396" t="n"/>
+      <c r="W6" s="396" t="n"/>
+      <c r="X6" s="396" t="n"/>
+      <c r="Y6" s="396" t="n"/>
+      <c r="Z6" s="396" t="n"/>
+      <c r="AA6" s="396" t="n"/>
+      <c r="AB6" s="396" t="n"/>
+      <c r="AC6" s="396" t="n"/>
+      <c r="AD6" s="396" t="n"/>
+      <c r="AE6" s="396" t="n"/>
+      <c r="AF6" s="396" t="n"/>
+      <c r="AG6" s="396" t="n"/>
+      <c r="AH6" s="396" t="n"/>
+      <c r="AI6" s="396" t="n"/>
+      <c r="AJ6" s="396" t="n"/>
+      <c r="AK6" s="396" t="n"/>
+      <c r="AL6" s="396" t="n"/>
+      <c r="AM6" s="396" t="n"/>
+      <c r="AN6" s="396" t="n"/>
+      <c r="AO6" s="396" t="n"/>
+      <c r="AP6" s="397" t="n"/>
+      <c r="AQ6" s="398" t="n"/>
+      <c r="AR6" s="398" t="n"/>
+      <c r="AS6" s="398" t="n"/>
+      <c r="AT6" s="398" t="n"/>
+      <c r="AU6" s="398" t="n"/>
+      <c r="AV6" s="399" t="n"/>
+      <c r="AW6" s="400" t="n"/>
+      <c r="AX6" s="400" t="n"/>
+      <c r="AY6" s="400" t="n"/>
+      <c r="AZ6" s="400" t="n"/>
+      <c r="BA6" s="400" t="n"/>
+      <c r="BB6" s="400" t="n"/>
+      <c r="BC6" s="400" t="n"/>
+      <c r="BD6" s="401" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="402" t="n"/>
+      <c r="B7" s="393" t="n"/>
+      <c r="C7" s="393" t="n"/>
+      <c r="D7" s="393" t="n"/>
+      <c r="E7" s="393" t="n"/>
+      <c r="F7" s="393" t="n"/>
+      <c r="G7" s="393" t="n"/>
+      <c r="H7" s="393" t="n"/>
+      <c r="I7" s="393" t="n"/>
+      <c r="J7" s="393" t="n"/>
+      <c r="K7" s="393" t="n"/>
+      <c r="L7" s="393" t="n"/>
+      <c r="M7" s="393" t="n"/>
+      <c r="N7" s="393" t="n"/>
+      <c r="O7" s="393" t="n"/>
+      <c r="P7" s="393" t="n"/>
+      <c r="Q7" s="393" t="n"/>
+      <c r="R7" s="393" t="n"/>
+      <c r="S7" s="393" t="n"/>
+      <c r="T7" s="393" t="n"/>
+      <c r="U7" s="393" t="n"/>
+      <c r="V7" s="393" t="n"/>
+      <c r="W7" s="393" t="n"/>
+      <c r="X7" s="393" t="n"/>
+      <c r="Y7" s="393" t="n"/>
+      <c r="Z7" s="393" t="n"/>
+      <c r="AA7" s="393" t="n"/>
+      <c r="AB7" s="393" t="n"/>
+      <c r="AC7" s="393" t="n"/>
+      <c r="AD7" s="393" t="n"/>
+      <c r="AE7" s="393" t="n"/>
+      <c r="AF7" s="393" t="n"/>
+      <c r="AG7" s="393" t="n"/>
+      <c r="AH7" s="393" t="n"/>
+      <c r="AI7" s="393" t="n"/>
+      <c r="AJ7" s="393" t="n"/>
+      <c r="AK7" s="393" t="n"/>
+      <c r="AL7" s="393" t="n"/>
+      <c r="AM7" s="393" t="n"/>
+      <c r="AN7" s="393" t="n"/>
+      <c r="AO7" s="393" t="n"/>
+      <c r="AP7" s="393" t="n"/>
+      <c r="AQ7" s="393" t="n"/>
+      <c r="AR7" s="393" t="n"/>
+      <c r="AS7" s="393" t="n"/>
+      <c r="AT7" s="393" t="n"/>
+      <c r="AU7" s="393" t="n"/>
+      <c r="AV7" s="393" t="n"/>
+      <c r="AW7" s="393" t="n"/>
+      <c r="AX7" s="393" t="n"/>
+      <c r="AY7" s="393" t="n"/>
+      <c r="AZ7" s="393" t="n"/>
+      <c r="BA7" s="393" t="n"/>
+      <c r="BB7" s="393" t="n"/>
+      <c r="BC7" s="393" t="n"/>
+      <c r="BD7" s="393" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="22" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="22" t="n"/>
-      <c r="R8" s="22" t="n"/>
-      <c r="S8" s="22" t="n"/>
-      <c r="T8" s="22" t="n"/>
-      <c r="U8" s="22" t="n"/>
-      <c r="V8" s="22" t="n"/>
-      <c r="W8" s="22" t="n"/>
-      <c r="X8" s="22" t="n"/>
-      <c r="Y8" s="22" t="n"/>
-      <c r="Z8" s="22" t="n"/>
-      <c r="AA8" s="22" t="n"/>
-      <c r="AB8" s="22" t="n"/>
-      <c r="AC8" s="22" t="n"/>
-      <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="22" t="n"/>
-      <c r="AF8" s="22" t="n"/>
-      <c r="AG8" s="22" t="n"/>
-      <c r="AH8" s="22" t="n"/>
-      <c r="AI8" s="22" t="n"/>
-      <c r="AJ8" s="22" t="n"/>
-      <c r="AK8" s="22" t="n"/>
-      <c r="AL8" s="22" t="n"/>
-      <c r="AM8" s="22" t="n"/>
-      <c r="AN8" s="22" t="n"/>
-      <c r="AO8" s="22" t="n"/>
-      <c r="AP8" s="22" t="n"/>
-      <c r="AQ8" s="22" t="n"/>
-      <c r="AR8" s="22" t="n"/>
-      <c r="AS8" s="22" t="n"/>
-      <c r="AT8" s="22" t="n"/>
-      <c r="AU8" s="22" t="n"/>
-      <c r="AV8" s="22" t="n"/>
-      <c r="AW8" s="22" t="n"/>
-      <c r="AX8" s="22" t="n"/>
-      <c r="AY8" s="22" t="n"/>
-      <c r="AZ8" s="22" t="n"/>
-      <c r="BA8" s="22" t="n"/>
-      <c r="BB8" s="22" t="n"/>
-      <c r="BC8" s="22" t="n"/>
-      <c r="BD8" s="23" t="n"/>
+      <c r="B8" s="394" t="n"/>
+      <c r="C8" s="394" t="n"/>
+      <c r="D8" s="394" t="n"/>
+      <c r="E8" s="394" t="n"/>
+      <c r="F8" s="394" t="n"/>
+      <c r="G8" s="394" t="n"/>
+      <c r="H8" s="394" t="n"/>
+      <c r="I8" s="394" t="n"/>
+      <c r="J8" s="394" t="n"/>
+      <c r="K8" s="394" t="n"/>
+      <c r="L8" s="394" t="n"/>
+      <c r="M8" s="394" t="n"/>
+      <c r="N8" s="394" t="n"/>
+      <c r="O8" s="394" t="n"/>
+      <c r="P8" s="394" t="n"/>
+      <c r="Q8" s="394" t="n"/>
+      <c r="R8" s="394" t="n"/>
+      <c r="S8" s="394" t="n"/>
+      <c r="T8" s="394" t="n"/>
+      <c r="U8" s="394" t="n"/>
+      <c r="V8" s="394" t="n"/>
+      <c r="W8" s="394" t="n"/>
+      <c r="X8" s="394" t="n"/>
+      <c r="Y8" s="394" t="n"/>
+      <c r="Z8" s="394" t="n"/>
+      <c r="AA8" s="394" t="n"/>
+      <c r="AB8" s="394" t="n"/>
+      <c r="AC8" s="394" t="n"/>
+      <c r="AD8" s="394" t="n"/>
+      <c r="AE8" s="394" t="n"/>
+      <c r="AF8" s="394" t="n"/>
+      <c r="AG8" s="394" t="n"/>
+      <c r="AH8" s="394" t="n"/>
+      <c r="AI8" s="394" t="n"/>
+      <c r="AJ8" s="394" t="n"/>
+      <c r="AK8" s="394" t="n"/>
+      <c r="AL8" s="394" t="n"/>
+      <c r="AM8" s="394" t="n"/>
+      <c r="AN8" s="394" t="n"/>
+      <c r="AO8" s="394" t="n"/>
+      <c r="AP8" s="394" t="n"/>
+      <c r="AQ8" s="394" t="n"/>
+      <c r="AR8" s="394" t="n"/>
+      <c r="AS8" s="394" t="n"/>
+      <c r="AT8" s="394" t="n"/>
+      <c r="AU8" s="394" t="n"/>
+      <c r="AV8" s="394" t="n"/>
+      <c r="AW8" s="394" t="n"/>
+      <c r="AX8" s="394" t="n"/>
+      <c r="AY8" s="394" t="n"/>
+      <c r="AZ8" s="394" t="n"/>
+      <c r="BA8" s="394" t="n"/>
+      <c r="BB8" s="394" t="n"/>
+      <c r="BC8" s="394" t="n"/>
+      <c r="BD8" s="395" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="277" t="inlineStr">
@@ -9879,67 +9786,67 @@
       <c r="BC19" s="305" t="n"/>
       <c r="BD19" s="306" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="37" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="22" t="n"/>
-      <c r="U20" s="22" t="n"/>
-      <c r="V20" s="22" t="n"/>
-      <c r="W20" s="22" t="n"/>
-      <c r="X20" s="22" t="n"/>
-      <c r="Y20" s="22" t="n"/>
-      <c r="Z20" s="22" t="n"/>
-      <c r="AA20" s="22" t="n"/>
-      <c r="AB20" s="22" t="n"/>
-      <c r="AC20" s="22" t="n"/>
-      <c r="AD20" s="22" t="n"/>
-      <c r="AE20" s="22" t="n"/>
-      <c r="AF20" s="22" t="n"/>
-      <c r="AG20" s="22" t="n"/>
-      <c r="AH20" s="22" t="n"/>
-      <c r="AI20" s="22" t="n"/>
-      <c r="AJ20" s="22" t="n"/>
-      <c r="AK20" s="22" t="n"/>
-      <c r="AL20" s="22" t="n"/>
-      <c r="AM20" s="22" t="n"/>
-      <c r="AN20" s="22" t="n"/>
-      <c r="AO20" s="22" t="n"/>
-      <c r="AP20" s="22" t="n"/>
-      <c r="AQ20" s="22" t="n"/>
-      <c r="AR20" s="22" t="n"/>
-      <c r="AS20" s="22" t="n"/>
-      <c r="AT20" s="22" t="n"/>
-      <c r="AU20" s="22" t="n"/>
-      <c r="AV20" s="22" t="n"/>
-      <c r="AW20" s="22" t="n"/>
-      <c r="AX20" s="22" t="n"/>
-      <c r="AY20" s="22" t="n"/>
-      <c r="AZ20" s="22" t="n"/>
-      <c r="BA20" s="22" t="n"/>
-      <c r="BB20" s="22" t="n"/>
-      <c r="BC20" s="22" t="n"/>
-      <c r="BD20" s="23" t="n"/>
+      <c r="B20" s="394" t="n"/>
+      <c r="C20" s="394" t="n"/>
+      <c r="D20" s="394" t="n"/>
+      <c r="E20" s="394" t="n"/>
+      <c r="F20" s="394" t="n"/>
+      <c r="G20" s="394" t="n"/>
+      <c r="H20" s="394" t="n"/>
+      <c r="I20" s="394" t="n"/>
+      <c r="J20" s="394" t="n"/>
+      <c r="K20" s="394" t="n"/>
+      <c r="L20" s="394" t="n"/>
+      <c r="M20" s="394" t="n"/>
+      <c r="N20" s="394" t="n"/>
+      <c r="O20" s="394" t="n"/>
+      <c r="P20" s="394" t="n"/>
+      <c r="Q20" s="394" t="n"/>
+      <c r="R20" s="394" t="n"/>
+      <c r="S20" s="394" t="n"/>
+      <c r="T20" s="394" t="n"/>
+      <c r="U20" s="394" t="n"/>
+      <c r="V20" s="394" t="n"/>
+      <c r="W20" s="394" t="n"/>
+      <c r="X20" s="394" t="n"/>
+      <c r="Y20" s="394" t="n"/>
+      <c r="Z20" s="394" t="n"/>
+      <c r="AA20" s="394" t="n"/>
+      <c r="AB20" s="394" t="n"/>
+      <c r="AC20" s="394" t="n"/>
+      <c r="AD20" s="394" t="n"/>
+      <c r="AE20" s="394" t="n"/>
+      <c r="AF20" s="394" t="n"/>
+      <c r="AG20" s="394" t="n"/>
+      <c r="AH20" s="394" t="n"/>
+      <c r="AI20" s="394" t="n"/>
+      <c r="AJ20" s="394" t="n"/>
+      <c r="AK20" s="394" t="n"/>
+      <c r="AL20" s="394" t="n"/>
+      <c r="AM20" s="394" t="n"/>
+      <c r="AN20" s="394" t="n"/>
+      <c r="AO20" s="394" t="n"/>
+      <c r="AP20" s="394" t="n"/>
+      <c r="AQ20" s="394" t="n"/>
+      <c r="AR20" s="394" t="n"/>
+      <c r="AS20" s="394" t="n"/>
+      <c r="AT20" s="394" t="n"/>
+      <c r="AU20" s="394" t="n"/>
+      <c r="AV20" s="394" t="n"/>
+      <c r="AW20" s="394" t="n"/>
+      <c r="AX20" s="394" t="n"/>
+      <c r="AY20" s="394" t="n"/>
+      <c r="AZ20" s="394" t="n"/>
+      <c r="BA20" s="394" t="n"/>
+      <c r="BB20" s="394" t="n"/>
+      <c r="BC20" s="394" t="n"/>
+      <c r="BD20" s="395" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -836,6 +836,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2609,7 +2612,6 @@
       <c r="BD24" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="62">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="K11:AB11"/>
@@ -3722,7 +3724,6 @@
       <c r="BD18" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="61">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="AQ3:AV3"/>
@@ -4832,7 +4833,6 @@
       <c r="BD18" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="82">
     <mergeCell ref="AV17:BD17"/>
     <mergeCell ref="AV11:BD11"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -1367,7 +1367,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR / Dept. Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -1437,7 +1437,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -2947,7 +2947,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR / Dept. Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -3017,7 +3017,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -4044,7 +4044,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR / Dept. Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -4114,7 +4114,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -5169,7 +5169,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR / Dept. Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -5239,7 +5239,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM804_Criteria" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM804_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM804_Assess'!$1:$6</definedName>
@@ -822,7 +824,7 @@
       <row>0</row>
       <rowOff>257175</rowOff>
     </from>
-    <ext cx="1552575" cy="438150"/>
+    <ext cx="5238750" cy="1514475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1281,7 +1283,7 @@
       <c r="AV2" s="29" t="n"/>
       <c r="AW2" s="46" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AX2" s="14" t="n"/>
@@ -1337,7 +1339,7 @@
       <c r="AV3" s="29" t="n"/>
       <c r="AW3" s="46" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AX3" s="14" t="n"/>
@@ -1367,7 +1369,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR / Dept. Manager</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -1437,7 +1439,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -1516,7 +1518,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Linked FRM-803 / FRM-807</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -1548,7 +1550,7 @@
       <c r="AB8" s="27" t="n"/>
       <c r="AC8" s="24" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Ref: SOP-801</t>
         </is>
       </c>
       <c r="AD8" s="6" t="n"/>
@@ -1560,7 +1562,11 @@
       <c r="AJ8" s="6" t="n"/>
       <c r="AK8" s="6" t="n"/>
       <c r="AL8" s="7" t="n"/>
-      <c r="AM8" s="25" t="n"/>
+      <c r="AM8" s="25" t="inlineStr">
+        <is>
+          <t>Retain: 5 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AN8" s="26" t="n"/>
       <c r="AO8" s="26" t="n"/>
       <c r="AP8" s="26" t="n"/>
@@ -2612,6 +2618,7 @@
       <c r="BD24" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="62">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="K11:AB11"/>
@@ -2947,7 +2954,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR / Dept. Manager</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -3017,7 +3024,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -3724,6 +3731,7 @@
       <c r="BD18" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="61">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="AQ3:AV3"/>
@@ -4044,7 +4052,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR / Dept. Manager</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -4114,7 +4122,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -4833,6 +4841,7 @@
       <c r="BD18" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="82">
     <mergeCell ref="AV17:BD17"/>
     <mergeCell ref="AV11:BD11"/>
@@ -5169,7 +5178,7 @@
       <c r="AV4" s="29" t="n"/>
       <c r="AW4" s="46" t="inlineStr">
         <is>
-          <t>HR / Dept. Manager</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -5239,7 +5248,7 @@
       <c r="AV5" s="51" t="n"/>
       <c r="AW5" s="52" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -6665,4 +6674,97 @@
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-803, FRM-807; Parent ref: SOP-801</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-804_Competence_Assessment.xlsx
@@ -4953,6 +4953,84 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Tên nhân viên
+</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t>Vị trí / Vai trò
+Chức danh và vai trò hiện tại.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Ngày đánh giá
+</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Người đánh giá
+</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Đánh giá năng lực
+ISO 9001 cl.7.2 — xác định năng lực cần thiết.</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Kỹ năng kỹ thuật
+Thực hành các công việc được giao.</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Kiến thức quy trình
+Hiểu biết SOP, WI liên quan.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Nhận thức chất lượng
+Biết cách xử lý khi phát hiện lỗi: HOLD, NCR, escalation.</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>An toàn
+Sử dụng PPE đúng, biết lối thoát hiểm.</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Vận hành thiết bị
+Thao tác máy CNC, dụng cụ đo, CMM.</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Kết luận
+COMPETENT = đủ năng lực, làm việc độc lập.
+NEEDS TRAINING = cần đào tạo thêm trước khi independent.
+NOT YET COMPETENT = chưa đủ, cần OJT.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5862,8 +5940,9 @@
       <c r="AN13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="inlineStr">
@@ -5918,8 +5997,9 @@
       <c r="AN14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="492" t="inlineStr">
@@ -5931,7 +6011,7 @@
       <c r="E15" s="491" t="n"/>
       <c r="F15" s="499" t="inlineStr">
         <is>
-          <t>Knowledge of applicable procedures / WI.</t>
+          <t>Knowledge of applicable procedures.</t>
         </is>
       </c>
       <c r="G15" s="493" t="n"/>
@@ -5974,8 +6054,9 @@
       <c r="AN15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="492" t="inlineStr">
@@ -6030,8 +6111,9 @@
       <c r="AN16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="492" t="inlineStr">
@@ -6086,8 +6168,9 @@
       <c r="AN17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="inlineStr">
@@ -6142,8 +6225,9 @@
       <c r="AN18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="inlineStr">
@@ -6175,7 +6259,7 @@
       <c r="U19" s="491" t="n"/>
       <c r="V19" s="495" t="inlineStr">
         <is>
-          <t>COMPETENT / NEEDS TRAINING / NOT YET COMPETENT.</t>
+          <t>COMPETENT / NEEDS TRAINING / NOT YET.</t>
         </is>
       </c>
       <c r="W19" s="493" t="n"/>
@@ -6198,8 +6282,9 @@
       <c r="AN19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="500" t="n"/>
@@ -6242,8 +6327,9 @@
       <c r="AN20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="502" t="n">
-        <v>8</v>
+      <c r="A21" s="502">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="482" t="n"/>
       <c r="C21" s="503" t="n"/>
@@ -6566,7 +6652,7 @@
     <row r="29" ht="24" customHeight="1" s="264">
       <c r="A29" s="514" t="inlineStr">
         <is>
-          <t>NOTICE — Per employee, annual or on change. Ref: SOP-801. Retain: 5 years.</t>
+          <t>NOTICE — Per employee, annual or on role change. Ref: SOP-801. Retain: 5 years.</t>
         </is>
       </c>
       <c r="B29" s="471" t="n"/>
@@ -6719,6 +6805,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
